--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -3692,7 +3692,6 @@
       <c r="U4" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="2"/>
       <c r="W4" t="s">
         <v>76</v>
       </c>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1904,7 +1904,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>新手期固定：5 分钟装扮盲盒</t>
+    <t>新手期固定：5 分钟装扮盲盒，开发阶段时间为十分之一，下同</t>
   </si>
   <si>
     <t>新手期固定：15 分钟新手礼盒</t>
@@ -14256,13 +14256,13 @@
         <v>1001</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -14291,13 +14291,13 @@
         <v>1002</v>
       </c>
       <c r="D6">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -14326,13 +14326,13 @@
         <v>2001</v>
       </c>
       <c r="D7">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -14361,13 +14361,13 @@
         <v>1001</v>
       </c>
       <c r="D8">
-        <v>2100</v>
+        <v>210</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2100</v>
+        <v>210</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -14396,13 +14396,13 @@
         <v>1002</v>
       </c>
       <c r="D9">
-        <v>2700</v>
+        <v>270</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2700</v>
+        <v>270</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -14431,13 +14431,13 @@
         <v>2001</v>
       </c>
       <c r="D10">
-        <v>3300</v>
+        <v>330</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>3300</v>
+        <v>330</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -14466,13 +14466,13 @@
         <v>1001</v>
       </c>
       <c r="D11">
-        <v>3900</v>
+        <v>390</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>3900</v>
+        <v>390</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -14501,13 +14501,13 @@
         <v>1002</v>
       </c>
       <c r="D12">
-        <v>4500</v>
+        <v>450</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>4500</v>
+        <v>450</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -14536,13 +14536,13 @@
         <v>2001</v>
       </c>
       <c r="D13">
-        <v>5100</v>
+        <v>510</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>5100</v>
+        <v>510</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -14571,13 +14571,13 @@
         <v>1001</v>
       </c>
       <c r="D14">
-        <v>5700</v>
+        <v>570</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>5700</v>
+        <v>570</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -14606,13 +14606,13 @@
         <v>1002</v>
       </c>
       <c r="D15">
-        <v>6300</v>
+        <v>630</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>6300</v>
+        <v>630</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -14641,13 +14641,13 @@
         <v>2001</v>
       </c>
       <c r="D16">
-        <v>6900</v>
+        <v>690</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>6900</v>
+        <v>690</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -14676,10 +14676,10 @@
         <v>1001</v>
       </c>
       <c r="D17">
-        <v>7500</v>
+        <v>750</v>
       </c>
       <c r="E17">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -14711,10 +14711,10 @@
         <v>2001</v>
       </c>
       <c r="D18">
-        <v>8400</v>
+        <v>840</v>
       </c>
       <c r="E18">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F18">
         <v>-1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="707">
   <si>
     <t>##var</t>
   </si>
@@ -313,121 +313,124 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>初始拥有</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Red\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>黑柴</t>
+  </si>
+  <si>
+    <t>装扮盲盒产出</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>白柴</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>Sesame</t>
+  </si>
+  <si>
+    <t>胡麻柴</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>Thin Red</t>
+  </si>
+  <si>
+    <t>瘦赤柴</t>
+  </si>
+  <si>
     <t>史诗</t>
   </si>
   <si>
-    <t>初始拥有</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Red\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Red.png</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>黑柴</t>
-  </si>
-  <si>
-    <t>装扮盲盒产出</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>Cream</t>
-  </si>
-  <si>
-    <t>白柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>Sesame</t>
-  </si>
-  <si>
-    <t>胡麻柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>Thin Red</t>
-  </si>
-  <si>
-    <t>瘦赤柴</t>
+    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Unshaven Red</t>
+  </si>
+  <si>
+    <t>胡渣赤柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
+    <t>Thin Black</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Unshaven Black</t>
+  </si>
+  <si>
+    <t>胡渣黑柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Thin Cream</t>
+  </si>
+  <si>
+    <t>瘦白柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>Unshaven Cream</t>
+  </si>
+  <si>
+    <t>胡渣白柴</t>
   </si>
   <si>
     <t>传说</t>
   </si>
   <si>
-    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Unshaven Red</t>
-  </si>
-  <si>
-    <t>胡渣赤柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>Thin Black</t>
-  </si>
-  <si>
-    <t>瘦黑柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
-  </si>
-  <si>
-    <t>Unshaven Black</t>
-  </si>
-  <si>
-    <t>胡渣黑柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_UnshavenBlack.png</t>
-  </si>
-  <si>
-    <t>Thin Cream</t>
-  </si>
-  <si>
-    <t>瘦白柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_ThinCream.png</t>
-  </si>
-  <si>
-    <t>Unshaven Cream</t>
-  </si>
-  <si>
-    <t>胡渣白柴</t>
-  </si>
-  <si>
     <t>v1\ItemIcon\Shiba_UnshavenCream.png</t>
   </si>
   <si>
     <t>Thin Sesame</t>
   </si>
   <si>
-    <t>瘦芝麻柴</t>
+    <t>瘦胡麻柴</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_ThinSesame.png</t>
@@ -436,7 +439,7 @@
     <t>Unshaven Sesame</t>
   </si>
   <si>
-    <t>胡渣芝麻柴</t>
+    <t>胡渣胡麻柴</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_UnshavenSesame.png</t>
@@ -451,7 +454,7 @@
     <t>Headwear</t>
   </si>
   <si>
-    <t>稀有</t>
+    <t>普通</t>
   </si>
   <si>
     <t>v1\Headwear\Beret_Green.png</t>
@@ -1274,9 +1277,6 @@
   </si>
   <si>
     <t>Refreshment</t>
-  </si>
-  <si>
-    <t>普通</t>
   </si>
   <si>
     <t>消耗品盲盒产出</t>
@@ -2158,6 +2158,12 @@
   </si>
   <si>
     <t>可脱光吗</t>
+  </si>
+  <si>
+    <t>瘦芝麻柴</t>
+  </si>
+  <si>
+    <t>胡渣芝麻柴</t>
   </si>
 </sst>
 </file>
@@ -4352,7 +4358,7 @@
         <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4379,7 +4385,7 @@
         <v>102</v>
       </c>
       <c r="T14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U14">
         <v>1010</v>
@@ -4411,16 +4417,16 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
         <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4447,7 +4453,7 @@
         <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U15">
         <v>1011</v>
@@ -4479,16 +4485,16 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
         <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4515,7 +4521,7 @@
         <v>106</v>
       </c>
       <c r="T16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="U16">
         <v>1012</v>
@@ -4552,16 +4558,16 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I18">
         <v>300</v>
@@ -4585,10 +4591,10 @@
         <v>300</v>
       </c>
       <c r="S18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -4617,16 +4623,16 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I19">
         <v>300</v>
@@ -4650,10 +4656,10 @@
         <v>300</v>
       </c>
       <c r="S19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -4682,16 +4688,16 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I20">
         <v>300</v>
@@ -4715,10 +4721,10 @@
         <v>300</v>
       </c>
       <c r="S20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -4747,16 +4753,16 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H21" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I21">
         <v>300</v>
@@ -4780,10 +4786,10 @@
         <v>300</v>
       </c>
       <c r="S21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -4812,16 +4818,16 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I22">
         <v>300</v>
@@ -4845,10 +4851,10 @@
         <v>300</v>
       </c>
       <c r="S22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -4877,16 +4883,16 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>300</v>
@@ -4910,10 +4916,10 @@
         <v>300</v>
       </c>
       <c r="S23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -4942,16 +4948,16 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24">
         <v>300</v>
@@ -4975,10 +4981,10 @@
         <v>300</v>
       </c>
       <c r="S24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -5007,16 +5013,16 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I25">
         <v>300</v>
@@ -5040,10 +5046,10 @@
         <v>300</v>
       </c>
       <c r="S25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -5072,16 +5078,16 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I26">
         <v>300</v>
@@ -5105,10 +5111,10 @@
         <v>300</v>
       </c>
       <c r="S26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -5137,16 +5143,16 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I27">
         <v>300</v>
@@ -5170,10 +5176,10 @@
         <v>300</v>
       </c>
       <c r="S27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -5202,16 +5208,16 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I28">
         <v>300</v>
@@ -5235,10 +5241,10 @@
         <v>300</v>
       </c>
       <c r="S28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -5267,16 +5273,16 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I29">
         <v>300</v>
@@ -5300,10 +5306,10 @@
         <v>300</v>
       </c>
       <c r="S29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W29">
         <v>0</v>
@@ -5332,16 +5338,16 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I30">
         <v>300</v>
@@ -5365,10 +5371,10 @@
         <v>300</v>
       </c>
       <c r="S30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5397,16 +5403,16 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I31">
         <v>300</v>
@@ -5430,10 +5436,10 @@
         <v>300</v>
       </c>
       <c r="S31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5462,16 +5468,16 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I32">
         <v>300</v>
@@ -5489,16 +5495,16 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5527,19 +5533,19 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5563,10 +5569,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="T33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -5595,19 +5601,19 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5631,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5663,19 +5669,19 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5699,10 +5705,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W35">
         <v>0</v>
@@ -5731,19 +5737,19 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5767,10 +5773,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T36" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -5799,16 +5805,16 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37">
         <v>300</v>
@@ -5832,10 +5838,10 @@
         <v>300</v>
       </c>
       <c r="S37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -5864,16 +5870,16 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I38">
         <v>300</v>
@@ -5897,10 +5903,10 @@
         <v>300</v>
       </c>
       <c r="S38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -5929,16 +5935,16 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I39">
         <v>300</v>
@@ -5962,10 +5968,10 @@
         <v>300</v>
       </c>
       <c r="S39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="T39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -5994,16 +6000,16 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H40" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I40">
         <v>300</v>
@@ -6027,10 +6033,10 @@
         <v>300</v>
       </c>
       <c r="S40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -6059,16 +6065,16 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H41" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I41">
         <v>300</v>
@@ -6092,10 +6098,10 @@
         <v>300</v>
       </c>
       <c r="S41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="T41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -6124,16 +6130,16 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I42">
         <v>300</v>
@@ -6157,10 +6163,10 @@
         <v>300</v>
       </c>
       <c r="S42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -6189,16 +6195,16 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H43" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -6222,10 +6228,10 @@
         <v>300</v>
       </c>
       <c r="S43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -6254,16 +6260,16 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I44">
         <v>300</v>
@@ -6287,10 +6293,10 @@
         <v>300</v>
       </c>
       <c r="S44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="T44" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="W44">
         <v>0</v>
@@ -6319,16 +6325,16 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E45" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -6352,10 +6358,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -6384,16 +6390,16 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I46">
         <v>300</v>
@@ -6417,10 +6423,10 @@
         <v>300</v>
       </c>
       <c r="S46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="T46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -6449,16 +6455,16 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H47" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I47">
         <v>300</v>
@@ -6482,10 +6488,10 @@
         <v>300</v>
       </c>
       <c r="S47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T47" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -6514,16 +6520,16 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H48" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I48">
         <v>300</v>
@@ -6547,10 +6553,10 @@
         <v>300</v>
       </c>
       <c r="S48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -6579,16 +6585,16 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H49" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I49">
         <v>300</v>
@@ -6612,10 +6618,10 @@
         <v>300</v>
       </c>
       <c r="S49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -6644,16 +6650,16 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H50" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I50">
         <v>300</v>
@@ -6677,10 +6683,10 @@
         <v>300</v>
       </c>
       <c r="S50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W50">
         <v>0</v>
@@ -6709,16 +6715,16 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E51" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I51">
         <v>300</v>
@@ -6742,10 +6748,10 @@
         <v>300</v>
       </c>
       <c r="S51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -6774,16 +6780,16 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I52">
         <v>300</v>
@@ -6807,10 +6813,10 @@
         <v>300</v>
       </c>
       <c r="S52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -6839,16 +6845,16 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H53" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I53">
         <v>300</v>
@@ -6872,10 +6878,10 @@
         <v>300</v>
       </c>
       <c r="S53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -6904,16 +6910,16 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H54" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -6937,10 +6943,10 @@
         <v>300</v>
       </c>
       <c r="S54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -6969,16 +6975,16 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H55" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I55">
         <v>300</v>
@@ -7002,10 +7008,10 @@
         <v>300</v>
       </c>
       <c r="S55" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T55" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -7034,16 +7040,16 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H56" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I56">
         <v>300</v>
@@ -7067,10 +7073,10 @@
         <v>300</v>
       </c>
       <c r="S56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="T56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -7099,16 +7105,16 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E57" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I57">
         <v>300</v>
@@ -7132,10 +7138,10 @@
         <v>300</v>
       </c>
       <c r="S57" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="W57">
         <v>0</v>
@@ -7164,16 +7170,16 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D58" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H58" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I58">
         <v>300</v>
@@ -7197,10 +7203,10 @@
         <v>300</v>
       </c>
       <c r="S58" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T58" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -7229,16 +7235,16 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H59" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I59">
         <v>300</v>
@@ -7262,10 +7268,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T59" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -7294,16 +7300,16 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D60" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I60">
         <v>300</v>
@@ -7327,10 +7333,10 @@
         <v>300</v>
       </c>
       <c r="S60" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T60" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -7359,16 +7365,16 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I61">
         <v>300</v>
@@ -7392,10 +7398,10 @@
         <v>300</v>
       </c>
       <c r="S61" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T61" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W61">
         <v>0</v>
@@ -7424,16 +7430,16 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -7457,10 +7463,10 @@
         <v>300</v>
       </c>
       <c r="S62" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T62" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -7489,16 +7495,16 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H63" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I63">
         <v>300</v>
@@ -7522,10 +7528,10 @@
         <v>300</v>
       </c>
       <c r="S63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="W63">
         <v>0</v>
@@ -7554,16 +7560,16 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H64" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I64">
         <v>300</v>
@@ -7587,10 +7593,10 @@
         <v>300</v>
       </c>
       <c r="S64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W64">
         <v>0</v>
@@ -7619,16 +7625,16 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D65" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H65" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I65">
         <v>300</v>
@@ -7652,10 +7658,10 @@
         <v>300</v>
       </c>
       <c r="S65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T65" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -7684,16 +7690,16 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H66" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I66">
         <v>300</v>
@@ -7717,10 +7723,10 @@
         <v>300</v>
       </c>
       <c r="S66" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T66" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -7749,16 +7755,16 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D67" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H67" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I67">
         <v>300</v>
@@ -7782,10 +7788,10 @@
         <v>300</v>
       </c>
       <c r="S67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -7814,16 +7820,16 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H68" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I68">
         <v>300</v>
@@ -7847,10 +7853,10 @@
         <v>300</v>
       </c>
       <c r="S68" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T68" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -7879,16 +7885,16 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D69" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I69">
         <v>300</v>
@@ -7912,10 +7918,10 @@
         <v>300</v>
       </c>
       <c r="S69" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T69" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -7944,16 +7950,16 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D70" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E70" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I70">
         <v>300</v>
@@ -7977,10 +7983,10 @@
         <v>300</v>
       </c>
       <c r="S70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="T70" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -8009,16 +8015,16 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D71" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H71" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I71">
         <v>300</v>
@@ -8042,10 +8048,10 @@
         <v>300</v>
       </c>
       <c r="S71" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="T71" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="W71">
         <v>0</v>
@@ -8074,16 +8080,16 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H72" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I72">
         <v>300</v>
@@ -8107,10 +8113,10 @@
         <v>300</v>
       </c>
       <c r="S72" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="W72">
         <v>0</v>
@@ -8139,16 +8145,16 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D73" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I73">
         <v>300</v>
@@ -8172,10 +8178,10 @@
         <v>300</v>
       </c>
       <c r="S73" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T73" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -8204,16 +8210,16 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E74" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H74" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I74">
         <v>300</v>
@@ -8237,10 +8243,10 @@
         <v>300</v>
       </c>
       <c r="S74" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="T74" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -8269,16 +8275,16 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D75" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E75" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I75">
         <v>300</v>
@@ -8302,10 +8308,10 @@
         <v>300</v>
       </c>
       <c r="S75" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T75" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W75">
         <v>0</v>
@@ -8334,16 +8340,16 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E76" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H76" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I76">
         <v>300</v>
@@ -8367,10 +8373,10 @@
         <v>300</v>
       </c>
       <c r="S76" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T76" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -8399,16 +8405,16 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D77" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E77" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H77" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I77">
         <v>300</v>
@@ -8432,10 +8438,10 @@
         <v>300</v>
       </c>
       <c r="S77" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T77" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -8464,16 +8470,16 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D78" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E78" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -8497,10 +8503,10 @@
         <v>300</v>
       </c>
       <c r="S78" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T78" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -8529,16 +8535,16 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D79" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E79" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I79">
         <v>300</v>
@@ -8562,10 +8568,10 @@
         <v>300</v>
       </c>
       <c r="S79" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T79" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W79">
         <v>0</v>
@@ -8594,16 +8600,16 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D80" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H80" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I80">
         <v>300</v>
@@ -8627,10 +8633,10 @@
         <v>300</v>
       </c>
       <c r="S80" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T80" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="W80">
         <v>0</v>
@@ -8659,16 +8665,16 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D81" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E81" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H81" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I81">
         <v>300</v>
@@ -8692,10 +8698,10 @@
         <v>300</v>
       </c>
       <c r="S81" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T81" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -8724,16 +8730,16 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D82" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E82" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -8757,10 +8763,10 @@
         <v>300</v>
       </c>
       <c r="S82" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T82" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -8789,16 +8795,16 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D83" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E83" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H83" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -8822,10 +8828,10 @@
         <v>300</v>
       </c>
       <c r="S83" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="T83" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -8854,16 +8860,16 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E84" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H84" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -8887,10 +8893,10 @@
         <v>300</v>
       </c>
       <c r="S84" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="T84" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="W84">
         <v>0</v>
@@ -8919,16 +8925,16 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D85" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E85" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H85" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="I85">
         <v>200</v>
@@ -8993,7 +8999,7 @@
         <v>416</v>
       </c>
       <c r="E86" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F86" t="s">
         <v>417</v>
@@ -9002,7 +9008,7 @@
         <v>9009</v>
       </c>
       <c r="H86" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I86">
         <v>200</v>
@@ -9070,7 +9076,7 @@
         <v>422</v>
       </c>
       <c r="E87" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F87" t="s">
         <v>417</v>
@@ -9079,7 +9085,7 @@
         <v>9009</v>
       </c>
       <c r="H87" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I87">
         <v>200</v>
@@ -9147,7 +9153,7 @@
         <v>426</v>
       </c>
       <c r="E88" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F88" t="s">
         <v>417</v>
@@ -9156,7 +9162,7 @@
         <v>9009</v>
       </c>
       <c r="H88" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I88">
         <v>200</v>
@@ -9224,7 +9230,7 @@
         <v>430</v>
       </c>
       <c r="E89" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F89" t="s">
         <v>417</v>
@@ -9233,7 +9239,7 @@
         <v>9009</v>
       </c>
       <c r="H89" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I89">
         <v>200</v>
@@ -9301,7 +9307,7 @@
         <v>434</v>
       </c>
       <c r="E90" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F90" t="s">
         <v>417</v>
@@ -9310,7 +9316,7 @@
         <v>9009</v>
       </c>
       <c r="H90" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I90">
         <v>200</v>
@@ -9378,7 +9384,7 @@
         <v>438</v>
       </c>
       <c r="E91" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F91" t="s">
         <v>417</v>
@@ -9387,7 +9393,7 @@
         <v>9009</v>
       </c>
       <c r="H91" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I91">
         <v>200</v>
@@ -9455,7 +9461,7 @@
         <v>442</v>
       </c>
       <c r="E92" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F92" t="s">
         <v>417</v>
@@ -9464,7 +9470,7 @@
         <v>9009</v>
       </c>
       <c r="H92" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I92">
         <v>200</v>
@@ -9532,10 +9538,10 @@
         <v>446</v>
       </c>
       <c r="E93" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H93" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I93">
         <v>200</v>
@@ -9603,7 +9609,7 @@
         <v>450</v>
       </c>
       <c r="E94" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F94" t="s">
         <v>417</v>
@@ -9612,7 +9618,7 @@
         <v>9009</v>
       </c>
       <c r="H94" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I94">
         <v>200</v>
@@ -9677,7 +9683,7 @@
         <v>454</v>
       </c>
       <c r="E95" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F95" t="s">
         <v>417</v>
@@ -9686,7 +9692,7 @@
         <v>9009</v>
       </c>
       <c r="H95" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I95">
         <v>200</v>
@@ -9757,7 +9763,7 @@
         <v>459</v>
       </c>
       <c r="H96" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="I96">
         <v>300</v>
@@ -9822,7 +9828,7 @@
         <v>464</v>
       </c>
       <c r="H97" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="I97">
         <v>300</v>
@@ -9893,7 +9899,7 @@
         <v>11001</v>
       </c>
       <c r="H98" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="I98">
         <v>300</v>
@@ -9949,13 +9955,13 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D99" t="s">
         <v>471</v>
       </c>
       <c r="E99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H99" t="s">
         <v>472</v>
@@ -9980,10 +9986,10 @@
       </c>
       <c r="R99" s="2"/>
       <c r="S99" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T99" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>474</v>
@@ -10015,7 +10021,7 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
         <v>475</v>
@@ -10049,7 +10055,7 @@
         <v>106</v>
       </c>
       <c r="T100" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="U100">
         <v>1012</v>
@@ -10080,7 +10086,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85 H92 H5:H8 H9:H13 H14:H16 H18:H45 H46:H50 H51:H62 H63:H72 H73:H84 H86:H89 H90:H91 H93:H94 H95:H98 H99:H100">
+      <formula1>枚举示例!$F$2:$F$7</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
@@ -10620,10 +10629,10 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>705</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10652,10 +10661,10 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>706</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -10689,10 +10698,10 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -10721,10 +10730,10 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -10753,10 +10762,10 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -10785,10 +10794,10 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -10817,10 +10826,10 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -10849,10 +10858,10 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -10881,10 +10890,10 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -10913,10 +10922,10 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -10945,10 +10954,10 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -10977,10 +10986,10 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -11009,10 +11018,10 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -11041,10 +11050,10 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -11073,10 +11082,10 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -11105,10 +11114,10 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -11137,10 +11146,10 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -11169,10 +11178,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -11201,10 +11210,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -11233,10 +11242,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11265,10 +11274,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -11297,10 +11306,10 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -11329,10 +11338,10 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11361,10 +11370,10 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -11393,10 +11402,10 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -11425,10 +11434,10 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11457,10 +11466,10 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11489,10 +11498,10 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -11521,10 +11530,10 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -11553,10 +11562,10 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -11585,10 +11594,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -11617,10 +11626,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11649,10 +11658,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -11681,10 +11690,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11713,10 +11722,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -11745,10 +11754,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -11777,10 +11786,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -11809,10 +11818,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -11841,10 +11850,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -11873,10 +11882,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -11905,10 +11914,10 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -11937,10 +11946,10 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -11969,10 +11978,10 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D58" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -12001,10 +12010,10 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12033,10 +12042,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D60" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12065,10 +12074,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12097,10 +12106,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12129,10 +12138,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12161,10 +12170,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -12193,10 +12202,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D65" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12225,10 +12234,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12257,10 +12266,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D67" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12289,10 +12298,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -12321,10 +12330,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D69" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -12353,10 +12362,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D70" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -12385,10 +12394,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D71" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -12417,10 +12426,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -12449,10 +12458,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D73" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -12481,10 +12490,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -12513,10 +12522,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D75" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -12545,10 +12554,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -12577,10 +12586,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D77" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -12609,10 +12618,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D78" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -12641,10 +12650,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D79" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -12673,10 +12682,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D80" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -12705,10 +12714,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D81" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -12737,10 +12746,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D82" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -12769,10 +12778,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D83" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -12801,10 +12810,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -12833,10 +12842,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D85" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -13281,7 +13290,7 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D99" t="s">
         <v>471</v>
@@ -13313,7 +13322,7 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
         <v>475</v>
@@ -13368,14 +13377,14 @@
         <v>477</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
         <v>478</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J2" s="6">
         <v>1</v>
@@ -13392,7 +13401,7 @@
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>482</v>
@@ -13401,7 +13410,7 @@
         <v>483</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
@@ -13425,7 +13434,7 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>489</v>
@@ -13434,7 +13443,7 @@
         <v>490</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
@@ -13458,7 +13467,7 @@
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>496</v>
@@ -13467,7 +13476,7 @@
         <v>497</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
@@ -13491,7 +13500,7 @@
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>503</v>
@@ -13524,7 +13533,7 @@
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>510</v>
@@ -13557,7 +13566,7 @@
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>518</v>
@@ -13583,7 +13592,7 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>524</v>
@@ -13609,7 +13618,7 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>530</v>
@@ -14846,7 +14855,7 @@
         <v>1001</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="E5">
         <v>7000</v>
@@ -14866,7 +14875,7 @@
         <v>1001</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>2200</v>
@@ -14886,7 +14895,7 @@
         <v>1001</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E7">
         <v>700</v>
@@ -14906,7 +14915,7 @@
         <v>1001</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -14931,7 +14940,7 @@
         <v>1002</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="E10">
         <v>5000</v>
@@ -14951,7 +14960,7 @@
         <v>1002</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>3000</v>
@@ -14971,7 +14980,7 @@
         <v>1002</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E12">
         <v>1700</v>
@@ -14991,7 +15000,7 @@
         <v>1002</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -15016,7 +15025,7 @@
         <v>2001</v>
       </c>
       <c r="D15" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="E15">
         <v>3000</v>
@@ -15036,7 +15045,7 @@
         <v>2001</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>7000</v>
@@ -15056,7 +15065,7 @@
         <v>2001</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -15076,7 +15085,7 @@
         <v>2001</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -15264,19 +15273,19 @@
         <v>100401</v>
       </c>
       <c r="C5" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F5" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -15322,19 +15331,19 @@
         <v>100501</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F7" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -15351,19 +15360,19 @@
         <v>100502</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F8" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -15380,19 +15389,19 @@
         <v>100503</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -15438,19 +15447,19 @@
         <v>100601</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -15467,19 +15476,19 @@
         <v>100602</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -15496,19 +15505,19 @@
         <v>100603</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -15525,19 +15534,19 @@
         <v>100604</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -15586,19 +15595,19 @@
         <v>100701</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D16">
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -15618,19 +15627,19 @@
         <v>100702</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D17">
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -15650,19 +15659,19 @@
         <v>100703</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D18">
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -15679,19 +15688,19 @@
         <v>100704</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D19">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -15967,7 +15976,7 @@
         <v>477</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
         <v>683</v>
@@ -15987,7 +15996,7 @@
         <v>483</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
         <v>686</v>
@@ -16007,7 +16016,7 @@
         <v>490</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>688</v>
@@ -16027,7 +16036,7 @@
         <v>497</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
         <v>690</v>
@@ -16169,7 +16178,7 @@
         <v>698</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -16183,7 +16192,7 @@
         <v>699</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -16197,7 +16206,7 @@
         <v>700</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -16205,12 +16214,12 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -16221,7 +16230,7 @@
         <v>701</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -16229,12 +16238,12 @@
     </row>
     <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="D12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -16354,7 +16363,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="B6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -16362,7 +16371,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -16370,7 +16379,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -16378,7 +16387,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -16386,7 +16395,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="B10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -16394,7 +16403,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -16402,7 +16411,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="B12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -16410,7 +16419,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="709">
   <si>
     <t>##var</t>
   </si>
@@ -1835,6 +1835,9 @@
     <t>直接展示奖励</t>
   </si>
   <si>
+    <t>IsLoopTrack</t>
+  </si>
+  <si>
     <t>StartSeconds</t>
   </si>
   <si>
@@ -1859,13 +1862,16 @@
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
-    <t>按玩家总游玩秒数计算的生效时间</t>
-  </si>
-  <si>
-    <t>循环间隔；固定时间点填 0</t>
-  </si>
-  <si>
-    <t>结束时间；无限循环填 -1</t>
+    <t>按玩家总游玩秒数计算的生效时间
+该数值主要用于Steam库存中判定玩家是否可以领取该奖励的时间下限</t>
+  </si>
+  <si>
+    <t>间隔时间
+玩家领取一个盲盒之后，等待下一个盲盒到达需要多长间隔时间</t>
+  </si>
+  <si>
+    <t>结束时间；无限循环填 -1
+策划注意导SteamJSON是需要确认改字段的用途</t>
   </si>
   <si>
     <t>最多发放次数；不限填 -1</t>
@@ -1880,10 +1886,13 @@
     <t>最多保留几个待领取资格</t>
   </si>
   <si>
+    <t>是循环生效的</t>
+  </si>
+  <si>
     <t>开始秒数</t>
   </si>
   <si>
-    <t>循环间隔秒数</t>
+    <t>间隔秒数</t>
   </si>
   <si>
     <t>结束秒数</t>
@@ -10087,7 +10096,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85 H92 H5:H8 H9:H13 H14:H16 H18:H45 H46:H50 H51:H62 H63:H72 H73:H84 H86:H89 H90:H91 H93:H94 H95:H98 H99:H100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H100">
       <formula1>枚举示例!$F$2:$F$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
@@ -10632,7 +10641,7 @@
         <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10664,7 +10673,7 @@
         <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -14099,24 +14108,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="10.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="13.1666666666667" customWidth="1"/>
-    <col min="9" max="9" width="10.25" customWidth="1"/>
-    <col min="10" max="10" width="11.0833333333333" customWidth="1"/>
-    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
-    <col min="12" max="12" width="45.25" customWidth="1"/>
+    <col min="3" max="4" width="10.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" customWidth="1"/>
+    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
+    <col min="13" max="13" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14148,10 +14157,13 @@
         <v>603</v>
       </c>
       <c r="K1" t="s">
+        <v>604</v>
+      </c>
+      <c r="L1" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -14162,7 +14174,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -14177,24 +14189,24 @@
         <v>31</v>
       </c>
       <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>31</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
       <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>605</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -14216,10 +14228,13 @@
         <v>611</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -14230,521 +14245,566 @@
         <v>576</v>
       </c>
       <c r="D4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K4" t="s">
+        <v>620</v>
+      </c>
+      <c r="L4" t="s">
         <v>584</v>
       </c>
-      <c r="L4" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
         <v>1001</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>30</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>30</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>1002</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>90</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
       <c r="F6">
+        <v>60</v>
+      </c>
+      <c r="G6">
         <v>90</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>100</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>2001</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>150</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
       <c r="F7">
+        <v>60</v>
+      </c>
+      <c r="G7">
         <v>150</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>10</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>1001</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>210</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
+        <v>60</v>
+      </c>
+      <c r="G8">
         <v>210</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>50</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>1002</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>270</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
       <c r="F9">
+        <v>60</v>
+      </c>
+      <c r="G9">
         <v>270</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>100</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>2001</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>330</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
         <v>330</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
       <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>10</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1001</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>390</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
+        <v>60</v>
+      </c>
+      <c r="G11">
         <v>390</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
       <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>50</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>1002</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>450</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
       <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
         <v>450</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>100</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>2001</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>510</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
       <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13">
         <v>510</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
       <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>10</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14">
         <v>1001</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>570</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
         <v>570</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
       <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
         <v>50</v>
       </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15">
         <v>1002</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>630</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15">
         <v>630</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
       <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
         <v>100</v>
       </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16">
         <v>2001</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>690</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
+        <v>60</v>
+      </c>
+      <c r="G16">
         <v>690</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
       <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
         <v>10</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17">
         <v>1001</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>750</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>180</v>
-      </c>
-      <c r="F17">
-        <v>-1</v>
       </c>
       <c r="G17">
         <v>-1</v>
       </c>
       <c r="H17">
+        <v>-1</v>
+      </c>
+      <c r="I17">
         <v>50</v>
       </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12">
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18">
         <v>2001</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18">
         <v>840</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>180</v>
-      </c>
-      <c r="F18">
-        <v>-1</v>
       </c>
       <c r="G18">
         <v>-1</v>
       </c>
       <c r="H18">
+        <v>-1</v>
+      </c>
+      <c r="I18">
         <v>10</v>
       </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>633</v>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -14777,10 +14837,10 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F1" t="s">
         <v>559</v>
@@ -14812,13 +14872,13 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>584</v>
@@ -14838,13 +14898,13 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F4" t="s">
         <v>584</v>
       </c>
       <c r="G4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -14864,7 +14924,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -14884,7 +14944,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -14904,7 +14964,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -14924,7 +14984,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -14949,7 +15009,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -14969,7 +15029,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -14989,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -15009,7 +15069,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -15119,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -15154,25 +15214,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1" t="s">
         <v>559</v>
       </c>
       <c r="I1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -15209,28 +15269,28 @@
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>584</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15241,33 +15301,33 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H4" t="s">
         <v>584</v>
       </c>
       <c r="I4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="J4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B5">
         <v>100401</v>
@@ -15299,33 +15359,33 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B7">
         <v>100501</v>
@@ -15354,7 +15414,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B8">
         <v>100502</v>
@@ -15383,7 +15443,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B9">
         <v>100503</v>
@@ -15415,33 +15475,33 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B11">
         <v>100601</v>
@@ -15470,7 +15530,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B12">
         <v>100602</v>
@@ -15499,7 +15559,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B13">
         <v>100603</v>
@@ -15528,7 +15588,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B14">
         <v>100604</v>
@@ -15555,7 +15615,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15563,33 +15623,33 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B16">
         <v>100701</v>
@@ -15616,12 +15676,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B17">
         <v>100702</v>
@@ -15648,12 +15708,12 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B18">
         <v>100703</v>
@@ -15682,7 +15742,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B19">
         <v>100704</v>
@@ -15714,33 +15774,33 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B21">
         <v>100801</v>
@@ -15769,7 +15829,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B22">
         <v>100901</v>
@@ -15798,28 +15858,28 @@
     </row>
     <row r="23" spans="1:10">
       <c r="B23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -15861,22 +15921,22 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="K1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -15917,20 +15977,20 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15947,25 +16007,25 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J4" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="K4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15979,13 +16039,13 @@
         <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -15999,13 +16059,13 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
+        <v>688</v>
+      </c>
+      <c r="F6" t="s">
         <v>686</v>
       </c>
-      <c r="F6" t="s">
-        <v>684</v>
-      </c>
       <c r="J6" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -16019,13 +16079,13 @@
         <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F7" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J7" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -16039,13 +16099,13 @@
         <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -16059,13 +16119,13 @@
         <v>472</v>
       </c>
       <c r="E9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F9" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -16079,13 +16139,13 @@
         <v>512</v>
       </c>
       <c r="E10" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F10" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -16113,10 +16173,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16133,7 +16193,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -16150,10 +16210,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16175,7 +16235,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D5" t="s">
         <v>136</v>
@@ -16189,7 +16249,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D6" t="s">
         <v>178</v>
@@ -16203,7 +16263,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D7" t="s">
         <v>199</v>
@@ -16227,7 +16287,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D10" t="s">
         <v>411</v>
@@ -16251,7 +16311,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D13" t="s">
         <v>459</v>
@@ -16328,7 +16388,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16350,7 +16410,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="716">
   <si>
     <t>##var</t>
   </si>
@@ -2063,6 +2063,9 @@
     <t>BlindBoxGlowPath</t>
   </si>
   <si>
+    <t>BlindBoxBackgroundColor</t>
+  </si>
+  <si>
     <t>BlindBoxBackgroundPath</t>
   </si>
   <si>
@@ -2079,6 +2082,9 @@
   </si>
   <si>
     <t>可选</t>
+  </si>
+  <si>
+    <t>16进制颜色代码</t>
   </si>
   <si>
     <t>开盲盒环节，该品质出现时，播放的音效。
@@ -2094,6 +2100,9 @@
     <t>盲盒发光图</t>
   </si>
   <si>
+    <t>背景颜色</t>
+  </si>
+  <si>
     <t>盲盒背景图</t>
   </si>
   <si>
@@ -2109,22 +2118,34 @@
     <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
   </si>
   <si>
+    <t>e3504a</t>
+  </si>
+  <si>
     <t>si</t>
   </si>
   <si>
     <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
   </si>
   <si>
+    <t>b574f0</t>
+  </si>
+  <si>
     <t>sol</t>
   </si>
   <si>
     <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
   </si>
   <si>
+    <t>0f7edc</t>
+  </si>
+  <si>
     <t>mi</t>
   </si>
   <si>
     <t>UI\BlindBox\BlindBox_Common_Closed.png</t>
+  </si>
+  <si>
+    <t>e4bf8f</t>
   </si>
   <si>
     <t>do</t>
@@ -10641,7 +10662,7 @@
         <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10673,7 +10694,7 @@
         <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -15891,7 +15912,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -15901,13 +15922,14 @@
     <col min="5" max="5" width="39.75" customWidth="1"/>
     <col min="6" max="6" width="38.5" customWidth="1"/>
     <col min="7" max="7" width="16.4166666666667" customWidth="1"/>
-    <col min="8" max="8" width="22.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="6.16666666666667" customWidth="1"/>
-    <col min="10" max="10" width="19.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="16.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="9" max="9" width="22.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="6.16666666666667" customWidth="1"/>
+    <col min="11" max="11" width="19.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="16.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15932,14 +15954,17 @@
       <c r="H1" t="s">
         <v>672</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" t="s">
         <v>673</v>
       </c>
       <c r="K1" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -15964,36 +15989,42 @@
       <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:11">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="J3" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -16007,28 +16038,31 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G4" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I4" t="s">
+        <v>685</v>
+      </c>
+      <c r="J4" t="s">
         <v>621</v>
       </c>
-      <c r="J4" t="s">
-        <v>683</v>
-      </c>
       <c r="K4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>686</v>
+      </c>
+      <c r="L4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -16039,16 +16073,19 @@
         <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F5" t="s">
-        <v>686</v>
-      </c>
-      <c r="J5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>689</v>
+      </c>
+      <c r="H5" t="s">
+        <v>690</v>
+      </c>
+      <c r="K5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -16059,16 +16096,19 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F6" t="s">
-        <v>686</v>
-      </c>
-      <c r="J6" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="H6" t="s">
+        <v>693</v>
+      </c>
+      <c r="K6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -16079,16 +16119,19 @@
         <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="F7" t="s">
-        <v>686</v>
-      </c>
-      <c r="J7" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>689</v>
+      </c>
+      <c r="H7" t="s">
+        <v>696</v>
+      </c>
+      <c r="K7" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -16099,16 +16142,19 @@
         <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F8" t="s">
-        <v>686</v>
-      </c>
-      <c r="J8" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>689</v>
+      </c>
+      <c r="H8" t="s">
+        <v>699</v>
+      </c>
+      <c r="K8" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -16119,16 +16165,19 @@
         <v>472</v>
       </c>
       <c r="E9" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F9" t="s">
-        <v>686</v>
-      </c>
-      <c r="I9" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>689</v>
+      </c>
+      <c r="H9" t="s">
+        <v>699</v>
+      </c>
+      <c r="J9" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -16139,13 +16188,16 @@
         <v>512</v>
       </c>
       <c r="E10" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F10" t="s">
-        <v>686</v>
-      </c>
-      <c r="I10" t="s">
-        <v>694</v>
+        <v>689</v>
+      </c>
+      <c r="H10" t="s">
+        <v>699</v>
+      </c>
+      <c r="J10" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -16173,10 +16225,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="D1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16193,7 +16245,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -16210,10 +16262,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="E3" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16235,7 +16287,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="D5" t="s">
         <v>136</v>
@@ -16249,7 +16301,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="D6" t="s">
         <v>178</v>
@@ -16263,7 +16315,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="D7" t="s">
         <v>199</v>
@@ -16287,7 +16339,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="D10" t="s">
         <v>411</v>
@@ -16311,7 +16363,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D13" t="s">
         <v>459</v>
@@ -16388,7 +16440,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16410,7 +16462,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="716">
   <si>
     <t>##var</t>
   </si>
@@ -2003,7 +2003,10 @@
     <t>StartRarity</t>
   </si>
   <si>
-    <t>MiddleRarity</t>
+    <t>MiddleRarity1</t>
+  </si>
+  <si>
+    <t>MiddleRarity2</t>
   </si>
   <si>
     <t>FinalRarity</t>
@@ -2042,16 +2045,13 @@
     <t>初始品质</t>
   </si>
   <si>
-    <t>过程品质</t>
+    <t>过程品质1</t>
   </si>
   <si>
     <t>最终品质</t>
   </si>
   <si>
     <t>是否提前结束</t>
-  </si>
-  <si>
-    <t>连升2品</t>
   </si>
   <si>
     <t>BlindBoxSpritePath</t>
@@ -15212,7 +15212,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -15220,14 +15220,14 @@
     <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="7.91666666666667" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="9.25" customWidth="1"/>
-    <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="8.41666666666667" customWidth="1"/>
-    <col min="9" max="9" width="11.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
+    <col min="6" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="8.41666666666667" customWidth="1"/>
+    <col min="10" max="10" width="11.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15250,13 +15250,16 @@
         <v>653</v>
       </c>
       <c r="H1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I1" t="s">
         <v>559</v>
       </c>
-      <c r="I1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="J1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -15279,42 +15282,48 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:10">
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>660</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -15322,33 +15331,36 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G4" t="s">
         <v>666</v>
       </c>
       <c r="H4" t="s">
+        <v>667</v>
+      </c>
+      <c r="I4" t="s">
         <v>584</v>
       </c>
-      <c r="I4" t="s">
-        <v>667</v>
-      </c>
       <c r="J4" t="s">
+        <v>668</v>
+      </c>
+      <c r="K4" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B5">
         <v>100401</v>
@@ -15368,45 +15380,51 @@
       <c r="G5" t="s">
         <v>137</v>
       </c>
-      <c r="H5" t="b">
-        <v>1</v>
+      <c r="H5" t="s">
+        <v>137</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I6" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>656</v>
+      </c>
+      <c r="J6" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B7">
         <v>100501</v>
@@ -15424,18 +15442,21 @@
         <v>137</v>
       </c>
       <c r="G7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H7" t="s">
         <v>90</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B8">
         <v>100502</v>
@@ -15450,21 +15471,24 @@
         <v>137</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
         <v>90</v>
       </c>
-      <c r="H8" t="b">
-        <v>1</v>
+      <c r="H8" t="s">
+        <v>90</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B9">
         <v>100503</v>
@@ -15476,7 +15500,7 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="F9" t="s">
         <v>90</v>
@@ -15484,45 +15508,51 @@
       <c r="G9" t="s">
         <v>90</v>
       </c>
-      <c r="H9" t="b">
-        <v>1</v>
+      <c r="H9" t="s">
+        <v>90</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I10" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>656</v>
+      </c>
+      <c r="J10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B11">
         <v>100601</v>
@@ -15537,21 +15567,24 @@
         <v>137</v>
       </c>
       <c r="F11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G11" t="s">
         <v>90</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>110</v>
       </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B12">
         <v>100602</v>
@@ -15566,21 +15599,24 @@
         <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" t="s">
         <v>110</v>
       </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B13">
         <v>100603</v>
@@ -15589,7 +15625,7 @@
         <v>110</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>90</v>
@@ -15598,18 +15634,21 @@
         <v>90</v>
       </c>
       <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" t="s">
         <v>110</v>
       </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B14">
         <v>100604</v>
@@ -15618,59 +15657,62 @@
         <v>110</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
         <v>110</v>
       </c>
-      <c r="H14" t="b">
-        <v>1</v>
+      <c r="H14" t="s">
+        <v>110</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I15" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>656</v>
+      </c>
+      <c r="J15" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B16">
         <v>100701</v>
@@ -15685,24 +15727,24 @@
         <v>137</v>
       </c>
       <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
         <v>110</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>126</v>
       </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="s">
-        <v>668</v>
+      <c r="J16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B17">
         <v>100702</v>
@@ -15714,27 +15756,27 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
         <v>90</v>
       </c>
       <c r="G17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" t="s">
         <v>126</v>
       </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
-      <c r="J17" t="s">
-        <v>668</v>
+      <c r="J17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B18">
         <v>100703</v>
@@ -15752,18 +15794,21 @@
         <v>110</v>
       </c>
       <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
         <v>126</v>
       </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
       <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B19">
         <v>100704</v>
@@ -15781,12 +15826,15 @@
         <v>110</v>
       </c>
       <c r="G19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" t="s">
         <v>126</v>
       </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
       <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -15795,33 +15843,36 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I20" t="s">
-        <v>655</v>
+        <v>656</v>
+      </c>
+      <c r="J20" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B21">
         <v>100801</v>
@@ -15841,16 +15892,19 @@
       <c r="G21" t="s">
         <v>472</v>
       </c>
-      <c r="H21" t="b">
-        <v>0</v>
+      <c r="H21" t="s">
+        <v>472</v>
       </c>
       <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B22">
         <v>100901</v>
@@ -15870,37 +15924,43 @@
       <c r="G22" t="s">
         <v>512</v>
       </c>
-      <c r="H22" t="b">
-        <v>0</v>
+      <c r="H22" t="s">
+        <v>512</v>
       </c>
       <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="B23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H23" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I23" t="s">
-        <v>655</v>
+        <v>656</v>
+      </c>
+      <c r="J23" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2127,7 +2127,7 @@
     <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
   </si>
   <si>
-    <t>b574f0</t>
+    <t>a869e3</t>
   </si>
   <si>
     <t>sol</t>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="718">
   <si>
     <t>##var</t>
   </si>
@@ -313,87 +313,96 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>初始拥有</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Red\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>黑柴</t>
+  </si>
+  <si>
+    <t>神话</t>
+  </si>
+  <si>
+    <t>装扮盲盒产出</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>白柴</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>Sesame</t>
+  </si>
+  <si>
+    <t>胡麻柴</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>Thin Red</t>
+  </si>
+  <si>
+    <t>瘦赤柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Unshaven Red</t>
+  </si>
+  <si>
+    <t>胡渣赤柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
+    <t>Thin Black</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
     <t>稀有</t>
   </si>
   <si>
-    <t>初始拥有</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Red\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Red.png</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>黑柴</t>
-  </si>
-  <si>
-    <t>装扮盲盒产出</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>Cream</t>
-  </si>
-  <si>
-    <t>白柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>Sesame</t>
-  </si>
-  <si>
-    <t>胡麻柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>Thin Red</t>
-  </si>
-  <si>
-    <t>瘦赤柴</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Unshaven Red</t>
-  </si>
-  <si>
-    <t>胡渣赤柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>Thin Black</t>
-  </si>
-  <si>
-    <t>瘦黑柴</t>
-  </si>
-  <si>
     <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
   </si>
   <si>
@@ -421,9 +430,6 @@
     <t>胡渣白柴</t>
   </si>
   <si>
-    <t>传说</t>
-  </si>
-  <si>
     <t>v1\ItemIcon\Shiba_UnshavenCream.png</t>
   </si>
   <si>
@@ -454,7 +460,7 @@
     <t>Headwear</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>优秀</t>
   </si>
   <si>
     <t>v1\Headwear\Beret_Green.png</t>
@@ -1474,148 +1480,154 @@
     <t>小狗本体</t>
   </si>
   <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>小狗头部装饰</t>
+  </si>
+  <si>
     <t>Legendary</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>在全部国家隐藏</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>小狗头部装饰</t>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
+    <t>小狗眼部装饰</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯</t>
-  </si>
-  <si>
-    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
-  </si>
-  <si>
-    <t>Serious</t>
-  </si>
-  <si>
-    <t>严肃</t>
-  </si>
-  <si>
-    <t>小狗眼部装饰</t>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
+    <t>手臂层的装饰</t>
   </si>
   <si>
     <t>Rare</t>
   </si>
   <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
-  </si>
-  <si>
-    <t>Bored</t>
-  </si>
-  <si>
-    <t>无聊</t>
-  </si>
-  <si>
-    <t>手臂层的装饰</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
+  </si>
+  <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
+    <t>玩家手臂衣服</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
+    <t>桌布</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>伊朗</t>
-  </si>
-  <si>
-    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
-  </si>
-  <si>
-    <t>Wink</t>
-  </si>
-  <si>
-    <t>媚眼</t>
-  </si>
-  <si>
-    <t>玩家手臂衣服</t>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
+    <t>背景</t>
   </si>
   <si>
     <t>Special1</t>
   </si>
   <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>Pakistan国家形象/政治</t>
-  </si>
-  <si>
-    <t>Excited</t>
-  </si>
-  <si>
-    <t>兴奋</t>
-  </si>
-  <si>
-    <t>桌布</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>玩家手部装饰</t>
   </si>
   <si>
     <t>Special2</t>
   </si>
   <si>
     <t>特殊2</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Starstruck</t>
-  </si>
-  <si>
-    <t>崇拜</t>
-  </si>
-  <si>
-    <t>背景</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>印尼</t>
-  </si>
-  <si>
-    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Silent</t>
-  </si>
-  <si>
-    <t>沉默</t>
-  </si>
-  <si>
-    <t>玩家手部装饰</t>
   </si>
   <si>
     <t>RU</t>
@@ -1970,28 +1982,7 @@
     <t>权重</t>
   </si>
   <si>
-    <t>标准盲盒：普通</t>
-  </si>
-  <si>
-    <t>标准盲盒：稀有</t>
-  </si>
-  <si>
-    <t>标准盲盒：史诗</t>
-  </si>
-  <si>
-    <t>标准盲盒：传说</t>
-  </si>
-  <si>
-    <t>新手盲盒：普通</t>
-  </si>
-  <si>
-    <t>新手盲盒：稀有</t>
-  </si>
-  <si>
-    <t>新手盲盒：史诗</t>
-  </si>
-  <si>
-    <t>新手盲盒：传说</t>
+    <t>新手盲盒概率会高一点</t>
   </si>
   <si>
     <t>测试活动盲盒：特殊1</t>
@@ -2052,6 +2043,9 @@
   </si>
   <si>
     <t>是否提前结束</t>
+  </si>
+  <si>
+    <t>连升2</t>
   </si>
   <si>
     <t>BlindBoxSpritePath</t>
@@ -2112,43 +2106,55 @@
     <t>升品特效路径</t>
   </si>
   <si>
+    <t>UI\BlindBox\BlindBox_Mythic_Closed.png</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
+  </si>
+  <si>
+    <t>e3504a</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>UI\BlindBox\BlindBox_Legendary_Closed.png</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
-  </si>
-  <si>
-    <t>e3504a</t>
+    <t>f0b811</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
+  </si>
+  <si>
+    <t>b574f0</t>
   </si>
   <si>
     <t>si</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
-  </si>
-  <si>
-    <t>a869e3</t>
+    <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
+  </si>
+  <si>
+    <t>0f7edc</t>
   </si>
   <si>
     <t>sol</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
-  </si>
-  <si>
-    <t>0f7edc</t>
-  </si>
-  <si>
-    <t>mi</t>
+    <t>UI\BlindBox\BlindBox_Unommon_Closed.png</t>
+  </si>
+  <si>
+    <t>68c68c</t>
   </si>
   <si>
     <t>UI\BlindBox\BlindBox_Common_Closed.png</t>
   </si>
   <si>
     <t>e4bf8f</t>
-  </si>
-  <si>
-    <t>do</t>
   </si>
   <si>
     <t>实际上特殊品质的盲盒没有显示图片的机会</t>
@@ -2820,7 +2826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2841,6 +2847,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2900,7 +2912,49 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3094,25 +3148,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="totalRow" dxfId="10"/>
+      <tableStyleElement type="firstColumn" dxfId="9"/>
+      <tableStyleElement type="lastColumn" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="18"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="16"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="15"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="14"/>
+      <tableStyleElement type="pageFieldValues" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3612,7 +3666,7 @@
       <c r="J3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="10"/>
       <c r="L3" s="1" t="s">
         <v>46</v>
       </c>
@@ -3844,7 +3898,7 @@
         <v>89</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I6">
         <v>200</v>
@@ -3853,7 +3907,7 @@
         <v>200</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -3868,10 +3922,10 @@
         <v>400</v>
       </c>
       <c r="S6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U6">
         <v>1002</v>
@@ -3903,16 +3957,16 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I7">
         <v>200</v>
@@ -3921,7 +3975,7 @@
         <v>200</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -3936,10 +3990,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="U7">
         <v>1003</v>
@@ -3971,16 +4025,16 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I8">
         <v>200</v>
@@ -3989,7 +4043,7 @@
         <v>200</v>
       </c>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -4004,10 +4058,10 @@
         <v>400</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="U8">
         <v>1004</v>
@@ -4039,16 +4093,16 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4057,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -4075,7 +4129,7 @@
         <v>92</v>
       </c>
       <c r="T9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U9">
         <v>1005</v>
@@ -4107,16 +4161,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4125,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -4143,7 +4197,7 @@
         <v>92</v>
       </c>
       <c r="T10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="U10">
         <v>1006</v>
@@ -4175,16 +4229,16 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4193,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -4208,10 +4262,10 @@
         <v>200</v>
       </c>
       <c r="S11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="U11">
         <v>1007</v>
@@ -4243,16 +4297,16 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
         <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4261,7 +4315,7 @@
         <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -4276,10 +4330,10 @@
         <v>200</v>
       </c>
       <c r="S12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U12">
         <v>1008</v>
@@ -4311,16 +4365,16 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4329,7 +4383,7 @@
         <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -4344,10 +4398,10 @@
         <v>200</v>
       </c>
       <c r="S13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="U13">
         <v>1009</v>
@@ -4379,16 +4433,16 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
         <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4397,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -4412,10 +4466,10 @@
         <v>200</v>
       </c>
       <c r="S14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="U14">
         <v>1010</v>
@@ -4447,16 +4501,16 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
         <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4465,7 +4519,7 @@
         <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -4480,10 +4534,10 @@
         <v>200</v>
       </c>
       <c r="S15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U15">
         <v>1011</v>
@@ -4515,16 +4569,16 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4533,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -4548,10 +4602,10 @@
         <v>200</v>
       </c>
       <c r="S16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U16">
         <v>1012</v>
@@ -4588,16 +4642,16 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I18">
         <v>300</v>
@@ -4606,7 +4660,7 @@
         <v>300</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -4621,10 +4675,10 @@
         <v>300</v>
       </c>
       <c r="S18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="T18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -4653,16 +4707,16 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I19">
         <v>300</v>
@@ -4671,7 +4725,7 @@
         <v>300</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -4686,10 +4740,10 @@
         <v>300</v>
       </c>
       <c r="S19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="T19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -4718,16 +4772,16 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I20">
         <v>300</v>
@@ -4736,7 +4790,7 @@
         <v>300</v>
       </c>
       <c r="K20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -4751,10 +4805,10 @@
         <v>300</v>
       </c>
       <c r="S20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -4783,16 +4837,16 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I21">
         <v>300</v>
@@ -4801,7 +4855,7 @@
         <v>300</v>
       </c>
       <c r="K21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -4816,10 +4870,10 @@
         <v>300</v>
       </c>
       <c r="S21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -4848,16 +4902,16 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I22">
         <v>300</v>
@@ -4866,7 +4920,7 @@
         <v>300</v>
       </c>
       <c r="K22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -4881,10 +4935,10 @@
         <v>300</v>
       </c>
       <c r="S22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -4913,16 +4967,16 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I23">
         <v>300</v>
@@ -4931,7 +4985,7 @@
         <v>300</v>
       </c>
       <c r="K23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -4946,10 +5000,10 @@
         <v>300</v>
       </c>
       <c r="S23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -4978,16 +5032,16 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I24">
         <v>300</v>
@@ -4996,7 +5050,7 @@
         <v>300</v>
       </c>
       <c r="K24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -5011,10 +5065,10 @@
         <v>300</v>
       </c>
       <c r="S24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -5043,16 +5097,16 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I25">
         <v>300</v>
@@ -5061,7 +5115,7 @@
         <v>300</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -5076,10 +5130,10 @@
         <v>300</v>
       </c>
       <c r="S25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="T25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -5108,16 +5162,16 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I26">
         <v>300</v>
@@ -5126,7 +5180,7 @@
         <v>300</v>
       </c>
       <c r="K26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -5141,10 +5195,10 @@
         <v>300</v>
       </c>
       <c r="S26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="T26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -5173,16 +5227,16 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H27" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I27">
         <v>300</v>
@@ -5191,7 +5245,7 @@
         <v>300</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -5206,10 +5260,10 @@
         <v>300</v>
       </c>
       <c r="S27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -5238,16 +5292,16 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I28">
         <v>300</v>
@@ -5256,7 +5310,7 @@
         <v>300</v>
       </c>
       <c r="K28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -5271,10 +5325,10 @@
         <v>300</v>
       </c>
       <c r="S28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -5303,16 +5357,16 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I29">
         <v>300</v>
@@ -5321,7 +5375,7 @@
         <v>300</v>
       </c>
       <c r="K29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -5336,10 +5390,10 @@
         <v>300</v>
       </c>
       <c r="S29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="T29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="W29">
         <v>0</v>
@@ -5368,16 +5422,16 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I30">
         <v>300</v>
@@ -5386,7 +5440,7 @@
         <v>300</v>
       </c>
       <c r="K30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -5401,10 +5455,10 @@
         <v>300</v>
       </c>
       <c r="S30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="T30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5433,16 +5487,16 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I31">
         <v>300</v>
@@ -5451,7 +5505,7 @@
         <v>300</v>
       </c>
       <c r="K31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -5466,10 +5520,10 @@
         <v>300</v>
       </c>
       <c r="S31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5498,16 +5552,16 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I32">
         <v>300</v>
@@ -5516,7 +5570,7 @@
         <v>300</v>
       </c>
       <c r="K32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -5531,10 +5585,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="T32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5563,19 +5617,19 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5599,10 +5653,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="T33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -5631,19 +5685,19 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5667,10 +5721,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T34" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5699,19 +5753,19 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F35" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H35" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5735,10 +5789,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="W35">
         <v>0</v>
@@ -5767,19 +5821,19 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H36" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5803,10 +5857,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="T36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -5835,16 +5889,16 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I37">
         <v>300</v>
@@ -5853,7 +5907,7 @@
         <v>300</v>
       </c>
       <c r="K37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -5868,10 +5922,10 @@
         <v>300</v>
       </c>
       <c r="S37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -5900,16 +5954,16 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H38" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I38">
         <v>300</v>
@@ -5918,7 +5972,7 @@
         <v>300</v>
       </c>
       <c r="K38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -5933,10 +5987,10 @@
         <v>300</v>
       </c>
       <c r="S38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="T38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -5965,16 +6019,16 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I39">
         <v>300</v>
@@ -5983,7 +6037,7 @@
         <v>300</v>
       </c>
       <c r="K39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -5998,10 +6052,10 @@
         <v>300</v>
       </c>
       <c r="S39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="T39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -6030,16 +6084,16 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I40">
         <v>300</v>
@@ -6048,7 +6102,7 @@
         <v>300</v>
       </c>
       <c r="K40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -6063,10 +6117,10 @@
         <v>300</v>
       </c>
       <c r="S40" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="T40" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -6095,16 +6149,16 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I41">
         <v>300</v>
@@ -6113,7 +6167,7 @@
         <v>300</v>
       </c>
       <c r="K41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -6128,10 +6182,10 @@
         <v>300</v>
       </c>
       <c r="S41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="T41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -6160,16 +6214,16 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I42">
         <v>300</v>
@@ -6178,7 +6232,7 @@
         <v>300</v>
       </c>
       <c r="K42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -6193,10 +6247,10 @@
         <v>300</v>
       </c>
       <c r="S42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -6225,16 +6279,16 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -6243,7 +6297,7 @@
         <v>300</v>
       </c>
       <c r="K43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -6258,10 +6312,10 @@
         <v>300</v>
       </c>
       <c r="S43" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T43" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -6290,16 +6344,16 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I44">
         <v>300</v>
@@ -6308,7 +6362,7 @@
         <v>300</v>
       </c>
       <c r="K44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -6323,10 +6377,10 @@
         <v>300</v>
       </c>
       <c r="S44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="T44" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="W44">
         <v>0</v>
@@ -6355,16 +6409,16 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H45" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -6388,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="T45" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -6420,16 +6474,16 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I46">
         <v>300</v>
@@ -6438,7 +6492,7 @@
         <v>300</v>
       </c>
       <c r="K46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -6453,10 +6507,10 @@
         <v>300</v>
       </c>
       <c r="S46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="T46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -6485,16 +6539,16 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H47" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I47">
         <v>300</v>
@@ -6503,7 +6557,7 @@
         <v>300</v>
       </c>
       <c r="K47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -6518,10 +6572,10 @@
         <v>300</v>
       </c>
       <c r="S47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -6550,16 +6604,16 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I48">
         <v>300</v>
@@ -6568,7 +6622,7 @@
         <v>300</v>
       </c>
       <c r="K48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -6583,10 +6637,10 @@
         <v>300</v>
       </c>
       <c r="S48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -6615,16 +6669,16 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H49" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I49">
         <v>300</v>
@@ -6633,7 +6687,7 @@
         <v>300</v>
       </c>
       <c r="K49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -6648,10 +6702,10 @@
         <v>300</v>
       </c>
       <c r="S49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="T49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -6680,16 +6734,16 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I50">
         <v>300</v>
@@ -6698,7 +6752,7 @@
         <v>300</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -6713,10 +6767,10 @@
         <v>300</v>
       </c>
       <c r="S50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="W50">
         <v>0</v>
@@ -6745,16 +6799,16 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E51" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H51" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I51">
         <v>300</v>
@@ -6763,7 +6817,7 @@
         <v>300</v>
       </c>
       <c r="K51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -6778,10 +6832,10 @@
         <v>300</v>
       </c>
       <c r="S51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="T51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -6810,16 +6864,16 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I52">
         <v>300</v>
@@ -6828,7 +6882,7 @@
         <v>300</v>
       </c>
       <c r="K52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -6843,10 +6897,10 @@
         <v>300</v>
       </c>
       <c r="S52" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="T52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -6875,16 +6929,16 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I53">
         <v>300</v>
@@ -6893,7 +6947,7 @@
         <v>300</v>
       </c>
       <c r="K53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -6908,10 +6962,10 @@
         <v>300</v>
       </c>
       <c r="S53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="T53" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -6940,16 +6994,16 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H54" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -6958,7 +7012,7 @@
         <v>300</v>
       </c>
       <c r="K54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -6973,10 +7027,10 @@
         <v>300</v>
       </c>
       <c r="S54" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T54" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -7005,16 +7059,16 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H55" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I55">
         <v>300</v>
@@ -7023,7 +7077,7 @@
         <v>300</v>
       </c>
       <c r="K55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -7038,10 +7092,10 @@
         <v>300</v>
       </c>
       <c r="S55" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T55" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -7070,16 +7124,16 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I56">
         <v>300</v>
@@ -7088,7 +7142,7 @@
         <v>300</v>
       </c>
       <c r="K56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -7103,10 +7157,10 @@
         <v>300</v>
       </c>
       <c r="S56" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T56" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -7135,16 +7189,16 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E57" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H57" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I57">
         <v>300</v>
@@ -7153,7 +7207,7 @@
         <v>300</v>
       </c>
       <c r="K57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -7168,10 +7222,10 @@
         <v>300</v>
       </c>
       <c r="S57" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T57" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="W57">
         <v>0</v>
@@ -7200,16 +7254,16 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E58" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I58">
         <v>300</v>
@@ -7218,7 +7272,7 @@
         <v>300</v>
       </c>
       <c r="K58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -7233,10 +7287,10 @@
         <v>300</v>
       </c>
       <c r="S58" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T58" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -7265,16 +7319,16 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D59" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E59" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H59" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I59">
         <v>300</v>
@@ -7298,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T59" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -7330,16 +7384,16 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E60" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I60">
         <v>300</v>
@@ -7348,7 +7402,7 @@
         <v>300</v>
       </c>
       <c r="K60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -7363,10 +7417,10 @@
         <v>300</v>
       </c>
       <c r="S60" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T60" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -7395,16 +7449,16 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E61" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I61">
         <v>300</v>
@@ -7413,7 +7467,7 @@
         <v>300</v>
       </c>
       <c r="K61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -7428,10 +7482,10 @@
         <v>300</v>
       </c>
       <c r="S61" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="T61" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W61">
         <v>0</v>
@@ -7460,16 +7514,16 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E62" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -7478,7 +7532,7 @@
         <v>300</v>
       </c>
       <c r="K62" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -7493,10 +7547,10 @@
         <v>300</v>
       </c>
       <c r="S62" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="T62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -7525,16 +7579,16 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E63" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H63" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I63">
         <v>300</v>
@@ -7543,7 +7597,7 @@
         <v>300</v>
       </c>
       <c r="K63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -7558,10 +7612,10 @@
         <v>300</v>
       </c>
       <c r="S63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="T63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="W63">
         <v>0</v>
@@ -7590,16 +7644,16 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E64" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H64" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I64">
         <v>300</v>
@@ -7608,7 +7662,7 @@
         <v>300</v>
       </c>
       <c r="K64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -7623,10 +7677,10 @@
         <v>300</v>
       </c>
       <c r="S64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T64" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W64">
         <v>0</v>
@@ -7655,16 +7709,16 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E65" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H65" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I65">
         <v>300</v>
@@ -7673,7 +7727,7 @@
         <v>300</v>
       </c>
       <c r="K65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -7688,10 +7742,10 @@
         <v>300</v>
       </c>
       <c r="S65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -7720,16 +7774,16 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D66" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H66" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I66">
         <v>300</v>
@@ -7738,7 +7792,7 @@
         <v>300</v>
       </c>
       <c r="K66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -7753,10 +7807,10 @@
         <v>300</v>
       </c>
       <c r="S66" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T66" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -7785,16 +7839,16 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E67" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H67" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I67">
         <v>300</v>
@@ -7803,7 +7857,7 @@
         <v>300</v>
       </c>
       <c r="K67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -7818,10 +7872,10 @@
         <v>300</v>
       </c>
       <c r="S67" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T67" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -7850,16 +7904,16 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D68" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E68" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H68" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I68">
         <v>300</v>
@@ -7868,7 +7922,7 @@
         <v>300</v>
       </c>
       <c r="K68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -7883,10 +7937,10 @@
         <v>300</v>
       </c>
       <c r="S68" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="T68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -7915,16 +7969,16 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D69" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E69" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H69" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I69">
         <v>300</v>
@@ -7933,7 +7987,7 @@
         <v>300</v>
       </c>
       <c r="K69" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -7948,10 +8002,10 @@
         <v>300</v>
       </c>
       <c r="S69" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -7980,16 +8034,16 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D70" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E70" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I70">
         <v>300</v>
@@ -7998,7 +8052,7 @@
         <v>300</v>
       </c>
       <c r="K70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -8013,10 +8067,10 @@
         <v>300</v>
       </c>
       <c r="S70" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T70" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -8045,16 +8099,16 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I71">
         <v>300</v>
@@ -8063,7 +8117,7 @@
         <v>300</v>
       </c>
       <c r="K71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -8078,10 +8132,10 @@
         <v>300</v>
       </c>
       <c r="S71" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T71" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="W71">
         <v>0</v>
@@ -8110,16 +8164,16 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E72" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H72" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I72">
         <v>300</v>
@@ -8128,7 +8182,7 @@
         <v>300</v>
       </c>
       <c r="K72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -8143,10 +8197,10 @@
         <v>300</v>
       </c>
       <c r="S72" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T72" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="W72">
         <v>0</v>
@@ -8175,16 +8229,16 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E73" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I73">
         <v>300</v>
@@ -8193,7 +8247,7 @@
         <v>300</v>
       </c>
       <c r="K73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -8208,10 +8262,10 @@
         <v>300</v>
       </c>
       <c r="S73" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="T73" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -8240,16 +8294,16 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E74" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H74" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I74">
         <v>300</v>
@@ -8258,7 +8312,7 @@
         <v>300</v>
       </c>
       <c r="K74" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -8273,10 +8327,10 @@
         <v>300</v>
       </c>
       <c r="S74" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T74" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -8305,16 +8359,16 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E75" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I75">
         <v>300</v>
@@ -8323,7 +8377,7 @@
         <v>300</v>
       </c>
       <c r="K75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -8338,10 +8392,10 @@
         <v>300</v>
       </c>
       <c r="S75" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T75" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="W75">
         <v>0</v>
@@ -8370,16 +8424,16 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E76" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H76" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I76">
         <v>300</v>
@@ -8388,7 +8442,7 @@
         <v>300</v>
       </c>
       <c r="K76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -8403,10 +8457,10 @@
         <v>300</v>
       </c>
       <c r="S76" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="T76" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -8435,16 +8489,16 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D77" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E77" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H77" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I77">
         <v>300</v>
@@ -8453,7 +8507,7 @@
         <v>300</v>
       </c>
       <c r="K77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -8468,10 +8522,10 @@
         <v>300</v>
       </c>
       <c r="S77" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="T77" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -8500,16 +8554,16 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E78" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -8518,7 +8572,7 @@
         <v>300</v>
       </c>
       <c r="K78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -8533,10 +8587,10 @@
         <v>300</v>
       </c>
       <c r="S78" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T78" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -8565,16 +8619,16 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D79" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E79" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I79">
         <v>300</v>
@@ -8583,7 +8637,7 @@
         <v>300</v>
       </c>
       <c r="K79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -8598,10 +8652,10 @@
         <v>300</v>
       </c>
       <c r="S79" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="T79" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="W79">
         <v>0</v>
@@ -8630,16 +8684,16 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E80" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H80" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I80">
         <v>300</v>
@@ -8648,7 +8702,7 @@
         <v>300</v>
       </c>
       <c r="K80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -8663,10 +8717,10 @@
         <v>300</v>
       </c>
       <c r="S80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="T80" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="W80">
         <v>0</v>
@@ -8695,16 +8749,16 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E81" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H81" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I81">
         <v>300</v>
@@ -8713,7 +8767,7 @@
         <v>300</v>
       </c>
       <c r="K81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -8728,10 +8782,10 @@
         <v>300</v>
       </c>
       <c r="S81" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="T81" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -8760,16 +8814,16 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E82" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -8778,7 +8832,7 @@
         <v>300</v>
       </c>
       <c r="K82" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -8793,10 +8847,10 @@
         <v>300</v>
       </c>
       <c r="S82" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T82" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -8825,16 +8879,16 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E83" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H83" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -8843,7 +8897,7 @@
         <v>300</v>
       </c>
       <c r="K83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -8858,10 +8912,10 @@
         <v>300</v>
       </c>
       <c r="S83" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T83" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -8890,16 +8944,16 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D84" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E84" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H84" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -8908,7 +8962,7 @@
         <v>300</v>
       </c>
       <c r="K84" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -8923,10 +8977,10 @@
         <v>300</v>
       </c>
       <c r="S84" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T84" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="W84">
         <v>0</v>
@@ -8955,16 +9009,16 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E85" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H85" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I85">
         <v>200</v>
@@ -8973,7 +9027,7 @@
         <v>300</v>
       </c>
       <c r="K85" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -8991,10 +9045,10 @@
         <v>300</v>
       </c>
       <c r="S85" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="T85" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="W85">
         <v>0</v>
@@ -9023,22 +9077,22 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E86" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F86" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G86">
         <v>9009</v>
       </c>
       <c r="H86" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I86">
         <v>200</v>
@@ -9047,7 +9101,7 @@
         <v>300</v>
       </c>
       <c r="K86" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -9065,13 +9119,13 @@
         <v>300</v>
       </c>
       <c r="S86" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="T86" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W86">
         <v>0</v>
@@ -9100,22 +9154,22 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E87" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F87" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G87">
         <v>9009</v>
       </c>
       <c r="H87" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I87">
         <v>200</v>
@@ -9124,7 +9178,7 @@
         <v>300</v>
       </c>
       <c r="K87" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -9142,13 +9196,13 @@
         <v>300</v>
       </c>
       <c r="S87" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T87" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W87">
         <v>0</v>
@@ -9177,22 +9231,22 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D88" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E88" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F88" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G88">
         <v>9009</v>
       </c>
       <c r="H88" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I88">
         <v>200</v>
@@ -9201,7 +9255,7 @@
         <v>300</v>
       </c>
       <c r="K88" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -9219,13 +9273,13 @@
         <v>300</v>
       </c>
       <c r="S88" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T88" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W88">
         <v>0</v>
@@ -9254,22 +9308,22 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F89" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G89">
         <v>9009</v>
       </c>
       <c r="H89" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I89">
         <v>200</v>
@@ -9278,7 +9332,7 @@
         <v>300</v>
       </c>
       <c r="K89" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -9296,13 +9350,13 @@
         <v>300</v>
       </c>
       <c r="S89" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T89" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W89">
         <v>0</v>
@@ -9331,22 +9385,22 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E90" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F90" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G90">
         <v>9009</v>
       </c>
       <c r="H90" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I90">
         <v>200</v>
@@ -9355,7 +9409,7 @@
         <v>300</v>
       </c>
       <c r="K90" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -9373,13 +9427,13 @@
         <v>300</v>
       </c>
       <c r="S90" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="T90" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W90">
         <v>0</v>
@@ -9408,22 +9462,22 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E91" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F91" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G91">
         <v>9009</v>
       </c>
       <c r="H91" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I91">
         <v>200</v>
@@ -9432,7 +9486,7 @@
         <v>300</v>
       </c>
       <c r="K91" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -9450,13 +9504,13 @@
         <v>300</v>
       </c>
       <c r="S91" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="T91" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W91">
         <v>0</v>
@@ -9485,22 +9539,22 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E92" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F92" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G92">
         <v>9009</v>
       </c>
       <c r="H92" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I92">
         <v>200</v>
@@ -9509,7 +9563,7 @@
         <v>300</v>
       </c>
       <c r="K92" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -9527,13 +9581,13 @@
         <v>300</v>
       </c>
       <c r="S92" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="T92" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W92">
         <v>0</v>
@@ -9562,16 +9616,16 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D93" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E93" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H93" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I93">
         <v>200</v>
@@ -9580,7 +9634,7 @@
         <v>300</v>
       </c>
       <c r="K93" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -9598,13 +9652,13 @@
         <v>300</v>
       </c>
       <c r="S93" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T93" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W93">
         <v>0</v>
@@ -9633,22 +9687,22 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D94" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E94" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F94" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G94">
         <v>9009</v>
       </c>
       <c r="H94" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I94">
         <v>200</v>
@@ -9657,7 +9711,7 @@
         <v>300</v>
       </c>
       <c r="K94" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -9675,10 +9729,10 @@
         <v>300</v>
       </c>
       <c r="S94" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="T94" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="W94">
         <v>0</v>
@@ -9707,22 +9761,22 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D95" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E95" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F95" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G95">
         <v>9009</v>
       </c>
       <c r="H95" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I95">
         <v>200</v>
@@ -9731,7 +9785,7 @@
         <v>300</v>
       </c>
       <c r="K95" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -9749,13 +9803,13 @@
         <v>300</v>
       </c>
       <c r="S95" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T95" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W95">
         <v>0</v>
@@ -9784,16 +9838,16 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D96" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E96" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H96" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I96">
         <v>300</v>
@@ -9817,10 +9871,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="T96" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="W96">
         <v>0</v>
@@ -9849,16 +9903,16 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E97" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H97" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I97">
         <v>300</v>
@@ -9882,13 +9936,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="T97" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="W97">
         <v>0</v>
@@ -9917,19 +9971,19 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E98" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G98">
         <v>11001</v>
       </c>
       <c r="H98" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I98">
         <v>300</v>
@@ -9953,10 +10007,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="T98" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="W98">
         <v>0</v>
@@ -9985,16 +10039,16 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E99" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H99" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I99">
         <v>100</v>
@@ -10003,7 +10057,7 @@
         <v>300</v>
       </c>
       <c r="K99" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -10016,13 +10070,13 @@
       </c>
       <c r="R99" s="2"/>
       <c r="S99" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T99" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="W99">
         <v>0</v>
@@ -10051,16 +10105,16 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E100" t="s">
         <v>89</v>
       </c>
       <c r="H100" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I100">
         <v>100</v>
@@ -10069,7 +10123,7 @@
         <v>100</v>
       </c>
       <c r="K100" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -10082,16 +10136,16 @@
       </c>
       <c r="R100" s="2"/>
       <c r="S100" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T100" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U100">
         <v>1012</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="W100">
         <v>0</v>
@@ -10116,9 +10170,29 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H$1:H$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"普通"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H100">
-      <formula1>枚举示例!$F$2:$F$7</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55 H59 H63 H73 H74 H75 H78 H79 H82 H83 H85 H90 H91 H92 H93 H5:H16 H18:H51 H52:H54 H56:H58 H60:H62 H64:H68 H69:H70 H71:H72 H76:H77 H80:H81 H86:H89 H94:H95 H96:H98 H99:H100">
+      <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
       <formula1>枚举示例!$C$18:$C$23</formula1>
@@ -10403,10 +10477,10 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -10435,10 +10509,10 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -10467,10 +10541,10 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -10499,10 +10573,10 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -10531,10 +10605,10 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -10563,10 +10637,10 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -10595,10 +10669,10 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -10627,10 +10701,10 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -10659,10 +10733,10 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10691,10 +10765,10 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -10728,10 +10802,10 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -10760,10 +10834,10 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -10792,10 +10866,10 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -10824,10 +10898,10 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -10856,10 +10930,10 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -10888,10 +10962,10 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -10920,10 +10994,10 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -10952,10 +11026,10 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -10984,10 +11058,10 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -11016,10 +11090,10 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -11048,10 +11122,10 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -11080,10 +11154,10 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -11112,10 +11186,10 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -11144,10 +11218,10 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -11176,10 +11250,10 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -11208,10 +11282,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -11240,10 +11314,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -11272,10 +11346,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11304,10 +11378,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -11336,10 +11410,10 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -11368,10 +11442,10 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11400,10 +11474,10 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -11432,10 +11506,10 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -11464,10 +11538,10 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11496,10 +11570,10 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11528,10 +11602,10 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -11560,10 +11634,10 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -11592,10 +11666,10 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -11624,10 +11698,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -11656,10 +11730,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11688,10 +11762,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -11720,10 +11794,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11752,10 +11826,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -11784,10 +11858,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -11816,10 +11890,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -11848,10 +11922,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -11880,10 +11954,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -11912,10 +11986,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -11944,10 +12018,10 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -11976,10 +12050,10 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -12008,10 +12082,10 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -12040,10 +12114,10 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D59" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12072,10 +12146,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12104,10 +12178,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12136,10 +12210,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12168,10 +12242,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12200,10 +12274,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -12232,10 +12306,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12264,10 +12338,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D66" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12296,10 +12370,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12328,10 +12402,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D68" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -12360,10 +12434,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D69" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -12392,10 +12466,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D70" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -12424,10 +12498,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -12456,10 +12530,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -12488,10 +12562,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -12520,10 +12594,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -12552,10 +12626,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -12584,10 +12658,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -12616,10 +12690,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D77" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -12648,10 +12722,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -12680,10 +12754,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D79" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -12712,10 +12786,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -12744,10 +12818,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -12776,10 +12850,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -12808,10 +12882,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -12840,10 +12914,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D84" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -12872,10 +12946,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -12904,10 +12978,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -12936,10 +13010,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -12968,10 +13042,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D88" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -13000,10 +13074,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -13032,10 +13106,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -13064,10 +13138,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -13096,10 +13170,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -13128,10 +13202,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D93" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -13160,10 +13234,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D94" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -13192,10 +13266,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D95" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -13224,10 +13298,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D96" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -13256,10 +13330,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -13288,10 +13362,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -13320,10 +13394,10 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -13352,10 +13426,10 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -13401,328 +13475,340 @@
         <v>89</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>126</v>
+        <v>478</v>
+      </c>
+      <c r="E2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J2" s="6">
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>472</v>
+        <v>505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F6" t="s">
+        <v>139</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>512</v>
+        <v>90</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>474</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>528</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="J9" s="6">
         <v>128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="J10" s="6">
         <v>256</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J11" s="6">
         <v>512</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J12" s="6">
         <v>1024</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="H13" s="6" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J13" s="6">
         <v>2048</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="6" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>91</v>
@@ -13730,42 +13816,42 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="6" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="6" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="6" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="6" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="6" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -13806,34 +13892,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="F1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="I1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="J1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -13847,10 +13933,10 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
@@ -13859,7 +13945,7 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -13882,81 +13968,81 @@
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="4" s="7" customFormat="1" spans="1:13">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4" s="9" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="G4" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="H4" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="I4" s="9" t="s">
         <v>587</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13964,13 +14050,13 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F5">
         <v>1000</v>
@@ -14002,13 +14088,13 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -14040,13 +14126,13 @@
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -14078,13 +14164,13 @@
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D8" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -14157,31 +14243,31 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="K1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="L1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -14228,31 +14314,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14263,37 +14349,37 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G4" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H4" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I4" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="K4" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="M4" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14331,7 +14417,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14369,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14407,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -14445,7 +14531,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14483,7 +14569,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14521,7 +14607,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14559,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14597,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -14635,7 +14721,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -14673,7 +14759,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -14711,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -14749,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -14787,7 +14873,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -14825,7 +14911,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -14837,17 +14923,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.08333333333333" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14858,16 +14945,16 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>641</v>
+      </c>
+      <c r="G1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -14883,29 +14970,30 @@
       <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>643</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -14913,22 +15001,22 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D4" t="s">
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>640</v>
-      </c>
-      <c r="F4" t="s">
-        <v>584</v>
+        <v>644</v>
       </c>
       <c r="G4" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>588</v>
+      </c>
+      <c r="H4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>100101</v>
       </c>
@@ -14936,19 +15024,20 @@
         <v>1001</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>7000</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <f>E5/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>100102</v>
       </c>
@@ -14956,19 +15045,20 @@
         <v>1001</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="E6">
-        <v>2200</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>6700</v>
+      </c>
+      <c r="F6" s="7">
+        <f>E6/10000</f>
+        <v>0.67</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>100103</v>
       </c>
@@ -14976,19 +15066,20 @@
         <v>1001</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>700</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>2200</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" ref="F7:F17" si="0">E7/10000</f>
+        <v>0.22</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>100104</v>
       </c>
@@ -14996,211 +15087,351 @@
         <v>1001</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E8">
+        <v>900</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9">
+        <v>100105</v>
+      </c>
+      <c r="C9">
+        <v>1001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9">
+        <v>180</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.018</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10">
+        <v>100106</v>
+      </c>
+      <c r="C10">
+        <v>1001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.002</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F5:F10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12">
+        <v>100201</v>
+      </c>
+      <c r="C12">
+        <v>1001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13">
+        <v>100202</v>
+      </c>
+      <c r="C13">
+        <v>1001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13">
+        <v>3700</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14">
+        <v>100203</v>
+      </c>
+      <c r="C14">
+        <v>1001</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14">
+        <v>4200</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15">
+        <v>100204</v>
+      </c>
+      <c r="C15">
+        <v>1001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15">
+        <v>1700</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16">
+        <v>100205</v>
+      </c>
+      <c r="C16">
+        <v>1001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16">
+        <v>380</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.038</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="B17">
+        <v>100206</v>
+      </c>
+      <c r="C17">
+        <v>1001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.002</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="7">
+        <f>SUM(F12:F17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="B19">
+        <v>200101</v>
+      </c>
+      <c r="C19">
+        <v>2001</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="B20">
+        <v>200102</v>
+      </c>
+      <c r="C20">
+        <v>2001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20">
+        <v>3000</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21">
+        <v>200103</v>
+      </c>
+      <c r="C21">
+        <v>2001</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21">
+        <v>7000</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="B22">
+        <v>200104</v>
+      </c>
+      <c r="C22">
+        <v>2001</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="B23">
+        <v>200105</v>
+      </c>
+      <c r="C23">
+        <v>2001</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24">
+        <v>200106</v>
+      </c>
+      <c r="C24">
+        <v>2001</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="B26">
+        <v>300101</v>
+      </c>
+      <c r="C26">
+        <v>3001</v>
+      </c>
+      <c r="D26" t="s">
+        <v>474</v>
+      </c>
+      <c r="E26">
         <v>100</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10">
-        <v>100201</v>
-      </c>
-      <c r="C10">
-        <v>1002</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10">
-        <v>5000</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11">
-        <v>100202</v>
-      </c>
-      <c r="C11">
-        <v>1002</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11">
-        <v>3000</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
         <v>646</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12">
-        <v>100203</v>
-      </c>
-      <c r="C12">
-        <v>1002</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12">
-        <v>1700</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13">
-        <v>100204</v>
-      </c>
-      <c r="C13">
-        <v>1002</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13">
-        <v>300</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15">
-        <v>200101</v>
-      </c>
-      <c r="C15">
-        <v>2001</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15">
-        <v>3000</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16">
-        <v>200102</v>
-      </c>
-      <c r="C16">
-        <v>2001</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16">
-        <v>7000</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="B17">
-        <v>200103</v>
-      </c>
-      <c r="C17">
-        <v>2001</v>
-      </c>
-      <c r="D17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="B18">
-        <v>200104</v>
-      </c>
-      <c r="C18">
-        <v>2001</v>
-      </c>
-      <c r="D18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20">
-        <v>300101</v>
-      </c>
-      <c r="C20">
-        <v>3001</v>
-      </c>
-      <c r="D20" t="s">
-        <v>472</v>
-      </c>
-      <c r="E20">
-        <v>100</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -15212,7 +15443,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -15235,28 +15466,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1" t="s">
+        <v>649</v>
+      </c>
+      <c r="G1" t="s">
         <v>650</v>
       </c>
-      <c r="D1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>651</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1" t="s">
         <v>652</v>
-      </c>
-      <c r="G1" t="s">
-        <v>653</v>
-      </c>
-      <c r="H1" t="s">
-        <v>654</v>
-      </c>
-      <c r="I1" t="s">
-        <v>559</v>
-      </c>
-      <c r="J1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -15296,31 +15527,31 @@
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15331,57 +15562,57 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E4" t="s">
+        <v>662</v>
+      </c>
+      <c r="F4" t="s">
         <v>663</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H4" t="s">
         <v>664</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
+        <v>588</v>
+      </c>
+      <c r="J4" t="s">
         <v>665</v>
       </c>
-      <c r="F4" t="s">
-        <v>666</v>
-      </c>
-      <c r="G4" t="s">
-        <v>666</v>
-      </c>
-      <c r="H4" t="s">
-        <v>667</v>
-      </c>
-      <c r="I4" t="s">
-        <v>584</v>
-      </c>
-      <c r="J4" t="s">
-        <v>668</v>
-      </c>
       <c r="K4" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B5">
         <v>100401</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -15395,57 +15626,57 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B7">
         <v>100501</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -15456,28 +15687,28 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B8">
         <v>100502</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D8">
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -15488,28 +15719,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B9">
         <v>100503</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -15523,57 +15754,57 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B11">
-        <v>100601</v>
+        <v>100501</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11">
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -15584,28 +15815,28 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B12">
-        <v>100602</v>
+        <v>100502</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D12">
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -15616,28 +15847,28 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B13">
-        <v>100603</v>
+        <v>100503</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -15647,29 +15878,26 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>656</v>
-      </c>
       <c r="B14">
-        <v>100604</v>
+        <v>100504</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -15683,57 +15911,57 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J15" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B16">
-        <v>100701</v>
+        <v>100601</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D16">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -15742,30 +15970,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B17">
-        <v>100702</v>
+        <v>100602</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
         <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -15773,31 +16001,34 @@
       <c r="J17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B18">
-        <v>100703</v>
+        <v>100603</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="H18" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -15805,31 +16036,34 @@
       <c r="J18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B19">
-        <v>100704</v>
+        <v>100604</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H19" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -15838,132 +16072,506 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J20" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B21">
+        <v>100701</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>653</v>
+      </c>
+      <c r="B22">
+        <v>100702</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>653</v>
+      </c>
+      <c r="B23">
+        <v>100703</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>653</v>
+      </c>
+      <c r="B24">
+        <v>100704</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>653</v>
+      </c>
+      <c r="C25" t="s">
+        <v>653</v>
+      </c>
+      <c r="D25" t="s">
+        <v>653</v>
+      </c>
+      <c r="E25" t="s">
+        <v>653</v>
+      </c>
+      <c r="F25" t="s">
+        <v>653</v>
+      </c>
+      <c r="G25" t="s">
+        <v>653</v>
+      </c>
+      <c r="H25" t="s">
+        <v>653</v>
+      </c>
+      <c r="I25" t="s">
+        <v>653</v>
+      </c>
+      <c r="J25" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>653</v>
+      </c>
+      <c r="B26">
         <v>100801</v>
       </c>
-      <c r="C21" t="s">
-        <v>472</v>
-      </c>
-      <c r="D21">
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>653</v>
+      </c>
+      <c r="B27">
+        <v>100802</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>653</v>
+      </c>
+      <c r="B28">
+        <v>100803</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>653</v>
+      </c>
+      <c r="B29">
+        <v>100804</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>653</v>
+      </c>
+      <c r="C30" t="s">
+        <v>653</v>
+      </c>
+      <c r="D30" t="s">
+        <v>653</v>
+      </c>
+      <c r="E30" t="s">
+        <v>653</v>
+      </c>
+      <c r="F30" t="s">
+        <v>653</v>
+      </c>
+      <c r="G30" t="s">
+        <v>653</v>
+      </c>
+      <c r="H30" t="s">
+        <v>653</v>
+      </c>
+      <c r="I30" t="s">
+        <v>653</v>
+      </c>
+      <c r="J30" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>653</v>
+      </c>
+      <c r="B31">
+        <v>200101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>474</v>
+      </c>
+      <c r="D31">
         <v>100</v>
       </c>
-      <c r="E21" t="s">
-        <v>472</v>
-      </c>
-      <c r="F21" t="s">
-        <v>472</v>
-      </c>
-      <c r="G21" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" t="s">
-        <v>472</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>656</v>
-      </c>
-      <c r="B22">
-        <v>100901</v>
-      </c>
-      <c r="C22" t="s">
-        <v>512</v>
-      </c>
-      <c r="D22">
+      <c r="E31" t="s">
+        <v>474</v>
+      </c>
+      <c r="F31" t="s">
+        <v>474</v>
+      </c>
+      <c r="G31" t="s">
+        <v>474</v>
+      </c>
+      <c r="H31" t="s">
+        <v>474</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>653</v>
+      </c>
+      <c r="B32">
+        <v>200201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>528</v>
+      </c>
+      <c r="D32">
         <v>100</v>
       </c>
-      <c r="E22" t="s">
-        <v>512</v>
-      </c>
-      <c r="F22" t="s">
-        <v>512</v>
-      </c>
-      <c r="G22" t="s">
-        <v>512</v>
-      </c>
-      <c r="H22" t="s">
-        <v>512</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="B23" t="s">
-        <v>656</v>
-      </c>
-      <c r="C23" t="s">
-        <v>656</v>
-      </c>
-      <c r="D23" t="s">
-        <v>656</v>
-      </c>
-      <c r="E23" t="s">
-        <v>656</v>
-      </c>
-      <c r="F23" t="s">
-        <v>656</v>
-      </c>
-      <c r="G23" t="s">
-        <v>656</v>
-      </c>
-      <c r="H23" t="s">
-        <v>656</v>
-      </c>
-      <c r="I23" t="s">
-        <v>656</v>
-      </c>
-      <c r="J23" t="s">
-        <v>656</v>
+      <c r="E32" t="s">
+        <v>528</v>
+      </c>
+      <c r="F32" t="s">
+        <v>528</v>
+      </c>
+      <c r="G32" t="s">
+        <v>528</v>
+      </c>
+      <c r="H32" t="s">
+        <v>528</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" t="s">
+        <v>653</v>
+      </c>
+      <c r="C33" t="s">
+        <v>653</v>
+      </c>
+      <c r="D33" t="s">
+        <v>653</v>
+      </c>
+      <c r="E33" t="s">
+        <v>653</v>
+      </c>
+      <c r="F33" t="s">
+        <v>653</v>
+      </c>
+      <c r="G33" t="s">
+        <v>653</v>
+      </c>
+      <c r="H33" t="s">
+        <v>653</v>
+      </c>
+      <c r="I33" t="s">
+        <v>653</v>
+      </c>
+      <c r="J33" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:H24 E30:H1048576">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E$1:H$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"普通"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:H29">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -15972,7 +16580,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -16003,25 +16611,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>667</v>
+      </c>
+      <c r="F1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G1" t="s">
         <v>669</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>670</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>671</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>672</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>673</v>
-      </c>
-      <c r="K1" t="s">
-        <v>674</v>
-      </c>
-      <c r="L1" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -16065,23 +16673,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16098,51 +16706,51 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
+        <v>679</v>
+      </c>
+      <c r="F4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G4" t="s">
         <v>681</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>682</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>683</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
+        <v>625</v>
+      </c>
+      <c r="K4" t="s">
         <v>684</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>685</v>
-      </c>
-      <c r="J4" t="s">
-        <v>621</v>
-      </c>
-      <c r="K4" t="s">
-        <v>686</v>
-      </c>
-      <c r="L4" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>126</v>
+      <c r="C5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
       </c>
       <c r="E5" t="s">
+        <v>686</v>
+      </c>
+      <c r="F5" t="s">
+        <v>687</v>
+      </c>
+      <c r="H5" t="s">
         <v>688</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
         <v>689</v>
-      </c>
-      <c r="H5" t="s">
-        <v>690</v>
-      </c>
-      <c r="K5" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -16150,22 +16758,22 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" t="s">
+        <v>687</v>
+      </c>
+      <c r="H6" t="s">
+        <v>691</v>
+      </c>
+      <c r="K6" t="s">
         <v>692</v>
-      </c>
-      <c r="F6" t="s">
-        <v>689</v>
-      </c>
-      <c r="H6" t="s">
-        <v>693</v>
-      </c>
-      <c r="K6" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -16173,22 +16781,22 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
+        <v>693</v>
+      </c>
+      <c r="F7" t="s">
+        <v>687</v>
+      </c>
+      <c r="H7" t="s">
+        <v>694</v>
+      </c>
+      <c r="K7" t="s">
         <v>695</v>
-      </c>
-      <c r="F7" t="s">
-        <v>689</v>
-      </c>
-      <c r="H7" t="s">
-        <v>696</v>
-      </c>
-      <c r="K7" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -16196,22 +16804,22 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" t="s">
+        <v>687</v>
+      </c>
+      <c r="H8" t="s">
+        <v>697</v>
+      </c>
+      <c r="K8" t="s">
         <v>698</v>
-      </c>
-      <c r="F8" t="s">
-        <v>689</v>
-      </c>
-      <c r="H8" t="s">
-        <v>699</v>
-      </c>
-      <c r="K8" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -16219,22 +16827,22 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>472</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F9" t="s">
+        <v>687</v>
+      </c>
+      <c r="H9" t="s">
+        <v>700</v>
+      </c>
+      <c r="K9" t="s">
         <v>689</v>
-      </c>
-      <c r="H9" t="s">
-        <v>699</v>
-      </c>
-      <c r="J9" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -16242,22 +16850,68 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>512</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F10" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H10" t="s">
-        <v>699</v>
-      </c>
-      <c r="J10" t="s">
+        <v>702</v>
+      </c>
+      <c r="K10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11">
+        <v>2001</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E11" t="s">
         <v>701</v>
+      </c>
+      <c r="F11" t="s">
+        <v>687</v>
+      </c>
+      <c r="H11" t="s">
+        <v>702</v>
+      </c>
+      <c r="J11" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12">
+        <v>2002</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="E12" t="s">
+        <v>701</v>
+      </c>
+      <c r="F12" t="s">
+        <v>687</v>
+      </c>
+      <c r="H12" t="s">
+        <v>702</v>
+      </c>
+      <c r="J12" t="s">
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -16285,10 +16939,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16305,7 +16959,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -16322,10 +16976,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16347,10 +17001,10 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -16361,10 +17015,10 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -16375,10 +17029,10 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -16386,12 +17040,12 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -16399,10 +17053,10 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -16410,12 +17064,12 @@
     </row>
     <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="D12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -16423,10 +17077,10 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -16434,7 +17088,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" spans="3:4">
@@ -16500,7 +17154,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16522,7 +17176,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -16535,7 +17189,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="B6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -16543,7 +17197,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -16551,7 +17205,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -16559,7 +17213,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -16567,7 +17221,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="B10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -16575,7 +17229,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -16583,7 +17237,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="B12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -16591,7 +17245,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -16599,7 +17253,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -16607,7 +17261,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -10191,7 +10191,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55 H59 H63 H73 H74 H75 H78 H79 H82 H83 H85 H90 H91 H92 H93 H5:H16 H18:H51 H52:H54 H56:H58 H60:H62 H64:H68 H69:H70 H71:H72 H76:H77 H80:H81 H86:H89 H94:H95 H96:H98 H99:H100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H83 H85:H100">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
@@ -15786,7 +15786,7 @@
         <v>653</v>
       </c>
       <c r="B11">
-        <v>100501</v>
+        <v>100601</v>
       </c>
       <c r="C11" t="s">
         <v>119</v>
@@ -15818,7 +15818,7 @@
         <v>653</v>
       </c>
       <c r="B12">
-        <v>100502</v>
+        <v>100602</v>
       </c>
       <c r="C12" t="s">
         <v>119</v>
@@ -15850,7 +15850,7 @@
         <v>653</v>
       </c>
       <c r="B13">
-        <v>100503</v>
+        <v>100603</v>
       </c>
       <c r="C13" t="s">
         <v>119</v>
@@ -15879,7 +15879,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="B14">
-        <v>100504</v>
+        <v>100604</v>
       </c>
       <c r="C14" t="s">
         <v>119</v>
@@ -15943,7 +15943,7 @@
         <v>653</v>
       </c>
       <c r="B16">
-        <v>100601</v>
+        <v>100701</v>
       </c>
       <c r="C16" t="s">
         <v>103</v>
@@ -15975,7 +15975,7 @@
         <v>653</v>
       </c>
       <c r="B17">
-        <v>100602</v>
+        <v>100702</v>
       </c>
       <c r="C17" t="s">
         <v>103</v>
@@ -16010,7 +16010,7 @@
         <v>653</v>
       </c>
       <c r="B18">
-        <v>100603</v>
+        <v>100703</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -16045,7 +16045,7 @@
         <v>653</v>
       </c>
       <c r="B19">
-        <v>100604</v>
+        <v>100704</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -16109,7 +16109,7 @@
         <v>653</v>
       </c>
       <c r="B21">
-        <v>100701</v>
+        <v>100801</v>
       </c>
       <c r="C21" t="s">
         <v>108</v>
@@ -16144,7 +16144,7 @@
         <v>653</v>
       </c>
       <c r="B22">
-        <v>100702</v>
+        <v>100802</v>
       </c>
       <c r="C22" t="s">
         <v>108</v>
@@ -16179,7 +16179,7 @@
         <v>653</v>
       </c>
       <c r="B23">
-        <v>100703</v>
+        <v>100803</v>
       </c>
       <c r="C23" t="s">
         <v>108</v>
@@ -16211,7 +16211,7 @@
         <v>653</v>
       </c>
       <c r="B24">
-        <v>100704</v>
+        <v>100804</v>
       </c>
       <c r="C24" t="s">
         <v>108</v>
@@ -16275,7 +16275,7 @@
         <v>653</v>
       </c>
       <c r="B26">
-        <v>100801</v>
+        <v>100901</v>
       </c>
       <c r="C26" t="s">
         <v>97</v>
@@ -16307,7 +16307,7 @@
         <v>653</v>
       </c>
       <c r="B27">
-        <v>100802</v>
+        <v>100902</v>
       </c>
       <c r="C27" t="s">
         <v>97</v>
@@ -16342,7 +16342,7 @@
         <v>653</v>
       </c>
       <c r="B28">
-        <v>100803</v>
+        <v>100903</v>
       </c>
       <c r="C28" t="s">
         <v>97</v>
@@ -16377,7 +16377,7 @@
         <v>653</v>
       </c>
       <c r="B29">
-        <v>100804</v>
+        <v>100904</v>
       </c>
       <c r="C29" t="s">
         <v>97</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -15156,7 +15156,7 @@
         <v>100201</v>
       </c>
       <c r="C12">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -15177,7 +15177,7 @@
         <v>100202</v>
       </c>
       <c r="C13">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -15201,7 +15201,7 @@
         <v>100203</v>
       </c>
       <c r="C14">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D14" t="s">
         <v>119</v>
@@ -15222,7 +15222,7 @@
         <v>100204</v>
       </c>
       <c r="C15">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D15" t="s">
         <v>103</v>
@@ -15243,7 +15243,7 @@
         <v>100205</v>
       </c>
       <c r="C16">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D16" t="s">
         <v>108</v>
@@ -15264,7 +15264,7 @@
         <v>100206</v>
       </c>
       <c r="C17">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D17" t="s">
         <v>97</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2145,7 +2145,7 @@
     <t>sol</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_Unommon_Closed.png</t>
+    <t>UI\BlindBox\BlindBox_Uncommon_Closed.png</t>
   </si>
   <si>
     <t>68c68c</t>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="632" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="717">
   <si>
     <t>##var</t>
   </si>
@@ -2185,9 +2185,6 @@
   </si>
   <si>
     <t>Theme</t>
-  </si>
-  <si>
-    <t>Card</t>
   </si>
   <si>
     <t>CanUnequip</t>
@@ -10736,7 +10733,7 @@
         <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10768,7 +10765,7 @@
         <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -16923,7 +16920,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -17032,7 +17029,7 @@
         <v>711</v>
       </c>
       <c r="D7" t="s">
-        <v>201</v>
+        <v>369</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -17040,62 +17037,70 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>369</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>712</v>
+      </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>252</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10">
-        <v>1005</v>
-      </c>
-      <c r="C10" t="s">
-        <v>712</v>
-      </c>
       <c r="D10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11">
+        <v>1006</v>
+      </c>
+      <c r="C11" t="s">
         <v>413</v>
       </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>252</v>
+        <v>413</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="D12" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13">
-        <v>1006</v>
-      </c>
-      <c r="C13" t="s">
-        <v>713</v>
-      </c>
       <c r="D13" t="s">
-        <v>461</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>466</v>
-      </c>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
       <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="3:4">
       <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="3:4">
       <c r="C25" s="6"/>
@@ -17120,14 +17125,6 @@
     <row r="30" spans="3:4">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="3:4">
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17154,7 +17151,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -17176,7 +17173,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="778">
   <si>
     <t>##var</t>
   </si>
@@ -149,10 +149,10 @@
     <t>ERarity</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>EAcquisitionType</t>
-  </si>
-  <si>
-    <t>bool</t>
   </si>
   <si>
     <t>list,string</t>
@@ -3764,11 +3764,14 @@
       <c r="J2" t="s">
         <v>32</v>
       </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
       <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" t="s">
         <v>37</v>
-      </c>
-      <c r="M2" t="s">
-        <v>38</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -3801,19 +3804,19 @@
         <v>40</v>
       </c>
       <c r="Z2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE2" t="s">
         <v>33</v>
@@ -11731,19 +11734,19 @@
         <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
         <v>33</v>
@@ -15389,10 +15392,10 @@
         <v>594</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>
@@ -15722,7 +15725,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -15740,13 +15743,13 @@
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
@@ -16412,7 +16415,7 @@
         <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
@@ -16957,10 +16960,10 @@
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="779">
   <si>
     <t>##var</t>
   </si>
@@ -2254,6 +2254,9 @@
   </si>
   <si>
     <t>Player</t>
+  </si>
+  <si>
+    <t>BodyDecoration</t>
   </si>
   <si>
     <t>Theme</t>
@@ -12180,7 +12183,7 @@
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -12212,7 +12215,7 @@
         <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -12406,7 +12409,7 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -13142,10 +13145,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D46" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -13174,10 +13177,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D47" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -13206,10 +13209,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D48" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -13238,10 +13241,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D49" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -13270,10 +13273,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D50" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -13302,10 +13305,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D51" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -13334,10 +13337,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D52" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -13366,10 +13369,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D53" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -13398,10 +13401,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D54" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -13430,10 +13433,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D55" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -13686,10 +13689,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D63" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -13750,10 +13753,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D65" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -13814,10 +13817,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D67" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -13974,10 +13977,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D72" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -14038,10 +14041,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D74" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -14102,10 +14105,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D76" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -14134,7 +14137,7 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D77" t="s">
         <v>397</v>
@@ -14166,7 +14169,7 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D78" t="s">
         <v>401</v>
@@ -14230,10 +14233,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D80" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -14262,10 +14265,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D81" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -18367,7 +18370,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -18488,62 +18491,63 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9">
+      <c r="D9" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
         <v>1005</v>
       </c>
-      <c r="C9" t="s">
-        <v>736</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C10" t="s">
+        <v>737</v>
+      </c>
+      <c r="D10" t="s">
         <v>263</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="D10" t="s">
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="B11">
+    <row r="12" spans="1:5">
+      <c r="B12">
         <v>1006</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>438</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>438</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="D12" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="D15" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="21" spans="3:4">
-      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="3:4">
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
       <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="3:4">
       <c r="C24" s="6"/>
@@ -18572,6 +18576,10 @@
     <row r="30" spans="3:4">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18598,7 +18606,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -18620,7 +18628,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="780">
   <si>
     <t>##var</t>
   </si>
@@ -1213,6 +1213,9 @@
     <t>锚纹身</t>
   </si>
   <si>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
     <t>v1\Player\Surface\AnchorTattoo.png</t>
   </si>
   <si>
@@ -1261,10 +1264,10 @@
     <t>体毛</t>
   </si>
   <si>
-    <t>v1\Player\Surface\Hair.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Hair.png</t>
+    <t>v1\Player\BodyDecoration\Hair.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\BodyDecoration_Hair.png</t>
   </si>
   <si>
     <t>Royal Mariner Onyx</t>
@@ -1754,6 +1757,9 @@
   </si>
   <si>
     <t>Syria国际制裁/政治/宗教</t>
+  </si>
+  <si>
+    <t>体表装饰</t>
   </si>
   <si>
     <t>CU</t>
@@ -2254,9 +2260,6 @@
   </si>
   <si>
     <t>Player</t>
-  </si>
-  <si>
-    <t>BodyDecoration</t>
   </si>
   <si>
     <t>Theme</t>
@@ -3009,7 +3012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3038,6 +3041,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3615,7 +3621,7 @@
   <cols>
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.6666666666667" customWidth="1"/>
     <col min="6" max="6" width="27.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.5833333333333" customWidth="1"/>
     <col min="10" max="12" width="14.3333333333333" customWidth="1"/>
@@ -3855,7 +3861,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -9421,7 +9427,7 @@
         <v>389</v>
       </c>
       <c r="E78" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F78" t="s">
         <v>162</v>
@@ -9466,10 +9472,10 @@
         <v>162</v>
       </c>
       <c r="T78" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="U78" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -9498,10 +9504,10 @@
         <v>8003</v>
       </c>
       <c r="C79" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D79" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E79" t="s">
         <v>385</v>
@@ -9549,10 +9555,10 @@
         <v>162</v>
       </c>
       <c r="T79" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U79" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X79">
         <v>0</v>
@@ -9581,10 +9587,10 @@
         <v>8004</v>
       </c>
       <c r="C80" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D80" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E80" t="s">
         <v>385</v>
@@ -9632,10 +9638,10 @@
         <v>162</v>
       </c>
       <c r="T80" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -9664,10 +9670,10 @@
         <v>8005</v>
       </c>
       <c r="C81" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D81" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E81" t="s">
         <v>385</v>
@@ -9715,10 +9721,10 @@
         <v>162</v>
       </c>
       <c r="T81" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="U81" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -9747,13 +9753,13 @@
         <v>8006</v>
       </c>
       <c r="C82" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D82" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E82" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F82" t="s">
         <v>162</v>
@@ -9762,7 +9768,7 @@
         <v>162</v>
       </c>
       <c r="H82" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -9798,10 +9804,10 @@
         <v>162</v>
       </c>
       <c r="T82" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U82" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -9830,10 +9836,10 @@
         <v>8007</v>
       </c>
       <c r="C83" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D83" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E83" t="s">
         <v>385</v>
@@ -9881,10 +9887,10 @@
         <v>162</v>
       </c>
       <c r="T83" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U83" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -9913,10 +9919,10 @@
         <v>8008</v>
       </c>
       <c r="C84" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D84" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E84" t="s">
         <v>385</v>
@@ -9964,10 +9970,10 @@
         <v>162</v>
       </c>
       <c r="T84" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U84" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -9996,10 +10002,10 @@
         <v>8009</v>
       </c>
       <c r="C85" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D85" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E85" t="s">
         <v>385</v>
@@ -10032,10 +10038,10 @@
         <v>300</v>
       </c>
       <c r="T85" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="U85" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="X85">
         <v>0</v>
@@ -10064,10 +10070,10 @@
         <v>8010</v>
       </c>
       <c r="C86" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D86" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E86" t="s">
         <v>385</v>
@@ -10100,10 +10106,10 @@
         <v>300</v>
       </c>
       <c r="T86" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U86" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -10132,10 +10138,10 @@
         <v>8011</v>
       </c>
       <c r="C87" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D87" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E87" t="s">
         <v>385</v>
@@ -10168,10 +10174,10 @@
         <v>300</v>
       </c>
       <c r="T87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U87" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -10203,10 +10209,10 @@
         <v>8012</v>
       </c>
       <c r="C88" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D88" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E88" t="s">
         <v>385</v>
@@ -10254,10 +10260,10 @@
         <v>162</v>
       </c>
       <c r="T88" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U88" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="V88" t="s">
         <v>162</v>
@@ -10307,10 +10313,10 @@
         <v>8013</v>
       </c>
       <c r="C89" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E89" t="s">
         <v>385</v>
@@ -10358,10 +10364,10 @@
         <v>162</v>
       </c>
       <c r="T89" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="U89" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="V89" t="s">
         <v>162</v>
@@ -10408,13 +10414,13 @@
         <v>9001</v>
       </c>
       <c r="C90" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E90" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H90" t="s">
         <v>141</v>
@@ -10429,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -10447,10 +10453,10 @@
         <v>300</v>
       </c>
       <c r="T90" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="U90" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -10479,16 +10485,16 @@
         <v>9002</v>
       </c>
       <c r="C91" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D91" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E91" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F91" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G91">
         <v>9009</v>
@@ -10506,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -10524,13 +10530,13 @@
         <v>300</v>
       </c>
       <c r="T91" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U91" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X91">
         <v>0</v>
@@ -10559,16 +10565,16 @@
         <v>9003</v>
       </c>
       <c r="C92" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D92" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E92" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F92" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G92">
         <v>9009</v>
@@ -10586,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -10604,13 +10610,13 @@
         <v>300</v>
       </c>
       <c r="T92" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U92" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -10639,16 +10645,16 @@
         <v>9004</v>
       </c>
       <c r="C93" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D93" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E93" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F93" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G93">
         <v>9009</v>
@@ -10666,7 +10672,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -10684,13 +10690,13 @@
         <v>300</v>
       </c>
       <c r="T93" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="U93" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -10719,16 +10725,16 @@
         <v>9005</v>
       </c>
       <c r="C94" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D94" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E94" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F94" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G94">
         <v>9009</v>
@@ -10746,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -10764,13 +10770,13 @@
         <v>300</v>
       </c>
       <c r="T94" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="U94" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -10799,16 +10805,16 @@
         <v>9006</v>
       </c>
       <c r="C95" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D95" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E95" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F95" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G95">
         <v>9009</v>
@@ -10826,7 +10832,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -10844,13 +10850,13 @@
         <v>300</v>
       </c>
       <c r="T95" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="U95" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -10879,16 +10885,16 @@
         <v>9007</v>
       </c>
       <c r="C96" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D96" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E96" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F96" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G96">
         <v>9009</v>
@@ -10906,7 +10912,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -10924,13 +10930,13 @@
         <v>300</v>
       </c>
       <c r="T96" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U96" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -10959,16 +10965,16 @@
         <v>9008</v>
       </c>
       <c r="C97" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D97" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E97" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F97" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G97">
         <v>9009</v>
@@ -10986,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -11004,13 +11010,13 @@
         <v>300</v>
       </c>
       <c r="T97" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="U97" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -11039,13 +11045,13 @@
         <v>9009</v>
       </c>
       <c r="C98" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D98" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E98" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H98" t="s">
         <v>92</v>
@@ -11060,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -11078,13 +11084,13 @@
         <v>300</v>
       </c>
       <c r="T98" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="U98" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -11113,16 +11119,16 @@
         <v>9010</v>
       </c>
       <c r="C99" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D99" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E99" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F99" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G99">
         <v>9009</v>
@@ -11140,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -11158,10 +11164,10 @@
         <v>300</v>
       </c>
       <c r="T99" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="U99" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="X99">
         <v>0</v>
@@ -11190,16 +11196,16 @@
         <v>9011</v>
       </c>
       <c r="C100" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D100" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E100" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F100" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G100">
         <v>9009</v>
@@ -11217,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -11235,13 +11241,13 @@
         <v>300</v>
       </c>
       <c r="T100" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="U100" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -11270,13 +11276,13 @@
         <v>10001</v>
       </c>
       <c r="C101" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D101" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E101" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H101" t="s">
         <v>92</v>
@@ -11306,10 +11312,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="U101" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="X101">
         <v>0</v>
@@ -11338,13 +11344,13 @@
         <v>11001</v>
       </c>
       <c r="C102" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D102" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E102" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H102" t="s">
         <v>92</v>
@@ -11374,13 +11380,13 @@
         <v>0</v>
       </c>
       <c r="T102" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U102" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="X102">
         <v>0</v>
@@ -11409,13 +11415,13 @@
         <v>11002</v>
       </c>
       <c r="C103" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D103" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E103" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G103">
         <v>11001</v>
@@ -11448,10 +11454,10 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U103" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="X103">
         <v>0</v>
@@ -11483,13 +11489,13 @@
         <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E104" t="s">
         <v>140</v>
       </c>
       <c r="H104" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I104">
         <v>100</v>
@@ -11501,7 +11507,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -11520,7 +11526,7 @@
         <v>159</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -11552,13 +11558,13 @@
         <v>135</v>
       </c>
       <c r="D105" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E105" t="s">
         <v>91</v>
       </c>
       <c r="H105" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I105">
         <v>100</v>
@@ -11570,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -11592,7 +11598,7 @@
         <v>1012</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="X105">
         <v>0</v>
@@ -12183,7 +12189,7 @@
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -12215,7 +12221,7 @@
         <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -12409,7 +12415,7 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -13145,10 +13151,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D46" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -13177,10 +13183,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D47" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -13209,10 +13215,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D48" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -13241,10 +13247,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D49" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -13273,10 +13279,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D50" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -13305,10 +13311,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D51" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -13337,10 +13343,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D52" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -13369,10 +13375,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D53" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -13401,10 +13407,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D54" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -13433,10 +13439,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D55" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -13689,10 +13695,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D63" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -13753,10 +13759,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D65" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -13817,10 +13823,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D67" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -13977,10 +13983,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D72" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -14041,10 +14047,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D74" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -14105,10 +14111,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D76" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -14137,10 +14143,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D77" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -14169,10 +14175,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D78" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -14201,10 +14207,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D79" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -14233,10 +14239,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D80" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -14265,10 +14271,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D81" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -14297,10 +14303,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D82" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -14329,10 +14335,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D83" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -14361,10 +14367,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D84" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -14393,10 +14399,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D85" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -14425,10 +14431,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D86" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -14457,10 +14463,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D87" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -14489,10 +14495,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D88" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -14521,10 +14527,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D89" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -14553,10 +14559,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D90" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -14585,10 +14591,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D91" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -14617,10 +14623,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D92" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14649,10 +14655,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D93" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -14681,10 +14687,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D94" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -14713,10 +14719,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D95" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14745,10 +14751,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D96" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -14777,10 +14783,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D97" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -14809,10 +14815,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D98" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -14844,7 +14850,7 @@
         <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -14876,7 +14882,7 @@
         <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -14922,17 +14928,17 @@
         <v>91</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F2" t="s">
         <v>99</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>213</v>
@@ -14941,13 +14947,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14955,32 +14961,32 @@
         <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -14988,32 +14994,32 @@
         <v>191</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -15021,32 +15027,32 @@
         <v>212</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -15054,32 +15060,32 @@
         <v>230</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F6" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -15087,32 +15093,32 @@
         <v>263</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -15120,31 +15126,31 @@
         <v>308</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -15152,110 +15158,116 @@
         <v>385</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J9" s="6">
         <v>128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J10" s="6">
         <v>256</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J11" s="6">
         <v>512</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J12" s="6">
         <v>1024</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" spans="2:16">
+      <c r="B13" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>572</v>
+      </c>
       <c r="H13" s="6" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J13" s="6">
         <v>2048</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="6" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>93</v>
@@ -15263,7 +15275,7 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="6" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>100</v>
@@ -15271,34 +15283,34 @@
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="6" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -15339,34 +15351,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15380,10 +15392,10 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
@@ -15392,7 +15404,7 @@
         <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -15415,40 +15427,40 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" s="9" customFormat="1" spans="1:13">
@@ -15456,40 +15468,40 @@
         <v>41</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15497,13 +15509,13 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F5">
         <v>2000</v>
@@ -15535,13 +15547,13 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>621</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>619</v>
       </c>
       <c r="F6">
         <v>2000</v>
@@ -15573,13 +15585,13 @@
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F7">
         <v>2000</v>
@@ -15611,13 +15623,13 @@
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D8" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -15690,31 +15702,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="I1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15761,31 +15773,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15796,37 +15808,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="I4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15864,7 +15876,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15902,7 +15914,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15940,7 +15952,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -15978,7 +15990,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16016,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16054,7 +16066,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16092,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -16130,7 +16142,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -16168,7 +16180,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -16206,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -16244,7 +16256,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -16282,7 +16294,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -16320,7 +16332,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -16358,7 +16370,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -16392,13 +16404,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -16427,17 +16439,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -16448,19 +16460,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -16640,7 +16652,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -16753,7 +16765,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16773,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -16793,7 +16805,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -16813,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -16833,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -16853,7 +16865,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -16869,7 +16881,7 @@
         <v>3001</v>
       </c>
       <c r="D26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -16878,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -16913,28 +16925,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -16977,28 +16989,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -17009,31 +17021,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D4" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H4" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J4" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -17449,7 +17461,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -17484,7 +17496,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -17583,7 +17595,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -17618,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -17781,7 +17793,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -17816,7 +17828,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -17851,7 +17863,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -17894,22 +17906,22 @@
         <v>200101</v>
       </c>
       <c r="C31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -17926,22 +17938,22 @@
         <v>200201</v>
       </c>
       <c r="C32" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F32" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G32" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H32" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -18058,25 +18070,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="K1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="L1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -18120,23 +18132,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -18153,28 +18165,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G4" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="I4" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="J4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K4" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L4" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -18182,22 +18194,22 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F5" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H5" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="K5" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -18205,22 +18217,22 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F6" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H6" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K6" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -18228,22 +18240,22 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F7" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H7" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="K7" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -18251,22 +18263,22 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -18274,22 +18286,22 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F9" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H9" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K9" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -18297,22 +18309,22 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F10" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H10" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="K10" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -18320,22 +18332,22 @@
         <v>2001</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H11" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="J11" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -18343,22 +18355,22 @@
         <v>2002</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E12" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F12" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H12" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="J12" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -18386,10 +18398,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -18406,7 +18418,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -18423,10 +18435,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -18448,7 +18460,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -18462,7 +18474,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -18476,7 +18488,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D7" t="s">
         <v>385</v>
@@ -18492,7 +18504,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>736</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -18500,7 +18512,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D10" t="s">
         <v>263</v>
@@ -18519,10 +18531,10 @@
         <v>1006</v>
       </c>
       <c r="C12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -18530,12 +18542,12 @@
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -18590,11 +18602,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
     <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18606,7 +18618,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -18628,7 +18640,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18697,7 +18709,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -18705,7 +18717,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -18713,10 +18725,18 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>390</v>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -1219,7 +1219,7 @@
     <t>v1\Player\Surface\AnchorTattoo.png</t>
   </si>
   <si>
-    <t>v1\ItemIcon\Accessory_AnchorTattoo.png</t>
+    <t>v1\ItemIcon\BodyDecoration_AnchorTattoo.png</t>
   </si>
   <si>
     <t>Canine D88</t>
@@ -3012,7 +3012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3041,9 +3041,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3861,7 +3858,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -15246,10 +15243,10 @@
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>572</v>
       </c>
       <c r="H13" s="6" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -1216,7 +1216,7 @@
     <t>BodyDecoration</t>
   </si>
   <si>
-    <t>v1\Player\Surface\AnchorTattoo.png</t>
+    <t>v1\Player\BodyDecoration\AnchorTattoo.png</t>
   </si>
   <si>
     <t>v1\ItemIcon\BodyDecoration_AnchorTattoo.png</t>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2398,10 +2398,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2882,16 +2888,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2900,119 +2903,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3039,6 +3045,9 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3858,7 +3867,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4525,7 +4534,7 @@
         <v>110</v>
       </c>
       <c r="I12">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4545,8 +4554,8 @@
       <c r="O12">
         <v>100</v>
       </c>
-      <c r="P12">
-        <v>200</v>
+      <c r="P12" s="9">
+        <v>200000</v>
       </c>
       <c r="T12" t="s">
         <v>101</v>
@@ -15460,44 +15469,44 @@
         <v>606</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" spans="1:13">
+    <row r="4" s="10" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>618</v>
       </c>
     </row>
@@ -16545,7 +16554,7 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="9">
         <v>90000</v>
       </c>
       <c r="F8" s="7">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1006,6 +1006,9 @@
     <t>灰色A</t>
   </si>
   <si>
+    <t>特殊2</t>
+  </si>
+  <si>
     <t>v1\Background\GrayA.png</t>
   </si>
   <si>
@@ -1703,9 +1706,6 @@
   </si>
   <si>
     <t>Special2</t>
-  </si>
-  <si>
-    <t>特殊2</t>
   </si>
   <si>
     <t>RU</t>
@@ -2398,10 +2398,21 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2888,137 +2899,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3049,11 +3060,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3867,7 +3884,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="12"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4551,10 +4568,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
-      <c r="P12" s="9">
+      <c r="O12" s="13">
+        <v>100000</v>
+      </c>
+      <c r="P12" s="13">
         <v>200000</v>
       </c>
       <c r="T12" t="s">
@@ -8078,8 +8095,8 @@
       <c r="E61" t="s">
         <v>308</v>
       </c>
-      <c r="H61" t="s">
-        <v>92</v>
+      <c r="H61" s="13" t="s">
+        <v>321</v>
       </c>
       <c r="I61">
         <v>300</v>
@@ -8106,10 +8123,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -8138,16 +8155,16 @@
         <v>7005</v>
       </c>
       <c r="C62" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E62" t="s">
         <v>308</v>
       </c>
-      <c r="H62" t="s">
-        <v>141</v>
+      <c r="H62" s="13" t="s">
+        <v>321</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -8174,10 +8191,10 @@
         <v>300</v>
       </c>
       <c r="T62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="U62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -8206,16 +8223,16 @@
         <v>7006</v>
       </c>
       <c r="C63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D63" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E63" t="s">
         <v>308</v>
       </c>
-      <c r="H63" t="s">
-        <v>141</v>
+      <c r="H63" s="13" t="s">
+        <v>321</v>
       </c>
       <c r="I63">
         <v>300</v>
@@ -8242,10 +8259,10 @@
         <v>300</v>
       </c>
       <c r="T63" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="U63" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -8274,10 +8291,10 @@
         <v>7007</v>
       </c>
       <c r="C64" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E64" t="s">
         <v>308</v>
@@ -8310,10 +8327,10 @@
         <v>300</v>
       </c>
       <c r="T64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="U64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -8342,10 +8359,10 @@
         <v>7008</v>
       </c>
       <c r="C65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D65" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E65" t="s">
         <v>308</v>
@@ -8393,10 +8410,10 @@
         <v>162</v>
       </c>
       <c r="T65" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="U65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X65">
         <v>0</v>
@@ -8425,10 +8442,10 @@
         <v>7009</v>
       </c>
       <c r="C66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D66" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E66" t="s">
         <v>308</v>
@@ -8476,10 +8493,10 @@
         <v>162</v>
       </c>
       <c r="T66" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="U66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -8508,10 +8525,10 @@
         <v>7010</v>
       </c>
       <c r="C67" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D67" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E67" t="s">
         <v>308</v>
@@ -8559,10 +8576,10 @@
         <v>162</v>
       </c>
       <c r="T67" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U67" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="X67">
         <v>0</v>
@@ -8591,10 +8608,10 @@
         <v>7011</v>
       </c>
       <c r="C68" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D68" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E68" t="s">
         <v>308</v>
@@ -8642,10 +8659,10 @@
         <v>162</v>
       </c>
       <c r="T68" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="U68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X68">
         <v>0</v>
@@ -8674,10 +8691,10 @@
         <v>7012</v>
       </c>
       <c r="C69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D69" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E69" t="s">
         <v>308</v>
@@ -8725,10 +8742,10 @@
         <v>162</v>
       </c>
       <c r="T69" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U69" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -8757,10 +8774,10 @@
         <v>7013</v>
       </c>
       <c r="C70" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E70" t="s">
         <v>308</v>
@@ -8808,10 +8825,10 @@
         <v>162</v>
       </c>
       <c r="T70" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U70" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X70">
         <v>0</v>
@@ -8840,10 +8857,10 @@
         <v>7014</v>
       </c>
       <c r="C71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D71" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E71" t="s">
         <v>308</v>
@@ -8891,10 +8908,10 @@
         <v>162</v>
       </c>
       <c r="T71" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U71" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X71">
         <v>0</v>
@@ -8923,10 +8940,10 @@
         <v>7015</v>
       </c>
       <c r="C72" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D72" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E72" t="s">
         <v>308</v>
@@ -8974,10 +8991,10 @@
         <v>162</v>
       </c>
       <c r="T72" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="U72" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X72">
         <v>0</v>
@@ -9006,10 +9023,10 @@
         <v>7016</v>
       </c>
       <c r="C73" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D73" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E73" t="s">
         <v>308</v>
@@ -9057,10 +9074,10 @@
         <v>162</v>
       </c>
       <c r="T73" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U73" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X73">
         <v>0</v>
@@ -9089,10 +9106,10 @@
         <v>7017</v>
       </c>
       <c r="C74" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D74" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E74" t="s">
         <v>308</v>
@@ -9140,10 +9157,10 @@
         <v>162</v>
       </c>
       <c r="T74" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="U74" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -9172,10 +9189,10 @@
         <v>7018</v>
       </c>
       <c r="C75" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D75" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E75" t="s">
         <v>308</v>
@@ -9208,10 +9225,10 @@
         <v>300</v>
       </c>
       <c r="T75" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U75" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X75">
         <v>0</v>
@@ -9243,10 +9260,10 @@
         <v>7019</v>
       </c>
       <c r="C76" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D76" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E76" t="s">
         <v>308</v>
@@ -9294,10 +9311,10 @@
         <v>162</v>
       </c>
       <c r="T76" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="U76" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="V76" t="s">
         <v>162</v>
@@ -9344,13 +9361,13 @@
         <v>8001</v>
       </c>
       <c r="C77" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D77" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E77" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F77" t="s">
         <v>162</v>
@@ -9395,10 +9412,10 @@
         <v>162</v>
       </c>
       <c r="T77" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U77" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="X77">
         <v>0</v>
@@ -9427,13 +9444,13 @@
         <v>8002</v>
       </c>
       <c r="C78" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D78" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E78" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F78" t="s">
         <v>162</v>
@@ -9441,8 +9458,8 @@
       <c r="G78" t="s">
         <v>162</v>
       </c>
-      <c r="H78" t="s">
-        <v>141</v>
+      <c r="H78" s="13" t="s">
+        <v>321</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -9478,10 +9495,10 @@
         <v>162</v>
       </c>
       <c r="T78" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="U78" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -9510,13 +9527,13 @@
         <v>8003</v>
       </c>
       <c r="C79" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D79" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E79" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F79" t="s">
         <v>162</v>
@@ -9561,10 +9578,10 @@
         <v>162</v>
       </c>
       <c r="T79" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U79" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X79">
         <v>0</v>
@@ -9593,13 +9610,13 @@
         <v>8004</v>
       </c>
       <c r="C80" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D80" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E80" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F80" t="s">
         <v>162</v>
@@ -9644,10 +9661,10 @@
         <v>162</v>
       </c>
       <c r="T80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="U80" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -9676,13 +9693,13 @@
         <v>8005</v>
       </c>
       <c r="C81" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D81" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E81" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F81" t="s">
         <v>162</v>
@@ -9727,10 +9744,10 @@
         <v>162</v>
       </c>
       <c r="T81" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U81" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -9759,13 +9776,13 @@
         <v>8006</v>
       </c>
       <c r="C82" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D82" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E82" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F82" t="s">
         <v>162</v>
@@ -9773,8 +9790,8 @@
       <c r="G82" t="s">
         <v>162</v>
       </c>
-      <c r="H82" t="s">
-        <v>92</v>
+      <c r="H82" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -9810,10 +9827,10 @@
         <v>162</v>
       </c>
       <c r="T82" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U82" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -9842,13 +9859,13 @@
         <v>8007</v>
       </c>
       <c r="C83" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D83" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E83" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F83" t="s">
         <v>162</v>
@@ -9893,10 +9910,10 @@
         <v>162</v>
       </c>
       <c r="T83" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="U83" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -9925,13 +9942,13 @@
         <v>8008</v>
       </c>
       <c r="C84" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D84" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E84" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F84" t="s">
         <v>162</v>
@@ -9976,10 +9993,10 @@
         <v>162</v>
       </c>
       <c r="T84" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="U84" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -10008,13 +10025,13 @@
         <v>8009</v>
       </c>
       <c r="C85" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D85" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E85" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H85" t="s">
         <v>141</v>
@@ -10044,10 +10061,10 @@
         <v>300</v>
       </c>
       <c r="T85" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="U85" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="X85">
         <v>0</v>
@@ -10076,13 +10093,13 @@
         <v>8010</v>
       </c>
       <c r="C86" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D86" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H86" t="s">
         <v>141</v>
@@ -10112,10 +10129,10 @@
         <v>300</v>
       </c>
       <c r="T86" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U86" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -10144,13 +10161,13 @@
         <v>8011</v>
       </c>
       <c r="C87" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E87" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H87" t="s">
         <v>99</v>
@@ -10180,10 +10197,10 @@
         <v>300</v>
       </c>
       <c r="T87" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="U87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -10215,13 +10232,13 @@
         <v>8012</v>
       </c>
       <c r="C88" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D88" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E88" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F88" t="s">
         <v>162</v>
@@ -10266,10 +10283,10 @@
         <v>162</v>
       </c>
       <c r="T88" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="U88" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="V88" t="s">
         <v>162</v>
@@ -10319,13 +10336,13 @@
         <v>8013</v>
       </c>
       <c r="C89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D89" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E89" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F89" t="s">
         <v>162</v>
@@ -10370,10 +10387,10 @@
         <v>162</v>
       </c>
       <c r="T89" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="U89" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="V89" t="s">
         <v>162</v>
@@ -10420,13 +10437,13 @@
         <v>9001</v>
       </c>
       <c r="C90" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E90" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H90" t="s">
         <v>141</v>
@@ -10441,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -10459,10 +10476,10 @@
         <v>300</v>
       </c>
       <c r="T90" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U90" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -10491,16 +10508,16 @@
         <v>9002</v>
       </c>
       <c r="C91" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D91" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E91" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F91" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G91">
         <v>9009</v>
@@ -10518,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -10536,13 +10553,13 @@
         <v>300</v>
       </c>
       <c r="T91" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="U91" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X91">
         <v>0</v>
@@ -10571,16 +10588,16 @@
         <v>9003</v>
       </c>
       <c r="C92" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D92" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E92" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F92" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G92">
         <v>9009</v>
@@ -10598,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -10616,13 +10633,13 @@
         <v>300</v>
       </c>
       <c r="T92" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U92" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -10651,16 +10668,16 @@
         <v>9004</v>
       </c>
       <c r="C93" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D93" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E93" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F93" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G93">
         <v>9009</v>
@@ -10678,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -10696,13 +10713,13 @@
         <v>300</v>
       </c>
       <c r="T93" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="U93" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -10731,16 +10748,16 @@
         <v>9005</v>
       </c>
       <c r="C94" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D94" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E94" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F94" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G94">
         <v>9009</v>
@@ -10758,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -10776,13 +10793,13 @@
         <v>300</v>
       </c>
       <c r="T94" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="U94" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -10811,16 +10828,16 @@
         <v>9006</v>
       </c>
       <c r="C95" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D95" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E95" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F95" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G95">
         <v>9009</v>
@@ -10838,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -10856,13 +10873,13 @@
         <v>300</v>
       </c>
       <c r="T95" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="U95" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -10891,16 +10908,16 @@
         <v>9007</v>
       </c>
       <c r="C96" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D96" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E96" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F96" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G96">
         <v>9009</v>
@@ -10918,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -10936,13 +10953,13 @@
         <v>300</v>
       </c>
       <c r="T96" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U96" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -10971,16 +10988,16 @@
         <v>9008</v>
       </c>
       <c r="C97" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D97" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E97" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F97" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G97">
         <v>9009</v>
@@ -10998,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -11016,13 +11033,13 @@
         <v>300</v>
       </c>
       <c r="T97" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="U97" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -11051,13 +11068,13 @@
         <v>9009</v>
       </c>
       <c r="C98" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D98" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E98" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H98" t="s">
         <v>92</v>
@@ -11072,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -11090,13 +11107,13 @@
         <v>300</v>
       </c>
       <c r="T98" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="U98" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -11125,16 +11142,16 @@
         <v>9010</v>
       </c>
       <c r="C99" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D99" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E99" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F99" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G99">
         <v>9009</v>
@@ -11152,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -11170,10 +11187,10 @@
         <v>300</v>
       </c>
       <c r="T99" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="U99" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="X99">
         <v>0</v>
@@ -11202,16 +11219,16 @@
         <v>9011</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D100" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E100" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F100" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G100">
         <v>9009</v>
@@ -11229,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -11247,13 +11264,13 @@
         <v>300</v>
       </c>
       <c r="T100" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="U100" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -11282,13 +11299,13 @@
         <v>10001</v>
       </c>
       <c r="C101" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D101" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E101" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H101" t="s">
         <v>92</v>
@@ -11318,10 +11335,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="U101" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="X101">
         <v>0</v>
@@ -11350,13 +11367,13 @@
         <v>11001</v>
       </c>
       <c r="C102" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D102" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E102" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H102" t="s">
         <v>92</v>
@@ -11386,13 +11403,13 @@
         <v>0</v>
       </c>
       <c r="T102" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="U102" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="X102">
         <v>0</v>
@@ -11421,13 +11438,13 @@
         <v>11002</v>
       </c>
       <c r="C103" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D103" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E103" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G103">
         <v>11001</v>
@@ -11460,10 +11477,10 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="U103" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="X103">
         <v>0</v>
@@ -11495,13 +11512,13 @@
         <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E104" t="s">
         <v>140</v>
       </c>
       <c r="H104" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I104">
         <v>100</v>
@@ -11513,7 +11530,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -11532,7 +11549,7 @@
         <v>159</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -11564,13 +11581,13 @@
         <v>135</v>
       </c>
       <c r="D105" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E105" t="s">
         <v>91</v>
       </c>
       <c r="H105" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I105">
         <v>100</v>
@@ -11582,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -11604,7 +11621,7 @@
         <v>1012</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="X105">
         <v>0</v>
@@ -13605,10 +13622,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -13637,10 +13654,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -13669,10 +13686,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -13733,10 +13750,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -13797,10 +13814,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D66" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -13861,10 +13878,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D68" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -13893,10 +13910,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D69" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -13925,10 +13942,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D70" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -13957,10 +13974,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D71" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -14021,10 +14038,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D73" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -14085,10 +14102,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D75" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -14152,7 +14169,7 @@
         <v>774</v>
       </c>
       <c r="D77" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -14184,7 +14201,7 @@
         <v>775</v>
       </c>
       <c r="D78" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -14213,10 +14230,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D79" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -14309,10 +14326,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D82" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -14341,10 +14358,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D83" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -14373,10 +14390,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D84" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -14405,10 +14422,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -14437,10 +14454,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D86" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -14469,10 +14486,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D87" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -14501,10 +14518,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D88" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -14533,10 +14550,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D89" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -14565,10 +14582,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D90" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -14597,10 +14614,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D91" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -14629,10 +14646,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D92" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14661,10 +14678,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D93" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -14693,10 +14710,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D94" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -14725,10 +14742,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D95" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14757,10 +14774,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D96" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -14789,10 +14806,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D97" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -14821,10 +14838,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D98" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -14856,7 +14873,7 @@
         <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -14888,7 +14905,7 @@
         <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -14934,17 +14951,17 @@
         <v>91</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F2" t="s">
         <v>99</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>213</v>
@@ -14953,13 +14970,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14967,32 +14984,32 @@
         <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -15000,32 +15017,32 @@
         <v>191</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -15033,32 +15050,32 @@
         <v>212</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -15066,32 +15083,32 @@
         <v>230</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F6" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -15099,32 +15116,32 @@
         <v>263</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -15132,45 +15149,45 @@
         <v>308</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>555</v>
@@ -15193,7 +15210,7 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>560</v>
@@ -15213,7 +15230,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>564</v>
@@ -15233,7 +15250,7 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>568</v>
@@ -15253,7 +15270,7 @@
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>572</v>
@@ -15292,7 +15309,7 @@
         <v>578</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -15300,7 +15317,7 @@
         <v>579</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="2:3">
@@ -15469,44 +15486,44 @@
         <v>606</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" spans="1:13">
+    <row r="4" s="11" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>618</v>
       </c>
     </row>
@@ -16555,11 +16572,11 @@
         <v>105</v>
       </c>
       <c r="E8" s="9">
-        <v>90000</v>
+        <v>900</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -16575,12 +16592,12 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9">
-        <v>180</v>
+      <c r="E9" s="10">
+        <v>180000</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>0.018</v>
+        <v>18</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -16613,7 +16630,7 @@
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>9.91</v>
+        <v>18.982</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -16887,7 +16904,7 @@
         <v>3001</v>
       </c>
       <c r="D26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -17912,22 +17929,22 @@
         <v>200101</v>
       </c>
       <c r="C31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -17944,22 +17961,22 @@
         <v>200201</v>
       </c>
       <c r="C32" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="F32" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="G32" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="H32" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -18200,7 +18217,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -18223,7 +18240,7 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>110</v>
@@ -18246,7 +18263,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>105</v>
@@ -18269,7 +18286,7 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>121</v>
@@ -18292,7 +18309,7 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>141</v>
@@ -18315,7 +18332,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>92</v>
@@ -18338,10 +18355,10 @@
         <v>2001</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E11" t="s">
         <v>727</v>
@@ -18361,10 +18378,10 @@
         <v>2002</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>554</v>
+        <v>321</v>
       </c>
       <c r="E12" t="s">
         <v>727</v>
@@ -18497,7 +18514,7 @@
         <v>737</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -18510,7 +18527,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -18537,10 +18554,10 @@
         <v>1006</v>
       </c>
       <c r="C12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -18548,12 +18565,12 @@
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -18683,7 +18700,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -18715,7 +18732,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -18723,7 +18740,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -18731,7 +18748,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -18739,7 +18756,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -1006,706 +1006,706 @@
     <t>灰色A</t>
   </si>
   <si>
+    <t>v1\Background\GrayA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayA.png</t>
+  </si>
+  <si>
+    <t>Gray B</t>
+  </si>
+  <si>
+    <t>灰色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GrayB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayB.png</t>
+  </si>
+  <si>
+    <t>Green A</t>
+  </si>
+  <si>
+    <t>绿色A</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenA.png</t>
+  </si>
+  <si>
+    <t>Green B</t>
+  </si>
+  <si>
+    <t>绿色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenB.png</t>
+  </si>
+  <si>
+    <t>Evergreen Parlor</t>
+  </si>
+  <si>
+    <t>常青厅</t>
+  </si>
+  <si>
+    <t>v1\Background\EvergreenParlor.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_EvergreenParlor.png</t>
+  </si>
+  <si>
+    <t>Orange A</t>
+  </si>
+  <si>
+    <t>橙色A</t>
+  </si>
+  <si>
+    <t>v1\Background\OrangeA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_OrangeA.png</t>
+  </si>
+  <si>
+    <t>Honey Hall</t>
+  </si>
+  <si>
+    <t>蜂蜜厅</t>
+  </si>
+  <si>
+    <t>v1\Background\HoneyHall.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_HoneyHall.png</t>
+  </si>
+  <si>
+    <t>Pink A</t>
+  </si>
+  <si>
+    <t>粉色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PinkA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PinkA.png</t>
+  </si>
+  <si>
+    <t>Midnight Theater</t>
+  </si>
+  <si>
+    <t>午夜剧场</t>
+  </si>
+  <si>
+    <t>v1\Background\MidnightTheater.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_MidnightTheater.png</t>
+  </si>
+  <si>
+    <t>Purple A</t>
+  </si>
+  <si>
+    <t>紫色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PurpleA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PurpleA.png</t>
+  </si>
+  <si>
+    <t>Red A</t>
+  </si>
+  <si>
+    <t>红色A</t>
+  </si>
+  <si>
+    <t>v1\Background\RedA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedA.png</t>
+  </si>
+  <si>
+    <t>Red B</t>
+  </si>
+  <si>
+    <t>红色B</t>
+  </si>
+  <si>
+    <t>v1\Background\RedB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedB.png</t>
+  </si>
+  <si>
+    <t>Twitter Blue</t>
+  </si>
+  <si>
+    <t>Twitter蓝</t>
+  </si>
+  <si>
+    <t>v1\Background\TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>Sage Manor</t>
+  </si>
+  <si>
+    <t>鼠尾草庄园</t>
+  </si>
+  <si>
+    <t>v1\Background\SageManor.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_SageManor.png</t>
+  </si>
+  <si>
+    <t>Yellow A</t>
+  </si>
+  <si>
+    <t>黄色A</t>
+  </si>
+  <si>
+    <t>v1\Background\YellowA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_YellowA.png</t>
+  </si>
+  <si>
+    <t>Evergreen Parlor Burgundy</t>
+  </si>
+  <si>
+    <t>酒红常青厅</t>
+  </si>
+  <si>
+    <t>v1\Background\EvergreenParlor_Burgundy.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_EvergreenParlor_Burgundy.png</t>
+  </si>
+  <si>
+    <t>Canine D21</t>
+  </si>
+  <si>
+    <t>Canine D21手表</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Canine_D21.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Canine_D21.png</t>
+  </si>
+  <si>
+    <t>Anchor Tattoo</t>
+  </si>
+  <si>
+    <t>锚纹身</t>
+  </si>
+  <si>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
+    <t>v1\Player\BodyDecoration\AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\BodyDecoration_AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>Canine D88</t>
+  </si>
+  <si>
+    <t>Canine D88手表</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Canine_D88.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Canine_D88.png</t>
+  </si>
+  <si>
+    <t>Bracelet Feng Shui</t>
+  </si>
+  <si>
+    <t>风水手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Bracelet_FengShui.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Bracelet_FengShui.png</t>
+  </si>
+  <si>
+    <t>Bracelet Good Luck</t>
+  </si>
+  <si>
+    <t>好运手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Bracelet_GoodLuck.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Bracelet_GoodLuck.png</t>
+  </si>
+  <si>
+    <t>Hair</t>
+  </si>
+  <si>
+    <t>体毛</t>
+  </si>
+  <si>
+    <t>v1\Player\BodyDecoration\Hair.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\BodyDecoration_Hair.png</t>
+  </si>
+  <si>
+    <t>Royal Mariner Onyx</t>
+  </si>
+  <si>
+    <t>黑色Royal Mariner</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RoyalMariner_Onyx.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RoyalMariner_Onyx.png</t>
+  </si>
+  <si>
+    <t>Royal Mariner Emerald</t>
+  </si>
+  <si>
+    <t>绿色Royal Mariner</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RoyalMariner_Emerald.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RoyalMariner_Emerald.png</t>
+  </si>
+  <si>
+    <t>Text Wristband Green</t>
+  </si>
+  <si>
+    <t>绿色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>Text Wristband Red</t>
+  </si>
+  <si>
+    <t>红色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>WSOP Gold Bracelet</t>
+  </si>
+  <si>
+    <t>WSOP金手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>Canine D35</t>
+  </si>
+  <si>
+    <t>Canine D35手表</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Canine_D35.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Canine_D35.png</t>
+  </si>
+  <si>
+    <t>Royal Mariner Ruby</t>
+  </si>
+  <si>
+    <t>红色Royal Mariner</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RoyalMariner_Ruby.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RoyalMariner_Ruby.png</t>
+  </si>
+  <si>
+    <t>Black Tea</t>
+  </si>
+  <si>
+    <t>红茶</t>
+  </si>
+  <si>
+    <t>Refreshment</t>
+  </si>
+  <si>
+    <t>消耗品盲盒产出</t>
+  </si>
+  <si>
+    <t>v1\Treat\BlackTea.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_BlackTea.png</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>波尔多</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯|阿联酋|马来西亚|印尼</t>
+  </si>
+  <si>
+    <t>v1\Treat\Bordeaux.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Bordeaux.png</t>
+  </si>
+  <si>
+    <t>一些国家不允许饮酒，替换成水</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>勃艮第</t>
+  </si>
+  <si>
+    <t>v1\Treat\Burgundy.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Burgundy.png</t>
+  </si>
+  <si>
+    <t>Chardonnay</t>
+  </si>
+  <si>
+    <t>霞多丽</t>
+  </si>
+  <si>
+    <t>v1\Treat\Chardonnay.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Chardonnay.png</t>
+  </si>
+  <si>
+    <t>Shot Glass</t>
+  </si>
+  <si>
+    <t>子弹杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\ShotGlass.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_ShotGlass.png</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>郁金香杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tulip.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tulip.png</t>
+  </si>
+  <si>
+    <t>Tumbler</t>
+  </si>
+  <si>
+    <t>平底杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tumbler.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tumbler.png</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>年份酒</t>
+  </si>
+  <si>
+    <t>v1\Treat\Vintage.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Vintage.png</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>凉白开</t>
+  </si>
+  <si>
+    <t>v1\Treat\Water.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Water.png</t>
+  </si>
+  <si>
+    <t>Whisky</t>
+  </si>
+  <si>
+    <t>威士忌</t>
+  </si>
+  <si>
+    <t>v1\Treat\Whisky.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Whisky.png</t>
+  </si>
+  <si>
+    <t>Whisky Cigar</t>
+  </si>
+  <si>
+    <t>威士忌雪茄</t>
+  </si>
+  <si>
+    <t>v1\Treat\WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>Basic Card Back</t>
+  </si>
+  <si>
+    <t>基础背</t>
+  </si>
+  <si>
+    <t>CardBack</t>
+  </si>
+  <si>
+    <t>v1\CardBack\Basic.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardBack_Basic.png</t>
+  </si>
+  <si>
+    <t>Kibble Card Face</t>
+  </si>
+  <si>
+    <t>狗粮卡面</t>
+  </si>
+  <si>
+    <t>CardFace</t>
+  </si>
+  <si>
+    <t>v1\CardFace\Classic\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Kibble.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Classic.png</t>
+  </si>
+  <si>
+    <t>测试活动功能帽</t>
+  </si>
+  <si>
+    <t>特殊1</t>
+  </si>
+  <si>
+    <t>活动产出</t>
+  </si>
+  <si>
+    <t>测试活动功能使用</t>
+  </si>
+  <si>
+    <t>测试活动功能柴</t>
+  </si>
+  <si>
+    <t>小狗本体</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>小狗头部装饰</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
+    <t>小狗眼部装饰</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
+    <t>手臂层的装饰</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
+  </si>
+  <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
+    <t>玩家手臂衣服</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
+    <t>桌布</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
+    <t>背景</t>
+  </si>
+  <si>
+    <t>Special1</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>玩家手部装饰</t>
+  </si>
+  <si>
+    <t>Special2</t>
+  </si>
+  <si>
     <t>特殊2</t>
-  </si>
-  <si>
-    <t>v1\Background\GrayA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_GrayA.png</t>
-  </si>
-  <si>
-    <t>Gray B</t>
-  </si>
-  <si>
-    <t>灰色B</t>
-  </si>
-  <si>
-    <t>v1\Background\GrayB.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_GrayB.png</t>
-  </si>
-  <si>
-    <t>Green A</t>
-  </si>
-  <si>
-    <t>绿色A</t>
-  </si>
-  <si>
-    <t>v1\Background\GreenA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_GreenA.png</t>
-  </si>
-  <si>
-    <t>Green B</t>
-  </si>
-  <si>
-    <t>绿色B</t>
-  </si>
-  <si>
-    <t>v1\Background\GreenB.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_GreenB.png</t>
-  </si>
-  <si>
-    <t>Evergreen Parlor</t>
-  </si>
-  <si>
-    <t>常青厅</t>
-  </si>
-  <si>
-    <t>v1\Background\EvergreenParlor.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_EvergreenParlor.png</t>
-  </si>
-  <si>
-    <t>Orange A</t>
-  </si>
-  <si>
-    <t>橙色A</t>
-  </si>
-  <si>
-    <t>v1\Background\OrangeA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_OrangeA.png</t>
-  </si>
-  <si>
-    <t>Honey Hall</t>
-  </si>
-  <si>
-    <t>蜂蜜厅</t>
-  </si>
-  <si>
-    <t>v1\Background\HoneyHall.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_HoneyHall.png</t>
-  </si>
-  <si>
-    <t>Pink A</t>
-  </si>
-  <si>
-    <t>粉色A</t>
-  </si>
-  <si>
-    <t>v1\Background\PinkA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_PinkA.png</t>
-  </si>
-  <si>
-    <t>Midnight Theater</t>
-  </si>
-  <si>
-    <t>午夜剧场</t>
-  </si>
-  <si>
-    <t>v1\Background\MidnightTheater.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_MidnightTheater.png</t>
-  </si>
-  <si>
-    <t>Purple A</t>
-  </si>
-  <si>
-    <t>紫色A</t>
-  </si>
-  <si>
-    <t>v1\Background\PurpleA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_PurpleA.png</t>
-  </si>
-  <si>
-    <t>Red A</t>
-  </si>
-  <si>
-    <t>红色A</t>
-  </si>
-  <si>
-    <t>v1\Background\RedA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_RedA.png</t>
-  </si>
-  <si>
-    <t>Red B</t>
-  </si>
-  <si>
-    <t>红色B</t>
-  </si>
-  <si>
-    <t>v1\Background\RedB.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_RedB.png</t>
-  </si>
-  <si>
-    <t>Twitter Blue</t>
-  </si>
-  <si>
-    <t>Twitter蓝</t>
-  </si>
-  <si>
-    <t>v1\Background\TwitterBlue.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_TwitterBlue.png</t>
-  </si>
-  <si>
-    <t>Sage Manor</t>
-  </si>
-  <si>
-    <t>鼠尾草庄园</t>
-  </si>
-  <si>
-    <t>v1\Background\SageManor.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_SageManor.png</t>
-  </si>
-  <si>
-    <t>Yellow A</t>
-  </si>
-  <si>
-    <t>黄色A</t>
-  </si>
-  <si>
-    <t>v1\Background\YellowA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_YellowA.png</t>
-  </si>
-  <si>
-    <t>Evergreen Parlor Burgundy</t>
-  </si>
-  <si>
-    <t>酒红常青厅</t>
-  </si>
-  <si>
-    <t>v1\Background\EvergreenParlor_Burgundy.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Background_EvergreenParlor_Burgundy.png</t>
-  </si>
-  <si>
-    <t>Canine D21</t>
-  </si>
-  <si>
-    <t>Canine D21手表</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\Canine_D21.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Canine_D21.png</t>
-  </si>
-  <si>
-    <t>Anchor Tattoo</t>
-  </si>
-  <si>
-    <t>锚纹身</t>
-  </si>
-  <si>
-    <t>BodyDecoration</t>
-  </si>
-  <si>
-    <t>v1\Player\BodyDecoration\AnchorTattoo.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\BodyDecoration_AnchorTattoo.png</t>
-  </si>
-  <si>
-    <t>Canine D88</t>
-  </si>
-  <si>
-    <t>Canine D88手表</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\Canine_D88.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Canine_D88.png</t>
-  </si>
-  <si>
-    <t>Bracelet Feng Shui</t>
-  </si>
-  <si>
-    <t>风水手链</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\Bracelet_FengShui.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Bracelet_FengShui.png</t>
-  </si>
-  <si>
-    <t>Bracelet Good Luck</t>
-  </si>
-  <si>
-    <t>好运手链</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\Bracelet_GoodLuck.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Bracelet_GoodLuck.png</t>
-  </si>
-  <si>
-    <t>Hair</t>
-  </si>
-  <si>
-    <t>体毛</t>
-  </si>
-  <si>
-    <t>v1\Player\BodyDecoration\Hair.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\BodyDecoration_Hair.png</t>
-  </si>
-  <si>
-    <t>Royal Mariner Onyx</t>
-  </si>
-  <si>
-    <t>黑色Royal Mariner</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\RoyalMariner_Onyx.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_RoyalMariner_Onyx.png</t>
-  </si>
-  <si>
-    <t>Royal Mariner Emerald</t>
-  </si>
-  <si>
-    <t>绿色Royal Mariner</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\RoyalMariner_Emerald.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_RoyalMariner_Emerald.png</t>
-  </si>
-  <si>
-    <t>Text Wristband Green</t>
-  </si>
-  <si>
-    <t>绿色文字腕带</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\TextWristband_Green.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_TextWristband_Green.png</t>
-  </si>
-  <si>
-    <t>Text Wristband Red</t>
-  </si>
-  <si>
-    <t>红色文字腕带</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\TextWristband_Red.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_TextWristband_Red.png</t>
-  </si>
-  <si>
-    <t>WSOP Gold Bracelet</t>
-  </si>
-  <si>
-    <t>WSOP金手链</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\WSOPGoldBracelet.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
-  </si>
-  <si>
-    <t>Canine D35</t>
-  </si>
-  <si>
-    <t>Canine D35手表</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\Canine_D35.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Canine_D35.png</t>
-  </si>
-  <si>
-    <t>Royal Mariner Ruby</t>
-  </si>
-  <si>
-    <t>红色Royal Mariner</t>
-  </si>
-  <si>
-    <t>v1\Player\Accessory\RoyalMariner_Ruby.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_RoyalMariner_Ruby.png</t>
-  </si>
-  <si>
-    <t>Black Tea</t>
-  </si>
-  <si>
-    <t>红茶</t>
-  </si>
-  <si>
-    <t>Refreshment</t>
-  </si>
-  <si>
-    <t>消耗品盲盒产出</t>
-  </si>
-  <si>
-    <t>v1\Treat\BlackTea.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_BlackTea.png</t>
-  </si>
-  <si>
-    <t>Bordeaux</t>
-  </si>
-  <si>
-    <t>波尔多</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯|阿联酋|马来西亚|印尼</t>
-  </si>
-  <si>
-    <t>v1\Treat\Bordeaux.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Bordeaux.png</t>
-  </si>
-  <si>
-    <t>一些国家不允许饮酒，替换成水</t>
-  </si>
-  <si>
-    <t>Burgundy</t>
-  </si>
-  <si>
-    <t>勃艮第</t>
-  </si>
-  <si>
-    <t>v1\Treat\Burgundy.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Burgundy.png</t>
-  </si>
-  <si>
-    <t>Chardonnay</t>
-  </si>
-  <si>
-    <t>霞多丽</t>
-  </si>
-  <si>
-    <t>v1\Treat\Chardonnay.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Chardonnay.png</t>
-  </si>
-  <si>
-    <t>Shot Glass</t>
-  </si>
-  <si>
-    <t>子弹杯</t>
-  </si>
-  <si>
-    <t>v1\Treat\ShotGlass.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_ShotGlass.png</t>
-  </si>
-  <si>
-    <t>Tulip</t>
-  </si>
-  <si>
-    <t>郁金香杯</t>
-  </si>
-  <si>
-    <t>v1\Treat\Tulip.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Tulip.png</t>
-  </si>
-  <si>
-    <t>Tumbler</t>
-  </si>
-  <si>
-    <t>平底杯</t>
-  </si>
-  <si>
-    <t>v1\Treat\Tumbler.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Tumbler.png</t>
-  </si>
-  <si>
-    <t>Vintage</t>
-  </si>
-  <si>
-    <t>年份酒</t>
-  </si>
-  <si>
-    <t>v1\Treat\Vintage.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Vintage.png</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>凉白开</t>
-  </si>
-  <si>
-    <t>v1\Treat\Water.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Water.png</t>
-  </si>
-  <si>
-    <t>Whisky</t>
-  </si>
-  <si>
-    <t>威士忌</t>
-  </si>
-  <si>
-    <t>v1\Treat\Whisky.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_Whisky.png</t>
-  </si>
-  <si>
-    <t>Whisky Cigar</t>
-  </si>
-  <si>
-    <t>威士忌雪茄</t>
-  </si>
-  <si>
-    <t>v1\Treat\WhiskyCagar.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Treat_WhiskyCagar.png</t>
-  </si>
-  <si>
-    <t>Basic Card Back</t>
-  </si>
-  <si>
-    <t>基础背</t>
-  </si>
-  <si>
-    <t>CardBack</t>
-  </si>
-  <si>
-    <t>v1\CardBack\Basic.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\CardBack_Basic.png</t>
-  </si>
-  <si>
-    <t>Kibble Card Face</t>
-  </si>
-  <si>
-    <t>狗粮卡面</t>
-  </si>
-  <si>
-    <t>CardFace</t>
-  </si>
-  <si>
-    <t>v1\CardFace\Classic\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\CardFace_Kibble.png</t>
-  </si>
-  <si>
-    <t>开发阶段先临时用经典卡面</t>
-  </si>
-  <si>
-    <t>Classic Card Face</t>
-  </si>
-  <si>
-    <t>经典卡面</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\CardFace_Classic.png</t>
-  </si>
-  <si>
-    <t>测试活动功能帽</t>
-  </si>
-  <si>
-    <t>特殊1</t>
-  </si>
-  <si>
-    <t>活动产出</t>
-  </si>
-  <si>
-    <t>测试活动功能使用</t>
-  </si>
-  <si>
-    <t>测试活动功能柴</t>
-  </si>
-  <si>
-    <t>小狗本体</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>在全部国家隐藏</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>小狗头部装饰</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯</t>
-  </si>
-  <si>
-    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
-  </si>
-  <si>
-    <t>Serious</t>
-  </si>
-  <si>
-    <t>严肃</t>
-  </si>
-  <si>
-    <t>小狗眼部装饰</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
-  </si>
-  <si>
-    <t>Bored</t>
-  </si>
-  <si>
-    <t>无聊</t>
-  </si>
-  <si>
-    <t>手臂层的装饰</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>伊朗</t>
-  </si>
-  <si>
-    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
-  </si>
-  <si>
-    <t>Wink</t>
-  </si>
-  <si>
-    <t>媚眼</t>
-  </si>
-  <si>
-    <t>玩家手臂衣服</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>Pakistan国家形象/政治</t>
-  </si>
-  <si>
-    <t>Excited</t>
-  </si>
-  <si>
-    <t>兴奋</t>
-  </si>
-  <si>
-    <t>桌布</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Starstruck</t>
-  </si>
-  <si>
-    <t>崇拜</t>
-  </si>
-  <si>
-    <t>背景</t>
-  </si>
-  <si>
-    <t>Special1</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>印尼</t>
-  </si>
-  <si>
-    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Silent</t>
-  </si>
-  <si>
-    <t>沉默</t>
-  </si>
-  <si>
-    <t>玩家手部装饰</t>
-  </si>
-  <si>
-    <t>Special2</t>
   </si>
   <si>
     <t>RU</t>
@@ -2398,7 +2398,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2407,18 +2407,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2899,137 +2887,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3060,17 +3048,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3884,7 +3866,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="12"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4568,11 +4550,11 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="13">
-        <v>100000</v>
-      </c>
-      <c r="P12" s="13">
-        <v>200000</v>
+      <c r="O12" s="9">
+        <v>100</v>
+      </c>
+      <c r="P12" s="9">
+        <v>200</v>
       </c>
       <c r="T12" t="s">
         <v>101</v>
@@ -8095,8 +8077,8 @@
       <c r="E61" t="s">
         <v>308</v>
       </c>
-      <c r="H61" s="13" t="s">
-        <v>321</v>
+      <c r="H61" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="I61">
         <v>300</v>
@@ -8123,10 +8105,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
+        <v>321</v>
+      </c>
+      <c r="U61" t="s">
         <v>322</v>
-      </c>
-      <c r="U61" t="s">
-        <v>323</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -8155,16 +8137,16 @@
         <v>7005</v>
       </c>
       <c r="C62" t="s">
+        <v>323</v>
+      </c>
+      <c r="D62" t="s">
         <v>324</v>
-      </c>
-      <c r="D62" t="s">
-        <v>325</v>
       </c>
       <c r="E62" t="s">
         <v>308</v>
       </c>
-      <c r="H62" s="13" t="s">
-        <v>321</v>
+      <c r="H62" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -8191,10 +8173,10 @@
         <v>300</v>
       </c>
       <c r="T62" t="s">
+        <v>325</v>
+      </c>
+      <c r="U62" t="s">
         <v>326</v>
-      </c>
-      <c r="U62" t="s">
-        <v>327</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -8223,16 +8205,16 @@
         <v>7006</v>
       </c>
       <c r="C63" t="s">
+        <v>327</v>
+      </c>
+      <c r="D63" t="s">
         <v>328</v>
-      </c>
-      <c r="D63" t="s">
-        <v>329</v>
       </c>
       <c r="E63" t="s">
         <v>308</v>
       </c>
-      <c r="H63" s="13" t="s">
-        <v>321</v>
+      <c r="H63" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I63">
         <v>300</v>
@@ -8259,10 +8241,10 @@
         <v>300</v>
       </c>
       <c r="T63" t="s">
+        <v>329</v>
+      </c>
+      <c r="U63" t="s">
         <v>330</v>
-      </c>
-      <c r="U63" t="s">
-        <v>331</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -8291,10 +8273,10 @@
         <v>7007</v>
       </c>
       <c r="C64" t="s">
+        <v>331</v>
+      </c>
+      <c r="D64" t="s">
         <v>332</v>
-      </c>
-      <c r="D64" t="s">
-        <v>333</v>
       </c>
       <c r="E64" t="s">
         <v>308</v>
@@ -8327,10 +8309,10 @@
         <v>300</v>
       </c>
       <c r="T64" t="s">
+        <v>333</v>
+      </c>
+      <c r="U64" t="s">
         <v>334</v>
-      </c>
-      <c r="U64" t="s">
-        <v>335</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -8359,10 +8341,10 @@
         <v>7008</v>
       </c>
       <c r="C65" t="s">
+        <v>335</v>
+      </c>
+      <c r="D65" t="s">
         <v>336</v>
-      </c>
-      <c r="D65" t="s">
-        <v>337</v>
       </c>
       <c r="E65" t="s">
         <v>308</v>
@@ -8410,10 +8392,10 @@
         <v>162</v>
       </c>
       <c r="T65" t="s">
+        <v>337</v>
+      </c>
+      <c r="U65" t="s">
         <v>338</v>
-      </c>
-      <c r="U65" t="s">
-        <v>339</v>
       </c>
       <c r="X65">
         <v>0</v>
@@ -8442,10 +8424,10 @@
         <v>7009</v>
       </c>
       <c r="C66" t="s">
+        <v>339</v>
+      </c>
+      <c r="D66" t="s">
         <v>340</v>
-      </c>
-      <c r="D66" t="s">
-        <v>341</v>
       </c>
       <c r="E66" t="s">
         <v>308</v>
@@ -8493,10 +8475,10 @@
         <v>162</v>
       </c>
       <c r="T66" t="s">
+        <v>341</v>
+      </c>
+      <c r="U66" t="s">
         <v>342</v>
-      </c>
-      <c r="U66" t="s">
-        <v>343</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -8525,10 +8507,10 @@
         <v>7010</v>
       </c>
       <c r="C67" t="s">
+        <v>343</v>
+      </c>
+      <c r="D67" t="s">
         <v>344</v>
-      </c>
-      <c r="D67" t="s">
-        <v>345</v>
       </c>
       <c r="E67" t="s">
         <v>308</v>
@@ -8576,10 +8558,10 @@
         <v>162</v>
       </c>
       <c r="T67" t="s">
+        <v>345</v>
+      </c>
+      <c r="U67" t="s">
         <v>346</v>
-      </c>
-      <c r="U67" t="s">
-        <v>347</v>
       </c>
       <c r="X67">
         <v>0</v>
@@ -8608,10 +8590,10 @@
         <v>7011</v>
       </c>
       <c r="C68" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" t="s">
         <v>348</v>
-      </c>
-      <c r="D68" t="s">
-        <v>349</v>
       </c>
       <c r="E68" t="s">
         <v>308</v>
@@ -8659,10 +8641,10 @@
         <v>162</v>
       </c>
       <c r="T68" t="s">
+        <v>349</v>
+      </c>
+      <c r="U68" t="s">
         <v>350</v>
-      </c>
-      <c r="U68" t="s">
-        <v>351</v>
       </c>
       <c r="X68">
         <v>0</v>
@@ -8691,10 +8673,10 @@
         <v>7012</v>
       </c>
       <c r="C69" t="s">
+        <v>351</v>
+      </c>
+      <c r="D69" t="s">
         <v>352</v>
-      </c>
-      <c r="D69" t="s">
-        <v>353</v>
       </c>
       <c r="E69" t="s">
         <v>308</v>
@@ -8742,10 +8724,10 @@
         <v>162</v>
       </c>
       <c r="T69" t="s">
+        <v>353</v>
+      </c>
+      <c r="U69" t="s">
         <v>354</v>
-      </c>
-      <c r="U69" t="s">
-        <v>355</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -8774,10 +8756,10 @@
         <v>7013</v>
       </c>
       <c r="C70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D70" t="s">
         <v>356</v>
-      </c>
-      <c r="D70" t="s">
-        <v>357</v>
       </c>
       <c r="E70" t="s">
         <v>308</v>
@@ -8825,10 +8807,10 @@
         <v>162</v>
       </c>
       <c r="T70" t="s">
+        <v>357</v>
+      </c>
+      <c r="U70" t="s">
         <v>358</v>
-      </c>
-      <c r="U70" t="s">
-        <v>359</v>
       </c>
       <c r="X70">
         <v>0</v>
@@ -8857,10 +8839,10 @@
         <v>7014</v>
       </c>
       <c r="C71" t="s">
+        <v>359</v>
+      </c>
+      <c r="D71" t="s">
         <v>360</v>
-      </c>
-      <c r="D71" t="s">
-        <v>361</v>
       </c>
       <c r="E71" t="s">
         <v>308</v>
@@ -8908,10 +8890,10 @@
         <v>162</v>
       </c>
       <c r="T71" t="s">
+        <v>361</v>
+      </c>
+      <c r="U71" t="s">
         <v>362</v>
-      </c>
-      <c r="U71" t="s">
-        <v>363</v>
       </c>
       <c r="X71">
         <v>0</v>
@@ -8940,10 +8922,10 @@
         <v>7015</v>
       </c>
       <c r="C72" t="s">
+        <v>363</v>
+      </c>
+      <c r="D72" t="s">
         <v>364</v>
-      </c>
-      <c r="D72" t="s">
-        <v>365</v>
       </c>
       <c r="E72" t="s">
         <v>308</v>
@@ -8991,10 +8973,10 @@
         <v>162</v>
       </c>
       <c r="T72" t="s">
+        <v>365</v>
+      </c>
+      <c r="U72" t="s">
         <v>366</v>
-      </c>
-      <c r="U72" t="s">
-        <v>367</v>
       </c>
       <c r="X72">
         <v>0</v>
@@ -9023,10 +9005,10 @@
         <v>7016</v>
       </c>
       <c r="C73" t="s">
+        <v>367</v>
+      </c>
+      <c r="D73" t="s">
         <v>368</v>
-      </c>
-      <c r="D73" t="s">
-        <v>369</v>
       </c>
       <c r="E73" t="s">
         <v>308</v>
@@ -9074,10 +9056,10 @@
         <v>162</v>
       </c>
       <c r="T73" t="s">
+        <v>369</v>
+      </c>
+      <c r="U73" t="s">
         <v>370</v>
-      </c>
-      <c r="U73" t="s">
-        <v>371</v>
       </c>
       <c r="X73">
         <v>0</v>
@@ -9106,10 +9088,10 @@
         <v>7017</v>
       </c>
       <c r="C74" t="s">
+        <v>371</v>
+      </c>
+      <c r="D74" t="s">
         <v>372</v>
-      </c>
-      <c r="D74" t="s">
-        <v>373</v>
       </c>
       <c r="E74" t="s">
         <v>308</v>
@@ -9157,10 +9139,10 @@
         <v>162</v>
       </c>
       <c r="T74" t="s">
+        <v>373</v>
+      </c>
+      <c r="U74" t="s">
         <v>374</v>
-      </c>
-      <c r="U74" t="s">
-        <v>375</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -9189,10 +9171,10 @@
         <v>7018</v>
       </c>
       <c r="C75" t="s">
+        <v>375</v>
+      </c>
+      <c r="D75" t="s">
         <v>376</v>
-      </c>
-      <c r="D75" t="s">
-        <v>377</v>
       </c>
       <c r="E75" t="s">
         <v>308</v>
@@ -9225,10 +9207,10 @@
         <v>300</v>
       </c>
       <c r="T75" t="s">
+        <v>377</v>
+      </c>
+      <c r="U75" t="s">
         <v>378</v>
-      </c>
-      <c r="U75" t="s">
-        <v>379</v>
       </c>
       <c r="X75">
         <v>0</v>
@@ -9260,10 +9242,10 @@
         <v>7019</v>
       </c>
       <c r="C76" t="s">
+        <v>379</v>
+      </c>
+      <c r="D76" t="s">
         <v>380</v>
-      </c>
-      <c r="D76" t="s">
-        <v>381</v>
       </c>
       <c r="E76" t="s">
         <v>308</v>
@@ -9311,10 +9293,10 @@
         <v>162</v>
       </c>
       <c r="T76" t="s">
+        <v>381</v>
+      </c>
+      <c r="U76" t="s">
         <v>382</v>
-      </c>
-      <c r="U76" t="s">
-        <v>383</v>
       </c>
       <c r="V76" t="s">
         <v>162</v>
@@ -9361,13 +9343,13 @@
         <v>8001</v>
       </c>
       <c r="C77" t="s">
+        <v>383</v>
+      </c>
+      <c r="D77" t="s">
         <v>384</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>385</v>
-      </c>
-      <c r="E77" t="s">
-        <v>386</v>
       </c>
       <c r="F77" t="s">
         <v>162</v>
@@ -9412,10 +9394,10 @@
         <v>162</v>
       </c>
       <c r="T77" t="s">
+        <v>386</v>
+      </c>
+      <c r="U77" t="s">
         <v>387</v>
-      </c>
-      <c r="U77" t="s">
-        <v>388</v>
       </c>
       <c r="X77">
         <v>0</v>
@@ -9444,22 +9426,22 @@
         <v>8002</v>
       </c>
       <c r="C78" t="s">
+        <v>388</v>
+      </c>
+      <c r="D78" t="s">
         <v>389</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>390</v>
       </c>
-      <c r="E78" t="s">
-        <v>391</v>
-      </c>
       <c r="F78" t="s">
         <v>162</v>
       </c>
       <c r="G78" t="s">
         <v>162</v>
       </c>
-      <c r="H78" s="13" t="s">
-        <v>321</v>
+      <c r="H78" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -9495,10 +9477,10 @@
         <v>162</v>
       </c>
       <c r="T78" t="s">
+        <v>391</v>
+      </c>
+      <c r="U78" t="s">
         <v>392</v>
-      </c>
-      <c r="U78" t="s">
-        <v>393</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -9527,13 +9509,13 @@
         <v>8003</v>
       </c>
       <c r="C79" t="s">
+        <v>393</v>
+      </c>
+      <c r="D79" t="s">
         <v>394</v>
       </c>
-      <c r="D79" t="s">
-        <v>395</v>
-      </c>
       <c r="E79" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F79" t="s">
         <v>162</v>
@@ -9578,10 +9560,10 @@
         <v>162</v>
       </c>
       <c r="T79" t="s">
+        <v>395</v>
+      </c>
+      <c r="U79" t="s">
         <v>396</v>
-      </c>
-      <c r="U79" t="s">
-        <v>397</v>
       </c>
       <c r="X79">
         <v>0</v>
@@ -9610,13 +9592,13 @@
         <v>8004</v>
       </c>
       <c r="C80" t="s">
+        <v>397</v>
+      </c>
+      <c r="D80" t="s">
         <v>398</v>
       </c>
-      <c r="D80" t="s">
-        <v>399</v>
-      </c>
       <c r="E80" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F80" t="s">
         <v>162</v>
@@ -9661,10 +9643,10 @@
         <v>162</v>
       </c>
       <c r="T80" t="s">
+        <v>399</v>
+      </c>
+      <c r="U80" t="s">
         <v>400</v>
-      </c>
-      <c r="U80" t="s">
-        <v>401</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -9693,13 +9675,13 @@
         <v>8005</v>
       </c>
       <c r="C81" t="s">
+        <v>401</v>
+      </c>
+      <c r="D81" t="s">
         <v>402</v>
       </c>
-      <c r="D81" t="s">
-        <v>403</v>
-      </c>
       <c r="E81" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F81" t="s">
         <v>162</v>
@@ -9744,10 +9726,10 @@
         <v>162</v>
       </c>
       <c r="T81" t="s">
+        <v>403</v>
+      </c>
+      <c r="U81" t="s">
         <v>404</v>
-      </c>
-      <c r="U81" t="s">
-        <v>405</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -9776,13 +9758,13 @@
         <v>8006</v>
       </c>
       <c r="C82" t="s">
+        <v>405</v>
+      </c>
+      <c r="D82" t="s">
         <v>406</v>
       </c>
-      <c r="D82" t="s">
-        <v>407</v>
-      </c>
       <c r="E82" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F82" t="s">
         <v>162</v>
@@ -9827,10 +9809,10 @@
         <v>162</v>
       </c>
       <c r="T82" t="s">
+        <v>407</v>
+      </c>
+      <c r="U82" t="s">
         <v>408</v>
-      </c>
-      <c r="U82" t="s">
-        <v>409</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -9859,13 +9841,13 @@
         <v>8007</v>
       </c>
       <c r="C83" t="s">
+        <v>409</v>
+      </c>
+      <c r="D83" t="s">
         <v>410</v>
       </c>
-      <c r="D83" t="s">
-        <v>411</v>
-      </c>
       <c r="E83" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F83" t="s">
         <v>162</v>
@@ -9910,10 +9892,10 @@
         <v>162</v>
       </c>
       <c r="T83" t="s">
+        <v>411</v>
+      </c>
+      <c r="U83" t="s">
         <v>412</v>
-      </c>
-      <c r="U83" t="s">
-        <v>413</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -9942,13 +9924,13 @@
         <v>8008</v>
       </c>
       <c r="C84" t="s">
+        <v>413</v>
+      </c>
+      <c r="D84" t="s">
         <v>414</v>
       </c>
-      <c r="D84" t="s">
-        <v>415</v>
-      </c>
       <c r="E84" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F84" t="s">
         <v>162</v>
@@ -9993,10 +9975,10 @@
         <v>162</v>
       </c>
       <c r="T84" t="s">
+        <v>415</v>
+      </c>
+      <c r="U84" t="s">
         <v>416</v>
-      </c>
-      <c r="U84" t="s">
-        <v>417</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -10025,13 +10007,13 @@
         <v>8009</v>
       </c>
       <c r="C85" t="s">
+        <v>417</v>
+      </c>
+      <c r="D85" t="s">
         <v>418</v>
       </c>
-      <c r="D85" t="s">
-        <v>419</v>
-      </c>
       <c r="E85" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H85" t="s">
         <v>141</v>
@@ -10061,10 +10043,10 @@
         <v>300</v>
       </c>
       <c r="T85" t="s">
+        <v>419</v>
+      </c>
+      <c r="U85" t="s">
         <v>420</v>
-      </c>
-      <c r="U85" t="s">
-        <v>421</v>
       </c>
       <c r="X85">
         <v>0</v>
@@ -10093,13 +10075,13 @@
         <v>8010</v>
       </c>
       <c r="C86" t="s">
+        <v>421</v>
+      </c>
+      <c r="D86" t="s">
         <v>422</v>
       </c>
-      <c r="D86" t="s">
-        <v>423</v>
-      </c>
       <c r="E86" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H86" t="s">
         <v>141</v>
@@ -10129,10 +10111,10 @@
         <v>300</v>
       </c>
       <c r="T86" t="s">
+        <v>423</v>
+      </c>
+      <c r="U86" t="s">
         <v>424</v>
-      </c>
-      <c r="U86" t="s">
-        <v>425</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -10161,13 +10143,13 @@
         <v>8011</v>
       </c>
       <c r="C87" t="s">
+        <v>425</v>
+      </c>
+      <c r="D87" t="s">
         <v>426</v>
       </c>
-      <c r="D87" t="s">
-        <v>427</v>
-      </c>
       <c r="E87" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H87" t="s">
         <v>99</v>
@@ -10197,10 +10179,10 @@
         <v>300</v>
       </c>
       <c r="T87" t="s">
+        <v>427</v>
+      </c>
+      <c r="U87" t="s">
         <v>428</v>
-      </c>
-      <c r="U87" t="s">
-        <v>429</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -10232,13 +10214,13 @@
         <v>8012</v>
       </c>
       <c r="C88" t="s">
+        <v>429</v>
+      </c>
+      <c r="D88" t="s">
         <v>430</v>
       </c>
-      <c r="D88" t="s">
-        <v>431</v>
-      </c>
       <c r="E88" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F88" t="s">
         <v>162</v>
@@ -10283,10 +10265,10 @@
         <v>162</v>
       </c>
       <c r="T88" t="s">
+        <v>431</v>
+      </c>
+      <c r="U88" t="s">
         <v>432</v>
-      </c>
-      <c r="U88" t="s">
-        <v>433</v>
       </c>
       <c r="V88" t="s">
         <v>162</v>
@@ -10336,13 +10318,13 @@
         <v>8013</v>
       </c>
       <c r="C89" t="s">
+        <v>433</v>
+      </c>
+      <c r="D89" t="s">
         <v>434</v>
       </c>
-      <c r="D89" t="s">
-        <v>435</v>
-      </c>
       <c r="E89" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F89" t="s">
         <v>162</v>
@@ -10387,10 +10369,10 @@
         <v>162</v>
       </c>
       <c r="T89" t="s">
+        <v>435</v>
+      </c>
+      <c r="U89" t="s">
         <v>436</v>
-      </c>
-      <c r="U89" t="s">
-        <v>437</v>
       </c>
       <c r="V89" t="s">
         <v>162</v>
@@ -10437,13 +10419,13 @@
         <v>9001</v>
       </c>
       <c r="C90" t="s">
+        <v>437</v>
+      </c>
+      <c r="D90" t="s">
         <v>438</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>439</v>
-      </c>
-      <c r="E90" t="s">
-        <v>440</v>
       </c>
       <c r="H90" t="s">
         <v>141</v>
@@ -10458,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -10476,10 +10458,10 @@
         <v>300</v>
       </c>
       <c r="T90" t="s">
+        <v>441</v>
+      </c>
+      <c r="U90" t="s">
         <v>442</v>
-      </c>
-      <c r="U90" t="s">
-        <v>443</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -10508,16 +10490,16 @@
         <v>9002</v>
       </c>
       <c r="C91" t="s">
+        <v>443</v>
+      </c>
+      <c r="D91" t="s">
         <v>444</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>439</v>
+      </c>
+      <c r="F91" t="s">
         <v>445</v>
-      </c>
-      <c r="E91" t="s">
-        <v>440</v>
-      </c>
-      <c r="F91" t="s">
-        <v>446</v>
       </c>
       <c r="G91">
         <v>9009</v>
@@ -10535,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -10553,13 +10535,13 @@
         <v>300</v>
       </c>
       <c r="T91" t="s">
+        <v>446</v>
+      </c>
+      <c r="U91" t="s">
         <v>447</v>
       </c>
-      <c r="U91" t="s">
+      <c r="W91" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="W91" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="X91">
         <v>0</v>
@@ -10588,16 +10570,16 @@
         <v>9003</v>
       </c>
       <c r="C92" t="s">
+        <v>449</v>
+      </c>
+      <c r="D92" t="s">
         <v>450</v>
       </c>
-      <c r="D92" t="s">
-        <v>451</v>
-      </c>
       <c r="E92" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F92" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G92">
         <v>9009</v>
@@ -10615,7 +10597,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -10633,13 +10615,13 @@
         <v>300</v>
       </c>
       <c r="T92" t="s">
+        <v>451</v>
+      </c>
+      <c r="U92" t="s">
         <v>452</v>
       </c>
-      <c r="U92" t="s">
-        <v>453</v>
-      </c>
       <c r="W92" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -10668,16 +10650,16 @@
         <v>9004</v>
       </c>
       <c r="C93" t="s">
+        <v>453</v>
+      </c>
+      <c r="D93" t="s">
         <v>454</v>
       </c>
-      <c r="D93" t="s">
-        <v>455</v>
-      </c>
       <c r="E93" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F93" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G93">
         <v>9009</v>
@@ -10695,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -10713,13 +10695,13 @@
         <v>300</v>
       </c>
       <c r="T93" t="s">
+        <v>455</v>
+      </c>
+      <c r="U93" t="s">
         <v>456</v>
       </c>
-      <c r="U93" t="s">
-        <v>457</v>
-      </c>
       <c r="W93" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -10748,16 +10730,16 @@
         <v>9005</v>
       </c>
       <c r="C94" t="s">
+        <v>457</v>
+      </c>
+      <c r="D94" t="s">
         <v>458</v>
       </c>
-      <c r="D94" t="s">
-        <v>459</v>
-      </c>
       <c r="E94" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F94" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G94">
         <v>9009</v>
@@ -10775,7 +10757,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -10793,13 +10775,13 @@
         <v>300</v>
       </c>
       <c r="T94" t="s">
+        <v>459</v>
+      </c>
+      <c r="U94" t="s">
         <v>460</v>
       </c>
-      <c r="U94" t="s">
-        <v>461</v>
-      </c>
       <c r="W94" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -10828,16 +10810,16 @@
         <v>9006</v>
       </c>
       <c r="C95" t="s">
+        <v>461</v>
+      </c>
+      <c r="D95" t="s">
         <v>462</v>
       </c>
-      <c r="D95" t="s">
-        <v>463</v>
-      </c>
       <c r="E95" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F95" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G95">
         <v>9009</v>
@@ -10855,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -10873,13 +10855,13 @@
         <v>300</v>
       </c>
       <c r="T95" t="s">
+        <v>463</v>
+      </c>
+      <c r="U95" t="s">
         <v>464</v>
       </c>
-      <c r="U95" t="s">
-        <v>465</v>
-      </c>
       <c r="W95" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -10908,16 +10890,16 @@
         <v>9007</v>
       </c>
       <c r="C96" t="s">
+        <v>465</v>
+      </c>
+      <c r="D96" t="s">
         <v>466</v>
       </c>
-      <c r="D96" t="s">
-        <v>467</v>
-      </c>
       <c r="E96" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F96" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G96">
         <v>9009</v>
@@ -10935,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -10953,13 +10935,13 @@
         <v>300</v>
       </c>
       <c r="T96" t="s">
+        <v>467</v>
+      </c>
+      <c r="U96" t="s">
         <v>468</v>
       </c>
-      <c r="U96" t="s">
-        <v>469</v>
-      </c>
       <c r="W96" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -10988,16 +10970,16 @@
         <v>9008</v>
       </c>
       <c r="C97" t="s">
+        <v>469</v>
+      </c>
+      <c r="D97" t="s">
         <v>470</v>
       </c>
-      <c r="D97" t="s">
-        <v>471</v>
-      </c>
       <c r="E97" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F97" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G97">
         <v>9009</v>
@@ -11015,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -11033,13 +11015,13 @@
         <v>300</v>
       </c>
       <c r="T97" t="s">
+        <v>471</v>
+      </c>
+      <c r="U97" t="s">
         <v>472</v>
       </c>
-      <c r="U97" t="s">
-        <v>473</v>
-      </c>
       <c r="W97" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -11068,13 +11050,13 @@
         <v>9009</v>
       </c>
       <c r="C98" t="s">
+        <v>473</v>
+      </c>
+      <c r="D98" t="s">
         <v>474</v>
       </c>
-      <c r="D98" t="s">
-        <v>475</v>
-      </c>
       <c r="E98" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H98" t="s">
         <v>92</v>
@@ -11089,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -11107,13 +11089,13 @@
         <v>300</v>
       </c>
       <c r="T98" t="s">
+        <v>475</v>
+      </c>
+      <c r="U98" t="s">
         <v>476</v>
       </c>
-      <c r="U98" t="s">
-        <v>477</v>
-      </c>
       <c r="W98" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -11142,16 +11124,16 @@
         <v>9010</v>
       </c>
       <c r="C99" t="s">
+        <v>477</v>
+      </c>
+      <c r="D99" t="s">
         <v>478</v>
       </c>
-      <c r="D99" t="s">
-        <v>479</v>
-      </c>
       <c r="E99" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F99" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G99">
         <v>9009</v>
@@ -11169,7 +11151,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -11187,10 +11169,10 @@
         <v>300</v>
       </c>
       <c r="T99" t="s">
+        <v>479</v>
+      </c>
+      <c r="U99" t="s">
         <v>480</v>
-      </c>
-      <c r="U99" t="s">
-        <v>481</v>
       </c>
       <c r="X99">
         <v>0</v>
@@ -11219,16 +11201,16 @@
         <v>9011</v>
       </c>
       <c r="C100" t="s">
+        <v>481</v>
+      </c>
+      <c r="D100" t="s">
         <v>482</v>
       </c>
-      <c r="D100" t="s">
-        <v>483</v>
-      </c>
       <c r="E100" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F100" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G100">
         <v>9009</v>
@@ -11246,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -11264,13 +11246,13 @@
         <v>300</v>
       </c>
       <c r="T100" t="s">
+        <v>483</v>
+      </c>
+      <c r="U100" t="s">
         <v>484</v>
       </c>
-      <c r="U100" t="s">
-        <v>485</v>
-      </c>
       <c r="W100" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -11299,13 +11281,13 @@
         <v>10001</v>
       </c>
       <c r="C101" t="s">
+        <v>485</v>
+      </c>
+      <c r="D101" t="s">
         <v>486</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>487</v>
-      </c>
-      <c r="E101" t="s">
-        <v>488</v>
       </c>
       <c r="H101" t="s">
         <v>92</v>
@@ -11335,10 +11317,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="s">
+        <v>488</v>
+      </c>
+      <c r="U101" t="s">
         <v>489</v>
-      </c>
-      <c r="U101" t="s">
-        <v>490</v>
       </c>
       <c r="X101">
         <v>0</v>
@@ -11367,13 +11349,13 @@
         <v>11001</v>
       </c>
       <c r="C102" t="s">
+        <v>490</v>
+      </c>
+      <c r="D102" t="s">
         <v>491</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>492</v>
-      </c>
-      <c r="E102" t="s">
-        <v>493</v>
       </c>
       <c r="H102" t="s">
         <v>92</v>
@@ -11403,13 +11385,13 @@
         <v>0</v>
       </c>
       <c r="T102" t="s">
+        <v>493</v>
+      </c>
+      <c r="U102" t="s">
         <v>494</v>
       </c>
-      <c r="U102" t="s">
+      <c r="W102" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="W102" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="X102">
         <v>0</v>
@@ -11438,13 +11420,13 @@
         <v>11002</v>
       </c>
       <c r="C103" t="s">
+        <v>496</v>
+      </c>
+      <c r="D103" t="s">
         <v>497</v>
       </c>
-      <c r="D103" t="s">
-        <v>498</v>
-      </c>
       <c r="E103" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G103">
         <v>11001</v>
@@ -11477,10 +11459,10 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="U103" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="X103">
         <v>0</v>
@@ -11512,13 +11494,13 @@
         <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E104" t="s">
         <v>140</v>
       </c>
       <c r="H104" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I104">
         <v>100</v>
@@ -11530,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -11549,7 +11531,7 @@
         <v>159</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -11581,13 +11563,13 @@
         <v>135</v>
       </c>
       <c r="D105" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E105" t="s">
         <v>91</v>
       </c>
       <c r="H105" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I105">
         <v>100</v>
@@ -11599,7 +11581,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -11621,7 +11603,7 @@
         <v>1012</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="X105">
         <v>0</v>
@@ -13622,10 +13604,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
+        <v>323</v>
+      </c>
+      <c r="D60" t="s">
         <v>324</v>
-      </c>
-      <c r="D60" t="s">
-        <v>325</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -13654,10 +13636,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
+        <v>327</v>
+      </c>
+      <c r="D61" t="s">
         <v>328</v>
-      </c>
-      <c r="D61" t="s">
-        <v>329</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -13686,10 +13668,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" t="s">
         <v>332</v>
-      </c>
-      <c r="D62" t="s">
-        <v>333</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -13750,10 +13732,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
+        <v>339</v>
+      </c>
+      <c r="D64" t="s">
         <v>340</v>
-      </c>
-      <c r="D64" t="s">
-        <v>341</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -13814,10 +13796,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
+        <v>347</v>
+      </c>
+      <c r="D66" t="s">
         <v>348</v>
-      </c>
-      <c r="D66" t="s">
-        <v>349</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -13878,10 +13860,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
+        <v>355</v>
+      </c>
+      <c r="D68" t="s">
         <v>356</v>
-      </c>
-      <c r="D68" t="s">
-        <v>357</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -13910,10 +13892,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
+        <v>359</v>
+      </c>
+      <c r="D69" t="s">
         <v>360</v>
-      </c>
-      <c r="D69" t="s">
-        <v>361</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -13942,10 +13924,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
+        <v>363</v>
+      </c>
+      <c r="D70" t="s">
         <v>364</v>
-      </c>
-      <c r="D70" t="s">
-        <v>365</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -13974,10 +13956,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
+        <v>367</v>
+      </c>
+      <c r="D71" t="s">
         <v>368</v>
-      </c>
-      <c r="D71" t="s">
-        <v>369</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -14038,10 +14020,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
+        <v>375</v>
+      </c>
+      <c r="D73" t="s">
         <v>376</v>
-      </c>
-      <c r="D73" t="s">
-        <v>377</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -14102,10 +14084,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
+        <v>388</v>
+      </c>
+      <c r="D75" t="s">
         <v>389</v>
-      </c>
-      <c r="D75" t="s">
-        <v>390</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -14169,7 +14151,7 @@
         <v>774</v>
       </c>
       <c r="D77" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -14201,7 +14183,7 @@
         <v>775</v>
       </c>
       <c r="D78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -14230,10 +14212,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
+        <v>405</v>
+      </c>
+      <c r="D79" t="s">
         <v>406</v>
-      </c>
-      <c r="D79" t="s">
-        <v>407</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -14326,10 +14308,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
+        <v>417</v>
+      </c>
+      <c r="D82" t="s">
         <v>418</v>
-      </c>
-      <c r="D82" t="s">
-        <v>419</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -14358,10 +14340,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
+        <v>421</v>
+      </c>
+      <c r="D83" t="s">
         <v>422</v>
-      </c>
-      <c r="D83" t="s">
-        <v>423</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -14390,10 +14372,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
+        <v>425</v>
+      </c>
+      <c r="D84" t="s">
         <v>426</v>
-      </c>
-      <c r="D84" t="s">
-        <v>427</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -14422,10 +14404,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
+        <v>437</v>
+      </c>
+      <c r="D85" t="s">
         <v>438</v>
-      </c>
-      <c r="D85" t="s">
-        <v>439</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -14454,10 +14436,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
+        <v>443</v>
+      </c>
+      <c r="D86" t="s">
         <v>444</v>
-      </c>
-      <c r="D86" t="s">
-        <v>445</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -14486,10 +14468,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
+        <v>449</v>
+      </c>
+      <c r="D87" t="s">
         <v>450</v>
-      </c>
-      <c r="D87" t="s">
-        <v>451</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -14518,10 +14500,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
+        <v>453</v>
+      </c>
+      <c r="D88" t="s">
         <v>454</v>
-      </c>
-      <c r="D88" t="s">
-        <v>455</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -14550,10 +14532,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
+        <v>457</v>
+      </c>
+      <c r="D89" t="s">
         <v>458</v>
-      </c>
-      <c r="D89" t="s">
-        <v>459</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -14582,10 +14564,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
+        <v>461</v>
+      </c>
+      <c r="D90" t="s">
         <v>462</v>
-      </c>
-      <c r="D90" t="s">
-        <v>463</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -14614,10 +14596,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
+        <v>465</v>
+      </c>
+      <c r="D91" t="s">
         <v>466</v>
-      </c>
-      <c r="D91" t="s">
-        <v>467</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -14646,10 +14628,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
+        <v>469</v>
+      </c>
+      <c r="D92" t="s">
         <v>470</v>
-      </c>
-      <c r="D92" t="s">
-        <v>471</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14678,10 +14660,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
+        <v>473</v>
+      </c>
+      <c r="D93" t="s">
         <v>474</v>
-      </c>
-      <c r="D93" t="s">
-        <v>475</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -14710,10 +14692,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
+        <v>477</v>
+      </c>
+      <c r="D94" t="s">
         <v>478</v>
-      </c>
-      <c r="D94" t="s">
-        <v>479</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -14742,10 +14724,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
+        <v>481</v>
+      </c>
+      <c r="D95" t="s">
         <v>482</v>
-      </c>
-      <c r="D95" t="s">
-        <v>483</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14774,10 +14756,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
+        <v>485</v>
+      </c>
+      <c r="D96" t="s">
         <v>486</v>
-      </c>
-      <c r="D96" t="s">
-        <v>487</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -14806,10 +14788,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
+        <v>490</v>
+      </c>
+      <c r="D97" t="s">
         <v>491</v>
-      </c>
-      <c r="D97" t="s">
-        <v>492</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -14838,10 +14820,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
+        <v>496</v>
+      </c>
+      <c r="D98" t="s">
         <v>497</v>
-      </c>
-      <c r="D98" t="s">
-        <v>498</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -14873,7 +14855,7 @@
         <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -14905,7 +14887,7 @@
         <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -14951,17 +14933,17 @@
         <v>91</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="E2" t="s">
         <v>505</v>
-      </c>
-      <c r="E2" t="s">
-        <v>506</v>
       </c>
       <c r="F2" t="s">
         <v>99</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>213</v>
@@ -14970,13 +14952,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>509</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14984,32 +14966,32 @@
         <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>511</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>512</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>513</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>514</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>516</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -15017,32 +14999,32 @@
         <v>191</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>519</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>520</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>521</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>523</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -15050,32 +15032,32 @@
         <v>212</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>525</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>526</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>527</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>528</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>530</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -15083,32 +15065,32 @@
         <v>230</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E6" t="s">
         <v>532</v>
-      </c>
-      <c r="E6" t="s">
-        <v>533</v>
       </c>
       <c r="F6" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>534</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>535</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="O6" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -15116,32 +15098,32 @@
         <v>263</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>539</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>540</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>541</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>542</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -15149,45 +15131,45 @@
         <v>308</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>548</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>549</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>551</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>554</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>555</v>
@@ -15210,7 +15192,7 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>560</v>
@@ -15230,7 +15212,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>564</v>
@@ -15250,7 +15232,7 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>568</v>
@@ -15270,7 +15252,7 @@
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>572</v>
@@ -15309,7 +15291,7 @@
         <v>578</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -15317,7 +15299,7 @@
         <v>579</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="2:3">
@@ -15486,44 +15468,44 @@
         <v>606</v>
       </c>
     </row>
-    <row r="4" s="11" customFormat="1" spans="1:13">
+    <row r="4" s="10" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>618</v>
       </c>
     </row>
@@ -16592,12 +16574,12 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="10">
-        <v>180000</v>
+      <c r="E9" s="9">
+        <v>180</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>0.018</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -16630,7 +16612,7 @@
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>18.982</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -16904,7 +16886,7 @@
         <v>3001</v>
       </c>
       <c r="D26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -17929,22 +17911,22 @@
         <v>200101</v>
       </c>
       <c r="C31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -17961,22 +17943,22 @@
         <v>200201</v>
       </c>
       <c r="C32" t="s">
-        <v>321</v>
+        <v>554</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>321</v>
+        <v>554</v>
       </c>
       <c r="F32" t="s">
-        <v>321</v>
+        <v>554</v>
       </c>
       <c r="G32" t="s">
-        <v>321</v>
+        <v>554</v>
       </c>
       <c r="H32" t="s">
-        <v>321</v>
+        <v>554</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -18217,7 +18199,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -18240,7 +18222,7 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>110</v>
@@ -18263,7 +18245,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>105</v>
@@ -18286,7 +18268,7 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>121</v>
@@ -18309,7 +18291,7 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>141</v>
@@ -18332,7 +18314,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>92</v>
@@ -18355,10 +18337,10 @@
         <v>2001</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E11" t="s">
         <v>727</v>
@@ -18378,10 +18360,10 @@
         <v>2002</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>554</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="E12" t="s">
         <v>727</v>
@@ -18514,7 +18496,7 @@
         <v>737</v>
       </c>
       <c r="D7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -18527,7 +18509,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -18554,10 +18536,10 @@
         <v>1006</v>
       </c>
       <c r="C12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -18565,12 +18547,12 @@
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -18700,7 +18682,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -18732,7 +18714,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -18740,7 +18722,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -18748,7 +18730,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -18756,7 +18738,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="796">
   <si>
     <t>##var</t>
   </si>
@@ -673,10 +673,10 @@
     <t>v1\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
   </si>
   <si>
-    <t>Male A</t>
-  </si>
-  <si>
-    <t>男性手臂A</t>
+    <t>Type 1</t>
+  </si>
+  <si>
+    <t>手臂颜色类型1</t>
   </si>
   <si>
     <t>Arm</t>
@@ -685,46 +685,70 @@
     <t>全球</t>
   </si>
   <si>
-    <t>v1\Player\Arm\MaleA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleA.png</t>
-  </si>
-  <si>
-    <t>Male B</t>
-  </si>
-  <si>
-    <t>男性手臂B</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleB.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleB.png</t>
-  </si>
-  <si>
-    <t>Male C</t>
-  </si>
-  <si>
-    <t>男性手臂C</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleC.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleC.png</t>
-  </si>
-  <si>
-    <t>Male D</t>
-  </si>
-  <si>
-    <t>男性手臂D</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleD.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleD.png</t>
+    <t>v1\Player\Arm\Type1.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type1.png</t>
+  </si>
+  <si>
+    <t>Type 2</t>
+  </si>
+  <si>
+    <t>手臂颜色类型2</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type2.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type2.png</t>
+  </si>
+  <si>
+    <t>Type 3</t>
+  </si>
+  <si>
+    <t>手臂颜色类型3</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type3.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type3.png</t>
+  </si>
+  <si>
+    <t>Type 4</t>
+  </si>
+  <si>
+    <t>手臂颜色类型4</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type4.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type4.png</t>
+  </si>
+  <si>
+    <t>Type 5</t>
+  </si>
+  <si>
+    <t>手臂颜色类型5</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type5.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type5.png</t>
+  </si>
+  <si>
+    <t>Type 6</t>
+  </si>
+  <si>
+    <t>手臂颜色类型6</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type6.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type6.png</t>
   </si>
   <si>
     <t>Baseball Jacket Black</t>
@@ -2278,6 +2302,30 @@
   </si>
   <si>
     <t>Lucky</t>
+  </si>
+  <si>
+    <t>Male A</t>
+  </si>
+  <si>
+    <t>男性手臂A</t>
+  </si>
+  <si>
+    <t>Male B</t>
+  </si>
+  <si>
+    <t>男性手臂B</t>
+  </si>
+  <si>
+    <t>Male C</t>
+  </si>
+  <si>
+    <t>男性手臂C</t>
+  </si>
+  <si>
+    <t>Male D</t>
+  </si>
+  <si>
+    <t>男性手臂D</t>
   </si>
   <si>
     <t>Full Tilt Like</t>
@@ -3621,7 +3669,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH105"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
@@ -6405,7 +6453,7 @@
     </row>
     <row r="39" spans="2:30">
       <c r="B39">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C39" t="s">
         <v>228</v>
@@ -6414,40 +6462,43 @@
         <v>229</v>
       </c>
       <c r="E39" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>93</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
         <v>230</v>
       </c>
-      <c r="H39" t="s">
-        <v>141</v>
-      </c>
-      <c r="I39">
-        <v>300</v>
-      </c>
-      <c r="J39">
-        <v>300</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="s">
-        <v>100</v>
-      </c>
-      <c r="M39" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>1001</v>
-      </c>
-      <c r="O39">
-        <v>300</v>
-      </c>
-      <c r="P39">
-        <v>300</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>231</v>
-      </c>
-      <c r="U39" t="s">
-        <v>232</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -6473,49 +6524,52 @@
     </row>
     <row r="40" spans="2:30">
       <c r="B40">
-        <v>5002</v>
+        <v>4006</v>
       </c>
       <c r="C40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" t="s">
         <v>233</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" t="s">
+        <v>213</v>
+      </c>
+      <c r="H40" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>93</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="T40" t="s">
         <v>234</v>
       </c>
-      <c r="E40" t="s">
-        <v>230</v>
-      </c>
-      <c r="H40" t="s">
-        <v>105</v>
-      </c>
-      <c r="I40">
-        <v>300</v>
-      </c>
-      <c r="J40">
-        <v>300</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="s">
-        <v>100</v>
-      </c>
-      <c r="M40" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>1001</v>
-      </c>
-      <c r="O40">
-        <v>300</v>
-      </c>
-      <c r="P40">
-        <v>300</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="U40" t="s">
         <v>235</v>
-      </c>
-      <c r="U40" t="s">
-        <v>236</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -6541,19 +6595,19 @@
     </row>
     <row r="41" spans="2:30">
       <c r="B41">
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="C41" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" t="s">
         <v>237</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>238</v>
       </c>
-      <c r="E41" t="s">
-        <v>230</v>
-      </c>
       <c r="H41" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I41">
         <v>300</v>
@@ -6609,7 +6663,7 @@
     </row>
     <row r="42" spans="2:30">
       <c r="B42">
-        <v>5004</v>
+        <v>5002</v>
       </c>
       <c r="C42" t="s">
         <v>241</v>
@@ -6618,7 +6672,7 @@
         <v>242</v>
       </c>
       <c r="E42" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H42" t="s">
         <v>105</v>
@@ -6677,7 +6731,7 @@
     </row>
     <row r="43" spans="2:30">
       <c r="B43">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="C43" t="s">
         <v>245</v>
@@ -6686,10 +6740,10 @@
         <v>246</v>
       </c>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H43" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -6745,7 +6799,7 @@
     </row>
     <row r="44" spans="2:30">
       <c r="B44">
-        <v>5006</v>
+        <v>5004</v>
       </c>
       <c r="C44" t="s">
         <v>249</v>
@@ -6754,10 +6808,10 @@
         <v>250</v>
       </c>
       <c r="E44" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H44" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I44">
         <v>300</v>
@@ -6813,7 +6867,7 @@
     </row>
     <row r="45" spans="2:30">
       <c r="B45">
-        <v>5007</v>
+        <v>5005</v>
       </c>
       <c r="C45" t="s">
         <v>253</v>
@@ -6822,10 +6876,10 @@
         <v>254</v>
       </c>
       <c r="E45" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H45" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -6881,7 +6935,7 @@
     </row>
     <row r="46" spans="2:30">
       <c r="B46">
-        <v>5008</v>
+        <v>5006</v>
       </c>
       <c r="C46" t="s">
         <v>257</v>
@@ -6890,7 +6944,7 @@
         <v>258</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H46" t="s">
         <v>141</v>
@@ -6949,7 +7003,7 @@
     </row>
     <row r="47" spans="2:30">
       <c r="B47">
-        <v>6001</v>
+        <v>5007</v>
       </c>
       <c r="C47" t="s">
         <v>261</v>
@@ -6958,55 +7012,40 @@
         <v>262</v>
       </c>
       <c r="E47" t="s">
+        <v>238</v>
+      </c>
+      <c r="H47" t="s">
+        <v>121</v>
+      </c>
+      <c r="I47">
+        <v>300</v>
+      </c>
+      <c r="J47">
+        <v>300</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>100</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>1001</v>
+      </c>
+      <c r="O47">
+        <v>300</v>
+      </c>
+      <c r="P47">
+        <v>300</v>
+      </c>
+      <c r="T47" t="s">
         <v>263</v>
       </c>
-      <c r="F47" t="s">
-        <v>162</v>
-      </c>
-      <c r="G47" t="s">
-        <v>162</v>
-      </c>
-      <c r="H47" t="s">
-        <v>92</v>
-      </c>
-      <c r="I47">
-        <v>300</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>93</v>
-      </c>
-      <c r="M47" t="b">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>162</v>
-      </c>
-      <c r="R47" t="s">
-        <v>162</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" t="s">
+      <c r="U47" t="s">
         <v>264</v>
-      </c>
-      <c r="U47" t="s">
-        <v>265</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -7032,25 +7071,19 @@
     </row>
     <row r="48" spans="2:30">
       <c r="B48">
-        <v>6002</v>
+        <v>5008</v>
       </c>
       <c r="C48" t="s">
+        <v>265</v>
+      </c>
+      <c r="D48" t="s">
         <v>266</v>
       </c>
-      <c r="D48" t="s">
-        <v>267</v>
-      </c>
       <c r="E48" t="s">
-        <v>263</v>
-      </c>
-      <c r="F48" t="s">
-        <v>162</v>
-      </c>
-      <c r="G48" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="H48" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I48">
         <v>300</v>
@@ -7076,20 +7109,11 @@
       <c r="P48">
         <v>300</v>
       </c>
-      <c r="Q48" t="s">
-        <v>162</v>
-      </c>
-      <c r="R48" t="s">
-        <v>162</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T48" t="s">
+        <v>267</v>
+      </c>
+      <c r="U48" t="s">
         <v>268</v>
-      </c>
-      <c r="U48" t="s">
-        <v>269</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -7115,17 +7139,17 @@
     </row>
     <row r="49" spans="2:30">
       <c r="B49">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C49" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" t="s">
         <v>270</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>271</v>
       </c>
-      <c r="E49" t="s">
-        <v>263</v>
-      </c>
       <c r="F49" t="s">
         <v>162</v>
       </c>
@@ -7133,31 +7157,31 @@
         <v>162</v>
       </c>
       <c r="H49" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="I49">
         <v>300</v>
       </c>
       <c r="J49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="s">
         <v>162</v>
@@ -7198,7 +7222,7 @@
     </row>
     <row r="50" spans="2:30">
       <c r="B50">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C50" t="s">
         <v>274</v>
@@ -7207,7 +7231,7 @@
         <v>275</v>
       </c>
       <c r="E50" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F50" t="s">
         <v>162</v>
@@ -7281,7 +7305,7 @@
     </row>
     <row r="51" spans="2:30">
       <c r="B51">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C51" t="s">
         <v>278</v>
@@ -7290,7 +7314,7 @@
         <v>279</v>
       </c>
       <c r="E51" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F51" t="s">
         <v>162</v>
@@ -7364,7 +7388,7 @@
     </row>
     <row r="52" spans="2:30">
       <c r="B52">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C52" t="s">
         <v>282</v>
@@ -7373,7 +7397,7 @@
         <v>283</v>
       </c>
       <c r="E52" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -7447,7 +7471,7 @@
     </row>
     <row r="53" spans="2:30">
       <c r="B53">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C53" t="s">
         <v>286</v>
@@ -7456,7 +7480,7 @@
         <v>287</v>
       </c>
       <c r="E53" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F53" t="s">
         <v>162</v>
@@ -7465,7 +7489,7 @@
         <v>162</v>
       </c>
       <c r="H53" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I53">
         <v>300</v>
@@ -7530,7 +7554,7 @@
     </row>
     <row r="54" spans="2:30">
       <c r="B54">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="C54" t="s">
         <v>290</v>
@@ -7539,7 +7563,7 @@
         <v>291</v>
       </c>
       <c r="E54" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F54" t="s">
         <v>162</v>
@@ -7548,7 +7572,7 @@
         <v>162</v>
       </c>
       <c r="H54" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -7613,7 +7637,7 @@
     </row>
     <row r="55" spans="2:30">
       <c r="B55">
-        <v>6009</v>
+        <v>6007</v>
       </c>
       <c r="C55" t="s">
         <v>294</v>
@@ -7622,7 +7646,7 @@
         <v>295</v>
       </c>
       <c r="E55" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F55" t="s">
         <v>162</v>
@@ -7631,7 +7655,7 @@
         <v>162</v>
       </c>
       <c r="H55" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I55">
         <v>300</v>
@@ -7696,7 +7720,7 @@
     </row>
     <row r="56" spans="2:30">
       <c r="B56">
-        <v>6010</v>
+        <v>6008</v>
       </c>
       <c r="C56" t="s">
         <v>298</v>
@@ -7705,7 +7729,7 @@
         <v>299</v>
       </c>
       <c r="E56" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F56" t="s">
         <v>162</v>
@@ -7779,7 +7803,7 @@
     </row>
     <row r="57" spans="2:30">
       <c r="B57">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="C57" t="s">
         <v>302</v>
@@ -7788,7 +7812,7 @@
         <v>303</v>
       </c>
       <c r="E57" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F57" t="s">
         <v>162</v>
@@ -7797,7 +7821,7 @@
         <v>162</v>
       </c>
       <c r="H57" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="I57">
         <v>300</v>
@@ -7862,7 +7886,7 @@
     </row>
     <row r="58" spans="2:30">
       <c r="B58">
-        <v>7001</v>
+        <v>6010</v>
       </c>
       <c r="C58" t="s">
         <v>306</v>
@@ -7871,7 +7895,13 @@
         <v>307</v>
       </c>
       <c r="E58" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="F58" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" t="s">
+        <v>162</v>
       </c>
       <c r="H58" t="s">
         <v>141</v>
@@ -7900,11 +7930,20 @@
       <c r="P58">
         <v>300</v>
       </c>
+      <c r="Q58" t="s">
+        <v>162</v>
+      </c>
+      <c r="R58" t="s">
+        <v>162</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T58" t="s">
+        <v>308</v>
+      </c>
+      <c r="U58" t="s">
         <v>309</v>
-      </c>
-      <c r="U58" t="s">
-        <v>310</v>
       </c>
       <c r="X58">
         <v>0</v>
@@ -7930,19 +7969,25 @@
     </row>
     <row r="59" spans="2:30">
       <c r="B59">
-        <v>7002</v>
+        <v>6011</v>
       </c>
       <c r="C59" t="s">
+        <v>310</v>
+      </c>
+      <c r="D59" t="s">
         <v>311</v>
       </c>
-      <c r="D59" t="s">
-        <v>312</v>
-      </c>
       <c r="E59" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="F59" t="s">
+        <v>162</v>
+      </c>
+      <c r="G59" t="s">
+        <v>162</v>
       </c>
       <c r="H59" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I59">
         <v>300</v>
@@ -7968,11 +8013,20 @@
       <c r="P59">
         <v>300</v>
       </c>
+      <c r="Q59" t="s">
+        <v>162</v>
+      </c>
+      <c r="R59" t="s">
+        <v>162</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T59" t="s">
+        <v>312</v>
+      </c>
+      <c r="U59" t="s">
         <v>313</v>
-      </c>
-      <c r="U59" t="s">
-        <v>314</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -7998,16 +8052,16 @@
     </row>
     <row r="60" spans="2:30">
       <c r="B60">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="C60" t="s">
+        <v>314</v>
+      </c>
+      <c r="D60" t="s">
         <v>315</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>316</v>
-      </c>
-      <c r="E60" t="s">
-        <v>308</v>
       </c>
       <c r="H60" t="s">
         <v>141</v>
@@ -8066,7 +8120,7 @@
     </row>
     <row r="61" spans="2:30">
       <c r="B61">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="C61" t="s">
         <v>319</v>
@@ -8075,34 +8129,34 @@
         <v>320</v>
       </c>
       <c r="E61" t="s">
-        <v>308</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>92</v>
+        <v>316</v>
+      </c>
+      <c r="H61" t="s">
+        <v>141</v>
       </c>
       <c r="I61">
         <v>300</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T61" t="s">
         <v>321</v>
@@ -8134,7 +8188,7 @@
     </row>
     <row r="62" spans="2:30">
       <c r="B62">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C62" t="s">
         <v>323</v>
@@ -8143,10 +8197,10 @@
         <v>324</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>121</v>
+        <v>316</v>
+      </c>
+      <c r="H62" t="s">
+        <v>141</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -8202,7 +8256,7 @@
     </row>
     <row r="63" spans="2:30">
       <c r="B63">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="C63" t="s">
         <v>327</v>
@@ -8211,34 +8265,34 @@
         <v>328</v>
       </c>
       <c r="E63" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="I63">
         <v>300</v>
       </c>
       <c r="J63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T63" t="s">
         <v>329</v>
@@ -8270,7 +8324,7 @@
     </row>
     <row r="64" spans="2:30">
       <c r="B64">
-        <v>7007</v>
+        <v>7005</v>
       </c>
       <c r="C64" t="s">
         <v>331</v>
@@ -8279,10 +8333,10 @@
         <v>332</v>
       </c>
       <c r="E64" t="s">
-        <v>308</v>
-      </c>
-      <c r="H64" t="s">
-        <v>141</v>
+        <v>316</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I64">
         <v>300</v>
@@ -8338,7 +8392,7 @@
     </row>
     <row r="65" spans="1:34">
       <c r="B65">
-        <v>7008</v>
+        <v>7006</v>
       </c>
       <c r="C65" t="s">
         <v>335</v>
@@ -8347,16 +8401,10 @@
         <v>336</v>
       </c>
       <c r="E65" t="s">
-        <v>308</v>
-      </c>
-      <c r="F65" t="s">
-        <v>162</v>
-      </c>
-      <c r="G65" t="s">
-        <v>162</v>
-      </c>
-      <c r="H65" t="s">
-        <v>110</v>
+        <v>316</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I65">
         <v>300</v>
@@ -8382,15 +8430,6 @@
       <c r="P65">
         <v>300</v>
       </c>
-      <c r="Q65" t="s">
-        <v>162</v>
-      </c>
-      <c r="R65" t="s">
-        <v>162</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T65" t="s">
         <v>337</v>
       </c>
@@ -8421,7 +8460,7 @@
     </row>
     <row r="66" spans="1:34">
       <c r="B66">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="C66" t="s">
         <v>339</v>
@@ -8430,16 +8469,10 @@
         <v>340</v>
       </c>
       <c r="E66" t="s">
-        <v>308</v>
-      </c>
-      <c r="F66" t="s">
-        <v>162</v>
-      </c>
-      <c r="G66" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="H66" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I66">
         <v>300</v>
@@ -8465,15 +8498,6 @@
       <c r="P66">
         <v>300</v>
       </c>
-      <c r="Q66" t="s">
-        <v>162</v>
-      </c>
-      <c r="R66" t="s">
-        <v>162</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T66" t="s">
         <v>341</v>
       </c>
@@ -8504,7 +8528,7 @@
     </row>
     <row r="67" spans="1:34">
       <c r="B67">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="C67" t="s">
         <v>343</v>
@@ -8513,7 +8537,7 @@
         <v>344</v>
       </c>
       <c r="E67" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F67" t="s">
         <v>162</v>
@@ -8522,7 +8546,7 @@
         <v>162</v>
       </c>
       <c r="H67" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="I67">
         <v>300</v>
@@ -8587,7 +8611,7 @@
     </row>
     <row r="68" spans="1:34">
       <c r="B68">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="C68" t="s">
         <v>347</v>
@@ -8596,7 +8620,7 @@
         <v>348</v>
       </c>
       <c r="E68" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F68" t="s">
         <v>162</v>
@@ -8670,7 +8694,7 @@
     </row>
     <row r="69" spans="1:34">
       <c r="B69">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="C69" t="s">
         <v>351</v>
@@ -8679,7 +8703,7 @@
         <v>352</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F69" t="s">
         <v>162</v>
@@ -8688,7 +8712,7 @@
         <v>162</v>
       </c>
       <c r="H69" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I69">
         <v>300</v>
@@ -8753,7 +8777,7 @@
     </row>
     <row r="70" spans="1:34">
       <c r="B70">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="C70" t="s">
         <v>355</v>
@@ -8762,7 +8786,7 @@
         <v>356</v>
       </c>
       <c r="E70" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F70" t="s">
         <v>162</v>
@@ -8836,7 +8860,7 @@
     </row>
     <row r="71" spans="1:34">
       <c r="B71">
-        <v>7014</v>
+        <v>7012</v>
       </c>
       <c r="C71" t="s">
         <v>359</v>
@@ -8845,7 +8869,7 @@
         <v>360</v>
       </c>
       <c r="E71" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F71" t="s">
         <v>162</v>
@@ -8854,7 +8878,7 @@
         <v>162</v>
       </c>
       <c r="H71" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I71">
         <v>300</v>
@@ -8919,7 +8943,7 @@
     </row>
     <row r="72" spans="1:34">
       <c r="B72">
-        <v>7015</v>
+        <v>7013</v>
       </c>
       <c r="C72" t="s">
         <v>363</v>
@@ -8928,7 +8952,7 @@
         <v>364</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F72" t="s">
         <v>162</v>
@@ -8937,7 +8961,7 @@
         <v>162</v>
       </c>
       <c r="H72" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I72">
         <v>300</v>
@@ -9002,7 +9026,7 @@
     </row>
     <row r="73" spans="1:34">
       <c r="B73">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="C73" t="s">
         <v>367</v>
@@ -9011,7 +9035,7 @@
         <v>368</v>
       </c>
       <c r="E73" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F73" t="s">
         <v>162</v>
@@ -9020,7 +9044,7 @@
         <v>162</v>
       </c>
       <c r="H73" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I73">
         <v>300</v>
@@ -9085,7 +9109,7 @@
     </row>
     <row r="74" spans="1:34">
       <c r="B74">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="C74" t="s">
         <v>371</v>
@@ -9094,7 +9118,7 @@
         <v>372</v>
       </c>
       <c r="E74" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F74" t="s">
         <v>162</v>
@@ -9103,7 +9127,7 @@
         <v>162</v>
       </c>
       <c r="H74" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I74">
         <v>300</v>
@@ -9168,7 +9192,7 @@
     </row>
     <row r="75" spans="1:34">
       <c r="B75">
-        <v>7018</v>
+        <v>7016</v>
       </c>
       <c r="C75" t="s">
         <v>375</v>
@@ -9177,10 +9201,16 @@
         <v>376</v>
       </c>
       <c r="E75" t="s">
-        <v>308</v>
+        <v>316</v>
+      </c>
+      <c r="F75" t="s">
+        <v>162</v>
+      </c>
+      <c r="G75" t="s">
+        <v>162</v>
       </c>
       <c r="H75" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I75">
         <v>300</v>
@@ -9206,6 +9236,15 @@
       <c r="P75">
         <v>300</v>
       </c>
+      <c r="Q75" t="s">
+        <v>162</v>
+      </c>
+      <c r="R75" t="s">
+        <v>162</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T75" t="s">
         <v>377</v>
       </c>
@@ -9235,11 +9274,8 @@
       </c>
     </row>
     <row r="76" spans="1:34">
-      <c r="A76" t="s">
-        <v>162</v>
-      </c>
       <c r="B76">
-        <v>7019</v>
+        <v>7017</v>
       </c>
       <c r="C76" t="s">
         <v>379</v>
@@ -9248,7 +9284,7 @@
         <v>380</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F76" t="s">
         <v>162</v>
@@ -9298,12 +9334,6 @@
       <c r="U76" t="s">
         <v>382</v>
       </c>
-      <c r="V76" t="s">
-        <v>162</v>
-      </c>
-      <c r="W76" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="X76">
         <v>0</v>
       </c>
@@ -9324,23 +9354,11 @@
       </c>
       <c r="AD76" t="b">
         <v>0</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH76" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:34">
       <c r="B77">
-        <v>8001</v>
+        <v>7018</v>
       </c>
       <c r="C77" t="s">
         <v>383</v>
@@ -9349,16 +9367,10 @@
         <v>384</v>
       </c>
       <c r="E77" t="s">
-        <v>385</v>
-      </c>
-      <c r="F77" t="s">
-        <v>162</v>
-      </c>
-      <c r="G77" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="H77" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I77">
         <v>300</v>
@@ -9384,55 +9396,49 @@
       <c r="P77">
         <v>300</v>
       </c>
-      <c r="Q77" t="s">
-        <v>162</v>
-      </c>
-      <c r="R77" t="s">
-        <v>162</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T77" t="s">
+        <v>385</v>
+      </c>
+      <c r="U77" t="s">
         <v>386</v>
       </c>
-      <c r="U77" t="s">
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
+      <c r="A78" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78">
+        <v>7019</v>
+      </c>
+      <c r="C78" t="s">
         <v>387</v>
       </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:34">
-      <c r="B78">
-        <v>8002</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>388</v>
       </c>
-      <c r="D78" t="s">
-        <v>389</v>
-      </c>
       <c r="E78" t="s">
-        <v>390</v>
+        <v>316</v>
       </c>
       <c r="F78" t="s">
         <v>162</v>
@@ -9440,8 +9446,8 @@
       <c r="G78" t="s">
         <v>162</v>
       </c>
-      <c r="H78" s="9" t="s">
-        <v>121</v>
+      <c r="H78" t="s">
+        <v>105</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -9477,10 +9483,16 @@
         <v>162</v>
       </c>
       <c r="T78" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="U78" t="s">
-        <v>392</v>
+        <v>390</v>
+      </c>
+      <c r="V78" t="s">
+        <v>162</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -9502,20 +9514,32 @@
       </c>
       <c r="AD78" t="b">
         <v>0</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:34">
       <c r="B79">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="C79" t="s">
+        <v>391</v>
+      </c>
+      <c r="D79" t="s">
+        <v>392</v>
+      </c>
+      <c r="E79" t="s">
         <v>393</v>
-      </c>
-      <c r="D79" t="s">
-        <v>394</v>
-      </c>
-      <c r="E79" t="s">
-        <v>385</v>
       </c>
       <c r="F79" t="s">
         <v>162</v>
@@ -9560,10 +9584,10 @@
         <v>162</v>
       </c>
       <c r="T79" t="s">
+        <v>394</v>
+      </c>
+      <c r="U79" t="s">
         <v>395</v>
-      </c>
-      <c r="U79" t="s">
-        <v>396</v>
       </c>
       <c r="X79">
         <v>0</v>
@@ -9589,25 +9613,25 @@
     </row>
     <row r="80" spans="1:34">
       <c r="B80">
-        <v>8004</v>
+        <v>8002</v>
       </c>
       <c r="C80" t="s">
+        <v>396</v>
+      </c>
+      <c r="D80" t="s">
         <v>397</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>398</v>
       </c>
-      <c r="E80" t="s">
-        <v>385</v>
-      </c>
       <c r="F80" t="s">
         <v>162</v>
       </c>
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" t="s">
-        <v>105</v>
+      <c r="H80" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I80">
         <v>300</v>
@@ -9672,7 +9696,7 @@
     </row>
     <row r="81" spans="1:34">
       <c r="B81">
-        <v>8005</v>
+        <v>8003</v>
       </c>
       <c r="C81" t="s">
         <v>401</v>
@@ -9681,7 +9705,7 @@
         <v>402</v>
       </c>
       <c r="E81" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F81" t="s">
         <v>162</v>
@@ -9690,7 +9714,7 @@
         <v>162</v>
       </c>
       <c r="H81" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I81">
         <v>300</v>
@@ -9755,7 +9779,7 @@
     </row>
     <row r="82" spans="1:34">
       <c r="B82">
-        <v>8006</v>
+        <v>8004</v>
       </c>
       <c r="C82" t="s">
         <v>405</v>
@@ -9764,7 +9788,7 @@
         <v>406</v>
       </c>
       <c r="E82" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F82" t="s">
         <v>162</v>
@@ -9772,8 +9796,8 @@
       <c r="G82" t="s">
         <v>162</v>
       </c>
-      <c r="H82" s="9" t="s">
-        <v>141</v>
+      <c r="H82" t="s">
+        <v>105</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -9838,7 +9862,7 @@
     </row>
     <row r="83" spans="1:34">
       <c r="B83">
-        <v>8007</v>
+        <v>8005</v>
       </c>
       <c r="C83" t="s">
         <v>409</v>
@@ -9847,7 +9871,7 @@
         <v>410</v>
       </c>
       <c r="E83" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F83" t="s">
         <v>162</v>
@@ -9856,7 +9880,7 @@
         <v>162</v>
       </c>
       <c r="H83" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -9921,7 +9945,7 @@
     </row>
     <row r="84" spans="1:34">
       <c r="B84">
-        <v>8008</v>
+        <v>8006</v>
       </c>
       <c r="C84" t="s">
         <v>413</v>
@@ -9930,7 +9954,7 @@
         <v>414</v>
       </c>
       <c r="E84" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F84" t="s">
         <v>162</v>
@@ -9938,8 +9962,8 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" t="s">
-        <v>110</v>
+      <c r="H84" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -10004,7 +10028,7 @@
     </row>
     <row r="85" spans="1:34">
       <c r="B85">
-        <v>8009</v>
+        <v>8007</v>
       </c>
       <c r="C85" t="s">
         <v>417</v>
@@ -10013,10 +10037,16 @@
         <v>418</v>
       </c>
       <c r="E85" t="s">
-        <v>385</v>
+        <v>393</v>
+      </c>
+      <c r="F85" t="s">
+        <v>162</v>
+      </c>
+      <c r="G85" t="s">
+        <v>162</v>
       </c>
       <c r="H85" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I85">
         <v>300</v>
@@ -10042,6 +10072,15 @@
       <c r="P85">
         <v>300</v>
       </c>
+      <c r="Q85" t="s">
+        <v>162</v>
+      </c>
+      <c r="R85" t="s">
+        <v>162</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T85" t="s">
         <v>419</v>
       </c>
@@ -10072,7 +10111,7 @@
     </row>
     <row r="86" spans="1:34">
       <c r="B86">
-        <v>8010</v>
+        <v>8008</v>
       </c>
       <c r="C86" t="s">
         <v>421</v>
@@ -10081,10 +10120,16 @@
         <v>422</v>
       </c>
       <c r="E86" t="s">
-        <v>385</v>
+        <v>393</v>
+      </c>
+      <c r="F86" t="s">
+        <v>162</v>
+      </c>
+      <c r="G86" t="s">
+        <v>162</v>
       </c>
       <c r="H86" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I86">
         <v>300</v>
@@ -10110,6 +10155,15 @@
       <c r="P86">
         <v>300</v>
       </c>
+      <c r="Q86" t="s">
+        <v>162</v>
+      </c>
+      <c r="R86" t="s">
+        <v>162</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T86" t="s">
         <v>423</v>
       </c>
@@ -10140,7 +10194,7 @@
     </row>
     <row r="87" spans="1:34">
       <c r="B87">
-        <v>8011</v>
+        <v>8009</v>
       </c>
       <c r="C87" t="s">
         <v>425</v>
@@ -10149,10 +10203,10 @@
         <v>426</v>
       </c>
       <c r="E87" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="H87" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="I87">
         <v>300</v>
@@ -10207,11 +10261,8 @@
       </c>
     </row>
     <row r="88" spans="1:34">
-      <c r="A88" t="s">
-        <v>162</v>
-      </c>
       <c r="B88">
-        <v>8012</v>
+        <v>8010</v>
       </c>
       <c r="C88" t="s">
         <v>429</v>
@@ -10220,16 +10271,10 @@
         <v>430</v>
       </c>
       <c r="E88" t="s">
-        <v>385</v>
-      </c>
-      <c r="F88" t="s">
-        <v>162</v>
-      </c>
-      <c r="G88" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="H88" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I88">
         <v>300</v>
@@ -10255,27 +10300,12 @@
       <c r="P88">
         <v>300</v>
       </c>
-      <c r="Q88" t="s">
-        <v>162</v>
-      </c>
-      <c r="R88" t="s">
-        <v>162</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T88" t="s">
         <v>431</v>
       </c>
       <c r="U88" t="s">
         <v>432</v>
       </c>
-      <c r="V88" t="s">
-        <v>162</v>
-      </c>
-      <c r="W88" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="X88">
         <v>0</v>
       </c>
@@ -10297,25 +10327,10 @@
       <c r="AD88" t="b">
         <v>0</v>
       </c>
-      <c r="AE88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH88" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="89" spans="1:34">
-      <c r="A89" t="s">
-        <v>162</v>
-      </c>
       <c r="B89">
-        <v>8013</v>
+        <v>8011</v>
       </c>
       <c r="C89" t="s">
         <v>433</v>
@@ -10324,16 +10339,10 @@
         <v>434</v>
       </c>
       <c r="E89" t="s">
-        <v>385</v>
-      </c>
-      <c r="F89" t="s">
-        <v>162</v>
-      </c>
-      <c r="G89" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="H89" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I89">
         <v>300</v>
@@ -10359,27 +10368,12 @@
       <c r="P89">
         <v>300</v>
       </c>
-      <c r="Q89" t="s">
-        <v>162</v>
-      </c>
-      <c r="R89" t="s">
-        <v>162</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T89" t="s">
         <v>435</v>
       </c>
       <c r="U89" t="s">
         <v>436</v>
       </c>
-      <c r="V89" t="s">
-        <v>162</v>
-      </c>
-      <c r="W89" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="X89">
         <v>0</v>
       </c>
@@ -10401,22 +10395,13 @@
       <c r="AD89" t="b">
         <v>0</v>
       </c>
-      <c r="AE89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH89" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="90" spans="1:34">
+      <c r="A90" t="s">
+        <v>162</v>
+      </c>
       <c r="B90">
-        <v>9001</v>
+        <v>8012</v>
       </c>
       <c r="C90" t="s">
         <v>437</v>
@@ -10425,13 +10410,19 @@
         <v>438</v>
       </c>
       <c r="E90" t="s">
-        <v>439</v>
+        <v>393</v>
+      </c>
+      <c r="F90" t="s">
+        <v>162</v>
+      </c>
+      <c r="G90" t="s">
+        <v>162</v>
       </c>
       <c r="H90" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I90">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J90">
         <v>300</v>
@@ -10440,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>440</v>
+        <v>100</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -10449,66 +10440,93 @@
         <v>1001</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>300</v>
+        <v>300</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>162</v>
+      </c>
+      <c r="R90" t="s">
+        <v>162</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="T90" t="s">
+        <v>439</v>
+      </c>
+      <c r="U90" t="s">
+        <v>440</v>
+      </c>
+      <c r="V90" t="s">
+        <v>162</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:34">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91">
+        <v>8013</v>
+      </c>
+      <c r="C91" t="s">
         <v>441</v>
       </c>
-      <c r="U90" t="s">
+      <c r="D91" t="s">
         <v>442</v>
       </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:34">
-      <c r="B91">
-        <v>9002</v>
-      </c>
-      <c r="C91" t="s">
-        <v>443</v>
-      </c>
-      <c r="D91" t="s">
-        <v>444</v>
-      </c>
       <c r="E91" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="F91" t="s">
-        <v>445</v>
-      </c>
-      <c r="G91">
-        <v>9009</v>
+        <v>162</v>
+      </c>
+      <c r="G91" t="s">
+        <v>162</v>
       </c>
       <c r="H91" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I91">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J91">
         <v>300</v>
@@ -10517,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>440</v>
+        <v>100</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -10526,22 +10544,31 @@
         <v>1001</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>300</v>
+        <v>300</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>162</v>
+      </c>
+      <c r="R91" t="s">
+        <v>162</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="T91" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="U91" t="s">
-        <v>447</v>
+        <v>444</v>
+      </c>
+      <c r="V91" t="s">
+        <v>162</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>448</v>
+        <v>162</v>
       </c>
       <c r="X91">
         <v>0</v>
@@ -10559,33 +10586,39 @@
         <v>0</v>
       </c>
       <c r="AC91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="b">
         <v>0</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:34">
       <c r="B92">
-        <v>9003</v>
+        <v>9001</v>
       </c>
       <c r="C92" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D92" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E92" t="s">
-        <v>439</v>
-      </c>
-      <c r="F92" t="s">
-        <v>445</v>
-      </c>
-      <c r="G92">
-        <v>9009</v>
+        <v>447</v>
       </c>
       <c r="H92" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I92">
         <v>200</v>
@@ -10597,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -10615,13 +10648,10 @@
         <v>300</v>
       </c>
       <c r="T92" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="U92" t="s">
-        <v>452</v>
-      </c>
-      <c r="W92" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -10647,19 +10677,19 @@
     </row>
     <row r="93" spans="1:34">
       <c r="B93">
-        <v>9004</v>
+        <v>9002</v>
       </c>
       <c r="C93" t="s">
+        <v>451</v>
+      </c>
+      <c r="D93" t="s">
+        <v>452</v>
+      </c>
+      <c r="E93" t="s">
+        <v>447</v>
+      </c>
+      <c r="F93" t="s">
         <v>453</v>
-      </c>
-      <c r="D93" t="s">
-        <v>454</v>
-      </c>
-      <c r="E93" t="s">
-        <v>439</v>
-      </c>
-      <c r="F93" t="s">
-        <v>445</v>
       </c>
       <c r="G93">
         <v>9009</v>
@@ -10677,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -10695,13 +10725,13 @@
         <v>300</v>
       </c>
       <c r="T93" t="s">
+        <v>454</v>
+      </c>
+      <c r="U93" t="s">
         <v>455</v>
       </c>
-      <c r="U93" t="s">
+      <c r="W93" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="W93" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -10727,7 +10757,7 @@
     </row>
     <row r="94" spans="1:34">
       <c r="B94">
-        <v>9005</v>
+        <v>9003</v>
       </c>
       <c r="C94" t="s">
         <v>457</v>
@@ -10736,10 +10766,10 @@
         <v>458</v>
       </c>
       <c r="E94" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F94" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G94">
         <v>9009</v>
@@ -10757,7 +10787,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -10781,7 +10811,7 @@
         <v>460</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -10807,7 +10837,7 @@
     </row>
     <row r="95" spans="1:34">
       <c r="B95">
-        <v>9006</v>
+        <v>9004</v>
       </c>
       <c r="C95" t="s">
         <v>461</v>
@@ -10816,16 +10846,16 @@
         <v>462</v>
       </c>
       <c r="E95" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F95" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G95">
         <v>9009</v>
       </c>
       <c r="H95" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I95">
         <v>200</v>
@@ -10837,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -10861,7 +10891,7 @@
         <v>464</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -10887,7 +10917,7 @@
     </row>
     <row r="96" spans="1:34">
       <c r="B96">
-        <v>9007</v>
+        <v>9005</v>
       </c>
       <c r="C96" t="s">
         <v>465</v>
@@ -10896,16 +10926,16 @@
         <v>466</v>
       </c>
       <c r="E96" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F96" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G96">
         <v>9009</v>
       </c>
       <c r="H96" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I96">
         <v>200</v>
@@ -10917,7 +10947,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -10941,7 +10971,7 @@
         <v>468</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -10967,7 +10997,7 @@
     </row>
     <row r="97" spans="2:30">
       <c r="B97">
-        <v>9008</v>
+        <v>9006</v>
       </c>
       <c r="C97" t="s">
         <v>469</v>
@@ -10976,16 +11006,16 @@
         <v>470</v>
       </c>
       <c r="E97" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F97" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G97">
         <v>9009</v>
       </c>
       <c r="H97" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I97">
         <v>200</v>
@@ -10997,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -11021,7 +11051,7 @@
         <v>472</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -11047,7 +11077,7 @@
     </row>
     <row r="98" spans="2:30">
       <c r="B98">
-        <v>9009</v>
+        <v>9007</v>
       </c>
       <c r="C98" t="s">
         <v>473</v>
@@ -11056,10 +11086,16 @@
         <v>474</v>
       </c>
       <c r="E98" t="s">
-        <v>439</v>
+        <v>447</v>
+      </c>
+      <c r="F98" t="s">
+        <v>453</v>
+      </c>
+      <c r="G98">
+        <v>9009</v>
       </c>
       <c r="H98" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I98">
         <v>200</v>
@@ -11071,13 +11107,13 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -11095,7 +11131,7 @@
         <v>476</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -11121,7 +11157,7 @@
     </row>
     <row r="99" spans="2:30">
       <c r="B99">
-        <v>9010</v>
+        <v>9008</v>
       </c>
       <c r="C99" t="s">
         <v>477</v>
@@ -11130,10 +11166,10 @@
         <v>478</v>
       </c>
       <c r="E99" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F99" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G99">
         <v>9009</v>
@@ -11151,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -11174,6 +11210,9 @@
       <c r="U99" t="s">
         <v>480</v>
       </c>
+      <c r="W99" s="2" t="s">
+        <v>456</v>
+      </c>
       <c r="X99">
         <v>0</v>
       </c>
@@ -11198,7 +11237,7 @@
     </row>
     <row r="100" spans="2:30">
       <c r="B100">
-        <v>9011</v>
+        <v>9009</v>
       </c>
       <c r="C100" t="s">
         <v>481</v>
@@ -11207,16 +11246,10 @@
         <v>482</v>
       </c>
       <c r="E100" t="s">
-        <v>439</v>
-      </c>
-      <c r="F100" t="s">
-        <v>445</v>
-      </c>
-      <c r="G100">
-        <v>9009</v>
+        <v>447</v>
       </c>
       <c r="H100" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="I100">
         <v>200</v>
@@ -11228,13 +11261,13 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -11252,7 +11285,7 @@
         <v>484</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -11278,7 +11311,7 @@
     </row>
     <row r="101" spans="2:30">
       <c r="B101">
-        <v>10001</v>
+        <v>9010</v>
       </c>
       <c r="C101" t="s">
         <v>485</v>
@@ -11287,41 +11320,50 @@
         <v>486</v>
       </c>
       <c r="E101" t="s">
+        <v>447</v>
+      </c>
+      <c r="F101" t="s">
+        <v>453</v>
+      </c>
+      <c r="G101">
+        <v>9009</v>
+      </c>
+      <c r="H101" t="s">
+        <v>105</v>
+      </c>
+      <c r="I101">
+        <v>200</v>
+      </c>
+      <c r="J101">
+        <v>300</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>448</v>
+      </c>
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>1001</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>300</v>
+      </c>
+      <c r="T101" t="s">
         <v>487</v>
       </c>
-      <c r="H101" t="s">
-        <v>92</v>
-      </c>
-      <c r="I101">
-        <v>300</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" t="s">
-        <v>93</v>
-      </c>
-      <c r="M101" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="T101" t="s">
+      <c r="U101" t="s">
         <v>488</v>
       </c>
-      <c r="U101" t="s">
-        <v>489</v>
-      </c>
       <c r="X101">
         <v>0</v>
       </c>
@@ -11338,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="AC101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
@@ -11346,52 +11388,61 @@
     </row>
     <row r="102" spans="2:30">
       <c r="B102">
-        <v>11001</v>
+        <v>9011</v>
       </c>
       <c r="C102" t="s">
+        <v>489</v>
+      </c>
+      <c r="D102" t="s">
         <v>490</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>447</v>
+      </c>
+      <c r="F102" t="s">
+        <v>453</v>
+      </c>
+      <c r="G102">
+        <v>9009</v>
+      </c>
+      <c r="H102" t="s">
+        <v>110</v>
+      </c>
+      <c r="I102">
+        <v>200</v>
+      </c>
+      <c r="J102">
+        <v>300</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="s">
+        <v>448</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>1001</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>300</v>
+      </c>
+      <c r="T102" t="s">
         <v>491</v>
       </c>
-      <c r="E102" t="s">
+      <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="H102" t="s">
-        <v>92</v>
-      </c>
-      <c r="I102">
-        <v>300</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
-        <v>93</v>
-      </c>
-      <c r="M102" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="T102" t="s">
-        <v>493</v>
-      </c>
-      <c r="U102" t="s">
-        <v>494</v>
-      </c>
       <c r="W102" s="2" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="X102">
         <v>0</v>
@@ -11409,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="AC102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD102" t="b">
         <v>0</v>
@@ -11417,19 +11468,16 @@
     </row>
     <row r="103" spans="2:30">
       <c r="B103">
-        <v>11002</v>
+        <v>10001</v>
       </c>
       <c r="C103" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D103" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E103" t="s">
-        <v>492</v>
-      </c>
-      <c r="G103">
-        <v>11001</v>
+        <v>495</v>
       </c>
       <c r="H103" t="s">
         <v>92</v>
@@ -11459,171 +11507,313 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="U103" t="s">
+        <v>497</v>
+      </c>
+      <c r="X103">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:30">
+      <c r="B104">
+        <v>11001</v>
+      </c>
+      <c r="C104" t="s">
         <v>498</v>
-      </c>
-      <c r="X103">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" customFormat="1" spans="2:30">
-      <c r="B104">
-        <v>92005</v>
-      </c>
-      <c r="C104" t="s">
-        <v>156</v>
       </c>
       <c r="D104" t="s">
         <v>499</v>
       </c>
       <c r="E104" t="s">
+        <v>500</v>
+      </c>
+      <c r="H104" t="s">
+        <v>92</v>
+      </c>
+      <c r="I104">
+        <v>300</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>93</v>
+      </c>
+      <c r="M104" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="T104" t="s">
+        <v>501</v>
+      </c>
+      <c r="U104" t="s">
+        <v>502</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="X104">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:30">
+      <c r="B105">
+        <v>11002</v>
+      </c>
+      <c r="C105" t="s">
+        <v>504</v>
+      </c>
+      <c r="D105" t="s">
+        <v>505</v>
+      </c>
+      <c r="E105" t="s">
+        <v>500</v>
+      </c>
+      <c r="G105">
+        <v>11001</v>
+      </c>
+      <c r="H105" t="s">
+        <v>92</v>
+      </c>
+      <c r="I105">
+        <v>300</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>93</v>
+      </c>
+      <c r="M105" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="T105" t="s">
+        <v>501</v>
+      </c>
+      <c r="U105" t="s">
+        <v>506</v>
+      </c>
+      <c r="X105">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="2:30">
+      <c r="B106">
+        <v>92005</v>
+      </c>
+      <c r="C106" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106" t="s">
+        <v>507</v>
+      </c>
+      <c r="E106" t="s">
         <v>140</v>
       </c>
-      <c r="H104" t="s">
-        <v>500</v>
-      </c>
-      <c r="I104">
+      <c r="H106" t="s">
+        <v>508</v>
+      </c>
+      <c r="I106">
         <v>100</v>
       </c>
-      <c r="J104">
-        <v>300</v>
-      </c>
-      <c r="K104" t="b">
-        <v>0</v>
-      </c>
-      <c r="L104" t="s">
-        <v>501</v>
-      </c>
-      <c r="M104" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104">
+      <c r="J106">
+        <v>300</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="s">
+        <v>509</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106">
         <v>1001</v>
       </c>
-      <c r="R104">
+      <c r="R106">
         <v>100</v>
       </c>
-      <c r="S104" s="2"/>
-      <c r="T104" t="s">
+      <c r="S106" s="2"/>
+      <c r="T106" t="s">
         <v>158</v>
       </c>
-      <c r="U104" t="s">
+      <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W104" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="X104">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" customFormat="1" spans="2:30">
-      <c r="B105">
+      <c r="W106" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="2:30">
+      <c r="B107">
         <v>91012</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>135</v>
       </c>
-      <c r="D105" t="s">
-        <v>503</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="D107" t="s">
+        <v>511</v>
+      </c>
+      <c r="E107" t="s">
         <v>91</v>
       </c>
-      <c r="H105" t="s">
-        <v>500</v>
-      </c>
-      <c r="I105">
+      <c r="H107" t="s">
+        <v>508</v>
+      </c>
+      <c r="I107">
         <v>100</v>
       </c>
-      <c r="J105">
+      <c r="J107">
         <v>100</v>
       </c>
-      <c r="K105" t="b">
-        <v>0</v>
-      </c>
-      <c r="L105" t="s">
-        <v>501</v>
-      </c>
-      <c r="M105" t="b">
-        <v>0</v>
-      </c>
-      <c r="N105">
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
+        <v>509</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107">
         <v>1001</v>
       </c>
-      <c r="R105">
+      <c r="R107">
         <v>100</v>
       </c>
-      <c r="S105" s="2"/>
-      <c r="T105" t="s">
+      <c r="S107" s="2"/>
+      <c r="T107" t="s">
         <v>111</v>
       </c>
-      <c r="U105" t="s">
+      <c r="U107" t="s">
         <v>137</v>
       </c>
-      <c r="V105">
+      <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W105" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="X105">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="b">
+      <c r="W107" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11649,10 +11839,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H75 H77:H86 H90:H105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H34 H35:H40 H41:H77 H79:H88 H92:H107">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L75 L77:L87 L90:L105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L37 L38:L40 L41:L77 L79:L89 L92:L107">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12194,7 +12384,7 @@
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -12226,7 +12416,7 @@
         <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -12420,7 +12610,7 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -12740,10 +12930,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>752</v>
       </c>
       <c r="D33" t="s">
-        <v>211</v>
+        <v>753</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -12772,10 +12962,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>754</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>755</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -12804,10 +12994,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>756</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>757</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -12836,10 +13026,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>758</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>759</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -12868,10 +13058,10 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -12900,10 +13090,10 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D38" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -12932,10 +13122,10 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D39" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -12964,10 +13154,10 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D40" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -12996,10 +13186,10 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D41" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -13028,10 +13218,10 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D42" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -13060,10 +13250,10 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -13092,10 +13282,10 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -13124,10 +13314,10 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D45" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -13156,10 +13346,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="D46" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -13188,10 +13378,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="D47" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -13220,10 +13410,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="D48" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -13252,10 +13442,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="D49" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -13284,10 +13474,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="D50" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -13316,10 +13506,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="D51" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -13348,10 +13538,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="D52" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -13380,10 +13570,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>758</v>
+        <v>774</v>
       </c>
       <c r="D53" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -13412,10 +13602,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="D54" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -13444,10 +13634,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="D55" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -13476,10 +13666,10 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D56" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -13508,10 +13698,10 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -13540,10 +13730,10 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -13572,10 +13762,10 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -13604,10 +13794,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -13636,10 +13826,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -13668,10 +13858,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -13700,10 +13890,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="D63" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -13732,10 +13922,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D64" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -13764,10 +13954,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
       <c r="D65" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -13796,10 +13986,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D66" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -13828,10 +14018,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="D67" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -13860,10 +14050,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D68" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -13892,10 +14082,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -13924,10 +14114,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D70" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -13956,10 +14146,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D71" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -13988,10 +14178,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="D72" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -14020,10 +14210,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D73" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -14052,10 +14242,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="D74" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -14084,10 +14274,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D75" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -14116,10 +14306,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="D76" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -14148,10 +14338,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="D77" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -14180,10 +14370,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="D78" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -14212,10 +14402,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D79" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -14244,10 +14434,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="D80" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -14276,10 +14466,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="D81" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -14308,10 +14498,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D82" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -14340,10 +14530,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D83" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -14372,10 +14562,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D84" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -14404,10 +14594,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -14436,10 +14626,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D86" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -14468,10 +14658,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D87" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -14500,10 +14690,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D88" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -14532,10 +14722,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D89" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -14564,10 +14754,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D90" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -14596,10 +14786,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D91" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -14628,10 +14818,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D92" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14660,10 +14850,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="D93" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -14692,10 +14882,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D94" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -14724,10 +14914,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D95" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14756,10 +14946,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D96" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -14788,10 +14978,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D97" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -14820,10 +15010,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D98" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -14855,7 +15045,7 @@
         <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -14887,7 +15077,7 @@
         <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -14933,17 +15123,17 @@
         <v>91</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F2" t="s">
         <v>99</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>213</v>
@@ -14952,13 +15142,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14966,32 +15156,32 @@
         <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -14999,32 +15189,32 @@
         <v>191</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -15032,247 +15222,247 @@
         <v>212</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="E6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="F6" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="J9" s="6">
         <v>128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="J10" s="6">
         <v>256</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="J11" s="6">
         <v>512</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="J12" s="6">
         <v>1024</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="6" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="J13" s="6">
         <v>2048</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>93</v>
@@ -15280,7 +15470,7 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="6" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>100</v>
@@ -15288,34 +15478,34 @@
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="6" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="6" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="6" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -15356,34 +15546,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="F1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="G1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="H1" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="I1" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="J1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="K1" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="L1" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="M1" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15397,10 +15587,10 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="E2" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
@@ -15409,7 +15599,7 @@
         <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -15432,40 +15622,40 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" s="10" customFormat="1" spans="1:13">
@@ -15473,40 +15663,40 @@
         <v>41</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15514,13 +15704,13 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="F5">
         <v>2000</v>
@@ -15552,13 +15742,13 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="F6">
         <v>2000</v>
@@ -15590,13 +15780,13 @@
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="F7">
         <v>2000</v>
@@ -15628,13 +15818,13 @@
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D8" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -15707,31 +15897,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="E1" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="G1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="H1" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="I1" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="J1" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="K1" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="L1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15778,31 +15968,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15813,37 +16003,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D4" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="E4" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="F4" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="G4" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="H4" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="I4" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="J4" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="K4" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="L4" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M4" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15881,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15919,7 +16109,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15957,7 +16147,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -15995,7 +16185,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16033,7 +16223,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16071,7 +16261,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16109,7 +16299,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -16147,7 +16337,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -16185,7 +16375,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -16223,7 +16413,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -16261,7 +16451,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -16299,7 +16489,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -16337,7 +16527,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -16375,7 +16565,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -16409,13 +16599,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="E1" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="G1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -16444,17 +16634,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -16465,19 +16655,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="G4" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="H4" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -16657,7 +16847,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -16770,7 +16960,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16790,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -16810,7 +17000,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -16830,7 +17020,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -16850,7 +17040,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -16870,7 +17060,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -16886,7 +17076,7 @@
         <v>3001</v>
       </c>
       <c r="D26" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -16895,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -16930,28 +17120,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D1" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="E1" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="F1" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="G1" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="H1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="I1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="J1" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -16994,28 +17184,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -17026,31 +17216,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="D4" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="E4" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="F4" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="G4" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H4" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I4" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="J4" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="K4" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -17466,7 +17656,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -17501,7 +17691,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -17600,7 +17790,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -17635,7 +17825,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -17798,7 +17988,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -17833,7 +18023,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -17868,7 +18058,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -17911,22 +18101,22 @@
         <v>200101</v>
       </c>
       <c r="C31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="G31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -17943,22 +18133,22 @@
         <v>200201</v>
       </c>
       <c r="C32" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F32" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="G32" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="H32" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -18075,25 +18265,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="F1" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="G1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="H1" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="I1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="K1" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="L1" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -18137,23 +18327,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -18170,28 +18360,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="F4" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="G4" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="H4" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="I4" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="J4" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="K4" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="L4" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -18199,22 +18389,22 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="F5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H5" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="K5" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -18222,22 +18412,22 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="F6" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H6" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="K6" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -18245,22 +18435,22 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="F7" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H7" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="K7" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -18268,22 +18458,22 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F8" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="K8" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -18291,22 +18481,22 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="F9" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H9" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="K9" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -18314,22 +18504,22 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F10" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H10" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="K10" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -18337,22 +18527,22 @@
         <v>2001</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F11" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H11" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="J11" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -18360,22 +18550,22 @@
         <v>2002</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H12" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="J12" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -18403,10 +18593,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="D1" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -18423,7 +18613,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -18440,10 +18630,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="E3" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -18465,7 +18655,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -18479,7 +18669,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -18493,10 +18683,10 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -18504,12 +18694,12 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -18517,10 +18707,10 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="D10" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -18528,7 +18718,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -18536,10 +18726,10 @@
         <v>1006</v>
       </c>
       <c r="C12" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D12" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -18547,12 +18737,12 @@
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -18623,7 +18813,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -18645,7 +18835,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18682,7 +18872,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -18690,7 +18880,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="B10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -18698,7 +18888,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -18706,7 +18896,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="B12" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -18714,7 +18904,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -18722,7 +18912,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -18730,7 +18920,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -18738,7 +18928,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="798">
   <si>
     <t>##var</t>
   </si>
@@ -2292,7 +2292,13 @@
     <t>CanUnequip</t>
   </si>
   <si>
+    <t>DefaultItemId</t>
+  </si>
+  <si>
     <t>可脱光吗</t>
+  </si>
+  <si>
+    <t>默认穿戴物品id</t>
   </si>
   <si>
     <t>瘦芝麻柴</t>
@@ -11839,10 +11845,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H34 H35:H40 H41:H77 H79:H88 H92:H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L37 L38:L40 L41:L77 L79:L89 L92:L107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12384,7 +12390,7 @@
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -12416,7 +12422,7 @@
         <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -12610,7 +12616,7 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -12930,10 +12936,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D33" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -12962,10 +12968,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D34" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -12994,10 +13000,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D35" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -13026,10 +13032,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D36" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -13346,10 +13352,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D46" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -13378,10 +13384,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D47" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -13410,10 +13416,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D48" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -13442,10 +13448,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D49" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -13474,10 +13480,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D50" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -13506,10 +13512,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D51" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -13538,10 +13544,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D52" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -13570,10 +13576,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D53" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -13602,10 +13608,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D54" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -13634,10 +13640,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D55" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -13890,10 +13896,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D63" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -13954,10 +13960,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D65" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -14018,10 +14024,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D67" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -14178,10 +14184,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D72" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -14242,10 +14248,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D74" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -14306,10 +14312,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D76" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -14338,7 +14344,7 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D77" t="s">
         <v>406</v>
@@ -14370,7 +14376,7 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D78" t="s">
         <v>410</v>
@@ -14434,10 +14440,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D80" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -14466,10 +14472,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D81" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -18797,15 +18803,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -18815,8 +18822,11 @@
       <c r="C1" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -18826,8 +18836,11 @@
       <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -18835,18 +18848,24 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>749</v>
+      </c>
+      <c r="D3" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>91</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>140</v>
       </c>
@@ -18854,7 +18873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>191</v>
       </c>
@@ -18862,15 +18881,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>212</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>393</v>
       </c>
@@ -18878,7 +18900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
         <v>238</v>
       </c>
@@ -18886,23 +18908,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
         <v>271</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>316</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>447</v>
       </c>
@@ -18910,23 +18938,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>495</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>500</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>398</v>
       </c>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -15719,7 +15719,7 @@
         <v>629</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -15757,7 +15757,7 @@
         <v>629</v>
       </c>
       <c r="F6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -15795,7 +15795,7 @@
         <v>629</v>
       </c>
       <c r="F7">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G7">
         <v>3</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,6 @@
     <sheet name="BlindBoxVisual" sheetId="16" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
-    <sheet name="Item_SteamDef" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="751">
   <si>
     <t>##var</t>
   </si>
@@ -2299,147 +2298,6 @@
   </si>
   <si>
     <t>默认穿戴物品id</t>
-  </si>
-  <si>
-    <t>瘦芝麻柴</t>
-  </si>
-  <si>
-    <t>胡渣芝麻柴</t>
-  </si>
-  <si>
-    <t>Lucky</t>
-  </si>
-  <si>
-    <t>Male A</t>
-  </si>
-  <si>
-    <t>男性手臂A</t>
-  </si>
-  <si>
-    <t>Male B</t>
-  </si>
-  <si>
-    <t>男性手臂B</t>
-  </si>
-  <si>
-    <t>Male C</t>
-  </si>
-  <si>
-    <t>男性手臂C</t>
-  </si>
-  <si>
-    <t>Male D</t>
-  </si>
-  <si>
-    <t>男性手臂D</t>
-  </si>
-  <si>
-    <t>Full Tilt Like</t>
-  </si>
-  <si>
-    <t>Full Tilt风格</t>
-  </si>
-  <si>
-    <t>Hustler Like</t>
-  </si>
-  <si>
-    <t>Hustler风格</t>
-  </si>
-  <si>
-    <t>Les Ambassadeurs Like</t>
-  </si>
-  <si>
-    <t>Les Ambassadeurs风格</t>
-  </si>
-  <si>
-    <t>Maestral Like</t>
-  </si>
-  <si>
-    <t>Maestral风格</t>
-  </si>
-  <si>
-    <t>Mezcal Like</t>
-  </si>
-  <si>
-    <t>Mezcal风格</t>
-  </si>
-  <si>
-    <t>Poker Go Like</t>
-  </si>
-  <si>
-    <t>Poker Go风格</t>
-  </si>
-  <si>
-    <t>Pure Indigo</t>
-  </si>
-  <si>
-    <t>纯靛蓝</t>
-  </si>
-  <si>
-    <t>Pure Purple</t>
-  </si>
-  <si>
-    <t>纯紫色</t>
-  </si>
-  <si>
-    <t>Pure Teal</t>
-  </si>
-  <si>
-    <t>纯青色</t>
-  </si>
-  <si>
-    <t>The King of Hill Like</t>
-  </si>
-  <si>
-    <t>King of Hill风格</t>
-  </si>
-  <si>
-    <t>Highstakes Poker Like</t>
-  </si>
-  <si>
-    <t>Highstakes Poker风格</t>
-  </si>
-  <si>
-    <t>Part Poker Like</t>
-  </si>
-  <si>
-    <t>Part Poker风格</t>
-  </si>
-  <si>
-    <t>Poker King Like</t>
-  </si>
-  <si>
-    <t>Poker King风格</t>
-  </si>
-  <si>
-    <t>World Poker Tour Like</t>
-  </si>
-  <si>
-    <t>World Poker Tour风格</t>
-  </si>
-  <si>
-    <t>A158UUA</t>
-  </si>
-  <si>
-    <t>F91UU</t>
-  </si>
-  <si>
-    <t>Feng Shui Bracelet</t>
-  </si>
-  <si>
-    <t>Good Luck Bracelet</t>
-  </si>
-  <si>
-    <t>Relax Driver Black</t>
-  </si>
-  <si>
-    <t>黑色Relax Driver</t>
-  </si>
-  <si>
-    <t>Relax Driver Green</t>
-  </si>
-  <si>
-    <t>绿色Relax Driver</t>
   </si>
 </sst>
 </file>
@@ -3075,23 +2933,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -3105,7 +2957,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3689,11 +3547,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="2" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="9" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7" style="9" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="10.5833333333333" customWidth="1"/>
     <col min="26" max="26" width="11.6666666666667" customWidth="1"/>
@@ -3708,16 +3566,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="1"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3804,16 +3662,16 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="1"/>
       <c r="E2" t="s">
         <v>34</v>
       </c>
@@ -3899,93 +3757,93 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:34">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:34">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="1" t="s">
+      <c r="L3" s="10"/>
+      <c r="M3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="5"/>
-      <c r="T3" s="1" t="s">
+      <c r="S3" s="11"/>
+      <c r="T3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="5"/>
-      <c r="X3" s="1" t="s">
+      <c r="W3" s="11"/>
+      <c r="X3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Z3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AA3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AB3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AD3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AE3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AG3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AH3" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E4" t="s">
@@ -4604,10 +4462,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="7">
         <v>100</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="7">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -5322,7 +5180,7 @@
       <c r="R23" t="s">
         <v>162</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="S23" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T23" t="s">
@@ -5680,7 +5538,7 @@
       <c r="R28" t="s">
         <v>162</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="S28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T28" t="s">
@@ -5692,7 +5550,7 @@
       <c r="V28" t="s">
         <v>162</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X28">
@@ -5784,7 +5642,7 @@
       <c r="R29" t="s">
         <v>162</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="S29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T29" t="s">
@@ -5796,7 +5654,7 @@
       <c r="V29" t="s">
         <v>162</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X29">
@@ -7195,7 +7053,7 @@
       <c r="R49" t="s">
         <v>162</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="S49" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T49" t="s">
@@ -7278,7 +7136,7 @@
       <c r="R50" t="s">
         <v>162</v>
       </c>
-      <c r="S50" s="2" t="s">
+      <c r="S50" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T50" t="s">
@@ -7361,7 +7219,7 @@
       <c r="R51" t="s">
         <v>162</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="S51" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T51" t="s">
@@ -7444,7 +7302,7 @@
       <c r="R52" t="s">
         <v>162</v>
       </c>
-      <c r="S52" s="2" t="s">
+      <c r="S52" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T52" t="s">
@@ -7527,7 +7385,7 @@
       <c r="R53" t="s">
         <v>162</v>
       </c>
-      <c r="S53" s="2" t="s">
+      <c r="S53" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T53" t="s">
@@ -7610,7 +7468,7 @@
       <c r="R54" t="s">
         <v>162</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="S54" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T54" t="s">
@@ -7693,7 +7551,7 @@
       <c r="R55" t="s">
         <v>162</v>
       </c>
-      <c r="S55" s="2" t="s">
+      <c r="S55" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T55" t="s">
@@ -7776,7 +7634,7 @@
       <c r="R56" t="s">
         <v>162</v>
       </c>
-      <c r="S56" s="2" t="s">
+      <c r="S56" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T56" t="s">
@@ -7859,7 +7717,7 @@
       <c r="R57" t="s">
         <v>162</v>
       </c>
-      <c r="S57" s="2" t="s">
+      <c r="S57" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T57" t="s">
@@ -7942,7 +7800,7 @@
       <c r="R58" t="s">
         <v>162</v>
       </c>
-      <c r="S58" s="2" t="s">
+      <c r="S58" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T58" t="s">
@@ -8025,7 +7883,7 @@
       <c r="R59" t="s">
         <v>162</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="S59" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T59" t="s">
@@ -8273,7 +8131,7 @@
       <c r="E63" t="s">
         <v>316</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="H63" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I63">
@@ -8341,7 +8199,7 @@
       <c r="E64" t="s">
         <v>316</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H64" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8409,7 +8267,7 @@
       <c r="E65" t="s">
         <v>316</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8584,7 +8442,7 @@
       <c r="R67" t="s">
         <v>162</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="S67" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T67" t="s">
@@ -8667,7 +8525,7 @@
       <c r="R68" t="s">
         <v>162</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="S68" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T68" t="s">
@@ -8750,7 +8608,7 @@
       <c r="R69" t="s">
         <v>162</v>
       </c>
-      <c r="S69" s="2" t="s">
+      <c r="S69" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T69" t="s">
@@ -8833,7 +8691,7 @@
       <c r="R70" t="s">
         <v>162</v>
       </c>
-      <c r="S70" s="2" t="s">
+      <c r="S70" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T70" t="s">
@@ -8916,7 +8774,7 @@
       <c r="R71" t="s">
         <v>162</v>
       </c>
-      <c r="S71" s="2" t="s">
+      <c r="S71" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T71" t="s">
@@ -8999,7 +8857,7 @@
       <c r="R72" t="s">
         <v>162</v>
       </c>
-      <c r="S72" s="2" t="s">
+      <c r="S72" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T72" t="s">
@@ -9082,7 +8940,7 @@
       <c r="R73" t="s">
         <v>162</v>
       </c>
-      <c r="S73" s="2" t="s">
+      <c r="S73" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T73" t="s">
@@ -9165,7 +9023,7 @@
       <c r="R74" t="s">
         <v>162</v>
       </c>
-      <c r="S74" s="2" t="s">
+      <c r="S74" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T74" t="s">
@@ -9248,7 +9106,7 @@
       <c r="R75" t="s">
         <v>162</v>
       </c>
-      <c r="S75" s="2" t="s">
+      <c r="S75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T75" t="s">
@@ -9331,7 +9189,7 @@
       <c r="R76" t="s">
         <v>162</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="S76" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T76" t="s">
@@ -9485,7 +9343,7 @@
       <c r="R78" t="s">
         <v>162</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="S78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T78" t="s">
@@ -9497,7 +9355,7 @@
       <c r="V78" t="s">
         <v>162</v>
       </c>
-      <c r="W78" s="2" t="s">
+      <c r="W78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X78">
@@ -9586,7 +9444,7 @@
       <c r="R79" t="s">
         <v>162</v>
       </c>
-      <c r="S79" s="2" t="s">
+      <c r="S79" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T79" t="s">
@@ -9636,7 +9494,7 @@
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" s="9" t="s">
+      <c r="H80" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I80">
@@ -9669,7 +9527,7 @@
       <c r="R80" t="s">
         <v>162</v>
       </c>
-      <c r="S80" s="2" t="s">
+      <c r="S80" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T80" t="s">
@@ -9752,7 +9610,7 @@
       <c r="R81" t="s">
         <v>162</v>
       </c>
-      <c r="S81" s="2" t="s">
+      <c r="S81" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T81" t="s">
@@ -9835,7 +9693,7 @@
       <c r="R82" t="s">
         <v>162</v>
       </c>
-      <c r="S82" s="2" t="s">
+      <c r="S82" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T82" t="s">
@@ -9918,7 +9776,7 @@
       <c r="R83" t="s">
         <v>162</v>
       </c>
-      <c r="S83" s="2" t="s">
+      <c r="S83" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T83" t="s">
@@ -9968,7 +9826,7 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" s="9" t="s">
+      <c r="H84" s="7" t="s">
         <v>141</v>
       </c>
       <c r="I84">
@@ -10001,7 +9859,7 @@
       <c r="R84" t="s">
         <v>162</v>
       </c>
-      <c r="S84" s="2" t="s">
+      <c r="S84" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T84" t="s">
@@ -10084,7 +9942,7 @@
       <c r="R85" t="s">
         <v>162</v>
       </c>
-      <c r="S85" s="2" t="s">
+      <c r="S85" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T85" t="s">
@@ -10167,7 +10025,7 @@
       <c r="R86" t="s">
         <v>162</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="S86" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T86" t="s">
@@ -10457,7 +10315,7 @@
       <c r="R90" t="s">
         <v>162</v>
       </c>
-      <c r="S90" s="2" t="s">
+      <c r="S90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T90" t="s">
@@ -10469,7 +10327,7 @@
       <c r="V90" t="s">
         <v>162</v>
       </c>
-      <c r="W90" s="2" t="s">
+      <c r="W90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X90">
@@ -10561,7 +10419,7 @@
       <c r="R91" t="s">
         <v>162</v>
       </c>
-      <c r="S91" s="2" t="s">
+      <c r="S91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T91" t="s">
@@ -10573,7 +10431,7 @@
       <c r="V91" t="s">
         <v>162</v>
       </c>
-      <c r="W91" s="2" t="s">
+      <c r="W91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X91">
@@ -10736,7 +10594,7 @@
       <c r="U93" t="s">
         <v>455</v>
       </c>
-      <c r="W93" s="2" t="s">
+      <c r="W93" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X93">
@@ -10816,7 +10674,7 @@
       <c r="U94" t="s">
         <v>460</v>
       </c>
-      <c r="W94" s="2" t="s">
+      <c r="W94" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X94">
@@ -10896,7 +10754,7 @@
       <c r="U95" t="s">
         <v>464</v>
       </c>
-      <c r="W95" s="2" t="s">
+      <c r="W95" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X95">
@@ -10976,7 +10834,7 @@
       <c r="U96" t="s">
         <v>468</v>
       </c>
-      <c r="W96" s="2" t="s">
+      <c r="W96" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X96">
@@ -11056,7 +10914,7 @@
       <c r="U97" t="s">
         <v>472</v>
       </c>
-      <c r="W97" s="2" t="s">
+      <c r="W97" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X97">
@@ -11136,7 +10994,7 @@
       <c r="U98" t="s">
         <v>476</v>
       </c>
-      <c r="W98" s="2" t="s">
+      <c r="W98" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X98">
@@ -11216,7 +11074,7 @@
       <c r="U99" t="s">
         <v>480</v>
       </c>
-      <c r="W99" s="2" t="s">
+      <c r="W99" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X99">
@@ -11290,7 +11148,7 @@
       <c r="U100" t="s">
         <v>484</v>
       </c>
-      <c r="W100" s="2" t="s">
+      <c r="W100" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X100">
@@ -11447,7 +11305,7 @@
       <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="2" t="s">
+      <c r="W102" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X102">
@@ -11586,7 +11444,7 @@
       <c r="U104" t="s">
         <v>502</v>
       </c>
-      <c r="W104" s="2" t="s">
+      <c r="W104" s="9" t="s">
         <v>503</v>
       </c>
       <c r="X104">
@@ -11719,14 +11577,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="2"/>
+      <c r="S106" s="9"/>
       <c r="T106" t="s">
         <v>158</v>
       </c>
       <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W106" s="2" t="s">
+      <c r="W106" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X106">
@@ -11788,7 +11646,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="2"/>
+      <c r="S107" s="9"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -11798,7 +11656,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="2" t="s">
+      <c r="W107" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X107">
@@ -11857,3262 +11715,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
-  <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="6.25" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="10.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="11.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="7.83333333333333" customWidth="1"/>
-    <col min="9" max="9" width="10.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="7.41666666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="7.41666666666667" customWidth="1"/>
-    <col min="13" max="13" width="5.41666666666667" customWidth="1"/>
-    <col min="14" max="14" width="5.66666666666667" customWidth="1"/>
-    <col min="15" max="15" width="5.91666666666667" customWidth="1"/>
-    <col min="16" max="16" width="3.25" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M4" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" t="s">
-        <v>87</v>
-      </c>
-      <c r="O4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8">
-        <v>1004</v>
-      </c>
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11">
-        <v>1007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12">
-        <v>1008</v>
-      </c>
-      <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13">
-        <v>1009</v>
-      </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="B14">
-        <v>1010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="B15">
-        <v>1011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" t="s">
-        <v>751</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="B16">
-        <v>1012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" t="s">
-        <v>752</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="B18">
-        <v>2001</v>
-      </c>
-      <c r="C18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="B19">
-        <v>2002</v>
-      </c>
-      <c r="C19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="B20">
-        <v>2003</v>
-      </c>
-      <c r="C20" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="B21">
-        <v>2004</v>
-      </c>
-      <c r="C21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="B22">
-        <v>2005</v>
-      </c>
-      <c r="C22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="B23">
-        <v>2006</v>
-      </c>
-      <c r="C23" t="s">
-        <v>753</v>
-      </c>
-      <c r="D23" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="B24">
-        <v>2007</v>
-      </c>
-      <c r="C24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="B25">
-        <v>2008</v>
-      </c>
-      <c r="C25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26">
-        <v>2009</v>
-      </c>
-      <c r="C26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="B27">
-        <v>2010</v>
-      </c>
-      <c r="C27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" t="s">
-        <v>178</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="B28">
-        <v>3001</v>
-      </c>
-      <c r="C28" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" t="s">
-        <v>190</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="B29">
-        <v>3002</v>
-      </c>
-      <c r="C29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="B30">
-        <v>3003</v>
-      </c>
-      <c r="C30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31">
-        <v>3004</v>
-      </c>
-      <c r="C31" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="B32">
-        <v>3005</v>
-      </c>
-      <c r="C32" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" t="s">
-        <v>207</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33">
-        <v>4001</v>
-      </c>
-      <c r="C33" t="s">
-        <v>754</v>
-      </c>
-      <c r="D33" t="s">
-        <v>755</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" t="s">
-        <v>96</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34">
-        <v>4002</v>
-      </c>
-      <c r="C34" t="s">
-        <v>756</v>
-      </c>
-      <c r="D34" t="s">
-        <v>757</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35">
-        <v>4003</v>
-      </c>
-      <c r="C35" t="s">
-        <v>758</v>
-      </c>
-      <c r="D35" t="s">
-        <v>759</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36">
-        <v>4004</v>
-      </c>
-      <c r="C36" t="s">
-        <v>760</v>
-      </c>
-      <c r="D36" t="s">
-        <v>761</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37">
-        <v>5001</v>
-      </c>
-      <c r="C37" t="s">
-        <v>236</v>
-      </c>
-      <c r="D37" t="s">
-        <v>237</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
-      </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38">
-        <v>5002</v>
-      </c>
-      <c r="C38" t="s">
-        <v>241</v>
-      </c>
-      <c r="D38" t="s">
-        <v>242</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39">
-        <v>5003</v>
-      </c>
-      <c r="C39" t="s">
-        <v>245</v>
-      </c>
-      <c r="D39" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40">
-        <v>5004</v>
-      </c>
-      <c r="C40" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" t="s">
-        <v>250</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41">
-        <v>5005</v>
-      </c>
-      <c r="C41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D41" t="s">
-        <v>254</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42">
-        <v>5006</v>
-      </c>
-      <c r="C42" t="s">
-        <v>257</v>
-      </c>
-      <c r="D42" t="s">
-        <v>258</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="B43">
-        <v>5007</v>
-      </c>
-      <c r="C43" t="s">
-        <v>261</v>
-      </c>
-      <c r="D43" t="s">
-        <v>262</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="B44">
-        <v>5008</v>
-      </c>
-      <c r="C44" t="s">
-        <v>265</v>
-      </c>
-      <c r="D44" t="s">
-        <v>266</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="B45">
-        <v>6001</v>
-      </c>
-      <c r="C45" t="s">
-        <v>269</v>
-      </c>
-      <c r="D45" t="s">
-        <v>270</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45" t="s">
-        <v>96</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="B46">
-        <v>6002</v>
-      </c>
-      <c r="C46" t="s">
-        <v>762</v>
-      </c>
-      <c r="D46" t="s">
-        <v>763</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="B47">
-        <v>6003</v>
-      </c>
-      <c r="C47" t="s">
-        <v>764</v>
-      </c>
-      <c r="D47" t="s">
-        <v>765</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" t="s">
-        <v>96</v>
-      </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="B48">
-        <v>6004</v>
-      </c>
-      <c r="C48" t="s">
-        <v>766</v>
-      </c>
-      <c r="D48" t="s">
-        <v>767</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="s">
-        <v>96</v>
-      </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49">
-        <v>6005</v>
-      </c>
-      <c r="C49" t="s">
-        <v>768</v>
-      </c>
-      <c r="D49" t="s">
-        <v>769</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="s">
-        <v>96</v>
-      </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50">
-        <v>6006</v>
-      </c>
-      <c r="C50" t="s">
-        <v>770</v>
-      </c>
-      <c r="D50" t="s">
-        <v>771</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51">
-        <v>6007</v>
-      </c>
-      <c r="C51" t="s">
-        <v>772</v>
-      </c>
-      <c r="D51" t="s">
-        <v>773</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="s">
-        <v>96</v>
-      </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52">
-        <v>6008</v>
-      </c>
-      <c r="C52" t="s">
-        <v>774</v>
-      </c>
-      <c r="D52" t="s">
-        <v>775</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53">
-        <v>6009</v>
-      </c>
-      <c r="C53" t="s">
-        <v>776</v>
-      </c>
-      <c r="D53" t="s">
-        <v>777</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53" t="s">
-        <v>96</v>
-      </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54">
-        <v>6010</v>
-      </c>
-      <c r="C54" t="s">
-        <v>778</v>
-      </c>
-      <c r="D54" t="s">
-        <v>779</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="s">
-        <v>96</v>
-      </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55">
-        <v>6011</v>
-      </c>
-      <c r="C55" t="s">
-        <v>780</v>
-      </c>
-      <c r="D55" t="s">
-        <v>781</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56">
-        <v>7001</v>
-      </c>
-      <c r="C56" t="s">
-        <v>314</v>
-      </c>
-      <c r="D56" t="s">
-        <v>315</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56" t="s">
-        <v>96</v>
-      </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57">
-        <v>7002</v>
-      </c>
-      <c r="C57" t="s">
-        <v>319</v>
-      </c>
-      <c r="D57" t="s">
-        <v>320</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57" t="s">
-        <v>96</v>
-      </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58">
-        <v>7003</v>
-      </c>
-      <c r="C58" t="s">
-        <v>323</v>
-      </c>
-      <c r="D58" t="s">
-        <v>324</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58" t="s">
-        <v>96</v>
-      </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59">
-        <v>7004</v>
-      </c>
-      <c r="C59" t="s">
-        <v>327</v>
-      </c>
-      <c r="D59" t="s">
-        <v>328</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59" t="s">
-        <v>96</v>
-      </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60">
-        <v>7005</v>
-      </c>
-      <c r="C60" t="s">
-        <v>331</v>
-      </c>
-      <c r="D60" t="s">
-        <v>332</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61">
-        <v>7006</v>
-      </c>
-      <c r="C61" t="s">
-        <v>335</v>
-      </c>
-      <c r="D61" t="s">
-        <v>336</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62">
-        <v>7007</v>
-      </c>
-      <c r="C62" t="s">
-        <v>339</v>
-      </c>
-      <c r="D62" t="s">
-        <v>340</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62" t="s">
-        <v>96</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63">
-        <v>7008</v>
-      </c>
-      <c r="C63" t="s">
-        <v>782</v>
-      </c>
-      <c r="D63" t="s">
-        <v>783</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>96</v>
-      </c>
-      <c r="G63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64">
-        <v>7009</v>
-      </c>
-      <c r="C64" t="s">
-        <v>347</v>
-      </c>
-      <c r="D64" t="s">
-        <v>348</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64" t="s">
-        <v>96</v>
-      </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65">
-        <v>7010</v>
-      </c>
-      <c r="C65" t="s">
-        <v>784</v>
-      </c>
-      <c r="D65" t="s">
-        <v>785</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65" t="s">
-        <v>96</v>
-      </c>
-      <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66">
-        <v>7011</v>
-      </c>
-      <c r="C66" t="s">
-        <v>355</v>
-      </c>
-      <c r="D66" t="s">
-        <v>356</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66" t="s">
-        <v>96</v>
-      </c>
-      <c r="G66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67">
-        <v>7012</v>
-      </c>
-      <c r="C67" t="s">
-        <v>786</v>
-      </c>
-      <c r="D67" t="s">
-        <v>787</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67" t="s">
-        <v>96</v>
-      </c>
-      <c r="G67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67" t="b">
-        <v>0</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68">
-        <v>7013</v>
-      </c>
-      <c r="C68" t="s">
-        <v>363</v>
-      </c>
-      <c r="D68" t="s">
-        <v>364</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
-        <v>96</v>
-      </c>
-      <c r="G68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" t="b">
-        <v>0</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69">
-        <v>7014</v>
-      </c>
-      <c r="C69" t="s">
-        <v>367</v>
-      </c>
-      <c r="D69" t="s">
-        <v>368</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69" t="s">
-        <v>96</v>
-      </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70">
-        <v>7015</v>
-      </c>
-      <c r="C70" t="s">
-        <v>371</v>
-      </c>
-      <c r="D70" t="s">
-        <v>372</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70" t="s">
-        <v>96</v>
-      </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71">
-        <v>7016</v>
-      </c>
-      <c r="C71" t="s">
-        <v>375</v>
-      </c>
-      <c r="D71" t="s">
-        <v>376</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71" t="s">
-        <v>96</v>
-      </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72">
-        <v>7017</v>
-      </c>
-      <c r="C72" t="s">
-        <v>788</v>
-      </c>
-      <c r="D72" t="s">
-        <v>789</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72" t="s">
-        <v>96</v>
-      </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73">
-        <v>7018</v>
-      </c>
-      <c r="C73" t="s">
-        <v>383</v>
-      </c>
-      <c r="D73" t="s">
-        <v>384</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73" t="s">
-        <v>96</v>
-      </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="b">
-        <v>0</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74">
-        <v>8001</v>
-      </c>
-      <c r="C74" t="s">
-        <v>790</v>
-      </c>
-      <c r="D74" t="s">
-        <v>790</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" t="s">
-        <v>96</v>
-      </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="b">
-        <v>0</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75">
-        <v>8002</v>
-      </c>
-      <c r="C75" t="s">
-        <v>396</v>
-      </c>
-      <c r="D75" t="s">
-        <v>397</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75" t="s">
-        <v>96</v>
-      </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" t="b">
-        <v>0</v>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76">
-        <v>8003</v>
-      </c>
-      <c r="C76" t="s">
-        <v>791</v>
-      </c>
-      <c r="D76" t="s">
-        <v>791</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76" t="s">
-        <v>96</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77">
-        <v>8004</v>
-      </c>
-      <c r="C77" t="s">
-        <v>792</v>
-      </c>
-      <c r="D77" t="s">
-        <v>406</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" t="s">
-        <v>96</v>
-      </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78">
-        <v>8005</v>
-      </c>
-      <c r="C78" t="s">
-        <v>793</v>
-      </c>
-      <c r="D78" t="s">
-        <v>410</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78" t="s">
-        <v>96</v>
-      </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79">
-        <v>8006</v>
-      </c>
-      <c r="C79" t="s">
-        <v>413</v>
-      </c>
-      <c r="D79" t="s">
-        <v>414</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79" t="s">
-        <v>96</v>
-      </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80">
-        <v>8007</v>
-      </c>
-      <c r="C80" t="s">
-        <v>794</v>
-      </c>
-      <c r="D80" t="s">
-        <v>795</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80" t="s">
-        <v>96</v>
-      </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81">
-        <v>8008</v>
-      </c>
-      <c r="C81" t="s">
-        <v>796</v>
-      </c>
-      <c r="D81" t="s">
-        <v>797</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81" t="s">
-        <v>96</v>
-      </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82">
-        <v>8009</v>
-      </c>
-      <c r="C82" t="s">
-        <v>425</v>
-      </c>
-      <c r="D82" t="s">
-        <v>426</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" t="s">
-        <v>96</v>
-      </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83">
-        <v>8010</v>
-      </c>
-      <c r="C83" t="s">
-        <v>429</v>
-      </c>
-      <c r="D83" t="s">
-        <v>430</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83" t="s">
-        <v>96</v>
-      </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84">
-        <v>8011</v>
-      </c>
-      <c r="C84" t="s">
-        <v>433</v>
-      </c>
-      <c r="D84" t="s">
-        <v>434</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84" t="s">
-        <v>96</v>
-      </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85">
-        <v>9001</v>
-      </c>
-      <c r="C85" t="s">
-        <v>445</v>
-      </c>
-      <c r="D85" t="s">
-        <v>446</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85" t="s">
-        <v>96</v>
-      </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="b">
-        <v>1</v>
-      </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86">
-        <v>9002</v>
-      </c>
-      <c r="C86" t="s">
-        <v>451</v>
-      </c>
-      <c r="D86" t="s">
-        <v>452</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="s">
-        <v>96</v>
-      </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="b">
-        <v>1</v>
-      </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87">
-        <v>9003</v>
-      </c>
-      <c r="C87" t="s">
-        <v>457</v>
-      </c>
-      <c r="D87" t="s">
-        <v>458</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" t="s">
-        <v>96</v>
-      </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="b">
-        <v>1</v>
-      </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88">
-        <v>9004</v>
-      </c>
-      <c r="C88" t="s">
-        <v>461</v>
-      </c>
-      <c r="D88" t="s">
-        <v>462</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88" t="s">
-        <v>96</v>
-      </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="b">
-        <v>1</v>
-      </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89">
-        <v>9005</v>
-      </c>
-      <c r="C89" t="s">
-        <v>465</v>
-      </c>
-      <c r="D89" t="s">
-        <v>466</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" t="s">
-        <v>96</v>
-      </c>
-      <c r="G89" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" t="b">
-        <v>1</v>
-      </c>
-      <c r="K89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90">
-        <v>9006</v>
-      </c>
-      <c r="C90" t="s">
-        <v>469</v>
-      </c>
-      <c r="D90" t="s">
-        <v>470</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90" t="s">
-        <v>96</v>
-      </c>
-      <c r="G90" t="b">
-        <v>1</v>
-      </c>
-      <c r="H90" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="b">
-        <v>1</v>
-      </c>
-      <c r="K90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91">
-        <v>9007</v>
-      </c>
-      <c r="C91" t="s">
-        <v>473</v>
-      </c>
-      <c r="D91" t="s">
-        <v>474</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91" t="s">
-        <v>96</v>
-      </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="b">
-        <v>1</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92">
-        <v>9008</v>
-      </c>
-      <c r="C92" t="s">
-        <v>477</v>
-      </c>
-      <c r="D92" t="s">
-        <v>478</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92" t="s">
-        <v>96</v>
-      </c>
-      <c r="G92" t="b">
-        <v>1</v>
-      </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>1</v>
-      </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93">
-        <v>9009</v>
-      </c>
-      <c r="C93" t="s">
-        <v>481</v>
-      </c>
-      <c r="D93" t="s">
-        <v>482</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93" t="s">
-        <v>96</v>
-      </c>
-      <c r="G93" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" t="b">
-        <v>0</v>
-      </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94">
-        <v>9010</v>
-      </c>
-      <c r="C94" t="s">
-        <v>485</v>
-      </c>
-      <c r="D94" t="s">
-        <v>486</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94" t="s">
-        <v>96</v>
-      </c>
-      <c r="G94" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" t="b">
-        <v>0</v>
-      </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="b">
-        <v>1</v>
-      </c>
-      <c r="K94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
-      <c r="B95">
-        <v>9011</v>
-      </c>
-      <c r="C95" t="s">
-        <v>489</v>
-      </c>
-      <c r="D95" t="s">
-        <v>490</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95" t="s">
-        <v>96</v>
-      </c>
-      <c r="G95" t="b">
-        <v>1</v>
-      </c>
-      <c r="H95" t="b">
-        <v>0</v>
-      </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="b">
-        <v>1</v>
-      </c>
-      <c r="K95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96">
-        <v>10001</v>
-      </c>
-      <c r="C96" t="s">
-        <v>493</v>
-      </c>
-      <c r="D96" t="s">
-        <v>494</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96" t="s">
-        <v>96</v>
-      </c>
-      <c r="G96" t="b">
-        <v>1</v>
-      </c>
-      <c r="H96" t="b">
-        <v>0</v>
-      </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97">
-        <v>11001</v>
-      </c>
-      <c r="C97" t="s">
-        <v>498</v>
-      </c>
-      <c r="D97" t="s">
-        <v>499</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97" t="s">
-        <v>96</v>
-      </c>
-      <c r="G97" t="b">
-        <v>1</v>
-      </c>
-      <c r="H97" t="b">
-        <v>0</v>
-      </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98">
-        <v>11002</v>
-      </c>
-      <c r="C98" t="s">
-        <v>504</v>
-      </c>
-      <c r="D98" t="s">
-        <v>505</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98" t="s">
-        <v>96</v>
-      </c>
-      <c r="G98" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
-      <c r="B99">
-        <v>92005</v>
-      </c>
-      <c r="C99" t="s">
-        <v>156</v>
-      </c>
-      <c r="D99" t="s">
-        <v>507</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99" t="s">
-        <v>96</v>
-      </c>
-      <c r="G99" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" t="b">
-        <v>0</v>
-      </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
-      <c r="B100">
-        <v>91012</v>
-      </c>
-      <c r="C100" t="s">
-        <v>135</v>
-      </c>
-      <c r="D100" t="s">
-        <v>511</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100" t="s">
-        <v>96</v>
-      </c>
-      <c r="G100" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" t="b">
-        <v>0</v>
-      </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -15125,10 +11727,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -15137,130 +11739,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="6">
-        <v>1</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="3" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="3">
         <v>2</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="3" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>4</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="3" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="3">
         <v>8</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="3" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -15269,248 +11871,248 @@
       <c r="F6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="3">
         <v>16</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="3" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="3">
         <v>32</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="3" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="3">
         <v>64</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="3" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="3">
         <v>128</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="3" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="3">
         <v>256</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="3" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="3">
         <v>512</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="3" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="3">
         <v>1024</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="3" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="3">
         <v>2048</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="3" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>591</v>
       </c>
     </row>
@@ -15542,7 +12144,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -15583,7 +12185,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -15623,85 +12225,85 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="4" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="4" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" spans="1:13">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="8" customFormat="1" spans="1:13">
+      <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>626</v>
       </c>
     </row>
@@ -15712,10 +12314,10 @@
       <c r="C5" t="s">
         <v>627</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>629</v>
       </c>
       <c r="F5">
@@ -15750,10 +12352,10 @@
       <c r="C6" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>629</v>
       </c>
       <c r="F6">
@@ -15788,10 +12390,10 @@
       <c r="C7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>629</v>
       </c>
       <c r="F7">
@@ -15829,7 +12431,7 @@
       <c r="D8" t="s">
         <v>634</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>635</v>
       </c>
       <c r="F8">
@@ -15858,13 +12460,13 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="E15" s="6"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="E16" s="6"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="6"/>
+      <c r="E17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15893,7 +12495,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -15931,7 +12533,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -15968,41 +12570,41 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="4" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="4" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
@@ -16590,7 +13192,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="5" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16634,22 +13236,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="4" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="4" t="s">
         <v>623</v>
       </c>
     </row>
@@ -16689,7 +13291,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -16710,7 +13312,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -16731,7 +13333,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -16749,10 +13351,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>900</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -16770,10 +13372,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>180</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -16794,7 +13396,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -16806,7 +13408,7 @@
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -16824,7 +13426,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16845,7 +13447,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -16869,7 +13471,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -16890,7 +13492,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -16911,7 +13513,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -16932,7 +13534,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -16944,7 +13546,7 @@
       <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -17182,35 +13784,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="4" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>693</v>
       </c>
     </row>
@@ -18258,13 +14860,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -18293,13 +14895,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -18327,28 +14929,28 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:12">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>712</v>
       </c>
     </row>
@@ -18417,10 +15019,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -18440,10 +15042,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -18463,10 +15065,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -18486,10 +15088,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
@@ -18509,10 +15111,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -18532,10 +15134,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>508</v>
       </c>
       <c r="E11" t="s">
@@ -18555,10 +15157,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
@@ -18592,10 +15194,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -18609,10 +15211,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -18626,10 +15228,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
@@ -18757,42 +15359,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="6"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="6"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18813,7 +15415,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -18827,13 +15429,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -18841,13 +15443,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>749</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="703" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="BlindBoxVisual" sheetId="16" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
+    <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="818">
   <si>
     <t>##var</t>
   </si>
@@ -2298,6 +2299,207 @@
   </si>
   <si>
     <t>默认穿戴物品id</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>TooltipKey</t>
+  </si>
+  <si>
+    <t>BannerTexturePath</t>
+  </si>
+  <si>
+    <t>BadgeTexturePath</t>
+  </si>
+  <si>
+    <t>PreClaimUrl</t>
+  </si>
+  <si>
+    <t>PostClaimUrl</t>
+  </si>
+  <si>
+    <t>OpenCheckType</t>
+  </si>
+  <si>
+    <t>RewardType</t>
+  </si>
+  <si>
+    <t>RewardItemId</t>
+  </si>
+  <si>
+    <t>RewardChips</t>
+  </si>
+  <si>
+    <t>SequentialPackId</t>
+  </si>
+  <si>
+    <t>SteamPromoItemDefId</t>
+  </si>
+  <si>
+    <t>ClaimLimit</t>
+  </si>
+  <si>
+    <t>ELinkTreeOpenCheckType</t>
+  </si>
+  <si>
+    <t>ELinkTreeRewardType</t>
+  </si>
+  <si>
+    <t>稳定机器名，代码和存档/Steam 记录用，不要随意改名</t>
+  </si>
+  <si>
+    <t>显示顺序，数字越小越靠前</t>
+  </si>
+  <si>
+    <t>是否显示这个入口</t>
+  </si>
+  <si>
+    <t>Tooltip 本地化 key；当前也可直接作为显示名来源</t>
+  </si>
+  <si>
+    <t>Banner 图片路径；可填 res:// 或项目相对路径</t>
+  </si>
+  <si>
+    <t>角标图片路径；空则使用默认礼物角标</t>
+  </si>
+  <si>
+    <t>领奖前点击打开的外部链接，可带 UTM</t>
+  </si>
+  <si>
+    <t>领奖后点击打开的外部链接，可带 UTM</t>
+  </si>
+  <si>
+    <t>打开校验方式；当前合法值见 ELinkTreeOpenCheckType</t>
+  </si>
+  <si>
+    <t>奖励类型；当前合法值见 ELinkTreeRewardType</t>
+  </si>
+  <si>
+    <t>RewardType=FixedItem 时发放的 Item.Id；不用填 0</t>
+  </si>
+  <si>
+    <t>RewardType=FixedChips 时发放的固定筹码数；不用填 0</t>
+  </si>
+  <si>
+    <t>RewardType=SequentialPack 时关联的顺序礼包 ID；当前不用填 0</t>
+  </si>
+  <si>
+    <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
+  </si>
+  <si>
+    <t>每个玩家最多领取次数；常规填 1</t>
+  </si>
+  <si>
+    <t>入口ID</t>
+  </si>
+  <si>
+    <t>机器名</t>
+  </si>
+  <si>
+    <t>排序</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>提示文本Key</t>
+  </si>
+  <si>
+    <t>Banner图片</t>
+  </si>
+  <si>
+    <t>角标图片</t>
+  </si>
+  <si>
+    <t>领奖前链接</t>
+  </si>
+  <si>
+    <t>领奖后链接</t>
+  </si>
+  <si>
+    <t>打开校验</t>
+  </si>
+  <si>
+    <t>奖励类型</t>
+  </si>
+  <si>
+    <t>奖励道具ID</t>
+  </si>
+  <si>
+    <t>奖励筹码</t>
+  </si>
+  <si>
+    <t>顺序礼包ID</t>
+  </si>
+  <si>
+    <t>Steam奖励定义ID</t>
+  </si>
+  <si>
+    <t>领取次数上限</t>
+  </si>
+  <si>
+    <t>TwitterFollow</t>
+  </si>
+  <si>
+    <t>Twitter</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_Twitter.png</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Icon_Gift.svg</t>
+  </si>
+  <si>
+    <t>https://x.com/intent/follow?screen_name=LuckyDogRise</t>
+  </si>
+  <si>
+    <t>https://x.com/LuckyDogRise</t>
+  </si>
+  <si>
+    <t>ShellOpenOk</t>
+  </si>
+  <si>
+    <t>FixedChips</t>
+  </si>
+  <si>
+    <t>SteamCommunity</t>
+  </si>
+  <si>
+    <t>Steam Community</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_SteamCommunity.png</t>
+  </si>
+  <si>
+    <t>https://steamcommunity.com/app/2583700</t>
+  </si>
+  <si>
+    <t>SteamStore</t>
+  </si>
+  <si>
+    <t>Steam Store</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_SteamStore.png</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_pre_claim</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_post_claim</t>
+  </si>
+  <si>
+    <t>XiaohongshuProfile</t>
+  </si>
+  <si>
+    <t>Xiaohongshu</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_Xiaohongshu.png</t>
+  </si>
+  <si>
+    <t>https://www.xiaohongshu.com/user/profile/647bc1b5000000001001f13a</t>
   </si>
 </sst>
 </file>
@@ -2933,6 +3135,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2941,9 +3146,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -3566,16 +3768,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3662,16 +3864,16 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>34</v>
       </c>
@@ -3757,93 +3959,93 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:34">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:34">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L3" s="10"/>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="S3" s="11"/>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="W3" s="11"/>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AH3" s="4" t="s">
+      <c r="AH3" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E4" t="s">
@@ -11715,6 +11917,448 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="6" width="16.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="36.75" customWidth="1"/>
+    <col min="8" max="8" width="22.75" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="13.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="21.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="21.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="15.6666666666667" customWidth="1"/>
+    <col min="15" max="15" width="20.0833333333333" customWidth="1"/>
+    <col min="16" max="17" width="22.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>598</v>
+      </c>
+      <c r="F1" t="s">
+        <v>752</v>
+      </c>
+      <c r="G1" t="s">
+        <v>753</v>
+      </c>
+      <c r="H1" t="s">
+        <v>754</v>
+      </c>
+      <c r="I1" t="s">
+        <v>755</v>
+      </c>
+      <c r="J1" t="s">
+        <v>756</v>
+      </c>
+      <c r="K1" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1" t="s">
+        <v>758</v>
+      </c>
+      <c r="M1" t="s">
+        <v>759</v>
+      </c>
+      <c r="N1" t="s">
+        <v>760</v>
+      </c>
+      <c r="O1" t="s">
+        <v>761</v>
+      </c>
+      <c r="P1" t="s">
+        <v>762</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>764</v>
+      </c>
+      <c r="L2" t="s">
+        <v>765</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>781</v>
+      </c>
+      <c r="C4" t="s">
+        <v>782</v>
+      </c>
+      <c r="D4" t="s">
+        <v>783</v>
+      </c>
+      <c r="E4" t="s">
+        <v>784</v>
+      </c>
+      <c r="F4" t="s">
+        <v>785</v>
+      </c>
+      <c r="G4" t="s">
+        <v>786</v>
+      </c>
+      <c r="H4" t="s">
+        <v>787</v>
+      </c>
+      <c r="I4" t="s">
+        <v>788</v>
+      </c>
+      <c r="J4" t="s">
+        <v>789</v>
+      </c>
+      <c r="K4" t="s">
+        <v>790</v>
+      </c>
+      <c r="L4" t="s">
+        <v>791</v>
+      </c>
+      <c r="M4" t="s">
+        <v>792</v>
+      </c>
+      <c r="N4" t="s">
+        <v>793</v>
+      </c>
+      <c r="O4" t="s">
+        <v>794</v>
+      </c>
+      <c r="P4" t="s">
+        <v>795</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>797</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>798</v>
+      </c>
+      <c r="G5" t="s">
+        <v>799</v>
+      </c>
+      <c r="H5" t="s">
+        <v>800</v>
+      </c>
+      <c r="I5" t="s">
+        <v>801</v>
+      </c>
+      <c r="J5" t="s">
+        <v>802</v>
+      </c>
+      <c r="K5" t="s">
+        <v>803</v>
+      </c>
+      <c r="L5" t="s">
+        <v>804</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>4500</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>805</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>806</v>
+      </c>
+      <c r="G6" t="s">
+        <v>807</v>
+      </c>
+      <c r="H6" t="s">
+        <v>800</v>
+      </c>
+      <c r="I6" t="s">
+        <v>808</v>
+      </c>
+      <c r="J6" t="s">
+        <v>808</v>
+      </c>
+      <c r="K6" t="s">
+        <v>803</v>
+      </c>
+      <c r="L6" t="s">
+        <v>804</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2500</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>810</v>
+      </c>
+      <c r="G7" t="s">
+        <v>811</v>
+      </c>
+      <c r="H7" t="s">
+        <v>800</v>
+      </c>
+      <c r="I7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J7" t="s">
+        <v>813</v>
+      </c>
+      <c r="K7" t="s">
+        <v>803</v>
+      </c>
+      <c r="L7" t="s">
+        <v>804</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>2500</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>814</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>815</v>
+      </c>
+      <c r="G8" t="s">
+        <v>816</v>
+      </c>
+      <c r="H8" t="s">
+        <v>800</v>
+      </c>
+      <c r="I8" t="s">
+        <v>817</v>
+      </c>
+      <c r="J8" t="s">
+        <v>817</v>
+      </c>
+      <c r="K8" t="s">
+        <v>803</v>
+      </c>
+      <c r="L8" t="s">
+        <v>804</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>4500</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -11727,10 +12371,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -11739,130 +12383,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="4" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -11871,248 +12515,248 @@
       <c r="F6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="4" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="4" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="4" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="4" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="4" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="4" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="4" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="4" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>591</v>
       </c>
     </row>
@@ -12144,7 +12788,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -12185,7 +12829,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -12225,49 +12869,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="109" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" spans="1:13">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -12314,10 +12958,10 @@
       <c r="C5" t="s">
         <v>627</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F5">
@@ -12352,10 +12996,10 @@
       <c r="C6" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F6">
@@ -12390,10 +13034,10 @@
       <c r="C7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F7">
@@ -12431,7 +13075,7 @@
       <c r="D8" t="s">
         <v>634</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>635</v>
       </c>
       <c r="F8">
@@ -12460,13 +13104,13 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="E15" s="3"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="E16" s="3"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="3"/>
+      <c r="E17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12495,7 +13139,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -12533,7 +13177,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -12570,41 +13214,41 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
@@ -13236,22 +13880,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>678</v>
       </c>
       <c r="F3" s="6"/>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>623</v>
       </c>
     </row>
@@ -13784,35 +14428,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>693</v>
       </c>
     </row>
@@ -14860,13 +15504,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -14895,13 +15539,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -14929,28 +15573,28 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>712</v>
       </c>
     </row>
@@ -15019,10 +15663,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -15042,10 +15686,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -15065,10 +15709,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -15088,10 +15732,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
@@ -15111,10 +15755,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -15134,10 +15778,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>508</v>
       </c>
       <c r="E11" t="s">
@@ -15157,10 +15801,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
@@ -15194,10 +15838,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -15211,10 +15855,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -15228,10 +15872,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
@@ -15359,42 +16003,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="3"/>
+      <c r="C22" s="4"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="3"/>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15415,7 +16059,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -15429,13 +16073,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -15443,13 +16087,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>749</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="819">
   <si>
     <t>##var</t>
   </si>
@@ -2460,19 +2460,22 @@
     <t>ShellOpenOk</t>
   </si>
   <si>
+    <t>FixedItem</t>
+  </si>
+  <si>
+    <t>SteamCommunity</t>
+  </si>
+  <si>
+    <t>Steam Community</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_SteamCommunity.png</t>
+  </si>
+  <si>
+    <t>https://steamcommunity.com/app/2583700</t>
+  </si>
+  <si>
     <t>FixedChips</t>
-  </si>
-  <si>
-    <t>SteamCommunity</t>
-  </si>
-  <si>
-    <t>Steam Community</t>
-  </si>
-  <si>
-    <t>UI/LinkTree/Banner_SteamCommunity.png</t>
-  </si>
-  <si>
-    <t>https://steamcommunity.com/app/2583700</t>
   </si>
   <si>
     <t>SteamStore</t>
@@ -12188,10 +12191,10 @@
         <v>804</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>92005</v>
       </c>
       <c r="N5">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -12235,7 +12238,7 @@
         <v>803</v>
       </c>
       <c r="L6" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -12258,7 +12261,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -12267,25 +12270,25 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H7" t="s">
         <v>800</v>
       </c>
       <c r="I7" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J7" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K7" t="s">
         <v>803</v>
       </c>
       <c r="L7" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -12308,7 +12311,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12317,19 +12320,19 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H8" t="s">
         <v>800</v>
       </c>
       <c r="I8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K8" t="s">
         <v>803</v>
@@ -12338,10 +12341,10 @@
         <v>804</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>91012</v>
       </c>
       <c r="N8">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="703" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
     <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
+    <sheet name="SteamItemDef" sheetId="18" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="866">
   <si>
     <t>##var</t>
   </si>
@@ -2503,6 +2504,147 @@
   </si>
   <si>
     <t>https://www.xiaohongshu.com/user/profile/647bc1b5000000001001f13a</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>PromoRule</t>
+  </si>
+  <si>
+    <t>GrantedManually</t>
+  </si>
+  <si>
+    <t>Tradable</t>
+  </si>
+  <si>
+    <t>Marketable</t>
+  </si>
+  <si>
+    <t>GameOnly</t>
+  </si>
+  <si>
+    <t>StoreHidden</t>
+  </si>
+  <si>
+    <t>AutoStack</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>Steam Inventory 内唯一的 ItemDef ID；发布后不得改作他用</t>
+  </si>
+  <si>
+    <t>稳定机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>Steam 定义类型；当前合法值见 ESteamItemDefType</t>
+  </si>
+  <si>
+    <t>Steam 后台英文名称；game_only 回执不向玩家展示</t>
+  </si>
+  <si>
+    <t>Steam 后台英文说明；game_only 回执不向玩家展示</t>
+  </si>
+  <si>
+    <t>Steam promo 属性；LinkTree 固定填 manual；补偿可填 owns:AppID</t>
+  </si>
+  <si>
+    <t>TRUE 时只能由 AddPromoItem/AddPromoItems 指定领取</t>
+  </si>
+  <si>
+    <t>是否允许 Steam 交易</t>
+  </si>
+  <si>
+    <t>是否允许 Steam 社区市场出售</t>
+  </si>
+  <si>
+    <t>TRUE 时不显示在 Steam 背包；回执和内部令牌填 TRUE</t>
+  </si>
+  <si>
+    <t>TRUE 时不在 Steam 物品商店展示</t>
+  </si>
+  <si>
+    <t>是否将同定义物品自动堆叠；一次性回执填 FALSE</t>
+  </si>
+  <si>
+    <t>Bundle/Generator 的内容配方；普通 Item 留空</t>
+  </si>
+  <si>
+    <t>是否参与导出到 Steam ItemDef 配置</t>
+  </si>
+  <si>
+    <t>Steam物品定义ID</t>
+  </si>
+  <si>
+    <t>Steam定义类型</t>
+  </si>
+  <si>
+    <t>英文名称</t>
+  </si>
+  <si>
+    <t>英文说明</t>
+  </si>
+  <si>
+    <t>促销规则</t>
+  </si>
+  <si>
+    <t>仅显式领取</t>
+  </si>
+  <si>
+    <t>可上市场</t>
+  </si>
+  <si>
+    <t>仅游戏内</t>
+  </si>
+  <si>
+    <t>商店隐藏</t>
+  </si>
+  <si>
+    <t>内容配方</t>
+  </si>
+  <si>
+    <t>LinkTreeTwitterFollowClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Twitter Follow</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Twitter follow reward.</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Steam Community</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Steam Community reward.</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Steam Store</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Steam Store reward.</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Xiaohongshu Profile</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Xiaohongshu profile reward.</t>
   </si>
 </sst>
 </file>
@@ -3134,9 +3276,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3752,11 +3897,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="9" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="10" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="9" customWidth="1"/>
+    <col min="23" max="23" width="7" style="10" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="10.5833333333333" customWidth="1"/>
     <col min="26" max="26" width="11.6666666666667" customWidth="1"/>
@@ -3771,16 +3916,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3867,16 +4012,16 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
         <v>34</v>
       </c>
@@ -3962,93 +4107,93 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:34">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:34">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="1" t="s">
+      <c r="L3" s="11"/>
+      <c r="M3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="1" t="s">
+      <c r="S3" s="12"/>
+      <c r="T3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="11"/>
-      <c r="X3" s="1" t="s">
+      <c r="W3" s="12"/>
+      <c r="X3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Z3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AA3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AB3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AD3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AE3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AG3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AH3" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E4" t="s">
@@ -4667,10 +4812,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="8">
         <v>100</v>
       </c>
-      <c r="P12" s="7">
+      <c r="P12" s="8">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -5385,7 +5530,7 @@
       <c r="R23" t="s">
         <v>162</v>
       </c>
-      <c r="S23" s="9" t="s">
+      <c r="S23" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T23" t="s">
@@ -5743,7 +5888,7 @@
       <c r="R28" t="s">
         <v>162</v>
       </c>
-      <c r="S28" s="9" t="s">
+      <c r="S28" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T28" t="s">
@@ -5755,7 +5900,7 @@
       <c r="V28" t="s">
         <v>162</v>
       </c>
-      <c r="W28" s="9" t="s">
+      <c r="W28" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X28">
@@ -5847,7 +5992,7 @@
       <c r="R29" t="s">
         <v>162</v>
       </c>
-      <c r="S29" s="9" t="s">
+      <c r="S29" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T29" t="s">
@@ -5859,7 +6004,7 @@
       <c r="V29" t="s">
         <v>162</v>
       </c>
-      <c r="W29" s="9" t="s">
+      <c r="W29" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X29">
@@ -7258,7 +7403,7 @@
       <c r="R49" t="s">
         <v>162</v>
       </c>
-      <c r="S49" s="9" t="s">
+      <c r="S49" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T49" t="s">
@@ -7341,7 +7486,7 @@
       <c r="R50" t="s">
         <v>162</v>
       </c>
-      <c r="S50" s="9" t="s">
+      <c r="S50" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T50" t="s">
@@ -7424,7 +7569,7 @@
       <c r="R51" t="s">
         <v>162</v>
       </c>
-      <c r="S51" s="9" t="s">
+      <c r="S51" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T51" t="s">
@@ -7507,7 +7652,7 @@
       <c r="R52" t="s">
         <v>162</v>
       </c>
-      <c r="S52" s="9" t="s">
+      <c r="S52" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T52" t="s">
@@ -7590,7 +7735,7 @@
       <c r="R53" t="s">
         <v>162</v>
       </c>
-      <c r="S53" s="9" t="s">
+      <c r="S53" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T53" t="s">
@@ -7673,7 +7818,7 @@
       <c r="R54" t="s">
         <v>162</v>
       </c>
-      <c r="S54" s="9" t="s">
+      <c r="S54" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T54" t="s">
@@ -7756,7 +7901,7 @@
       <c r="R55" t="s">
         <v>162</v>
       </c>
-      <c r="S55" s="9" t="s">
+      <c r="S55" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T55" t="s">
@@ -7839,7 +7984,7 @@
       <c r="R56" t="s">
         <v>162</v>
       </c>
-      <c r="S56" s="9" t="s">
+      <c r="S56" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T56" t="s">
@@ -7922,7 +8067,7 @@
       <c r="R57" t="s">
         <v>162</v>
       </c>
-      <c r="S57" s="9" t="s">
+      <c r="S57" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T57" t="s">
@@ -8005,7 +8150,7 @@
       <c r="R58" t="s">
         <v>162</v>
       </c>
-      <c r="S58" s="9" t="s">
+      <c r="S58" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T58" t="s">
@@ -8088,7 +8233,7 @@
       <c r="R59" t="s">
         <v>162</v>
       </c>
-      <c r="S59" s="9" t="s">
+      <c r="S59" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T59" t="s">
@@ -8336,7 +8481,7 @@
       <c r="E63" t="s">
         <v>316</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="8" t="s">
         <v>92</v>
       </c>
       <c r="I63">
@@ -8404,7 +8549,7 @@
       <c r="E64" t="s">
         <v>316</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="8" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8472,7 +8617,7 @@
       <c r="E65" t="s">
         <v>316</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="8" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8647,7 +8792,7 @@
       <c r="R67" t="s">
         <v>162</v>
       </c>
-      <c r="S67" s="9" t="s">
+      <c r="S67" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T67" t="s">
@@ -8730,7 +8875,7 @@
       <c r="R68" t="s">
         <v>162</v>
       </c>
-      <c r="S68" s="9" t="s">
+      <c r="S68" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T68" t="s">
@@ -8813,7 +8958,7 @@
       <c r="R69" t="s">
         <v>162</v>
       </c>
-      <c r="S69" s="9" t="s">
+      <c r="S69" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T69" t="s">
@@ -8896,7 +9041,7 @@
       <c r="R70" t="s">
         <v>162</v>
       </c>
-      <c r="S70" s="9" t="s">
+      <c r="S70" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T70" t="s">
@@ -8979,7 +9124,7 @@
       <c r="R71" t="s">
         <v>162</v>
       </c>
-      <c r="S71" s="9" t="s">
+      <c r="S71" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T71" t="s">
@@ -9062,7 +9207,7 @@
       <c r="R72" t="s">
         <v>162</v>
       </c>
-      <c r="S72" s="9" t="s">
+      <c r="S72" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T72" t="s">
@@ -9145,7 +9290,7 @@
       <c r="R73" t="s">
         <v>162</v>
       </c>
-      <c r="S73" s="9" t="s">
+      <c r="S73" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T73" t="s">
@@ -9228,7 +9373,7 @@
       <c r="R74" t="s">
         <v>162</v>
       </c>
-      <c r="S74" s="9" t="s">
+      <c r="S74" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T74" t="s">
@@ -9311,7 +9456,7 @@
       <c r="R75" t="s">
         <v>162</v>
       </c>
-      <c r="S75" s="9" t="s">
+      <c r="S75" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T75" t="s">
@@ -9394,7 +9539,7 @@
       <c r="R76" t="s">
         <v>162</v>
       </c>
-      <c r="S76" s="9" t="s">
+      <c r="S76" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T76" t="s">
@@ -9548,7 +9693,7 @@
       <c r="R78" t="s">
         <v>162</v>
       </c>
-      <c r="S78" s="9" t="s">
+      <c r="S78" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T78" t="s">
@@ -9560,7 +9705,7 @@
       <c r="V78" t="s">
         <v>162</v>
       </c>
-      <c r="W78" s="9" t="s">
+      <c r="W78" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X78">
@@ -9649,7 +9794,7 @@
       <c r="R79" t="s">
         <v>162</v>
       </c>
-      <c r="S79" s="9" t="s">
+      <c r="S79" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T79" t="s">
@@ -9699,7 +9844,7 @@
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" s="7" t="s">
+      <c r="H80" s="8" t="s">
         <v>121</v>
       </c>
       <c r="I80">
@@ -9732,7 +9877,7 @@
       <c r="R80" t="s">
         <v>162</v>
       </c>
-      <c r="S80" s="9" t="s">
+      <c r="S80" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T80" t="s">
@@ -9815,7 +9960,7 @@
       <c r="R81" t="s">
         <v>162</v>
       </c>
-      <c r="S81" s="9" t="s">
+      <c r="S81" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T81" t="s">
@@ -9898,7 +10043,7 @@
       <c r="R82" t="s">
         <v>162</v>
       </c>
-      <c r="S82" s="9" t="s">
+      <c r="S82" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T82" t="s">
@@ -9981,7 +10126,7 @@
       <c r="R83" t="s">
         <v>162</v>
       </c>
-      <c r="S83" s="9" t="s">
+      <c r="S83" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T83" t="s">
@@ -10031,7 +10176,7 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" s="7" t="s">
+      <c r="H84" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I84">
@@ -10064,7 +10209,7 @@
       <c r="R84" t="s">
         <v>162</v>
       </c>
-      <c r="S84" s="9" t="s">
+      <c r="S84" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T84" t="s">
@@ -10147,7 +10292,7 @@
       <c r="R85" t="s">
         <v>162</v>
       </c>
-      <c r="S85" s="9" t="s">
+      <c r="S85" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T85" t="s">
@@ -10230,7 +10375,7 @@
       <c r="R86" t="s">
         <v>162</v>
       </c>
-      <c r="S86" s="9" t="s">
+      <c r="S86" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T86" t="s">
@@ -10520,7 +10665,7 @@
       <c r="R90" t="s">
         <v>162</v>
       </c>
-      <c r="S90" s="9" t="s">
+      <c r="S90" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T90" t="s">
@@ -10532,7 +10677,7 @@
       <c r="V90" t="s">
         <v>162</v>
       </c>
-      <c r="W90" s="9" t="s">
+      <c r="W90" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X90">
@@ -10624,7 +10769,7 @@
       <c r="R91" t="s">
         <v>162</v>
       </c>
-      <c r="S91" s="9" t="s">
+      <c r="S91" s="10" t="s">
         <v>162</v>
       </c>
       <c r="T91" t="s">
@@ -10636,7 +10781,7 @@
       <c r="V91" t="s">
         <v>162</v>
       </c>
-      <c r="W91" s="9" t="s">
+      <c r="W91" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X91">
@@ -10799,7 +10944,7 @@
       <c r="U93" t="s">
         <v>455</v>
       </c>
-      <c r="W93" s="9" t="s">
+      <c r="W93" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X93">
@@ -10879,7 +11024,7 @@
       <c r="U94" t="s">
         <v>460</v>
       </c>
-      <c r="W94" s="9" t="s">
+      <c r="W94" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X94">
@@ -10959,7 +11104,7 @@
       <c r="U95" t="s">
         <v>464</v>
       </c>
-      <c r="W95" s="9" t="s">
+      <c r="W95" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X95">
@@ -11039,7 +11184,7 @@
       <c r="U96" t="s">
         <v>468</v>
       </c>
-      <c r="W96" s="9" t="s">
+      <c r="W96" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X96">
@@ -11119,7 +11264,7 @@
       <c r="U97" t="s">
         <v>472</v>
       </c>
-      <c r="W97" s="9" t="s">
+      <c r="W97" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X97">
@@ -11199,7 +11344,7 @@
       <c r="U98" t="s">
         <v>476</v>
       </c>
-      <c r="W98" s="9" t="s">
+      <c r="W98" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X98">
@@ -11279,7 +11424,7 @@
       <c r="U99" t="s">
         <v>480</v>
       </c>
-      <c r="W99" s="9" t="s">
+      <c r="W99" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X99">
@@ -11353,7 +11498,7 @@
       <c r="U100" t="s">
         <v>484</v>
       </c>
-      <c r="W100" s="9" t="s">
+      <c r="W100" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X100">
@@ -11510,7 +11655,7 @@
       <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="9" t="s">
+      <c r="W102" s="10" t="s">
         <v>456</v>
       </c>
       <c r="X102">
@@ -11649,7 +11794,7 @@
       <c r="U104" t="s">
         <v>502</v>
       </c>
-      <c r="W104" s="9" t="s">
+      <c r="W104" s="10" t="s">
         <v>503</v>
       </c>
       <c r="X104">
@@ -11782,14 +11927,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="9"/>
+      <c r="S106" s="10"/>
       <c r="T106" t="s">
         <v>158</v>
       </c>
       <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W106" s="9" t="s">
+      <c r="W106" s="10" t="s">
         <v>510</v>
       </c>
       <c r="X106">
@@ -11851,7 +11996,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="9"/>
+      <c r="S107" s="10"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -11861,7 +12006,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="9" t="s">
+      <c r="W107" s="10" t="s">
         <v>510</v>
       </c>
       <c r="X107">
@@ -12050,56 +12195,56 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="2" t="s">
         <v>780</v>
       </c>
     </row>
@@ -12200,7 +12345,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>901001</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -12250,7 +12395,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>901002</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -12300,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>901003</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -12350,9 +12495,415 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>901004</v>
       </c>
       <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="15.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="13.5833333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16384" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1" t="s">
+        <v>821</v>
+      </c>
+      <c r="H1" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1" t="s">
+        <v>823</v>
+      </c>
+      <c r="J1" t="s">
+        <v>824</v>
+      </c>
+      <c r="K1" t="s">
+        <v>825</v>
+      </c>
+      <c r="L1" t="s">
+        <v>826</v>
+      </c>
+      <c r="M1" t="s">
+        <v>827</v>
+      </c>
+      <c r="N1" t="s">
+        <v>828</v>
+      </c>
+      <c r="O1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C4" t="s">
+        <v>782</v>
+      </c>
+      <c r="D4" t="s">
+        <v>844</v>
+      </c>
+      <c r="E4" t="s">
+        <v>845</v>
+      </c>
+      <c r="F4" t="s">
+        <v>846</v>
+      </c>
+      <c r="G4" t="s">
+        <v>847</v>
+      </c>
+      <c r="H4" t="s">
+        <v>848</v>
+      </c>
+      <c r="I4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" t="s">
+        <v>849</v>
+      </c>
+      <c r="K4" t="s">
+        <v>850</v>
+      </c>
+      <c r="L4" t="s">
+        <v>851</v>
+      </c>
+      <c r="M4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" t="s">
+        <v>852</v>
+      </c>
+      <c r="O4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5">
+        <v>401001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>853</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>854</v>
+      </c>
+      <c r="F5" t="s">
+        <v>855</v>
+      </c>
+      <c r="G5" t="s">
+        <v>856</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6">
+        <v>401002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>857</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>858</v>
+      </c>
+      <c r="F6" t="s">
+        <v>859</v>
+      </c>
+      <c r="G6" t="s">
+        <v>856</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>162</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7">
+        <v>401003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>860</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>861</v>
+      </c>
+      <c r="F7" t="s">
+        <v>862</v>
+      </c>
+      <c r="G7" t="s">
+        <v>856</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8">
+        <v>401004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>863</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>864</v>
+      </c>
+      <c r="F8" t="s">
+        <v>865</v>
+      </c>
+      <c r="G8" t="s">
+        <v>856</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>162</v>
+      </c>
+      <c r="O8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12374,10 +12925,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -12386,130 +12937,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -12518,248 +13069,248 @@
       <c r="F6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="5" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>591</v>
       </c>
     </row>
@@ -12791,7 +13342,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -12832,7 +13383,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -12872,85 +13423,85 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="2" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:13">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="9" customFormat="1" spans="1:13">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>626</v>
       </c>
     </row>
@@ -12961,10 +13512,10 @@
       <c r="C5" t="s">
         <v>627</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>629</v>
       </c>
       <c r="F5">
@@ -12999,10 +13550,10 @@
       <c r="C6" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>629</v>
       </c>
       <c r="F6">
@@ -13037,10 +13588,10 @@
       <c r="C7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>629</v>
       </c>
       <c r="F7">
@@ -13078,7 +13629,7 @@
       <c r="D8" t="s">
         <v>634</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>635</v>
       </c>
       <c r="F8">
@@ -13107,13 +13658,13 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="E15" s="4"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="E16" s="4"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="4"/>
+      <c r="E17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13142,7 +13693,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -13180,7 +13731,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -13217,41 +13768,41 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
@@ -13839,7 +14390,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="6" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13883,22 +14434,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="2" t="s">
         <v>623</v>
       </c>
     </row>
@@ -13938,7 +14489,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -13959,7 +14510,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -13980,7 +14531,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -13998,10 +14549,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>900</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -14019,10 +14570,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>180</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -14043,7 +14594,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14055,7 +14606,7 @@
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="6">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -14073,7 +14624,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14094,7 +14645,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -14118,7 +14669,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -14139,7 +14690,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -14160,7 +14711,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -14181,7 +14732,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14193,7 +14744,7 @@
       <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="6">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -14431,35 +14982,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>693</v>
       </c>
     </row>
@@ -15507,13 +16058,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -15542,13 +16093,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -15576,28 +16127,28 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:12">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>712</v>
       </c>
     </row>
@@ -15666,10 +16217,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -15689,10 +16240,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -15712,10 +16263,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -15735,10 +16286,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
@@ -15758,10 +16309,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -15781,10 +16332,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>508</v>
       </c>
       <c r="E11" t="s">
@@ -15804,10 +16355,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
@@ -15841,10 +16392,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -15858,10 +16409,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -15875,10 +16426,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
@@ -16006,42 +16557,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16062,7 +16613,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -16076,13 +16627,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -16090,13 +16641,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>749</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -3276,12 +3276,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3897,11 +3894,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="10" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="9" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="10" customWidth="1"/>
+    <col min="23" max="23" width="7" style="9" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="10.5833333333333" customWidth="1"/>
     <col min="26" max="26" width="11.6666666666667" customWidth="1"/>
@@ -3916,16 +3913,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -4012,16 +4009,16 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>34</v>
       </c>
@@ -4107,93 +4104,93 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:34">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:34">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="10"/>
+      <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="12"/>
-      <c r="T3" s="2" t="s">
+      <c r="S3" s="11"/>
+      <c r="T3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="12"/>
-      <c r="X3" s="2" t="s">
+      <c r="W3" s="11"/>
+      <c r="X3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E4" t="s">
@@ -4812,10 +4809,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="7">
         <v>100</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="7">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -5530,7 +5527,7 @@
       <c r="R23" t="s">
         <v>162</v>
       </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T23" t="s">
@@ -5888,7 +5885,7 @@
       <c r="R28" t="s">
         <v>162</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T28" t="s">
@@ -5900,7 +5897,7 @@
       <c r="V28" t="s">
         <v>162</v>
       </c>
-      <c r="W28" s="10" t="s">
+      <c r="W28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X28">
@@ -5992,7 +5989,7 @@
       <c r="R29" t="s">
         <v>162</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="S29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T29" t="s">
@@ -6004,7 +6001,7 @@
       <c r="V29" t="s">
         <v>162</v>
       </c>
-      <c r="W29" s="10" t="s">
+      <c r="W29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X29">
@@ -7403,7 +7400,7 @@
       <c r="R49" t="s">
         <v>162</v>
       </c>
-      <c r="S49" s="10" t="s">
+      <c r="S49" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T49" t="s">
@@ -7486,7 +7483,7 @@
       <c r="R50" t="s">
         <v>162</v>
       </c>
-      <c r="S50" s="10" t="s">
+      <c r="S50" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T50" t="s">
@@ -7569,7 +7566,7 @@
       <c r="R51" t="s">
         <v>162</v>
       </c>
-      <c r="S51" s="10" t="s">
+      <c r="S51" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T51" t="s">
@@ -7652,7 +7649,7 @@
       <c r="R52" t="s">
         <v>162</v>
       </c>
-      <c r="S52" s="10" t="s">
+      <c r="S52" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T52" t="s">
@@ -7735,7 +7732,7 @@
       <c r="R53" t="s">
         <v>162</v>
       </c>
-      <c r="S53" s="10" t="s">
+      <c r="S53" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T53" t="s">
@@ -7818,7 +7815,7 @@
       <c r="R54" t="s">
         <v>162</v>
       </c>
-      <c r="S54" s="10" t="s">
+      <c r="S54" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T54" t="s">
@@ -7901,7 +7898,7 @@
       <c r="R55" t="s">
         <v>162</v>
       </c>
-      <c r="S55" s="10" t="s">
+      <c r="S55" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T55" t="s">
@@ -7984,7 +7981,7 @@
       <c r="R56" t="s">
         <v>162</v>
       </c>
-      <c r="S56" s="10" t="s">
+      <c r="S56" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T56" t="s">
@@ -8067,7 +8064,7 @@
       <c r="R57" t="s">
         <v>162</v>
       </c>
-      <c r="S57" s="10" t="s">
+      <c r="S57" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T57" t="s">
@@ -8150,7 +8147,7 @@
       <c r="R58" t="s">
         <v>162</v>
       </c>
-      <c r="S58" s="10" t="s">
+      <c r="S58" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T58" t="s">
@@ -8233,7 +8230,7 @@
       <c r="R59" t="s">
         <v>162</v>
       </c>
-      <c r="S59" s="10" t="s">
+      <c r="S59" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T59" t="s">
@@ -8481,7 +8478,7 @@
       <c r="E63" t="s">
         <v>316</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I63">
@@ -8549,7 +8546,7 @@
       <c r="E64" t="s">
         <v>316</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8617,7 +8614,7 @@
       <c r="E65" t="s">
         <v>316</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8792,7 +8789,7 @@
       <c r="R67" t="s">
         <v>162</v>
       </c>
-      <c r="S67" s="10" t="s">
+      <c r="S67" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T67" t="s">
@@ -8875,7 +8872,7 @@
       <c r="R68" t="s">
         <v>162</v>
       </c>
-      <c r="S68" s="10" t="s">
+      <c r="S68" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T68" t="s">
@@ -8958,7 +8955,7 @@
       <c r="R69" t="s">
         <v>162</v>
       </c>
-      <c r="S69" s="10" t="s">
+      <c r="S69" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T69" t="s">
@@ -9041,7 +9038,7 @@
       <c r="R70" t="s">
         <v>162</v>
       </c>
-      <c r="S70" s="10" t="s">
+      <c r="S70" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T70" t="s">
@@ -9124,7 +9121,7 @@
       <c r="R71" t="s">
         <v>162</v>
       </c>
-      <c r="S71" s="10" t="s">
+      <c r="S71" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T71" t="s">
@@ -9207,7 +9204,7 @@
       <c r="R72" t="s">
         <v>162</v>
       </c>
-      <c r="S72" s="10" t="s">
+      <c r="S72" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T72" t="s">
@@ -9290,7 +9287,7 @@
       <c r="R73" t="s">
         <v>162</v>
       </c>
-      <c r="S73" s="10" t="s">
+      <c r="S73" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T73" t="s">
@@ -9373,7 +9370,7 @@
       <c r="R74" t="s">
         <v>162</v>
       </c>
-      <c r="S74" s="10" t="s">
+      <c r="S74" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T74" t="s">
@@ -9456,7 +9453,7 @@
       <c r="R75" t="s">
         <v>162</v>
       </c>
-      <c r="S75" s="10" t="s">
+      <c r="S75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T75" t="s">
@@ -9539,7 +9536,7 @@
       <c r="R76" t="s">
         <v>162</v>
       </c>
-      <c r="S76" s="10" t="s">
+      <c r="S76" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T76" t="s">
@@ -9693,7 +9690,7 @@
       <c r="R78" t="s">
         <v>162</v>
       </c>
-      <c r="S78" s="10" t="s">
+      <c r="S78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T78" t="s">
@@ -9705,7 +9702,7 @@
       <c r="V78" t="s">
         <v>162</v>
       </c>
-      <c r="W78" s="10" t="s">
+      <c r="W78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X78">
@@ -9794,7 +9791,7 @@
       <c r="R79" t="s">
         <v>162</v>
       </c>
-      <c r="S79" s="10" t="s">
+      <c r="S79" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T79" t="s">
@@ -9844,7 +9841,7 @@
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I80">
@@ -9877,7 +9874,7 @@
       <c r="R80" t="s">
         <v>162</v>
       </c>
-      <c r="S80" s="10" t="s">
+      <c r="S80" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T80" t="s">
@@ -9960,7 +9957,7 @@
       <c r="R81" t="s">
         <v>162</v>
       </c>
-      <c r="S81" s="10" t="s">
+      <c r="S81" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T81" t="s">
@@ -10043,7 +10040,7 @@
       <c r="R82" t="s">
         <v>162</v>
       </c>
-      <c r="S82" s="10" t="s">
+      <c r="S82" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T82" t="s">
@@ -10126,7 +10123,7 @@
       <c r="R83" t="s">
         <v>162</v>
       </c>
-      <c r="S83" s="10" t="s">
+      <c r="S83" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T83" t="s">
@@ -10176,7 +10173,7 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="7" t="s">
         <v>141</v>
       </c>
       <c r="I84">
@@ -10209,7 +10206,7 @@
       <c r="R84" t="s">
         <v>162</v>
       </c>
-      <c r="S84" s="10" t="s">
+      <c r="S84" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T84" t="s">
@@ -10292,7 +10289,7 @@
       <c r="R85" t="s">
         <v>162</v>
       </c>
-      <c r="S85" s="10" t="s">
+      <c r="S85" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T85" t="s">
@@ -10375,7 +10372,7 @@
       <c r="R86" t="s">
         <v>162</v>
       </c>
-      <c r="S86" s="10" t="s">
+      <c r="S86" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T86" t="s">
@@ -10665,7 +10662,7 @@
       <c r="R90" t="s">
         <v>162</v>
       </c>
-      <c r="S90" s="10" t="s">
+      <c r="S90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T90" t="s">
@@ -10677,7 +10674,7 @@
       <c r="V90" t="s">
         <v>162</v>
       </c>
-      <c r="W90" s="10" t="s">
+      <c r="W90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X90">
@@ -10769,7 +10766,7 @@
       <c r="R91" t="s">
         <v>162</v>
       </c>
-      <c r="S91" s="10" t="s">
+      <c r="S91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T91" t="s">
@@ -10781,7 +10778,7 @@
       <c r="V91" t="s">
         <v>162</v>
       </c>
-      <c r="W91" s="10" t="s">
+      <c r="W91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X91">
@@ -10944,7 +10941,7 @@
       <c r="U93" t="s">
         <v>455</v>
       </c>
-      <c r="W93" s="10" t="s">
+      <c r="W93" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X93">
@@ -11024,7 +11021,7 @@
       <c r="U94" t="s">
         <v>460</v>
       </c>
-      <c r="W94" s="10" t="s">
+      <c r="W94" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X94">
@@ -11104,7 +11101,7 @@
       <c r="U95" t="s">
         <v>464</v>
       </c>
-      <c r="W95" s="10" t="s">
+      <c r="W95" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X95">
@@ -11184,7 +11181,7 @@
       <c r="U96" t="s">
         <v>468</v>
       </c>
-      <c r="W96" s="10" t="s">
+      <c r="W96" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X96">
@@ -11264,7 +11261,7 @@
       <c r="U97" t="s">
         <v>472</v>
       </c>
-      <c r="W97" s="10" t="s">
+      <c r="W97" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X97">
@@ -11344,7 +11341,7 @@
       <c r="U98" t="s">
         <v>476</v>
       </c>
-      <c r="W98" s="10" t="s">
+      <c r="W98" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X98">
@@ -11424,7 +11421,7 @@
       <c r="U99" t="s">
         <v>480</v>
       </c>
-      <c r="W99" s="10" t="s">
+      <c r="W99" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X99">
@@ -11498,7 +11495,7 @@
       <c r="U100" t="s">
         <v>484</v>
       </c>
-      <c r="W100" s="10" t="s">
+      <c r="W100" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X100">
@@ -11655,7 +11652,7 @@
       <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="10" t="s">
+      <c r="W102" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X102">
@@ -11794,7 +11791,7 @@
       <c r="U104" t="s">
         <v>502</v>
       </c>
-      <c r="W104" s="10" t="s">
+      <c r="W104" s="9" t="s">
         <v>503</v>
       </c>
       <c r="X104">
@@ -11927,14 +11924,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="10"/>
+      <c r="S106" s="9"/>
       <c r="T106" t="s">
         <v>158</v>
       </c>
       <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W106" s="10" t="s">
+      <c r="W106" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X106">
@@ -11996,7 +11993,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="10"/>
+      <c r="S107" s="9"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -12006,7 +12003,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="10" t="s">
+      <c r="W107" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X107">
@@ -12195,56 +12192,56 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="77" customHeight="1" spans="1:17">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>780</v>
       </c>
     </row>
@@ -12345,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>901001</v>
+        <v>401001</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -12395,7 +12392,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>901002</v>
+        <v>401002</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -12445,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>901003</v>
+        <v>401003</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -12495,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>901004</v>
+        <v>401004</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -12925,10 +12922,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -12937,130 +12934,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="5">
-        <v>1</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -13069,248 +13066,248 @@
       <c r="F6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>591</v>
       </c>
     </row>
@@ -13342,7 +13339,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -13383,7 +13380,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -13423,85 +13420,85 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:13">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" spans="1:13">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="8" customFormat="1" spans="1:13">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="8" t="s">
         <v>626</v>
       </c>
     </row>
@@ -13512,10 +13509,10 @@
       <c r="C5" t="s">
         <v>627</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F5">
@@ -13550,10 +13547,10 @@
       <c r="C6" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F6">
@@ -13588,10 +13585,10 @@
       <c r="C7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F7">
@@ -13629,7 +13626,7 @@
       <c r="D8" t="s">
         <v>634</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>635</v>
       </c>
       <c r="F8">
@@ -13658,13 +13655,13 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="E15" s="5"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="E16" s="5"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="5"/>
+      <c r="E17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13693,7 +13690,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -13731,7 +13728,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -13768,41 +13765,41 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
@@ -14390,7 +14387,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="5" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14434,22 +14431,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="1" t="s">
         <v>623</v>
       </c>
     </row>
@@ -14489,7 +14486,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -14510,7 +14507,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -14531,7 +14528,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -14549,10 +14546,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>900</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -14570,10 +14567,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>180</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -14594,7 +14591,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14606,7 +14603,7 @@
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -14624,7 +14621,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14645,7 +14642,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -14669,7 +14666,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -14690,7 +14687,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -14711,7 +14708,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -14732,7 +14729,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14744,7 +14741,7 @@
       <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -14982,35 +14979,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>693</v>
       </c>
     </row>
@@ -16058,13 +16055,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -16093,13 +16090,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -16127,28 +16124,28 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>712</v>
       </c>
     </row>
@@ -16217,10 +16214,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -16240,10 +16237,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -16263,10 +16260,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -16286,10 +16283,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
@@ -16309,10 +16306,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -16332,10 +16329,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>508</v>
       </c>
       <c r="E11" t="s">
@@ -16355,10 +16352,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
@@ -16392,10 +16389,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -16409,10 +16406,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -16426,10 +16423,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
@@ -16557,42 +16554,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="5"/>
+      <c r="C22" s="4"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16613,7 +16610,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -16627,13 +16624,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -16641,13 +16638,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>749</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -2305,6 +2305,9 @@
     <t>Key</t>
   </si>
   <si>
+    <t>IsPinned</t>
+  </si>
+  <si>
     <t>TooltipKey</t>
   </si>
   <si>
@@ -2338,9 +2341,6 @@
     <t>SteamPromoItemDefId</t>
   </si>
   <si>
-    <t>ClaimLimit</t>
-  </si>
-  <si>
     <t>ELinkTreeOpenCheckType</t>
   </si>
   <si>
@@ -2353,6 +2353,9 @@
     <t>显示顺序，数字越小越靠前</t>
   </si>
   <si>
+    <t>该值为TRUE 的条目始终参与 LinkTree 展示，不因奖励已领取而被替换，并优先占用展示位置</t>
+  </si>
+  <si>
     <t>是否显示这个入口</t>
   </si>
   <si>
@@ -2389,9 +2392,6 @@
     <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
   </si>
   <si>
-    <t>每个玩家最多领取次数；常规填 1</t>
-  </si>
-  <si>
     <t>入口ID</t>
   </si>
   <si>
@@ -2401,6 +2401,9 @@
     <t>排序</t>
   </si>
   <si>
+    <t>固定</t>
+  </si>
+  <si>
     <t>启用</t>
   </si>
   <si>
@@ -2435,9 +2438,6 @@
   </si>
   <si>
     <t>Steam奖励定义ID</t>
-  </si>
-  <si>
-    <t>领取次数上限</t>
   </si>
   <si>
     <t>TwitterFollow</t>
@@ -12072,18 +12072,19 @@
     <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
     <col min="3" max="3" width="17.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="16.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="36.75" customWidth="1"/>
-    <col min="8" max="8" width="22.75" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="13.0833333333333" customWidth="1"/>
-    <col min="11" max="11" width="21.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="15.6666666666667" customWidth="1"/>
-    <col min="15" max="15" width="20.0833333333333" customWidth="1"/>
-    <col min="16" max="17" width="22.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="10.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="16.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="36.75" customWidth="1"/>
+    <col min="9" max="9" width="22.75" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="13.0833333333333" customWidth="1"/>
+    <col min="12" max="12" width="21.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="21.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15.6666666666667" customWidth="1"/>
+    <col min="16" max="16" width="20.0833333333333" customWidth="1"/>
+    <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -12100,10 +12101,10 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F1" t="s">
         <v>598</v>
-      </c>
-      <c r="F1" t="s">
-        <v>752</v>
       </c>
       <c r="G1" t="s">
         <v>753</v>
@@ -12156,7 +12157,7 @@
         <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
         <v>33</v>
@@ -12171,13 +12172,13 @@
         <v>33</v>
       </c>
       <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
         <v>764</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>765</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -12306,46 +12307,46 @@
         <v>797</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>798</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>799</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>800</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>801</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>802</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>803</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>804</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>92005</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>401001</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -12356,46 +12357,46 @@
         <v>805</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
         <v>806</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>807</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>800</v>
-      </c>
-      <c r="I6" t="s">
-        <v>808</v>
       </c>
       <c r="J6" t="s">
         <v>808</v>
       </c>
       <c r="K6" t="s">
+        <v>808</v>
+      </c>
+      <c r="L6" t="s">
         <v>803</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>809</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
       <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>2500</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>401002</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -12406,46 +12407,46 @@
         <v>810</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
         <v>811</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>812</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>800</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>813</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>814</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>803</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>809</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>2500</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>401003</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -12459,43 +12460,43 @@
         <v>40</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>816</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>817</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>800</v>
-      </c>
-      <c r="I8" t="s">
-        <v>818</v>
       </c>
       <c r="J8" t="s">
         <v>818</v>
       </c>
       <c r="K8" t="s">
+        <v>818</v>
+      </c>
+      <c r="L8" t="s">
         <v>803</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>804</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>91012</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>401004</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12713,7 +12714,7 @@
         <v>852</v>
       </c>
       <c r="O4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" spans="1:15">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="870">
   <si>
     <t>##var</t>
   </si>
@@ -1835,6 +1835,9 @@
     <t>AutoCollectSeconds</t>
   </si>
   <si>
+    <t>HintIconPath</t>
+  </si>
+  <si>
     <t>IsSteamRequired</t>
   </si>
   <si>
@@ -1935,6 +1938,9 @@
     <t>三次升级表演</t>
   </si>
   <si>
+    <t>UI\BlindBox\HintIcon_Common.png</t>
+  </si>
+  <si>
     <t>新手盲盒</t>
   </si>
   <si>
@@ -1951,6 +1957,12 @@
   </si>
   <si>
     <t>直接展示奖励</t>
+  </si>
+  <si>
+    <t>盲盒券</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\HintIcon_Common_Ticket.png</t>
   </si>
   <si>
     <t>IsLoopTrack</t>
@@ -12050,10 +12062,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108 H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L108 L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12095,49 +12107,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="H1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="I1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="L1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="M1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="N1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="O1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="P1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="Q1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -12175,10 +12187,10 @@
         <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="M2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -12198,52 +12210,52 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12251,52 +12263,52 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C4" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D4" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="E4" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F4" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="G4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="H4" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="I4" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J4" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="K4" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="L4" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="M4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="N4" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="O4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="P4" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="Q4" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12304,7 +12316,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12316,25 +12328,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="H5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="J5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="K5" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12354,7 +12366,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12366,25 +12378,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H6" t="s">
+        <v>811</v>
+      </c>
+      <c r="I6" t="s">
+        <v>804</v>
+      </c>
+      <c r="J6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K6" t="s">
+        <v>812</v>
+      </c>
+      <c r="L6" t="s">
         <v>807</v>
       </c>
-      <c r="I6" t="s">
-        <v>800</v>
-      </c>
-      <c r="J6" t="s">
-        <v>808</v>
-      </c>
-      <c r="K6" t="s">
-        <v>808</v>
-      </c>
-      <c r="L6" t="s">
-        <v>803</v>
-      </c>
       <c r="M6" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12404,7 +12416,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12416,25 +12428,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="H7" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="I7" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="J7" t="s">
+        <v>817</v>
+      </c>
+      <c r="K7" t="s">
+        <v>818</v>
+      </c>
+      <c r="L7" t="s">
+        <v>807</v>
+      </c>
+      <c r="M7" t="s">
         <v>813</v>
-      </c>
-      <c r="K7" t="s">
-        <v>814</v>
-      </c>
-      <c r="L7" t="s">
-        <v>803</v>
-      </c>
-      <c r="M7" t="s">
-        <v>809</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12454,7 +12466,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12466,25 +12478,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="H8" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="I8" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="J8" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K8" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="L8" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M8" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12537,43 +12549,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="G1" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="H1" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="I1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="J1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="K1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="L1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="M1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="N1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="O1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -12628,46 +12640,46 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -12675,46 +12687,46 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C4" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D4" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="E4" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="F4" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="G4" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="H4" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="I4" t="s">
         <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="K4" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="L4" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="M4" t="s">
         <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="O4" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -12725,19 +12737,19 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="F5" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="G5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -12772,19 +12784,19 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D6" t="s">
         <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="F6" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="G6" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -12819,19 +12831,19 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="F7" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="G7" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -12866,19 +12878,19 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D8" t="s">
         <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="F8" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="G8" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -13321,7 +13333,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -13332,14 +13344,15 @@
     <col min="6" max="6" width="7.41666666666667" customWidth="1"/>
     <col min="7" max="7" width="12.25" customWidth="1"/>
     <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="25.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="12" width="19.9166666666667" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="9" max="9" width="36.75" customWidth="1"/>
+    <col min="10" max="10" width="18.75" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
+    <col min="13" max="13" width="19.9166666666667" customWidth="1"/>
+    <col min="14" max="14" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13379,8 +13392,11 @@
       <c r="M1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -13391,10 +13407,10 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
@@ -13403,16 +13419,16 @@
         <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
         <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
         <v>32</v>
@@ -13420,34 +13436,37 @@
       <c r="M2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>612</v>
+        <v>76</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>613</v>
@@ -13456,39 +13475,42 @@
         <v>614</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" spans="1:13">
+        <v>615</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>622</v>
+        <v>76</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>623</v>
@@ -13502,19 +13524,22 @@
       <c r="M4" s="8" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F5">
         <v>1000</v>
@@ -13525,14 +13550,14 @@
       <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
+      <c r="I5" t="s">
+        <v>631</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>0</v>
+      <c r="K5" t="b">
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -13540,19 +13565,22 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>632</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>630</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>629</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -13563,14 +13591,14 @@
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
+      <c r="I6" t="s">
+        <v>631</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="K6">
-        <v>0</v>
+      <c r="K6" t="b">
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -13578,19 +13606,22 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -13601,14 +13632,14 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
+      <c r="I7" t="s">
+        <v>631</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13616,19 +13647,22 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -13639,14 +13673,14 @@
       <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
+      <c r="I8" t="s">
+        <v>631</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
-      <c r="K8">
-        <v>0</v>
+      <c r="K8" t="b">
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13654,11 +13688,55 @@
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9">
+        <v>4001</v>
+      </c>
+      <c r="C9" t="s">
+        <v>638</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9" t="s">
+        <v>639</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
@@ -13701,31 +13779,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="F1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="H1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="I1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="J1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="L1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -13772,31 +13850,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13807,37 +13885,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D4" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="F4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G4" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H4" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I4" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="J4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="K4" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="L4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M4" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13875,7 +13953,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13913,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13951,7 +14029,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13989,7 +14067,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14027,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14065,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14103,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14141,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -14179,7 +14257,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -14217,7 +14295,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -14255,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -14293,7 +14371,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -14331,7 +14409,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -14369,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -14403,13 +14481,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -14438,17 +14516,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -14459,19 +14537,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14651,7 +14729,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14889,7 +14967,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -14924,28 +15002,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="I1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -14988,28 +15066,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15020,31 +15098,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D4" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="F4" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="G4" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="I4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J4" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="K4" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15460,7 +15538,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15495,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15594,7 +15672,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15629,7 +15707,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15792,7 +15870,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -15827,7 +15905,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -15862,7 +15940,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -16069,25 +16147,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="F1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="G1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="I1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="L1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -16131,23 +16209,23 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16164,28 +16242,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F4" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G4" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H4" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="I4" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="J4" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K4" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="L4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -16199,16 +16277,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="K5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -16222,16 +16300,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F6" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H6" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="K6" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -16245,16 +16323,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="F7" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K7" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -16268,16 +16346,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="F8" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H8" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="K8" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -16291,16 +16369,16 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F9" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H9" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K9" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -16314,16 +16392,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F10" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K10" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -16337,16 +16415,16 @@
         <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F11" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H11" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J11" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -16360,16 +16438,16 @@
         <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F12" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H12" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J12" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -16397,10 +16475,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16417,7 +16495,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -16434,10 +16512,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16459,7 +16537,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -16473,7 +16551,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -16487,7 +16565,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D7" t="s">
         <v>393</v>
@@ -16511,7 +16589,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D10" t="s">
         <v>271</v>
@@ -16618,10 +16696,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -16646,10 +16724,10 @@
         <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="875">
   <si>
     <t>##var</t>
   </si>
@@ -1829,6 +1829,9 @@
     <t>CostChips</t>
   </si>
   <si>
+    <t>HintValueMode</t>
+  </si>
+  <si>
     <t>MaxRevealClickCount</t>
   </si>
   <si>
@@ -1857,6 +1860,9 @@
   </si>
   <si>
     <t>EBlindBoxDisplayMode</t>
+  </si>
+  <si>
+    <t>EBlindBoxValueMode</t>
   </si>
   <si>
     <t>float</t>
@@ -1908,6 +1914,9 @@
     <t>消耗筹码</t>
   </si>
   <si>
+    <t>提示文字模式</t>
+  </si>
+  <si>
     <t>最大揭晓点击次数</t>
   </si>
   <si>
@@ -1938,6 +1947,9 @@
     <t>三次升级表演</t>
   </si>
   <si>
+    <t>Chips</t>
+  </si>
+  <si>
     <t>UI\BlindBox\HintIcon_Common.png</t>
   </si>
   <si>
@@ -1957,6 +1969,9 @@
   </si>
   <si>
     <t>直接展示奖励</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
   <si>
     <t>盲盒券</t>
@@ -12107,49 +12122,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="F1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G1" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="H1" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="I1" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="J1" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="K1" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="L1" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="M1" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="N1" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="O1" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="P1" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="Q1" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -12187,10 +12202,10 @@
         <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="M2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -12210,52 +12225,52 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12263,52 +12278,52 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C4" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D4" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E4" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="F4" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="G4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="H4" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="I4" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J4" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="K4" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="L4" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="M4" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="N4" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="O4" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="P4" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="Q4" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12316,7 +12331,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12328,25 +12343,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="H5" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="I5" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="J5" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="K5" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="L5" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="M5" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12366,7 +12381,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12378,25 +12393,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="H6" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="I6" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="J6" t="s">
+        <v>817</v>
+      </c>
+      <c r="K6" t="s">
+        <v>817</v>
+      </c>
+      <c r="L6" t="s">
         <v>812</v>
       </c>
-      <c r="K6" t="s">
-        <v>812</v>
-      </c>
-      <c r="L6" t="s">
-        <v>807</v>
-      </c>
       <c r="M6" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12416,7 +12431,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12428,25 +12443,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="H7" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="I7" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="J7" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="K7" t="s">
+        <v>823</v>
+      </c>
+      <c r="L7" t="s">
+        <v>812</v>
+      </c>
+      <c r="M7" t="s">
         <v>818</v>
-      </c>
-      <c r="L7" t="s">
-        <v>807</v>
-      </c>
-      <c r="M7" t="s">
-        <v>813</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12466,7 +12481,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12478,25 +12493,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="H8" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="I8" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="J8" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="K8" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="L8" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="M8" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12549,43 +12564,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D1" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="G1" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="H1" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="I1" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="J1" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="K1" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="L1" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="M1" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="N1" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="O1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -12640,46 +12655,46 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -12687,46 +12702,46 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C4" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D4" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="E4" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="F4" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="G4" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="H4" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="I4" t="s">
         <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="K4" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="L4" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="M4" t="s">
         <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="O4" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -12737,19 +12752,19 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="F5" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="G5" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -12784,19 +12799,19 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="D6" t="s">
         <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="F6" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="G6" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -12831,19 +12846,19 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
       </c>
       <c r="E7" t="s">
+        <v>870</v>
+      </c>
+      <c r="F7" t="s">
+        <v>871</v>
+      </c>
+      <c r="G7" t="s">
         <v>865</v>
-      </c>
-      <c r="F7" t="s">
-        <v>866</v>
-      </c>
-      <c r="G7" t="s">
-        <v>860</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -12878,19 +12893,19 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="D8" t="s">
         <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="F8" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="G8" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -13333,7 +13348,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -13341,18 +13356,19 @@
     <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
     <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
     <col min="5" max="5" width="22.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.41666666666667" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="36.75" customWidth="1"/>
-    <col min="10" max="10" width="18.75" customWidth="1"/>
-    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
-    <col min="12" max="12" width="17.25" customWidth="1"/>
-    <col min="13" max="13" width="19.9166666666667" customWidth="1"/>
-    <col min="14" max="14" width="21.25" customWidth="1"/>
+    <col min="6" max="6" width="8.75" customWidth="1"/>
+    <col min="7" max="7" width="19.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="20.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="36.75" customWidth="1"/>
+    <col min="11" max="11" width="14.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="23.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="28.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13395,8 +13411,11 @@
       <c r="N1" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -13407,31 +13426,31 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
       </c>
       <c r="G2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
-        <v>605</v>
-      </c>
       <c r="I2" t="s">
+        <v>607</v>
+      </c>
+      <c r="J2" t="s">
         <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
       </c>
       <c r="K2" t="s">
         <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
         <v>32</v>
@@ -13439,128 +13458,134 @@
       <c r="N2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:14">
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>613</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" spans="1:14">
+        <v>617</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>623</v>
-      </c>
       <c r="K4" s="8" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>629</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F5">
         <v>1000</v>
       </c>
-      <c r="G5">
-        <v>3</v>
+      <c r="G5" t="s">
+        <v>634</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" t="s">
-        <v>631</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>635</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="b">
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -13568,40 +13593,43 @@
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>630</v>
       </c>
       <c r="F6">
         <v>1000</v>
       </c>
-      <c r="G6">
-        <v>3</v>
+      <c r="G6" t="s">
+        <v>634</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" t="s">
-        <v>631</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>635</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="b">
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -13609,40 +13637,43 @@
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F7">
         <v>1000</v>
       </c>
-      <c r="G7">
-        <v>3</v>
+      <c r="G7" t="s">
+        <v>634</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" t="s">
-        <v>631</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>635</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -13650,40 +13681,43 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>3001</v>
       </c>
       <c r="C8" t="s">
+        <v>639</v>
+      </c>
+      <c r="D8" t="s">
+        <v>640</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>642</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8" t="s">
         <v>635</v>
       </c>
-      <c r="D8" t="s">
-        <v>636</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>631</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="b">
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -13691,40 +13725,43 @@
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9">
         <v>4001</v>
       </c>
       <c r="C9" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>3</v>
+      <c r="G9" t="s">
+        <v>642</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
-      <c r="I9" t="s">
-        <v>639</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>644</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="b">
+        <v>1</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -13732,11 +13769,14 @@
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
@@ -13779,31 +13819,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="E1" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="G1" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="H1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="I1" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="J1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -13850,31 +13890,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13885,37 +13925,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="G4" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="I4" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="J4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K4" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="L4" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="M4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13923,7 +13963,7 @@
         <v>1001</v>
       </c>
       <c r="C5">
-        <v>1001</v>
+        <v>4001</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -13953,7 +13993,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13991,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14029,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -14067,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14105,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14143,7 +14183,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14181,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14219,7 +14259,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -14257,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -14295,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -14333,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -14371,7 +14411,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -14409,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -14447,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -14459,7 +14499,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.08333333333333" customWidth="1"/>
@@ -14481,13 +14521,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="E1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="G1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -14516,17 +14556,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -14537,19 +14577,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G4" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14729,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14967,7 +15007,147 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>685</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28">
+        <v>400101</v>
+      </c>
+      <c r="C28">
+        <v>4001</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" ref="F28:F33" si="1">E28/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29">
+        <v>400102</v>
+      </c>
+      <c r="C29">
+        <v>4001</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29">
+        <v>6700</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="1"/>
+        <v>0.67</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30">
+        <v>400103</v>
+      </c>
+      <c r="C30">
+        <v>4001</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30">
+        <v>2200</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="1"/>
+        <v>0.22</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="B31">
+        <v>400104</v>
+      </c>
+      <c r="C31">
+        <v>4001</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="7">
+        <v>900</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="1"/>
+        <v>0.09</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="B32">
+        <v>400105</v>
+      </c>
+      <c r="C32">
+        <v>4001</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="7">
+        <v>180</v>
+      </c>
+      <c r="F32" s="5">
+        <f t="shared" si="1"/>
+        <v>0.018</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33">
+        <v>400106</v>
+      </c>
+      <c r="C33">
+        <v>4001</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33">
+        <v>20</v>
+      </c>
+      <c r="F33" s="5">
+        <f t="shared" si="1"/>
+        <v>0.002</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="F34" s="5">
+        <f>SUM(F28:F33)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15002,28 +15182,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="E1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F1" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G1" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="H1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="I1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J1" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -15066,28 +15246,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15098,31 +15278,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D4" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E4" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="F4" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G4" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="H4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="I4" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="J4" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="K4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15538,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15573,7 +15753,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15672,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15707,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15870,7 +16050,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -15905,7 +16085,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -15940,7 +16120,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -16147,25 +16327,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="F1" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G1" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="H1" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="I1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="K1" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L1" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -16209,23 +16389,23 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16242,28 +16422,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="F4" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="G4" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="H4" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="I4" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="J4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="K4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="L4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -16277,16 +16457,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="F5" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H5" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="K5" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -16300,16 +16480,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="F6" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H6" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="K6" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -16323,16 +16503,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="F7" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H7" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="K7" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -16346,16 +16526,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="F8" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H8" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="K8" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -16369,16 +16549,16 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="F9" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H9" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="K9" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -16392,16 +16572,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F10" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H10" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="K10" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -16415,16 +16595,16 @@
         <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F11" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H11" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="J11" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -16438,16 +16618,16 @@
         <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F12" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H12" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="J12" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -16475,10 +16655,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D1" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16495,7 +16675,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -16512,10 +16692,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E3" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16537,7 +16717,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -16551,7 +16731,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -16565,7 +16745,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D7" t="s">
         <v>393</v>
@@ -16589,7 +16769,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D10" t="s">
         <v>271</v>
@@ -16696,10 +16876,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="D1" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -16724,10 +16904,10 @@
         <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="D3" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1850,7 +1850,7 @@
     <t>HintIconPath</t>
   </si>
   <si>
-    <t>IsRequiresPlatformInventory</t>
+    <t>IsPlatformInventoryRequired</t>
   </si>
   <si>
     <t>IsEnabled</t>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2700,16 +2700,16 @@
     <t>Opens one decoration blind box.</t>
   </si>
   <si>
-    <t>DecorationBlindBoxTestV1Generator</t>
-  </si>
-  <si>
-    <t>测试用盲盒物品生成器</t>
+    <t>DecorationBlindBoxV1Generator</t>
+  </si>
+  <si>
+    <t>盲盒物品生成器V1</t>
   </si>
   <si>
     <t>Generator</t>
   </si>
   <si>
-    <t>Decoration Blind Box Test V1 Generator</t>
+    <t>Decoration Blind Box V1 Generator</t>
   </si>
   <si>
     <t>Generates one decoration reward.</t>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="948">
   <si>
     <t>##var</t>
   </si>
@@ -2006,6 +2006,9 @@
     <t>MaxPendingCount</t>
   </si>
   <si>
+    <t>SteamPlaytimeGeneratorItemDefId</t>
+  </si>
+  <si>
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
@@ -2033,6 +2036,12 @@
     <t>最多保留几个待领取资格</t>
   </si>
   <si>
+    <t>该调度到达资格时间时，通过 TriggerItemDrop 请求的 Steam playtimegenerator ItemDef ID。不接入 Steam 掉落时填 0。同一个 ItemDef ID 不建议被多条调度共用。</t>
+  </si>
+  <si>
+    <t>之所以分了12条新手期，而不是3种盲盒循环4次，是因为后续版本可以更精细的控制新手体验，例如先掉帽子盲盒、再掉眼镜盲盒、桌布……</t>
+  </si>
+  <si>
     <t>是循环生效的</t>
   </si>
   <si>
@@ -2055,6 +2064,9 @@
   </si>
   <si>
     <t>最大待领取数</t>
+  </si>
+  <si>
+    <t>Steam游玩时间生成器DefID</t>
   </si>
   <si>
     <t>备注</t>
@@ -2599,7 +2611,10 @@
     <t>是否将同定义物品自动堆叠；一次性回执填 FALSE</t>
   </si>
   <si>
-    <t>Bundle/Generator 的内容配方；普通 Item 留空</t>
+    <t>Bundle/Generator 的内容配方。
+留空表示不输出 bundle；
+填写 @AUTO 表示由转换器根据业务表生成；
+也可直接填写 Steam 配方，例如 101002x1;101003x1。</t>
   </si>
   <si>
     <t>是否参与导出到 Steam ItemDef 配置</t>
@@ -2711,6 +2726,177 @@
   </si>
   <si>
     <t>101002x1;101003x1</t>
+  </si>
+  <si>
+    <t>StandardBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>标准盲盒开箱成本</t>
+  </si>
+  <si>
+    <t>Standard Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one standard blind box.</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>新手盲盒开箱成本</t>
+  </si>
+  <si>
+    <t>Newbie Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one newbie blind box.</t>
+  </si>
+  <si>
+    <t>StandardBlindBoxV1Generator</t>
+  </si>
+  <si>
+    <t>标准盲盒物品生成器V1</t>
+  </si>
+  <si>
+    <t>Standard Blind Box V1 Generator</t>
+  </si>
+  <si>
+    <t>Generates one standard blind box reward.</t>
+  </si>
+  <si>
+    <t>@AUTO</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxV1Generator</t>
+  </si>
+  <si>
+    <t>新手盲盒物品生成器V1</t>
+  </si>
+  <si>
+    <t>Newbie Blind Box V1 Generator</t>
+  </si>
+  <si>
+    <t>Generates one newbie blind box reward.</t>
+  </si>
+  <si>
+    <t>404 表示游玩时间生成器</t>
+  </si>
+  <si>
+    <t>Schedule1001PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1001游玩时间掉落</t>
+  </si>
+  <si>
+    <t>PlaytimeGenerator</t>
+  </si>
+  <si>
+    <t>Schedule 1001 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1001.</t>
+  </si>
+  <si>
+    <t>402002x1</t>
+  </si>
+  <si>
+    <t>Schedule1002PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1002游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1002 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1002.</t>
+  </si>
+  <si>
+    <t>402003x1</t>
+  </si>
+  <si>
+    <t>Schedule1004PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1004游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1004 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1004.</t>
+  </si>
+  <si>
+    <t>Schedule1005PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1005游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1005 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1005.</t>
+  </si>
+  <si>
+    <t>Schedule1007PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1007游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1007 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1007.</t>
+  </si>
+  <si>
+    <t>Schedule1008PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1008游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1008 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1008.</t>
+  </si>
+  <si>
+    <t>Schedule1010PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1010游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1010 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1010.</t>
+  </si>
+  <si>
+    <t>Schedule1011PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1011游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1011 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1011.</t>
+  </si>
+  <si>
+    <t>Schedule1013PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1013循环游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1013 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the recurring standard blind box item configured by schedule 1013.</t>
   </si>
 </sst>
 </file>
@@ -2880,12 +3066,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2895,7 +3087,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
+        <fgColor rgb="FFEFE4B7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3224,7 +3416,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3248,16 +3440,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3266,89 +3458,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3356,6 +3548,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3379,14 +3574,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3704,6 +3902,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="14"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00EFE4B7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3976,11 +4179,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="10" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="12" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="10" customWidth="1"/>
+    <col min="23" max="23" width="7" style="12" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -3997,16 +4200,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="4"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -4022,15 +4225,12 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1"/>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1"/>
-      <c r="N1"/>
       <c r="O1" t="s">
         <v>10</v>
       </c>
@@ -4090,16 +4290,16 @@
       </c>
     </row>
     <row r="2" spans="1:35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="4"/>
       <c r="E2" t="s">
         <v>32</v>
       </c>
@@ -4124,8 +4324,6 @@
       <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
       <c r="O2" t="s">
         <v>30</v>
       </c>
@@ -4185,12 +4383,12 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -4205,7 +4403,7 @@
       <c r="J3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="13"/>
       <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
@@ -4216,14 +4414,14 @@
       <c r="R3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="12"/>
+      <c r="S3" s="2"/>
       <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="12"/>
+      <c r="W3" s="2"/>
       <c r="X3" s="1" t="s">
         <v>50</v>
       </c>
@@ -4262,16 +4460,16 @@
       </c>
     </row>
     <row r="4" spans="1:35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E4" t="s">
@@ -4362,71 +4560,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
-      <c r="B5">
+    <row r="5" s="11" customFormat="1" spans="1:35">
+      <c r="B5" s="11">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="11">
         <v>200</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="M5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="11">
         <v>1001</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="W5" s="11"/>
+      <c r="Y5" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
+      <c r="AA5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4485,9 +4684,7 @@
       <c r="Y6" t="s">
         <v>96</v>
       </c>
-      <c r="Z6" t="s">
-        <v>97</v>
-      </c>
+      <c r="Z6"/>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
@@ -4559,9 +4756,7 @@
       <c r="Y7" t="s">
         <v>96</v>
       </c>
-      <c r="Z7" t="s">
-        <v>103</v>
-      </c>
+      <c r="Z7"/>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
@@ -4628,11 +4823,12 @@
         <v>1004</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>101004</v>
       </c>
       <c r="Y8" t="s">
         <v>96</v>
       </c>
+      <c r="Z8"/>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
@@ -4699,11 +4895,12 @@
         <v>1005</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>101005</v>
       </c>
       <c r="Y9" t="s">
         <v>96</v>
       </c>
+      <c r="Z9"/>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
@@ -4770,11 +4967,12 @@
         <v>1006</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>101006</v>
       </c>
       <c r="Y10" t="s">
         <v>96</v>
       </c>
+      <c r="Z10"/>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
@@ -4841,11 +5039,12 @@
         <v>1007</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>101007</v>
       </c>
       <c r="Y11" t="s">
         <v>96</v>
       </c>
+      <c r="Z11"/>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
@@ -4896,10 +5095,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="9">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -4912,11 +5111,12 @@
         <v>1008</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>101008</v>
       </c>
       <c r="Y12" t="s">
         <v>96</v>
       </c>
+      <c r="Z12"/>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
@@ -4983,11 +5183,12 @@
         <v>1009</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>101009</v>
       </c>
       <c r="Y13" t="s">
         <v>96</v>
       </c>
+      <c r="Z13"/>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
@@ -5054,11 +5255,12 @@
         <v>1010</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>101010</v>
       </c>
       <c r="Y14" t="s">
         <v>96</v>
       </c>
+      <c r="Z14"/>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
@@ -5125,11 +5327,12 @@
         <v>1011</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>101011</v>
       </c>
       <c r="Y15" t="s">
         <v>96</v>
       </c>
+      <c r="Z15"/>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
@@ -5196,11 +5399,12 @@
         <v>1012</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>101012</v>
       </c>
       <c r="Y16" t="s">
         <v>96</v>
       </c>
+      <c r="Z16"/>
       <c r="AA16" t="b">
         <v>1</v>
       </c>
@@ -5269,11 +5473,12 @@
         <v>142</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>102001</v>
       </c>
       <c r="Y18" t="s">
         <v>96</v>
       </c>
+      <c r="Z18"/>
       <c r="AA18" t="b">
         <v>1</v>
       </c>
@@ -5337,11 +5542,12 @@
         <v>146</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>102002</v>
       </c>
       <c r="Y19" t="s">
         <v>96</v>
       </c>
+      <c r="Z19"/>
       <c r="AA19" t="b">
         <v>1</v>
       </c>
@@ -5405,11 +5611,12 @@
         <v>150</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>102003</v>
       </c>
       <c r="Y20" t="s">
         <v>96</v>
       </c>
+      <c r="Z20"/>
       <c r="AA20" t="b">
         <v>1</v>
       </c>
@@ -5473,11 +5680,12 @@
         <v>154</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>102004</v>
       </c>
       <c r="Y21" t="s">
         <v>96</v>
       </c>
+      <c r="Z21"/>
       <c r="AA21" t="b">
         <v>1</v>
       </c>
@@ -5541,11 +5749,12 @@
         <v>158</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>102005</v>
       </c>
       <c r="Y22" t="s">
         <v>96</v>
       </c>
+      <c r="Z22"/>
       <c r="AA22" t="b">
         <v>1</v>
       </c>
@@ -5614,7 +5823,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -5624,11 +5833,12 @@
         <v>163</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>102006</v>
       </c>
       <c r="Y23" t="s">
         <v>96</v>
       </c>
+      <c r="Z23"/>
       <c r="AA23" t="b">
         <v>1</v>
       </c>
@@ -5692,11 +5902,12 @@
         <v>167</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>102007</v>
       </c>
       <c r="Y24" t="s">
         <v>96</v>
       </c>
+      <c r="Z24"/>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
@@ -5760,11 +5971,12 @@
         <v>171</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>102008</v>
       </c>
       <c r="Y25" t="s">
         <v>96</v>
       </c>
+      <c r="Z25"/>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
@@ -5828,11 +6040,12 @@
         <v>175</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>102009</v>
       </c>
       <c r="Y26" t="s">
         <v>96</v>
       </c>
+      <c r="Z26"/>
       <c r="AA26" t="b">
         <v>1</v>
       </c>
@@ -5896,11 +6109,12 @@
         <v>179</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>102010</v>
       </c>
       <c r="Y27" t="s">
         <v>96</v>
       </c>
+      <c r="Z27"/>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
@@ -5972,7 +6186,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -5984,15 +6198,16 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="10" t="s">
+      <c r="W28" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>102011</v>
       </c>
       <c r="Y28" t="s">
         <v>96</v>
       </c>
+      <c r="Z28"/>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
@@ -6076,7 +6291,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="S29" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -6088,15 +6303,16 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="10" t="s">
+      <c r="W29" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>102012</v>
       </c>
       <c r="Y29" t="s">
         <v>96</v>
       </c>
+      <c r="Z29"/>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
@@ -6172,11 +6388,12 @@
         <v>192</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>103001</v>
       </c>
       <c r="Y30" t="s">
         <v>96</v>
       </c>
+      <c r="Z30"/>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
@@ -6240,11 +6457,12 @@
         <v>196</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>103002</v>
       </c>
       <c r="Y31" t="s">
         <v>96</v>
       </c>
+      <c r="Z31"/>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
@@ -6308,11 +6526,12 @@
         <v>200</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>103003</v>
       </c>
       <c r="Y32" t="s">
         <v>96</v>
       </c>
+      <c r="Z32"/>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
@@ -6376,11 +6595,12 @@
         <v>204</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>103004</v>
       </c>
       <c r="Y33" t="s">
         <v>96</v>
       </c>
+      <c r="Z33"/>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
@@ -6444,11 +6664,12 @@
         <v>208</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>103005</v>
       </c>
       <c r="Y34" t="s">
         <v>96</v>
       </c>
+      <c r="Z34"/>
       <c r="AA34" t="b">
         <v>1</v>
       </c>
@@ -6465,429 +6686,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:31">
-      <c r="B35">
+    <row r="35" s="11" customFormat="1" spans="2:31">
+      <c r="B35" s="11">
         <v>4001</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="I35" s="11">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11">
+        <v>0</v>
+      </c>
+      <c r="K35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M35" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="T35" t="s">
+      <c r="M35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="U35" t="s">
+      <c r="U35" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="s">
+      <c r="X35" s="11">
+        <v>104001</v>
+      </c>
+      <c r="Y35" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:31">
-      <c r="B36">
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="11" customFormat="1" spans="2:31">
+      <c r="B36" s="11">
         <v>4002</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="I36" s="11">
+        <v>0</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0</v>
+      </c>
+      <c r="K36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M36" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="T36" t="s">
+      <c r="M36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0</v>
+      </c>
+      <c r="O36" s="11">
+        <v>0</v>
+      </c>
+      <c r="P36" s="11">
+        <v>0</v>
+      </c>
+      <c r="T36" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="U36" t="s">
+      <c r="U36" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="s">
+      <c r="X36" s="11">
+        <v>104002</v>
+      </c>
+      <c r="Y36" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31">
-      <c r="B37">
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="11" customFormat="1" spans="2:31">
+      <c r="B37" s="11">
         <v>4003</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
+      <c r="I37" s="11">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0</v>
+      </c>
+      <c r="K37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M37" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="T37" t="s">
+      <c r="M37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="11">
+        <v>0</v>
+      </c>
+      <c r="O37" s="11">
+        <v>0</v>
+      </c>
+      <c r="P37" s="11">
+        <v>0</v>
+      </c>
+      <c r="T37" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="U37" t="s">
+      <c r="U37" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="s">
+      <c r="X37" s="11">
+        <v>104003</v>
+      </c>
+      <c r="Y37" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31">
-      <c r="B38">
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="11" customFormat="1" spans="2:31">
+      <c r="B38" s="11">
         <v>4004</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="I38" s="11">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11">
+        <v>0</v>
+      </c>
+      <c r="K38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M38" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="T38" t="s">
+      <c r="M38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="11">
+        <v>0</v>
+      </c>
+      <c r="O38" s="11">
+        <v>0</v>
+      </c>
+      <c r="P38" s="11">
+        <v>0</v>
+      </c>
+      <c r="T38" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="U38" t="s">
+      <c r="U38" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="s">
+      <c r="X38" s="11">
+        <v>104004</v>
+      </c>
+      <c r="Y38" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31">
-      <c r="B39">
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="11" customFormat="1" spans="2:31">
+      <c r="B39" s="11">
         <v>4005</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="I39" s="11">
+        <v>0</v>
+      </c>
+      <c r="J39" s="11">
+        <v>0</v>
+      </c>
+      <c r="K39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M39" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="M39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="11">
+        <v>0</v>
+      </c>
+      <c r="P39" s="11">
+        <v>0</v>
+      </c>
+      <c r="T39" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="U39" t="s">
+      <c r="U39" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="s">
+      <c r="X39" s="11">
+        <v>104005</v>
+      </c>
+      <c r="Y39" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31">
-      <c r="B40">
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="11" customFormat="1" spans="2:31">
+      <c r="B40" s="11">
         <v>4006</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="I40" s="11">
+        <v>0</v>
+      </c>
+      <c r="J40" s="11">
+        <v>0</v>
+      </c>
+      <c r="K40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M40" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="M40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="11">
+        <v>0</v>
+      </c>
+      <c r="O40" s="11">
+        <v>0</v>
+      </c>
+      <c r="P40" s="11">
+        <v>0</v>
+      </c>
+      <c r="T40" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U40" t="s">
+      <c r="U40" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="s">
+      <c r="X40" s="11">
+        <v>104006</v>
+      </c>
+      <c r="Y40" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
+      <c r="Z40" s="11"/>
+      <c r="AA40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6938,11 +7165,12 @@
         <v>239</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>105001</v>
       </c>
       <c r="Y41" t="s">
         <v>96</v>
       </c>
+      <c r="Z41"/>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
@@ -7006,11 +7234,12 @@
         <v>243</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>105002</v>
       </c>
       <c r="Y42" t="s">
         <v>96</v>
       </c>
+      <c r="Z42"/>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
@@ -7074,11 +7303,12 @@
         <v>247</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>105003</v>
       </c>
       <c r="Y43" t="s">
         <v>96</v>
       </c>
+      <c r="Z43"/>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
@@ -7142,11 +7372,12 @@
         <v>251</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>105004</v>
       </c>
       <c r="Y44" t="s">
         <v>96</v>
       </c>
+      <c r="Z44"/>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
@@ -7210,11 +7441,12 @@
         <v>255</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>105005</v>
       </c>
       <c r="Y45" t="s">
         <v>96</v>
       </c>
+      <c r="Z45"/>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
@@ -7278,11 +7510,12 @@
         <v>259</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>105006</v>
       </c>
       <c r="Y46" t="s">
         <v>96</v>
       </c>
+      <c r="Z46"/>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
@@ -7346,11 +7579,12 @@
         <v>263</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>105007</v>
       </c>
       <c r="Y47" t="s">
         <v>96</v>
       </c>
+      <c r="Z47"/>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
@@ -7414,11 +7648,12 @@
         <v>267</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>105008</v>
       </c>
       <c r="Y48" t="s">
         <v>96</v>
       </c>
+      <c r="Z48"/>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
@@ -7435,86 +7670,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:31">
-      <c r="B49">
+    <row r="49" s="11" customFormat="1" spans="2:31">
+      <c r="B49" s="11">
         <v>6001</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="F49" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="F49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I49">
-        <v>300</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
+      <c r="I49" s="11">
+        <v>300</v>
+      </c>
+      <c r="J49" s="11">
+        <v>0</v>
+      </c>
+      <c r="K49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" t="s">
+      <c r="M49" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="11">
+        <v>0</v>
+      </c>
+      <c r="O49" s="11">
+        <v>0</v>
+      </c>
+      <c r="P49" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="U49" t="s">
+      <c r="U49" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="s">
+      <c r="X49" s="11">
+        <v>106001</v>
+      </c>
+      <c r="Y49" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7570,7 +7806,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="10" t="s">
+      <c r="S50" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -7580,11 +7816,12 @@
         <v>276</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>106002</v>
       </c>
       <c r="Y50" t="s">
         <v>96</v>
       </c>
+      <c r="Z50"/>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
@@ -7653,7 +7890,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="10" t="s">
+      <c r="S51" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -7663,11 +7900,12 @@
         <v>280</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>106003</v>
       </c>
       <c r="Y51" t="s">
         <v>96</v>
       </c>
+      <c r="Z51"/>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
@@ -7736,7 +7974,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="10" t="s">
+      <c r="S52" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -7746,11 +7984,12 @@
         <v>284</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>106004</v>
       </c>
       <c r="Y52" t="s">
         <v>96</v>
       </c>
+      <c r="Z52"/>
       <c r="AA52" t="b">
         <v>1</v>
       </c>
@@ -7819,7 +8058,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="10" t="s">
+      <c r="S53" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -7829,11 +8068,12 @@
         <v>288</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>106005</v>
       </c>
       <c r="Y53" t="s">
         <v>96</v>
       </c>
+      <c r="Z53"/>
       <c r="AA53" t="b">
         <v>1</v>
       </c>
@@ -7902,7 +8142,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="10" t="s">
+      <c r="S54" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -7912,11 +8152,12 @@
         <v>292</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>106006</v>
       </c>
       <c r="Y54" t="s">
         <v>96</v>
       </c>
+      <c r="Z54"/>
       <c r="AA54" t="b">
         <v>1</v>
       </c>
@@ -7985,7 +8226,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="10" t="s">
+      <c r="S55" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -7995,11 +8236,12 @@
         <v>296</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>106007</v>
       </c>
       <c r="Y55" t="s">
         <v>96</v>
       </c>
+      <c r="Z55"/>
       <c r="AA55" t="b">
         <v>1</v>
       </c>
@@ -8068,7 +8310,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="10" t="s">
+      <c r="S56" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -8078,11 +8320,12 @@
         <v>300</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>106008</v>
       </c>
       <c r="Y56" t="s">
         <v>96</v>
       </c>
+      <c r="Z56"/>
       <c r="AA56" t="b">
         <v>1</v>
       </c>
@@ -8151,7 +8394,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="10" t="s">
+      <c r="S57" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -8161,11 +8404,12 @@
         <v>304</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>106009</v>
       </c>
       <c r="Y57" t="s">
         <v>96</v>
       </c>
+      <c r="Z57"/>
       <c r="AA57" t="b">
         <v>1</v>
       </c>
@@ -8234,7 +8478,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="10" t="s">
+      <c r="S58" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -8244,11 +8488,12 @@
         <v>308</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>106010</v>
       </c>
       <c r="Y58" t="s">
         <v>96</v>
       </c>
+      <c r="Z58"/>
       <c r="AA58" t="b">
         <v>1</v>
       </c>
@@ -8317,7 +8562,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="10" t="s">
+      <c r="S59" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -8327,11 +8572,12 @@
         <v>312</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>106011</v>
       </c>
       <c r="Y59" t="s">
         <v>96</v>
       </c>
+      <c r="Z59"/>
       <c r="AA59" t="b">
         <v>1</v>
       </c>
@@ -8395,11 +8641,12 @@
         <v>317</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>107001</v>
       </c>
       <c r="Y60" t="s">
         <v>96</v>
       </c>
+      <c r="Z60"/>
       <c r="AA60" t="b">
         <v>1</v>
       </c>
@@ -8463,11 +8710,12 @@
         <v>321</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>107002</v>
       </c>
       <c r="Y61" t="s">
         <v>96</v>
       </c>
+      <c r="Z61"/>
       <c r="AA61" t="b">
         <v>1</v>
       </c>
@@ -8531,11 +8779,12 @@
         <v>325</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>107003</v>
       </c>
       <c r="Y62" t="s">
         <v>96</v>
       </c>
+      <c r="Z62"/>
       <c r="AA62" t="b">
         <v>1</v>
       </c>
@@ -8552,71 +8801,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:31">
-      <c r="B63">
+    <row r="63" s="11" customFormat="1" spans="2:31">
+      <c r="B63" s="11">
         <v>7004</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I63">
-        <v>300</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
+      <c r="I63" s="11">
+        <v>300</v>
+      </c>
+      <c r="J63" s="11">
+        <v>0</v>
+      </c>
+      <c r="K63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M63" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="T63" t="s">
+      <c r="M63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
+      <c r="O63" s="11">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11">
+        <v>0</v>
+      </c>
+      <c r="T63" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="U63" t="s">
+      <c r="U63" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="s">
+      <c r="X63" s="11">
+        <v>107004</v>
+      </c>
+      <c r="Y63" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
+      <c r="Z63" s="11"/>
+      <c r="AA63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8633,7 +8883,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8667,11 +8917,12 @@
         <v>333</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>107005</v>
       </c>
       <c r="Y64" t="s">
         <v>96</v>
       </c>
+      <c r="Z64"/>
       <c r="AA64" t="b">
         <v>1</v>
       </c>
@@ -8701,7 +8952,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8735,11 +8986,12 @@
         <v>337</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>107006</v>
       </c>
       <c r="Y65" t="s">
         <v>96</v>
       </c>
+      <c r="Z65"/>
       <c r="AA65" t="b">
         <v>1</v>
       </c>
@@ -8803,11 +9055,12 @@
         <v>341</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>107007</v>
       </c>
       <c r="Y66" t="s">
         <v>96</v>
       </c>
+      <c r="Z66"/>
       <c r="AA66" t="b">
         <v>1</v>
       </c>
@@ -8876,7 +9129,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="10" t="s">
+      <c r="S67" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -8886,11 +9139,12 @@
         <v>345</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>107008</v>
       </c>
       <c r="Y67" t="s">
         <v>96</v>
       </c>
+      <c r="Z67"/>
       <c r="AA67" t="b">
         <v>1</v>
       </c>
@@ -8959,7 +9213,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="10" t="s">
+      <c r="S68" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -8969,11 +9223,12 @@
         <v>349</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>107009</v>
       </c>
       <c r="Y68" t="s">
         <v>96</v>
       </c>
+      <c r="Z68"/>
       <c r="AA68" t="b">
         <v>1</v>
       </c>
@@ -9042,7 +9297,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="10" t="s">
+      <c r="S69" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -9052,11 +9307,12 @@
         <v>353</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>107010</v>
       </c>
       <c r="Y69" t="s">
         <v>96</v>
       </c>
+      <c r="Z69"/>
       <c r="AA69" t="b">
         <v>1</v>
       </c>
@@ -9125,7 +9381,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="10" t="s">
+      <c r="S70" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -9135,11 +9391,12 @@
         <v>357</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>107011</v>
       </c>
       <c r="Y70" t="s">
         <v>96</v>
       </c>
+      <c r="Z70"/>
       <c r="AA70" t="b">
         <v>1</v>
       </c>
@@ -9208,7 +9465,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="10" t="s">
+      <c r="S71" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -9218,11 +9475,12 @@
         <v>361</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>107012</v>
       </c>
       <c r="Y71" t="s">
         <v>96</v>
       </c>
+      <c r="Z71"/>
       <c r="AA71" t="b">
         <v>1</v>
       </c>
@@ -9291,7 +9549,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="10" t="s">
+      <c r="S72" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -9301,11 +9559,12 @@
         <v>365</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>107013</v>
       </c>
       <c r="Y72" t="s">
         <v>96</v>
       </c>
+      <c r="Z72"/>
       <c r="AA72" t="b">
         <v>1</v>
       </c>
@@ -9374,7 +9633,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="10" t="s">
+      <c r="S73" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -9384,11 +9643,12 @@
         <v>369</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>107014</v>
       </c>
       <c r="Y73" t="s">
         <v>96</v>
       </c>
+      <c r="Z73"/>
       <c r="AA73" t="b">
         <v>1</v>
       </c>
@@ -9457,7 +9717,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="10" t="s">
+      <c r="S74" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -9467,11 +9727,12 @@
         <v>373</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>107015</v>
       </c>
       <c r="Y74" t="s">
         <v>96</v>
       </c>
+      <c r="Z74"/>
       <c r="AA74" t="b">
         <v>1</v>
       </c>
@@ -9540,7 +9801,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="10" t="s">
+      <c r="S75" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -9550,11 +9811,12 @@
         <v>377</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>107016</v>
       </c>
       <c r="Y75" t="s">
         <v>96</v>
       </c>
+      <c r="Z75"/>
       <c r="AA75" t="b">
         <v>1</v>
       </c>
@@ -9623,7 +9885,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="10" t="s">
+      <c r="S76" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -9633,11 +9895,12 @@
         <v>381</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>107017</v>
       </c>
       <c r="Y76" t="s">
         <v>96</v>
       </c>
+      <c r="Z76"/>
       <c r="AA76" t="b">
         <v>1</v>
       </c>
@@ -9701,11 +9964,12 @@
         <v>385</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>107018</v>
       </c>
       <c r="Y77" t="s">
         <v>96</v>
       </c>
+      <c r="Z77"/>
       <c r="AA77" t="b">
         <v>1</v>
       </c>
@@ -9777,7 +10041,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="10" t="s">
+      <c r="S78" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -9789,15 +10053,16 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="10" t="s">
+      <c r="W78" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>107019</v>
       </c>
       <c r="Y78" t="s">
         <v>96</v>
       </c>
+      <c r="Z78"/>
       <c r="AA78" t="b">
         <v>1</v>
       </c>
@@ -9878,7 +10143,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="10" t="s">
+      <c r="S79" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -9888,11 +10153,12 @@
         <v>394</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>108001</v>
       </c>
       <c r="Y79" t="s">
         <v>96</v>
       </c>
+      <c r="Z79"/>
       <c r="AA79" t="b">
         <v>1</v>
       </c>
@@ -9961,7 +10227,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="10" t="s">
+      <c r="S80" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -9971,11 +10237,12 @@
         <v>398</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>108003</v>
       </c>
       <c r="Y80" t="s">
         <v>96</v>
       </c>
+      <c r="Z80"/>
       <c r="AA80" t="b">
         <v>1</v>
       </c>
@@ -10044,7 +10311,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="10" t="s">
+      <c r="S81" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -10054,11 +10321,12 @@
         <v>402</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>108004</v>
       </c>
       <c r="Y81" t="s">
         <v>96</v>
       </c>
+      <c r="Z81"/>
       <c r="AA81" t="b">
         <v>1</v>
       </c>
@@ -10127,7 +10395,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="10" t="s">
+      <c r="S82" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -10137,11 +10405,12 @@
         <v>406</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>108005</v>
       </c>
       <c r="Y82" t="s">
         <v>96</v>
       </c>
+      <c r="Z82"/>
       <c r="AA82" t="b">
         <v>1</v>
       </c>
@@ -10210,7 +10479,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="10" t="s">
+      <c r="S83" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -10220,11 +10489,12 @@
         <v>410</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>108007</v>
       </c>
       <c r="Y83" t="s">
         <v>96</v>
       </c>
+      <c r="Z83"/>
       <c r="AA83" t="b">
         <v>1</v>
       </c>
@@ -10293,7 +10563,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="10" t="s">
+      <c r="S84" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -10303,11 +10573,12 @@
         <v>414</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>108008</v>
       </c>
       <c r="Y84" t="s">
         <v>96</v>
       </c>
+      <c r="Z84"/>
       <c r="AA84" t="b">
         <v>1</v>
       </c>
@@ -10371,11 +10642,12 @@
         <v>418</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>108009</v>
       </c>
       <c r="Y85" t="s">
         <v>96</v>
       </c>
+      <c r="Z85"/>
       <c r="AA85" t="b">
         <v>1</v>
       </c>
@@ -10439,11 +10711,12 @@
         <v>422</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>108010</v>
       </c>
       <c r="Y86" t="s">
         <v>96</v>
       </c>
+      <c r="Z86"/>
       <c r="AA86" t="b">
         <v>1</v>
       </c>
@@ -10507,11 +10780,12 @@
         <v>426</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>108011</v>
       </c>
       <c r="Y87" t="s">
         <v>96</v>
       </c>
+      <c r="Z87"/>
       <c r="AA87" t="b">
         <v>1</v>
       </c>
@@ -10583,7 +10857,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="10" t="s">
+      <c r="S88" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -10595,15 +10869,16 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="10" t="s">
+      <c r="W88" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>108012</v>
       </c>
       <c r="Y88" t="s">
         <v>96</v>
       </c>
+      <c r="Z88"/>
       <c r="AA88" t="b">
         <v>1</v>
       </c>
@@ -10687,7 +10962,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="10" t="s">
+      <c r="S89" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -10699,15 +10974,16 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="10" t="s">
+      <c r="W89" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>108013</v>
       </c>
       <c r="Y89" t="s">
         <v>96</v>
       </c>
+      <c r="Z89"/>
       <c r="AA89" t="b">
         <v>1</v>
       </c>
@@ -10786,11 +11062,12 @@
         <v>440</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>109001</v>
       </c>
       <c r="Y90" t="s">
         <v>96</v>
       </c>
+      <c r="Z90"/>
       <c r="AA90" t="b">
         <v>1</v>
       </c>
@@ -10862,15 +11139,16 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="10" t="s">
+      <c r="W91" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>109002</v>
       </c>
       <c r="Y91" t="s">
         <v>96</v>
       </c>
+      <c r="Z91"/>
       <c r="AA91" t="b">
         <v>1</v>
       </c>
@@ -10942,15 +11220,16 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="10" t="s">
+      <c r="W92" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>109003</v>
       </c>
       <c r="Y92" t="s">
         <v>96</v>
       </c>
+      <c r="Z92"/>
       <c r="AA92" t="b">
         <v>1</v>
       </c>
@@ -11022,15 +11301,16 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="10" t="s">
+      <c r="W93" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>109004</v>
       </c>
       <c r="Y93" t="s">
         <v>96</v>
       </c>
+      <c r="Z93"/>
       <c r="AA93" t="b">
         <v>1</v>
       </c>
@@ -11102,15 +11382,16 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="10" t="s">
+      <c r="W94" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>109005</v>
       </c>
       <c r="Y94" t="s">
         <v>96</v>
       </c>
+      <c r="Z94"/>
       <c r="AA94" t="b">
         <v>1</v>
       </c>
@@ -11182,15 +11463,16 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="10" t="s">
+      <c r="W95" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>109006</v>
       </c>
       <c r="Y95" t="s">
         <v>96</v>
       </c>
+      <c r="Z95"/>
       <c r="AA95" t="b">
         <v>1</v>
       </c>
@@ -11262,15 +11544,16 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="10" t="s">
+      <c r="W96" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>109007</v>
       </c>
       <c r="Y96" t="s">
         <v>96</v>
       </c>
+      <c r="Z96"/>
       <c r="AA96" t="b">
         <v>1</v>
       </c>
@@ -11342,15 +11625,16 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="10" t="s">
+      <c r="W97" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>109008</v>
       </c>
       <c r="Y97" t="s">
         <v>96</v>
       </c>
+      <c r="Z97"/>
       <c r="AA97" t="b">
         <v>1</v>
       </c>
@@ -11416,15 +11700,16 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="10" t="s">
+      <c r="W98" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>109009</v>
       </c>
       <c r="Y98" t="s">
         <v>96</v>
       </c>
+      <c r="Z98"/>
       <c r="AA98" t="b">
         <v>1</v>
       </c>
@@ -11497,11 +11782,12 @@
         <v>478</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>109010</v>
       </c>
       <c r="Y99" t="s">
         <v>96</v>
       </c>
+      <c r="Z99"/>
       <c r="AA99" t="b">
         <v>1</v>
       </c>
@@ -11573,15 +11859,16 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="10" t="s">
+      <c r="W100" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>109011</v>
       </c>
       <c r="Y100" t="s">
         <v>96</v>
       </c>
+      <c r="Z100"/>
       <c r="AA100" t="b">
         <v>1</v>
       </c>
@@ -11598,213 +11885,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:31">
-      <c r="B101">
+    <row r="101" s="11" customFormat="1" spans="2:31">
+      <c r="B101" s="11">
         <v>10001</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I101">
-        <v>300</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" t="s">
+      <c r="I101" s="11">
+        <v>300</v>
+      </c>
+      <c r="J101" s="11">
+        <v>0</v>
+      </c>
+      <c r="K101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M101" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="T101" t="s">
+      <c r="M101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="11">
+        <v>0</v>
+      </c>
+      <c r="O101" s="11">
+        <v>0</v>
+      </c>
+      <c r="P101" s="11">
+        <v>0</v>
+      </c>
+      <c r="T101" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="U101" t="s">
+      <c r="U101" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="X101">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="s">
+      <c r="X101" s="11">
+        <v>110001</v>
+      </c>
+      <c r="Y101" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:31">
-      <c r="B102">
+      <c r="Z101" s="11"/>
+      <c r="AA101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="11" customFormat="1" spans="2:31">
+      <c r="B102" s="11">
         <v>11001</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I102">
-        <v>300</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
+      <c r="I102" s="11">
+        <v>300</v>
+      </c>
+      <c r="J102" s="11">
+        <v>0</v>
+      </c>
+      <c r="K102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M102" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="T102" t="s">
+      <c r="M102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="11">
+        <v>0</v>
+      </c>
+      <c r="O102" s="11">
+        <v>0</v>
+      </c>
+      <c r="P102" s="11">
+        <v>0</v>
+      </c>
+      <c r="T102" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="U102" t="s">
+      <c r="U102" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="10" t="s">
+      <c r="W102" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="X102">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="s">
+      <c r="X102" s="11">
+        <v>111001</v>
+      </c>
+      <c r="Y102" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:31">
-      <c r="B103">
+      <c r="Z102" s="11"/>
+      <c r="AA102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="11" customFormat="1" spans="2:31">
+      <c r="B103" s="11">
         <v>11002</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="11">
         <v>11001</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I103">
-        <v>300</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" t="s">
+      <c r="I103" s="11">
+        <v>300</v>
+      </c>
+      <c r="J103" s="11">
+        <v>0</v>
+      </c>
+      <c r="K103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M103" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="T103" t="s">
+      <c r="M103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="11">
+        <v>0</v>
+      </c>
+      <c r="O103" s="11">
+        <v>0</v>
+      </c>
+      <c r="P103" s="11">
+        <v>0</v>
+      </c>
+      <c r="T103" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="U103" t="s">
+      <c r="U103" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="X103">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="s">
+      <c r="X103" s="11">
+        <v>111002</v>
+      </c>
+      <c r="Y103" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="b">
+      <c r="Z103" s="11"/>
+      <c r="AA103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11827,7 +12117,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="8" t="s">
+      <c r="H104" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -11860,7 +12150,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="10" t="s">
+      <c r="S104" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -11870,11 +12160,12 @@
         <v>501</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>112001</v>
       </c>
       <c r="Y104" t="s">
         <v>96</v>
       </c>
+      <c r="Z104"/>
       <c r="AA104" t="b">
         <v>1</v>
       </c>
@@ -11910,7 +12201,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="9" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -11943,7 +12234,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="10" t="s">
+      <c r="S105" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -11953,11 +12244,12 @@
         <v>505</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>112002</v>
       </c>
       <c r="Y105" t="s">
         <v>96</v>
       </c>
+      <c r="Z105"/>
       <c r="AA105" t="b">
         <v>1</v>
       </c>
@@ -12011,22 +12303,23 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="10"/>
+      <c r="S106" s="12"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="10" t="s">
+      <c r="W106" s="12" t="s">
         <v>509</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>192005</v>
       </c>
       <c r="Y106" t="s">
         <v>96</v>
       </c>
+      <c r="Z106"/>
       <c r="AA106" t="b">
         <v>1</v>
       </c>
@@ -12080,7 +12373,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="10"/>
+      <c r="S107" s="12"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -12090,15 +12383,16 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="10" t="s">
+      <c r="W107" s="12" t="s">
         <v>509</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>191012</v>
       </c>
       <c r="Y107" t="s">
         <v>96</v>
       </c>
+      <c r="Z107"/>
       <c r="AA107" t="b">
         <v>1</v>
       </c>
@@ -12142,10 +12436,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79 H104 H105 H5:H16 H18:H27 H30:H77 H80:H82 H83:H86 H90:H103 H106:H108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H86 H90:H108">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L79 L104 L105 L5:L16 L18:L27 L30:L77 L80:L82 L83:L87 L90:L103 L106:L108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L87 L90:L108">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12187,49 +12481,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="F1" t="s">
         <v>600</v>
       </c>
       <c r="G1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="H1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="I1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="J1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="K1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="L1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="M1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="N1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="O1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="P1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="Q1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -12267,10 +12561,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="M2" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -12293,49 +12587,49 @@
         <v>607</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12343,52 +12637,52 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C4" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E4" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="F4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="G4" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H4" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I4" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="J4" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="K4" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="L4" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="M4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="N4" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="O4" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="P4" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="Q4" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12396,7 +12690,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12408,25 +12702,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="H5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="I5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="K5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="L5" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="M5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12446,7 +12740,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12458,25 +12752,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="H6" t="s">
+        <v>820</v>
+      </c>
+      <c r="I6" t="s">
+        <v>813</v>
+      </c>
+      <c r="J6" t="s">
+        <v>821</v>
+      </c>
+      <c r="K6" t="s">
+        <v>821</v>
+      </c>
+      <c r="L6" t="s">
         <v>816</v>
       </c>
-      <c r="I6" t="s">
-        <v>809</v>
-      </c>
-      <c r="J6" t="s">
-        <v>817</v>
-      </c>
-      <c r="K6" t="s">
-        <v>817</v>
-      </c>
-      <c r="L6" t="s">
-        <v>812</v>
-      </c>
       <c r="M6" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12496,7 +12790,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12508,25 +12802,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="H7" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="I7" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J7" t="s">
+        <v>826</v>
+      </c>
+      <c r="K7" t="s">
+        <v>827</v>
+      </c>
+      <c r="L7" t="s">
+        <v>816</v>
+      </c>
+      <c r="M7" t="s">
         <v>822</v>
-      </c>
-      <c r="K7" t="s">
-        <v>823</v>
-      </c>
-      <c r="L7" t="s">
-        <v>812</v>
-      </c>
-      <c r="M7" t="s">
-        <v>818</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12546,7 +12840,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12558,25 +12852,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="H8" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="I8" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J8" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="K8" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="L8" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="M8" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12600,13 +12894,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
     <col min="3" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="18.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="32.5" customWidth="1"/>
     <col min="7" max="7" width="48.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="19.8333333333333" customWidth="1"/>
@@ -12629,40 +12923,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="E1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="H1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="I1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="J1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K1" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="L1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="M1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="N1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="O1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="P1" t="s">
         <v>600</v>
@@ -12720,46 +13014,46 @@
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>845</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>842</v>
+      <c r="H3" s="3" t="s">
+        <v>846</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -12767,49 +13061,49 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C4" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D4" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="E4" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F4" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="I4" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="L4" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="M4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="P4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -12820,22 +13114,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D5" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="G5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="H5" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -12870,22 +13164,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D6" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="G6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H6" t="s">
         <v>869</v>
-      </c>
-      <c r="H6" t="s">
-        <v>865</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -12920,22 +13214,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D7" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="G7" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="H7" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -12970,22 +13264,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D8" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="G8" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="H8" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -13025,7 +13319,7 @@
         <v>402001</v>
       </c>
       <c r="C10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D10" t="s">
         <v>642</v>
@@ -13034,13 +13328,13 @@
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="G10" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="H10" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -13075,19 +13369,19 @@
         <v>403001</v>
       </c>
       <c r="C11" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D11" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="E11" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="F11" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="G11" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="H11" t="s">
         <v>161</v>
@@ -13111,9 +13405,593 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="P11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13">
+        <v>402002</v>
+      </c>
+      <c r="C13" t="s">
+        <v>891</v>
+      </c>
+      <c r="D13" t="s">
+        <v>892</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" t="s">
+        <v>893</v>
+      </c>
+      <c r="G13" t="s">
+        <v>894</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14">
+        <v>402003</v>
+      </c>
+      <c r="C14" t="s">
+        <v>895</v>
+      </c>
+      <c r="D14" t="s">
+        <v>896</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>897</v>
+      </c>
+      <c r="G14" t="s">
+        <v>898</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16">
+        <v>403002</v>
+      </c>
+      <c r="C16" t="s">
+        <v>899</v>
+      </c>
+      <c r="D16" t="s">
+        <v>900</v>
+      </c>
+      <c r="E16" t="s">
+        <v>887</v>
+      </c>
+      <c r="F16" t="s">
+        <v>901</v>
+      </c>
+      <c r="G16" t="s">
+        <v>902</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>903</v>
+      </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="B17">
+        <v>403003</v>
+      </c>
+      <c r="C17" t="s">
+        <v>904</v>
+      </c>
+      <c r="D17" t="s">
+        <v>905</v>
+      </c>
+      <c r="E17" t="s">
+        <v>887</v>
+      </c>
+      <c r="F17" t="s">
+        <v>906</v>
+      </c>
+      <c r="G17" t="s">
+        <v>907</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>903</v>
+      </c>
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19">
+        <v>404001</v>
+      </c>
+      <c r="C19" t="s">
+        <v>909</v>
+      </c>
+      <c r="D19" t="s">
+        <v>910</v>
+      </c>
+      <c r="E19" t="s">
+        <v>911</v>
+      </c>
+      <c r="F19" t="s">
+        <v>912</v>
+      </c>
+      <c r="G19" t="s">
+        <v>913</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>914</v>
+      </c>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20">
+        <v>404002</v>
+      </c>
+      <c r="C20" t="s">
+        <v>915</v>
+      </c>
+      <c r="D20" t="s">
+        <v>916</v>
+      </c>
+      <c r="E20" t="s">
+        <v>911</v>
+      </c>
+      <c r="F20" t="s">
+        <v>917</v>
+      </c>
+      <c r="G20" t="s">
+        <v>918</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>919</v>
+      </c>
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21">
+        <v>404004</v>
+      </c>
+      <c r="C21" t="s">
+        <v>920</v>
+      </c>
+      <c r="D21" t="s">
+        <v>921</v>
+      </c>
+      <c r="E21" t="s">
+        <v>911</v>
+      </c>
+      <c r="F21" t="s">
+        <v>922</v>
+      </c>
+      <c r="G21" t="s">
+        <v>923</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>914</v>
+      </c>
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22">
+        <v>404005</v>
+      </c>
+      <c r="C22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E22" t="s">
+        <v>911</v>
+      </c>
+      <c r="F22" t="s">
+        <v>926</v>
+      </c>
+      <c r="G22" t="s">
+        <v>927</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>919</v>
+      </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="B23">
+        <v>404007</v>
+      </c>
+      <c r="C23" t="s">
+        <v>928</v>
+      </c>
+      <c r="D23" t="s">
+        <v>929</v>
+      </c>
+      <c r="E23" t="s">
+        <v>911</v>
+      </c>
+      <c r="F23" t="s">
+        <v>930</v>
+      </c>
+      <c r="G23" t="s">
+        <v>931</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>914</v>
+      </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="B24">
+        <v>404008</v>
+      </c>
+      <c r="C24" t="s">
+        <v>932</v>
+      </c>
+      <c r="D24" t="s">
+        <v>933</v>
+      </c>
+      <c r="E24" t="s">
+        <v>911</v>
+      </c>
+      <c r="F24" t="s">
+        <v>934</v>
+      </c>
+      <c r="G24" t="s">
+        <v>935</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>919</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="B25">
+        <v>404010</v>
+      </c>
+      <c r="C25" t="s">
+        <v>936</v>
+      </c>
+      <c r="D25" t="s">
+        <v>937</v>
+      </c>
+      <c r="E25" t="s">
+        <v>911</v>
+      </c>
+      <c r="F25" t="s">
+        <v>938</v>
+      </c>
+      <c r="G25" t="s">
+        <v>939</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>914</v>
+      </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="B26">
+        <v>404011</v>
+      </c>
+      <c r="C26" t="s">
+        <v>940</v>
+      </c>
+      <c r="D26" t="s">
+        <v>941</v>
+      </c>
+      <c r="E26" t="s">
+        <v>911</v>
+      </c>
+      <c r="F26" t="s">
+        <v>942</v>
+      </c>
+      <c r="G26" t="s">
+        <v>943</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>919</v>
+      </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="B27">
+        <v>404013</v>
+      </c>
+      <c r="C27" t="s">
+        <v>944</v>
+      </c>
+      <c r="D27" t="s">
+        <v>945</v>
+      </c>
+      <c r="E27" t="s">
+        <v>911</v>
+      </c>
+      <c r="F27" t="s">
+        <v>946</v>
+      </c>
+      <c r="G27" t="s">
+        <v>947</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>914</v>
+      </c>
+      <c r="P27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13135,10 +14013,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -13147,130 +14025,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="5">
-        <v>1</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="6" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="6">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="6">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="6" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -13279,248 +14157,248 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="6">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="6" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="6">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="6" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="6">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="6" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="6">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="6" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="6">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="6">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="6">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="6">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>591</v>
       </c>
     </row>
@@ -13553,7 +14431,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -13597,7 +14475,7 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -13681,47 +14559,47 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" spans="1:14">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="10" customFormat="1" spans="1:14">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>629</v>
       </c>
     </row>
@@ -13732,10 +14610,10 @@
       <c r="C5" t="s">
         <v>630</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F5">
@@ -13760,10 +14638,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>402002</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>403002</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -13773,10 +14651,10 @@
       <c r="C6" t="s">
         <v>635</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F6">
@@ -13801,10 +14679,10 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>402003</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>403003</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13814,10 +14692,10 @@
       <c r="C7" t="s">
         <v>637</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F7">
@@ -13858,7 +14736,7 @@
       <c r="D8" t="s">
         <v>639</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>640</v>
       </c>
       <c r="F8">
@@ -13896,10 +14774,10 @@
       <c r="C9" t="s">
         <v>642</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F9">
@@ -13931,13 +14809,13 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="5"/>
+      <c r="E17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13948,7 +14826,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -13962,11 +14840,12 @@
     <col min="10" max="10" width="10.25" customWidth="1"/>
     <col min="11" max="11" width="16.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
-    <col min="13" max="13" width="45.25" customWidth="1"/>
+    <col min="13" max="13" width="30.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -14002,9 +14881,12 @@
       <c r="L1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="M1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -14040,42 +14922,51 @@
       <c r="L2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:14">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+      <c r="M3" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
@@ -14085,37 +14976,40 @@
         <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E4" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F4" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H4" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="I4" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J4" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="K4" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="L4" t="s">
         <v>627</v>
       </c>
       <c r="M4" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>672</v>
+      </c>
+      <c r="N4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -14149,11 +15043,14 @@
       <c r="L5" t="b">
         <v>1</v>
       </c>
-      <c r="M5" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="M5">
+        <v>404001</v>
+      </c>
+      <c r="N5" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -14187,11 +15084,14 @@
       <c r="L6" t="b">
         <v>1</v>
       </c>
-      <c r="M6" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="M6">
+        <v>404002</v>
+      </c>
+      <c r="N6" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -14225,11 +15125,14 @@
       <c r="L7" t="b">
         <v>1</v>
       </c>
-      <c r="M7" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -14263,11 +15166,14 @@
       <c r="L8" t="b">
         <v>1</v>
       </c>
-      <c r="M8" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="M8">
+        <v>404004</v>
+      </c>
+      <c r="N8" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -14301,11 +15207,14 @@
       <c r="L9" t="b">
         <v>1</v>
       </c>
-      <c r="M9" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="M9">
+        <v>404005</v>
+      </c>
+      <c r="N9" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -14339,11 +15248,14 @@
       <c r="L10" t="b">
         <v>1</v>
       </c>
-      <c r="M10" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -14377,11 +15289,14 @@
       <c r="L11" t="b">
         <v>1</v>
       </c>
-      <c r="M11" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="M11">
+        <v>404007</v>
+      </c>
+      <c r="N11" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -14415,11 +15330,14 @@
       <c r="L12" t="b">
         <v>1</v>
       </c>
-      <c r="M12" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="M12">
+        <v>404008</v>
+      </c>
+      <c r="N12" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -14453,11 +15371,14 @@
       <c r="L13" t="b">
         <v>1</v>
       </c>
-      <c r="M13" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -14491,11 +15412,14 @@
       <c r="L14" t="b">
         <v>1</v>
       </c>
-      <c r="M14" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="M14">
+        <v>404010</v>
+      </c>
+      <c r="N14" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -14529,11 +15453,14 @@
       <c r="L15" t="b">
         <v>1</v>
       </c>
-      <c r="M15" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="M15">
+        <v>404011</v>
+      </c>
+      <c r="N15" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="B16">
         <v>1012</v>
       </c>
@@ -14567,11 +15494,14 @@
       <c r="L16" t="b">
         <v>1</v>
       </c>
-      <c r="M16" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17">
         <v>1013</v>
       </c>
@@ -14605,11 +15535,14 @@
       <c r="L17" t="b">
         <v>1</v>
       </c>
-      <c r="M17" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13">
+      <c r="M17">
+        <v>404013</v>
+      </c>
+      <c r="N17" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18">
         <v>1014</v>
       </c>
@@ -14643,8 +15576,11 @@
       <c r="L18" t="b">
         <v>1</v>
       </c>
-      <c r="M18" t="s">
-        <v>683</v>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -14663,7 +15599,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14678,10 +15614,10 @@
         <v>644</v>
       </c>
       <c r="D1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G1" t="s">
         <v>600</v>
@@ -14713,15 +15649,15 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F3" s="7"/>
+        <v>691</v>
+      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
         <v>627</v>
       </c>
@@ -14740,13 +15676,13 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G4" t="s">
         <v>627</v>
       </c>
       <c r="H4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14762,7 +15698,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -14783,7 +15719,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -14804,7 +15740,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -14822,10 +15758,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>900</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -14843,10 +15779,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>180</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -14867,7 +15803,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14879,7 +15815,7 @@
       <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -14897,7 +15833,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14918,7 +15854,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -14926,7 +15862,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14942,7 +15878,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -14963,7 +15899,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -14984,7 +15920,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -15005,7 +15941,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -15017,7 +15953,7 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -15164,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -15185,7 +16121,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="7">
         <f t="shared" ref="F28:F33" si="1">E28/10000</f>
         <v>0</v>
       </c>
@@ -15209,7 +16145,7 @@
       <c r="E29">
         <v>6700</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="7">
         <f t="shared" si="1"/>
         <v>0.67</v>
       </c>
@@ -15230,7 +16166,7 @@
       <c r="E30">
         <v>2200</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
@@ -15248,10 +16184,10 @@
       <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9">
         <v>900</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -15269,10 +16205,10 @@
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="9">
         <v>180</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="7">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -15293,7 +16229,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="7">
         <f t="shared" si="1"/>
         <v>0.002</v>
       </c>
@@ -15302,7 +16238,7 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="F34" s="6">
+      <c r="F34" s="7">
         <f>SUM(F28:F33)</f>
         <v>1</v>
       </c>
@@ -15339,28 +16275,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="F1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="G1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="H1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="I1" t="s">
         <v>600</v>
       </c>
       <c r="J1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -15403,28 +16339,28 @@
         <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15435,31 +16371,31 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D4" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E4" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F4" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="G4" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>
       </c>
       <c r="J4" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15875,7 +16811,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15910,7 +16846,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -16009,7 +16945,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -16044,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -16207,7 +17143,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -16242,7 +17178,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -16277,7 +17213,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -16471,48 +17407,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="F1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="G1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="H1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="I1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="K1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -16541,28 +17477,28 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>717</v>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>721</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16579,28 +17515,28 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="F4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="H4" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="I4" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="J4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="K4" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L4" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -16614,177 +17550,177 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="K5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F6" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H6" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K6" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F7" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H7" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="K7" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="F8" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H8" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="K8" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="F9" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H9" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="K9" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F10" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H10" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="K10" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>507</v>
       </c>
       <c r="E11" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F11" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H11" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J11" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F12" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H12" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J12" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -16805,54 +17741,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="E3" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16874,7 +17810,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -16888,7 +17824,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -16902,7 +17838,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -16926,7 +17862,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -16970,42 +17906,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="5"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17026,27 +17962,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -17054,17 +17990,17 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>758</v>
+      <c r="C3" s="5" t="s">
+        <v>762</v>
       </c>
       <c r="D3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="949">
   <si>
     <t>##var</t>
   </si>
@@ -2797,34 +2797,37 @@
     <t>Grants the blind box item configured by schedule 1001.</t>
   </si>
   <si>
+    <t>402001x1</t>
+  </si>
+  <si>
+    <t>Schedule1002PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1002游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1002 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1002.</t>
+  </si>
+  <si>
+    <t>402003x1</t>
+  </si>
+  <si>
+    <t>Schedule1004PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1004游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1004 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1004.</t>
+  </si>
+  <si>
     <t>402002x1</t>
-  </si>
-  <si>
-    <t>Schedule1002PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>调度1002游玩时间掉落</t>
-  </si>
-  <si>
-    <t>Schedule 1002 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by schedule 1002.</t>
-  </si>
-  <si>
-    <t>402003x1</t>
-  </si>
-  <si>
-    <t>Schedule1004PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>调度1004游玩时间掉落</t>
-  </si>
-  <si>
-    <t>Schedule 1004 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by schedule 1004.</t>
   </si>
   <si>
     <t>Schedule1005PlaytimeDrop</t>
@@ -4684,7 +4687,6 @@
       <c r="Y6" t="s">
         <v>96</v>
       </c>
-      <c r="Z6"/>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
@@ -4756,7 +4758,6 @@
       <c r="Y7" t="s">
         <v>96</v>
       </c>
-      <c r="Z7"/>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
@@ -4828,7 +4829,6 @@
       <c r="Y8" t="s">
         <v>96</v>
       </c>
-      <c r="Z8"/>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
@@ -4900,7 +4900,6 @@
       <c r="Y9" t="s">
         <v>96</v>
       </c>
-      <c r="Z9"/>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
@@ -4972,7 +4971,6 @@
       <c r="Y10" t="s">
         <v>96</v>
       </c>
-      <c r="Z10"/>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
@@ -5044,7 +5042,6 @@
       <c r="Y11" t="s">
         <v>96</v>
       </c>
-      <c r="Z11"/>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
@@ -5116,7 +5113,6 @@
       <c r="Y12" t="s">
         <v>96</v>
       </c>
-      <c r="Z12"/>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
@@ -5188,7 +5184,6 @@
       <c r="Y13" t="s">
         <v>96</v>
       </c>
-      <c r="Z13"/>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
@@ -5260,7 +5255,6 @@
       <c r="Y14" t="s">
         <v>96</v>
       </c>
-      <c r="Z14"/>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
@@ -5332,7 +5326,6 @@
       <c r="Y15" t="s">
         <v>96</v>
       </c>
-      <c r="Z15"/>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
@@ -5404,7 +5397,6 @@
       <c r="Y16" t="s">
         <v>96</v>
       </c>
-      <c r="Z16"/>
       <c r="AA16" t="b">
         <v>1</v>
       </c>
@@ -5478,7 +5470,6 @@
       <c r="Y18" t="s">
         <v>96</v>
       </c>
-      <c r="Z18"/>
       <c r="AA18" t="b">
         <v>1</v>
       </c>
@@ -5547,7 +5538,6 @@
       <c r="Y19" t="s">
         <v>96</v>
       </c>
-      <c r="Z19"/>
       <c r="AA19" t="b">
         <v>1</v>
       </c>
@@ -5616,7 +5606,6 @@
       <c r="Y20" t="s">
         <v>96</v>
       </c>
-      <c r="Z20"/>
       <c r="AA20" t="b">
         <v>1</v>
       </c>
@@ -5685,7 +5674,6 @@
       <c r="Y21" t="s">
         <v>96</v>
       </c>
-      <c r="Z21"/>
       <c r="AA21" t="b">
         <v>1</v>
       </c>
@@ -5754,7 +5742,6 @@
       <c r="Y22" t="s">
         <v>96</v>
       </c>
-      <c r="Z22"/>
       <c r="AA22" t="b">
         <v>1</v>
       </c>
@@ -5838,7 +5825,6 @@
       <c r="Y23" t="s">
         <v>96</v>
       </c>
-      <c r="Z23"/>
       <c r="AA23" t="b">
         <v>1</v>
       </c>
@@ -5907,7 +5893,6 @@
       <c r="Y24" t="s">
         <v>96</v>
       </c>
-      <c r="Z24"/>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
@@ -5976,7 +5961,6 @@
       <c r="Y25" t="s">
         <v>96</v>
       </c>
-      <c r="Z25"/>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
@@ -6045,7 +6029,6 @@
       <c r="Y26" t="s">
         <v>96</v>
       </c>
-      <c r="Z26"/>
       <c r="AA26" t="b">
         <v>1</v>
       </c>
@@ -6114,7 +6097,6 @@
       <c r="Y27" t="s">
         <v>96</v>
       </c>
-      <c r="Z27"/>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
@@ -6207,7 +6189,6 @@
       <c r="Y28" t="s">
         <v>96</v>
       </c>
-      <c r="Z28"/>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
@@ -6312,7 +6293,6 @@
       <c r="Y29" t="s">
         <v>96</v>
       </c>
-      <c r="Z29"/>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
@@ -6393,7 +6373,6 @@
       <c r="Y30" t="s">
         <v>96</v>
       </c>
-      <c r="Z30"/>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
@@ -6462,7 +6441,6 @@
       <c r="Y31" t="s">
         <v>96</v>
       </c>
-      <c r="Z31"/>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
@@ -6531,7 +6509,6 @@
       <c r="Y32" t="s">
         <v>96</v>
       </c>
-      <c r="Z32"/>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
@@ -6600,7 +6577,6 @@
       <c r="Y33" t="s">
         <v>96</v>
       </c>
-      <c r="Z33"/>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
@@ -6669,7 +6645,6 @@
       <c r="Y34" t="s">
         <v>96</v>
       </c>
-      <c r="Z34"/>
       <c r="AA34" t="b">
         <v>1</v>
       </c>
@@ -7170,7 +7145,6 @@
       <c r="Y41" t="s">
         <v>96</v>
       </c>
-      <c r="Z41"/>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
@@ -7239,7 +7213,6 @@
       <c r="Y42" t="s">
         <v>96</v>
       </c>
-      <c r="Z42"/>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
@@ -7308,7 +7281,6 @@
       <c r="Y43" t="s">
         <v>96</v>
       </c>
-      <c r="Z43"/>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
@@ -7377,7 +7349,6 @@
       <c r="Y44" t="s">
         <v>96</v>
       </c>
-      <c r="Z44"/>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
@@ -7446,7 +7417,6 @@
       <c r="Y45" t="s">
         <v>96</v>
       </c>
-      <c r="Z45"/>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
@@ -7515,7 +7485,6 @@
       <c r="Y46" t="s">
         <v>96</v>
       </c>
-      <c r="Z46"/>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
@@ -7584,7 +7553,6 @@
       <c r="Y47" t="s">
         <v>96</v>
       </c>
-      <c r="Z47"/>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
@@ -7653,7 +7621,6 @@
       <c r="Y48" t="s">
         <v>96</v>
       </c>
-      <c r="Z48"/>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
@@ -7821,7 +7788,6 @@
       <c r="Y50" t="s">
         <v>96</v>
       </c>
-      <c r="Z50"/>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
@@ -7905,7 +7871,6 @@
       <c r="Y51" t="s">
         <v>96</v>
       </c>
-      <c r="Z51"/>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
@@ -7989,7 +7954,6 @@
       <c r="Y52" t="s">
         <v>96</v>
       </c>
-      <c r="Z52"/>
       <c r="AA52" t="b">
         <v>1</v>
       </c>
@@ -8073,7 +8037,6 @@
       <c r="Y53" t="s">
         <v>96</v>
       </c>
-      <c r="Z53"/>
       <c r="AA53" t="b">
         <v>1</v>
       </c>
@@ -8157,7 +8120,6 @@
       <c r="Y54" t="s">
         <v>96</v>
       </c>
-      <c r="Z54"/>
       <c r="AA54" t="b">
         <v>1</v>
       </c>
@@ -8241,7 +8203,6 @@
       <c r="Y55" t="s">
         <v>96</v>
       </c>
-      <c r="Z55"/>
       <c r="AA55" t="b">
         <v>1</v>
       </c>
@@ -8325,7 +8286,6 @@
       <c r="Y56" t="s">
         <v>96</v>
       </c>
-      <c r="Z56"/>
       <c r="AA56" t="b">
         <v>1</v>
       </c>
@@ -8409,7 +8369,6 @@
       <c r="Y57" t="s">
         <v>96</v>
       </c>
-      <c r="Z57"/>
       <c r="AA57" t="b">
         <v>1</v>
       </c>
@@ -8493,7 +8452,6 @@
       <c r="Y58" t="s">
         <v>96</v>
       </c>
-      <c r="Z58"/>
       <c r="AA58" t="b">
         <v>1</v>
       </c>
@@ -8577,7 +8535,6 @@
       <c r="Y59" t="s">
         <v>96</v>
       </c>
-      <c r="Z59"/>
       <c r="AA59" t="b">
         <v>1</v>
       </c>
@@ -8646,7 +8603,6 @@
       <c r="Y60" t="s">
         <v>96</v>
       </c>
-      <c r="Z60"/>
       <c r="AA60" t="b">
         <v>1</v>
       </c>
@@ -8715,7 +8671,6 @@
       <c r="Y61" t="s">
         <v>96</v>
       </c>
-      <c r="Z61"/>
       <c r="AA61" t="b">
         <v>1</v>
       </c>
@@ -8784,7 +8739,6 @@
       <c r="Y62" t="s">
         <v>96</v>
       </c>
-      <c r="Z62"/>
       <c r="AA62" t="b">
         <v>1</v>
       </c>
@@ -8922,7 +8876,6 @@
       <c r="Y64" t="s">
         <v>96</v>
       </c>
-      <c r="Z64"/>
       <c r="AA64" t="b">
         <v>1</v>
       </c>
@@ -8991,7 +8944,6 @@
       <c r="Y65" t="s">
         <v>96</v>
       </c>
-      <c r="Z65"/>
       <c r="AA65" t="b">
         <v>1</v>
       </c>
@@ -9060,7 +9012,6 @@
       <c r="Y66" t="s">
         <v>96</v>
       </c>
-      <c r="Z66"/>
       <c r="AA66" t="b">
         <v>1</v>
       </c>
@@ -9144,7 +9095,6 @@
       <c r="Y67" t="s">
         <v>96</v>
       </c>
-      <c r="Z67"/>
       <c r="AA67" t="b">
         <v>1</v>
       </c>
@@ -9228,7 +9178,6 @@
       <c r="Y68" t="s">
         <v>96</v>
       </c>
-      <c r="Z68"/>
       <c r="AA68" t="b">
         <v>1</v>
       </c>
@@ -9312,7 +9261,6 @@
       <c r="Y69" t="s">
         <v>96</v>
       </c>
-      <c r="Z69"/>
       <c r="AA69" t="b">
         <v>1</v>
       </c>
@@ -9396,7 +9344,6 @@
       <c r="Y70" t="s">
         <v>96</v>
       </c>
-      <c r="Z70"/>
       <c r="AA70" t="b">
         <v>1</v>
       </c>
@@ -9480,7 +9427,6 @@
       <c r="Y71" t="s">
         <v>96</v>
       </c>
-      <c r="Z71"/>
       <c r="AA71" t="b">
         <v>1</v>
       </c>
@@ -9564,7 +9510,6 @@
       <c r="Y72" t="s">
         <v>96</v>
       </c>
-      <c r="Z72"/>
       <c r="AA72" t="b">
         <v>1</v>
       </c>
@@ -9648,7 +9593,6 @@
       <c r="Y73" t="s">
         <v>96</v>
       </c>
-      <c r="Z73"/>
       <c r="AA73" t="b">
         <v>1</v>
       </c>
@@ -9732,7 +9676,6 @@
       <c r="Y74" t="s">
         <v>96</v>
       </c>
-      <c r="Z74"/>
       <c r="AA74" t="b">
         <v>1</v>
       </c>
@@ -9816,7 +9759,6 @@
       <c r="Y75" t="s">
         <v>96</v>
       </c>
-      <c r="Z75"/>
       <c r="AA75" t="b">
         <v>1</v>
       </c>
@@ -9900,7 +9842,6 @@
       <c r="Y76" t="s">
         <v>96</v>
       </c>
-      <c r="Z76"/>
       <c r="AA76" t="b">
         <v>1</v>
       </c>
@@ -9969,7 +9910,6 @@
       <c r="Y77" t="s">
         <v>96</v>
       </c>
-      <c r="Z77"/>
       <c r="AA77" t="b">
         <v>1</v>
       </c>
@@ -10062,7 +10002,6 @@
       <c r="Y78" t="s">
         <v>96</v>
       </c>
-      <c r="Z78"/>
       <c r="AA78" t="b">
         <v>1</v>
       </c>
@@ -10158,7 +10097,6 @@
       <c r="Y79" t="s">
         <v>96</v>
       </c>
-      <c r="Z79"/>
       <c r="AA79" t="b">
         <v>1</v>
       </c>
@@ -10242,7 +10180,6 @@
       <c r="Y80" t="s">
         <v>96</v>
       </c>
-      <c r="Z80"/>
       <c r="AA80" t="b">
         <v>1</v>
       </c>
@@ -10326,7 +10263,6 @@
       <c r="Y81" t="s">
         <v>96</v>
       </c>
-      <c r="Z81"/>
       <c r="AA81" t="b">
         <v>1</v>
       </c>
@@ -10410,7 +10346,6 @@
       <c r="Y82" t="s">
         <v>96</v>
       </c>
-      <c r="Z82"/>
       <c r="AA82" t="b">
         <v>1</v>
       </c>
@@ -10494,7 +10429,6 @@
       <c r="Y83" t="s">
         <v>96</v>
       </c>
-      <c r="Z83"/>
       <c r="AA83" t="b">
         <v>1</v>
       </c>
@@ -10578,7 +10512,6 @@
       <c r="Y84" t="s">
         <v>96</v>
       </c>
-      <c r="Z84"/>
       <c r="AA84" t="b">
         <v>1</v>
       </c>
@@ -10647,7 +10580,6 @@
       <c r="Y85" t="s">
         <v>96</v>
       </c>
-      <c r="Z85"/>
       <c r="AA85" t="b">
         <v>1</v>
       </c>
@@ -10716,7 +10648,6 @@
       <c r="Y86" t="s">
         <v>96</v>
       </c>
-      <c r="Z86"/>
       <c r="AA86" t="b">
         <v>1</v>
       </c>
@@ -10785,7 +10716,6 @@
       <c r="Y87" t="s">
         <v>96</v>
       </c>
-      <c r="Z87"/>
       <c r="AA87" t="b">
         <v>1</v>
       </c>
@@ -10878,7 +10808,6 @@
       <c r="Y88" t="s">
         <v>96</v>
       </c>
-      <c r="Z88"/>
       <c r="AA88" t="b">
         <v>1</v>
       </c>
@@ -10983,7 +10912,6 @@
       <c r="Y89" t="s">
         <v>96</v>
       </c>
-      <c r="Z89"/>
       <c r="AA89" t="b">
         <v>1</v>
       </c>
@@ -11067,7 +10995,6 @@
       <c r="Y90" t="s">
         <v>96</v>
       </c>
-      <c r="Z90"/>
       <c r="AA90" t="b">
         <v>1</v>
       </c>
@@ -11148,7 +11075,6 @@
       <c r="Y91" t="s">
         <v>96</v>
       </c>
-      <c r="Z91"/>
       <c r="AA91" t="b">
         <v>1</v>
       </c>
@@ -11229,7 +11155,6 @@
       <c r="Y92" t="s">
         <v>96</v>
       </c>
-      <c r="Z92"/>
       <c r="AA92" t="b">
         <v>1</v>
       </c>
@@ -11310,7 +11235,6 @@
       <c r="Y93" t="s">
         <v>96</v>
       </c>
-      <c r="Z93"/>
       <c r="AA93" t="b">
         <v>1</v>
       </c>
@@ -11391,7 +11315,6 @@
       <c r="Y94" t="s">
         <v>96</v>
       </c>
-      <c r="Z94"/>
       <c r="AA94" t="b">
         <v>1</v>
       </c>
@@ -11472,7 +11395,6 @@
       <c r="Y95" t="s">
         <v>96</v>
       </c>
-      <c r="Z95"/>
       <c r="AA95" t="b">
         <v>1</v>
       </c>
@@ -11553,7 +11475,6 @@
       <c r="Y96" t="s">
         <v>96</v>
       </c>
-      <c r="Z96"/>
       <c r="AA96" t="b">
         <v>1</v>
       </c>
@@ -11634,7 +11555,6 @@
       <c r="Y97" t="s">
         <v>96</v>
       </c>
-      <c r="Z97"/>
       <c r="AA97" t="b">
         <v>1</v>
       </c>
@@ -11709,7 +11629,6 @@
       <c r="Y98" t="s">
         <v>96</v>
       </c>
-      <c r="Z98"/>
       <c r="AA98" t="b">
         <v>1</v>
       </c>
@@ -11787,7 +11706,6 @@
       <c r="Y99" t="s">
         <v>96</v>
       </c>
-      <c r="Z99"/>
       <c r="AA99" t="b">
         <v>1</v>
       </c>
@@ -11868,7 +11786,6 @@
       <c r="Y100" t="s">
         <v>96</v>
       </c>
-      <c r="Z100"/>
       <c r="AA100" t="b">
         <v>1</v>
       </c>
@@ -12165,7 +12082,6 @@
       <c r="Y104" t="s">
         <v>96</v>
       </c>
-      <c r="Z104"/>
       <c r="AA104" t="b">
         <v>1</v>
       </c>
@@ -12249,7 +12165,6 @@
       <c r="Y105" t="s">
         <v>96</v>
       </c>
-      <c r="Z105"/>
       <c r="AA105" t="b">
         <v>1</v>
       </c>
@@ -13725,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
@@ -13736,19 +13651,19 @@
         <v>404005</v>
       </c>
       <c r="C22" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D22" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E22" t="s">
         <v>911</v>
       </c>
       <c r="F22" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="G22" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -13780,19 +13695,19 @@
         <v>404007</v>
       </c>
       <c r="C23" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D23" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E23" t="s">
         <v>911</v>
       </c>
       <c r="F23" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G23" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -13813,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -13824,19 +13739,19 @@
         <v>404008</v>
       </c>
       <c r="C24" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D24" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E24" t="s">
         <v>911</v>
       </c>
       <c r="F24" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G24" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -13868,19 +13783,19 @@
         <v>404010</v>
       </c>
       <c r="C25" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D25" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E25" t="s">
         <v>911</v>
       </c>
       <c r="F25" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G25" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -13901,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -13912,19 +13827,19 @@
         <v>404011</v>
       </c>
       <c r="C26" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D26" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E26" t="s">
         <v>911</v>
       </c>
       <c r="F26" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G26" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -13956,19 +13871,19 @@
         <v>404013</v>
       </c>
       <c r="C27" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D27" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E27" t="s">
         <v>911</v>
       </c>
       <c r="F27" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G27" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -13989,7 +13904,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="957">
   <si>
     <t>##var</t>
   </si>
@@ -1997,49 +1997,43 @@
     <t>MaxGrantCount</t>
   </si>
   <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>CanAccumulate</t>
-  </si>
-  <si>
-    <t>MaxPendingCount</t>
-  </si>
-  <si>
     <t>SteamPlaytimeGeneratorItemDefId</t>
   </si>
   <si>
+    <t>SteamDropWindowSeconds</t>
+  </si>
+  <si>
+    <t>SteamDropMaxPerWindow</t>
+  </si>
+  <si>
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
-    <t>按玩家总游玩秒数计算的生效时间
-该数值主要用于Steam库存中判定玩家是否可以领取该奖励的时间下限</t>
-  </si>
-  <si>
-    <t>间隔时间
-玩家领取一个盲盒之后，等待下一个盲盒到达需要多长间隔时间</t>
-  </si>
-  <si>
-    <t>结束时间；无限循环填 -1
-策划注意导SteamJSON是需要确认改字段的用途</t>
+    <t>TRUE 表示正常阶段循环装扮券生产行</t>
+  </si>
+  <si>
+    <t>按玩家调度时钟计算的最早生效时间</t>
+  </si>
+  <si>
+    <t>非循环行为相对上次领取间隔；循环行为 Steam 装扮券掉落间隔</t>
+  </si>
+  <si>
+    <t>结束时间；无限循环填 -1</t>
   </si>
   <si>
     <t>最多发放次数；不限填 -1</t>
   </si>
   <si>
-    <t>开启优先级，数值越大越优先</t>
-  </si>
-  <si>
-    <t>是否允许累积多个待领取资格</t>
-  </si>
-  <si>
-    <t>最多保留几个待领取资格</t>
-  </si>
-  <si>
-    <t>该调度到达资格时间时，通过 TriggerItemDrop 请求的 Steam playtimegenerator ItemDef ID。不接入 Steam 掉落时填 0。同一个 ItemDef ID 不建议被多条调度共用。</t>
-  </si>
-  <si>
-    <t>之所以分了12条新手期，而不是3种盲盒循环4次，是因为后续版本可以更精细的控制新手体验，例如先掉帽子盲盒、再掉眼镜盲盒、桌布……</t>
+    <t>通过 TriggerItemDrop 请求的 Steam PlaytimeGenerator ItemDef ID；本地消耗品填 0</t>
+  </si>
+  <si>
+    <t>Steam 掉落窗口基础秒数；乘等待倍率后转为分钟；0 表示不启用</t>
+  </si>
+  <si>
+    <t>Steam 掉落窗口内最多发放次数；未启用窗口时填 0</t>
+  </si>
+  <si>
+    <t>前 12 条控制新手顺序；正常阶段只保留一条循环装扮券生产行</t>
   </si>
   <si>
     <t>是循环生效的</t>
@@ -2057,18 +2051,15 @@
     <t>最多发放次数</t>
   </si>
   <si>
-    <t>优先级</t>
-  </si>
-  <si>
-    <t>是否可累积</t>
-  </si>
-  <si>
-    <t>最大待领取数</t>
-  </si>
-  <si>
     <t>Steam游玩时间生成器DefID</t>
   </si>
   <si>
+    <t>Steam掉落窗口秒数</t>
+  </si>
+  <si>
+    <t>Steam窗口最大发放数</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -2078,7 +2069,7 @@
     <t>新手期固定：15 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：25 分钟 消耗品盲盒</t>
+    <t>新手期固定：25 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：35 分钟装扮盲盒</t>
@@ -2087,7 +2078,7 @@
     <t>新手期固定：45 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：55 分钟 消耗品 盲盒</t>
+    <t>新手期固定：55 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：65 分钟装扮盲盒</t>
@@ -2096,7 +2087,7 @@
     <t>新手期固定：75 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：85 分钟 消耗品 盲盒</t>
+    <t>新手期固定：85 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：95 分钟装扮盲盒</t>
@@ -2105,13 +2096,10 @@
     <t>新手期固定：105 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：115 分钟 消耗品 盲盒</t>
-  </si>
-  <si>
-    <t>正常期循环：125 分钟起每 30 分钟装扮盲盒</t>
-  </si>
-  <si>
-    <t>正常期循环：140 分钟起每 30 分钟 消耗品 盲盒</t>
+    <t>新手期固定：115 分钟消耗品盲盒</t>
+  </si>
+  <si>
+    <t>正常阶段：第 12 个奖励入账后启动；正式倍率下每 30 分钟生产装扮券，60 分钟窗口最多 2 张</t>
   </si>
   <si>
     <t>Rarity</t>
@@ -2575,6 +2563,12 @@
   </si>
   <si>
     <t>Bundle</t>
+  </si>
+  <si>
+    <t>SteamUseDropLimit</t>
+  </si>
+  <si>
+    <t>SteamDropLimit</t>
   </si>
   <si>
     <t>Steam Inventory 内唯一的 ItemDef ID；发布后不得改作他用</t>
@@ -2620,6 +2614,12 @@
     <t>是否参与导出到 Steam ItemDef 配置</t>
   </si>
   <si>
+    <t>仅用于未被启用 Schedule 引用的 PlaytimeGenerator；TRUE 时显式输出 Steam use_drop_limit</t>
+  </si>
+  <si>
+    <t>Steam 永久投放上限；退役 PlaytimeGenerator 填 0</t>
+  </si>
+  <si>
     <t>Steam物品定义ID</t>
   </si>
   <si>
@@ -2650,6 +2650,12 @@
     <t>内容配方</t>
   </si>
   <si>
+    <t>Steam启用投放上限</t>
+  </si>
+  <si>
+    <t>Steam投放上限</t>
+  </si>
+  <si>
     <t>LinkTreeTwitterFollowClaim</t>
   </si>
   <si>
@@ -2779,7 +2785,7 @@
     <t>Generates one newbie blind box reward.</t>
   </si>
   <si>
-    <t>404 表示游玩时间生成器</t>
+    <t>404 表示游玩时间用的生成器</t>
   </si>
   <si>
     <t>Schedule1001PlaytimeDrop</t>
@@ -2900,12 +2906,27 @@
   </si>
   <si>
     <t>Grants the recurring standard blind box item configured by schedule 1013.</t>
+  </si>
+  <si>
+    <t>405 表示掉落窗口用的生成器</t>
+  </si>
+  <si>
+    <t>RecurringDecorationBlindBoxDropV2</t>
+  </si>
+  <si>
+    <t>新版循环装扮盲盒券投放</t>
+  </si>
+  <si>
+    <t>Recurring Decoration Blind Box Drop V2</t>
+  </si>
+  <si>
+    <t>Grants recurring standard blind box vouchers under the Steam playtime drop window.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2914,158 +2935,158 @@
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <sz val="12"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3398,148 +3419,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3547,46 +3568,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3882,8 +3903,8 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+  <tableStyles count="2" defaultPivotStyle="PivotStylePreset2_Accent1" defaultTableStyle="TableStylePreset3_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -3892,7 +3913,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" count="10">
       <tableStyleElement type="headerRow" dxfId="23"/>
       <tableStyleElement type="totalRow" dxfId="22"/>
       <tableStyleElement type="firstRowStripe" dxfId="21"/>
@@ -3919,7 +3940,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -4162,6 +4183,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -12396,49 +12418,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="F1" t="s">
         <v>600</v>
       </c>
       <c r="G1" t="s">
+        <v>763</v>
+      </c>
+      <c r="H1" t="s">
+        <v>764</v>
+      </c>
+      <c r="I1" t="s">
+        <v>765</v>
+      </c>
+      <c r="J1" t="s">
         <v>766</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>767</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>768</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>769</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>770</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>771</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>772</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>773</v>
-      </c>
-      <c r="O1" t="s">
-        <v>774</v>
-      </c>
-      <c r="P1" t="s">
-        <v>775</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -12476,10 +12498,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="M2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -12502,49 +12524,49 @@
         <v>607</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12552,52 +12574,52 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>791</v>
+      </c>
+      <c r="C4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D4" t="s">
+        <v>793</v>
+      </c>
+      <c r="E4" t="s">
         <v>794</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>795</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>796</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>797</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>798</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>799</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>800</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>801</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>802</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>803</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>804</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>805</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>806</v>
-      </c>
-      <c r="O4" t="s">
-        <v>807</v>
-      </c>
-      <c r="P4" t="s">
-        <v>808</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12605,7 +12627,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12617,25 +12639,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>808</v>
+      </c>
+      <c r="H5" t="s">
+        <v>809</v>
+      </c>
+      <c r="I5" t="s">
+        <v>810</v>
+      </c>
+      <c r="J5" t="s">
         <v>811</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>812</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>813</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>814</v>
-      </c>
-      <c r="K5" t="s">
-        <v>815</v>
-      </c>
-      <c r="L5" t="s">
-        <v>816</v>
-      </c>
-      <c r="M5" t="s">
-        <v>817</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12655,7 +12677,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12667,25 +12689,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>816</v>
+      </c>
+      <c r="H6" t="s">
+        <v>817</v>
+      </c>
+      <c r="I6" t="s">
+        <v>810</v>
+      </c>
+      <c r="J6" t="s">
+        <v>818</v>
+      </c>
+      <c r="K6" t="s">
+        <v>818</v>
+      </c>
+      <c r="L6" t="s">
+        <v>813</v>
+      </c>
+      <c r="M6" t="s">
         <v>819</v>
-      </c>
-      <c r="H6" t="s">
-        <v>820</v>
-      </c>
-      <c r="I6" t="s">
-        <v>813</v>
-      </c>
-      <c r="J6" t="s">
-        <v>821</v>
-      </c>
-      <c r="K6" t="s">
-        <v>821</v>
-      </c>
-      <c r="L6" t="s">
-        <v>816</v>
-      </c>
-      <c r="M6" t="s">
-        <v>822</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12705,7 +12727,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12717,25 +12739,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
+        <v>821</v>
+      </c>
+      <c r="H7" t="s">
+        <v>822</v>
+      </c>
+      <c r="I7" t="s">
+        <v>810</v>
+      </c>
+      <c r="J7" t="s">
+        <v>823</v>
+      </c>
+      <c r="K7" t="s">
         <v>824</v>
       </c>
-      <c r="H7" t="s">
-        <v>825</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>813</v>
       </c>
-      <c r="J7" t="s">
-        <v>826</v>
-      </c>
-      <c r="K7" t="s">
-        <v>827</v>
-      </c>
-      <c r="L7" t="s">
-        <v>816</v>
-      </c>
       <c r="M7" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12755,7 +12777,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12767,25 +12789,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="H8" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="I8" t="s">
+        <v>810</v>
+      </c>
+      <c r="J8" t="s">
+        <v>828</v>
+      </c>
+      <c r="K8" t="s">
+        <v>828</v>
+      </c>
+      <c r="L8" t="s">
         <v>813</v>
       </c>
-      <c r="J8" t="s">
-        <v>831</v>
-      </c>
-      <c r="K8" t="s">
-        <v>831</v>
-      </c>
-      <c r="L8" t="s">
-        <v>816</v>
-      </c>
       <c r="M8" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12809,12 +12831,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
-    <col min="3" max="4" width="27" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="18.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="32.5" customWidth="1"/>
     <col min="7" max="7" width="48.0833333333333" customWidth="1"/>
@@ -12830,7 +12853,7 @@
     <col min="17" max="16384" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12838,46 +12861,52 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E1" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
+        <v>830</v>
+      </c>
+      <c r="H1" t="s">
+        <v>831</v>
+      </c>
+      <c r="I1" t="s">
+        <v>832</v>
+      </c>
+      <c r="J1" t="s">
         <v>833</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>834</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>835</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>836</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>837</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>838</v>
-      </c>
-      <c r="M1" t="s">
-        <v>839</v>
-      </c>
-      <c r="N1" t="s">
-        <v>840</v>
-      </c>
-      <c r="O1" t="s">
-        <v>841</v>
       </c>
       <c r="P1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>839</v>
+      </c>
+      <c r="R1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -12923,105 +12952,123 @@
       <c r="P2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:16">
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>845</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="R3" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C4" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="L4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="P4" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>795</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>866</v>
+      </c>
+      <c r="R4" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -13029,22 +13076,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="G5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="H5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -13070,8 +13117,14 @@
       <c r="P5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>161</v>
       </c>
@@ -13079,23 +13132,23 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
+        <v>875</v>
+      </c>
+      <c r="G6" t="s">
+        <v>876</v>
+      </c>
+      <c r="H6" t="s">
         <v>872</v>
       </c>
-      <c r="G6" t="s">
-        <v>873</v>
-      </c>
-      <c r="H6" t="s">
-        <v>869</v>
-      </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
@@ -13120,8 +13173,14 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>161</v>
       </c>
@@ -13129,22 +13188,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="D7" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G7" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="H7" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -13170,8 +13229,14 @@
       <c r="P7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>161</v>
       </c>
@@ -13179,22 +13244,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D8" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="G8" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="H8" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -13220,13 +13285,25 @@
       <c r="P8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>161</v>
       </c>
@@ -13234,7 +13311,7 @@
         <v>402001</v>
       </c>
       <c r="C10" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D10" t="s">
         <v>642</v>
@@ -13243,13 +13320,13 @@
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="G10" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="H10" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -13275,8 +13352,14 @@
       <c r="P10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>161</v>
       </c>
@@ -13284,19 +13367,19 @@
         <v>403001</v>
       </c>
       <c r="C11" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D11" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E11" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F11" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H11" t="s">
         <v>161</v>
@@ -13320,35 +13403,47 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13">
         <v>402002</v>
       </c>
       <c r="C13" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D13" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E13" t="s">
         <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="G13" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -13371,25 +13466,31 @@
       <c r="P13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="B14">
         <v>402003</v>
       </c>
       <c r="C14" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D14" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G14" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -13412,30 +13513,42 @@
       <c r="P14" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="B16">
         <v>403002</v>
       </c>
       <c r="C16" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D16" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E16" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F16" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="G16" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -13456,82 +13569,100 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="B17">
         <v>403003</v>
       </c>
       <c r="C17" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D17" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E17" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G17" t="s">
+        <v>910</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
         <v>906</v>
       </c>
-      <c r="G17" t="s">
-        <v>907</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>903</v>
-      </c>
       <c r="P17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>911</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="B19">
         <v>404001</v>
       </c>
       <c r="C19" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D19" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E19" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F19" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="G19" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -13552,30 +13683,36 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="B20">
         <v>404002</v>
       </c>
       <c r="C20" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D20" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E20" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F20" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="G20" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -13596,30 +13733,36 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="B21">
         <v>404004</v>
       </c>
       <c r="C21" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D21" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E21" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F21" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="G21" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -13640,30 +13783,36 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="B22">
         <v>404005</v>
       </c>
       <c r="C22" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D22" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E22" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F22" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="G22" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -13684,30 +13833,36 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="B23">
         <v>404007</v>
       </c>
       <c r="C23" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D23" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E23" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F23" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G23" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -13728,30 +13883,36 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="B24">
         <v>404008</v>
       </c>
       <c r="C24" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D24" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E24" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F24" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="G24" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -13772,30 +13933,36 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="B25">
         <v>404010</v>
       </c>
       <c r="C25" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D25" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E25" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F25" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="G25" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -13816,30 +13983,36 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="B26">
         <v>404011</v>
       </c>
       <c r="C26" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D26" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E26" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F26" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G26" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -13860,30 +14033,36 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="B27">
         <v>404013</v>
       </c>
       <c r="C27" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D27" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E27" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F27" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G27" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -13904,10 +14083,74 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="B29">
+        <v>405001</v>
+      </c>
+      <c r="C29" t="s">
+        <v>953</v>
+      </c>
+      <c r="D29" t="s">
+        <v>954</v>
+      </c>
+      <c r="E29" t="s">
+        <v>914</v>
+      </c>
+      <c r="F29" t="s">
+        <v>955</v>
+      </c>
+      <c r="G29" t="s">
+        <v>956</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>927</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14741,25 +14984,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
-    <col min="3" max="4" width="10.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.4166666666667" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="14.25" customWidth="1"/>
-    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" customWidth="1"/>
-    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
-    <col min="13" max="13" width="30.8333333333333" customWidth="1"/>
-    <col min="14" max="14" width="45.25" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="6.91666666666667"/>
+    <col customWidth="true" max="2" min="2" width="5.16666666666667"/>
+    <col customWidth="true" max="4" min="3" width="10.8333333333333"/>
+    <col customWidth="true" max="5" min="5" width="13.4166666666667"/>
+    <col customWidth="true" max="6" min="6" width="14"/>
+    <col customWidth="true" max="7" min="7" width="14.5"/>
+    <col customWidth="true" max="8" min="8" width="14.25"/>
+    <col customWidth="true" max="9" min="9" width="13.1666666666667"/>
+    <col customWidth="true" max="10" min="10" width="10.25"/>
+    <col customWidth="true" max="11" min="11" width="18.6666666666667"/>
+    <col customWidth="true" max="12" min="12" width="13.5"/>
+    <col customWidth="true" max="13" min="13" width="30.8333333333333"/>
+    <col customWidth="true" max="14" min="14" width="45.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -14785,22 +15028,19 @@
         <v>649</v>
       </c>
       <c r="I1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J1" t="s">
         <v>650</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>651</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>652</v>
       </c>
-      <c r="L1" t="s">
-        <v>600</v>
-      </c>
-      <c r="M1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -14826,27 +15066,27 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
         <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>35</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:14">
+    <row r="3" spans="1:13" s="1" customFormat="true" ht="128" customHeight="true">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -14862,25 +15102,22 @@
         <v>658</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
@@ -14891,40 +15128,37 @@
         <v>618</v>
       </c>
       <c r="D4" t="s">
+        <v>663</v>
+      </c>
+      <c r="E4" t="s">
         <v>664</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>665</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>666</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>667</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>627</v>
+      </c>
+      <c r="J4" t="s">
         <v>668</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>669</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>670</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>671</v>
       </c>
-      <c r="L4" t="s">
-        <v>627</v>
-      </c>
-      <c r="M4" t="s">
-        <v>672</v>
-      </c>
-      <c r="N4" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -14946,26 +15180,23 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>50</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>404001</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>404001</v>
-      </c>
-      <c r="N5" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -14987,26 +15218,23 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>404002</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>404002</v>
-      </c>
-      <c r="N6" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -15028,26 +15256,23 @@
       <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7" t="b">
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -15069,26 +15294,23 @@
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>404004</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>404004</v>
-      </c>
-      <c r="N8" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -15110,26 +15332,23 @@
       <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>404005</v>
       </c>
       <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>404005</v>
-      </c>
-      <c r="N9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -15151,26 +15370,23 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10" t="b">
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -15192,26 +15408,23 @@
       <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11">
-        <v>50</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>404007</v>
       </c>
       <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>404007</v>
-      </c>
-      <c r="N11" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -15233,26 +15446,23 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>404008</v>
       </c>
       <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>404008</v>
-      </c>
-      <c r="N12" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -15274,26 +15484,23 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13" t="b">
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -15315,26 +15522,23 @@
       <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>50</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>404010</v>
       </c>
       <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>404010</v>
-      </c>
-      <c r="N14" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -15356,26 +15560,23 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>404011</v>
       </c>
       <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>404011</v>
-      </c>
-      <c r="N15" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16">
         <v>1012</v>
       </c>
@@ -15397,78 +15598,39 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16" t="b">
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17">
-        <v>1013</v>
-      </c>
-      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="B18">
+        <v>2001</v>
+      </c>
+      <c r="C18">
         <v>1001</v>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>750</v>
-      </c>
-      <c r="F17">
-        <v>180</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-      <c r="H17">
-        <v>-1</v>
-      </c>
-      <c r="I17">
-        <v>50</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>404013</v>
-      </c>
-      <c r="N17" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18">
-        <v>1014</v>
-      </c>
-      <c r="C18">
-        <v>2001</v>
-      </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="F18">
         <v>180</v>
@@ -15479,23 +15641,20 @@
       <c r="H18">
         <v>-1</v>
       </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>405001</v>
       </c>
       <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>687</v>
+        <v>360</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -15529,10 +15688,10 @@
         <v>644</v>
       </c>
       <c r="D1" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G1" t="s">
         <v>600</v>
@@ -15564,13 +15723,13 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
@@ -15591,13 +15750,13 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G4" t="s">
         <v>627</v>
       </c>
       <c r="H4" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -15777,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -16015,7 +16174,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -16190,28 +16349,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F1" t="s">
+        <v>694</v>
+      </c>
+      <c r="G1" t="s">
         <v>695</v>
       </c>
-      <c r="D1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>696</v>
-      </c>
-      <c r="F1" t="s">
-        <v>697</v>
-      </c>
-      <c r="G1" t="s">
-        <v>698</v>
-      </c>
-      <c r="H1" t="s">
-        <v>699</v>
       </c>
       <c r="I1" t="s">
         <v>600</v>
       </c>
       <c r="J1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -16254,28 +16413,28 @@
         <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -16286,31 +16445,31 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E4" t="s">
+        <v>706</v>
+      </c>
+      <c r="F4" t="s">
         <v>707</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>707</v>
+      </c>
+      <c r="H4" t="s">
         <v>708</v>
-      </c>
-      <c r="E4" t="s">
-        <v>709</v>
-      </c>
-      <c r="F4" t="s">
-        <v>710</v>
-      </c>
-      <c r="G4" t="s">
-        <v>710</v>
-      </c>
-      <c r="H4" t="s">
-        <v>711</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>
       </c>
       <c r="J4" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="K4" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -16726,7 +16885,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -16761,7 +16920,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -16860,7 +17019,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -16895,7 +17054,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -17058,7 +17217,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -17093,7 +17252,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -17128,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -17335,25 +17494,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F1" t="s">
+        <v>712</v>
+      </c>
+      <c r="G1" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1" t="s">
         <v>714</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>715</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>716</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>717</v>
-      </c>
-      <c r="I1" t="s">
-        <v>718</v>
-      </c>
-      <c r="K1" t="s">
-        <v>719</v>
-      </c>
-      <c r="L1" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17397,23 +17556,23 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -17430,28 +17589,28 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
+        <v>723</v>
+      </c>
+      <c r="F4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G4" t="s">
+        <v>725</v>
+      </c>
+      <c r="H4" t="s">
         <v>726</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>727</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>671</v>
+      </c>
+      <c r="K4" t="s">
         <v>728</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4" t="s">
         <v>729</v>
-      </c>
-      <c r="I4" t="s">
-        <v>730</v>
-      </c>
-      <c r="J4" t="s">
-        <v>673</v>
-      </c>
-      <c r="K4" t="s">
-        <v>731</v>
-      </c>
-      <c r="L4" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -17465,16 +17624,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
+        <v>730</v>
+      </c>
+      <c r="F5" t="s">
+        <v>731</v>
+      </c>
+      <c r="H5" t="s">
+        <v>732</v>
+      </c>
+      <c r="K5" t="s">
         <v>733</v>
-      </c>
-      <c r="F5" t="s">
-        <v>734</v>
-      </c>
-      <c r="H5" t="s">
-        <v>735</v>
-      </c>
-      <c r="K5" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -17488,16 +17647,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F6" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H6" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="K6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -17511,16 +17670,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="K7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -17534,16 +17693,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F8" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H8" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="K8" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -17557,16 +17716,16 @@
         <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F9" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H9" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K9" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -17580,16 +17739,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F10" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H10" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="K10" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -17603,16 +17762,16 @@
         <v>507</v>
       </c>
       <c r="E11" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F11" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H11" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J11" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -17626,16 +17785,16 @@
         <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F12" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H12" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J12" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -17663,10 +17822,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D1" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -17683,7 +17842,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -17700,10 +17859,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -17725,7 +17884,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -17739,7 +17898,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -17753,7 +17912,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -17777,7 +17936,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -17884,10 +18043,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -17912,10 +18071,10 @@
         <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="994">
   <si>
     <t>##var</t>
   </si>
@@ -2367,7 +2367,13 @@
     <t>SequentialPackId</t>
   </si>
   <si>
-    <t>SteamPromoItemDefId</t>
+    <t>RewardBlindBoxId</t>
+  </si>
+  <si>
+    <t>SteamReceiptItemDefId</t>
+  </si>
+  <si>
+    <t>SteamClaimBundleItemDefId</t>
   </si>
   <si>
     <t>ELinkTreeOpenCheckType</t>
@@ -2418,7 +2424,16 @@
     <t>RewardType=SequentialPack 时关联的顺序礼包 ID；当前不用填 0</t>
   </si>
   <si>
-    <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
+    <t>RewardType=BlindBox 时填写 BlindBox.Id</t>
+  </si>
+  <si>
+    <t>领过奖励的玩家会在Steam服务器上留下凭证，防止再次领奖
+Bundle 中永久保留的回执。
+Banner 是否已领取只检查这个 ID。</t>
+  </si>
+  <si>
+    <t>客户端调用 AddPromoItem 的目标。
+必须指向 Type=Bundle、PromoRule=manual 的定义。</t>
   </si>
   <si>
     <t>入口ID</t>
@@ -2466,7 +2481,13 @@
     <t>顺序礼包ID</t>
   </si>
   <si>
-    <t>Steam奖励定义ID</t>
+    <t>奖励盲盒ID</t>
+  </si>
+  <si>
+    <t>Steam永久领取回执DefID</t>
+  </si>
+  <si>
+    <t>Steam领奖礼包DefID</t>
   </si>
   <si>
     <t>TwitterFollow</t>
@@ -2707,6 +2728,33 @@
     <t>Permanent receipt for the Xiaohongshu profile reward.</t>
   </si>
   <si>
+    <t>LinkTreeTwitterFollowClaimV2</t>
+  </si>
+  <si>
+    <t>推特领奖回执凭证</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityClaimV2</t>
+  </si>
+  <si>
+    <t>社区领奖回执凭证</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreClaimV2</t>
+  </si>
+  <si>
+    <t>商店页面领奖回执凭证</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileClaimV2</t>
+  </si>
+  <si>
+    <t>小红书领奖回执凭证</t>
+  </si>
+  <si>
+    <t>402表示开盒成本</t>
+  </si>
+  <si>
     <t>DecorationBlindBoxVoucher</t>
   </si>
   <si>
@@ -2716,6 +2764,33 @@
     <t>Opens one decoration blind box.</t>
   </si>
   <si>
+    <t>StandardBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>标准盲盒券</t>
+  </si>
+  <si>
+    <t>Standard Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one standard blind box.</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>新手盲盒券</t>
+  </si>
+  <si>
+    <t>Newbie Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one newbie blind box.</t>
+  </si>
+  <si>
+    <t>403盲盒物品生成器</t>
+  </si>
+  <si>
     <t>DecorationBlindBoxV1Generator</t>
   </si>
   <si>
@@ -2734,30 +2809,6 @@
     <t>101002x1;101003x1</t>
   </si>
   <si>
-    <t>StandardBlindBoxContainer</t>
-  </si>
-  <si>
-    <t>标准盲盒开箱成本</t>
-  </si>
-  <si>
-    <t>Standard Blind Box</t>
-  </si>
-  <si>
-    <t>A consumable Steam inventory item used to open one standard blind box.</t>
-  </si>
-  <si>
-    <t>NewbieBlindBoxContainer</t>
-  </si>
-  <si>
-    <t>新手盲盒开箱成本</t>
-  </si>
-  <si>
-    <t>Newbie Blind Box</t>
-  </si>
-  <si>
-    <t>A consumable Steam inventory item used to open one newbie blind box.</t>
-  </si>
-  <si>
     <t>StandardBlindBoxV1Generator</t>
   </si>
   <si>
@@ -2921,12 +2972,75 @@
   </si>
   <si>
     <t>Grants recurring standard blind box vouchers under the Steam playtime drop window.</t>
+  </si>
+  <si>
+    <t>406 表示礼包</t>
+  </si>
+  <si>
+    <t>LinkTreeTwitterFollowRewardBundleV2</t>
+  </si>
+  <si>
+    <t>推特领奖礼包</t>
+  </si>
+  <si>
+    <t>LinkTree Reward Bundle - Twitter Follow</t>
+  </si>
+  <si>
+    <t>Grants the permanent receipt and fixed item reward for the Twitter follow entry.</t>
+  </si>
+  <si>
+    <t>401005x1;192005x1</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityRewardBundleV2</t>
+  </si>
+  <si>
+    <t>Steam社区领奖礼包</t>
+  </si>
+  <si>
+    <t>LinkTree Reward Bundle - Steam Community</t>
+  </si>
+  <si>
+    <t>Grants the permanent receipt for the Steam Community entry. The chip reward is granted locally.</t>
+  </si>
+  <si>
+    <t>401006x1</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreRewardBundleV2</t>
+  </si>
+  <si>
+    <t>Steam商店领奖礼包</t>
+  </si>
+  <si>
+    <t>LinkTree Reward Bundle - Steam Store</t>
+  </si>
+  <si>
+    <t>Grants the permanent receipt for the Steam Store entry. The chip reward is granted locally.</t>
+  </si>
+  <si>
+    <t>401007x1</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileRewardBundleV2</t>
+  </si>
+  <si>
+    <t>小红书领奖礼包</t>
+  </si>
+  <si>
+    <t>LinkTree Reward Bundle - Xiaohongshu Profile</t>
+  </si>
+  <si>
+    <t>Grants the permanent receipt and fixed item reward for the Xiaohongshu profile entry.</t>
+  </si>
+  <si>
+    <t>401008x1;191012x1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2935,158 +3049,158 @@
   </numFmts>
   <fonts count="21">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <sz val="12"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3419,148 +3533,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3568,46 +3682,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="true">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3903,8 +4017,8 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultPivotStyle="PivotStylePreset2_Accent1" defaultTableStyle="TableStylePreset3_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -3913,7 +4027,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="23"/>
       <tableStyleElement type="totalRow" dxfId="22"/>
       <tableStyleElement type="firstRowStripe" dxfId="21"/>
@@ -3940,7 +4054,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -4183,7 +4297,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -12388,8 +12501,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
@@ -12407,10 +12520,12 @@
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="15.6666666666667" customWidth="1"/>
     <col min="16" max="16" width="20.0833333333333" customWidth="1"/>
-    <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
+    <col min="17" max="17" width="21.9166666666667" customWidth="1"/>
+    <col min="18" max="18" width="22.1666666666667" customWidth="1"/>
+    <col min="19" max="19" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12462,8 +12577,14 @@
       <c r="Q1" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>774</v>
+      </c>
+      <c r="S1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -12498,10 +12619,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -12515,8 +12636,14 @@
       <c r="Q2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -12524,110 +12651,122 @@
         <v>607</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>792</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D4" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="F4" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="G4" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="H4" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="I4" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="J4" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="K4" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="L4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M4" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="N4" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="O4" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="P4" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="Q4" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>810</v>
+      </c>
+      <c r="R4" t="s">
+        <v>811</v>
+      </c>
+      <c r="S4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12636,28 +12775,28 @@
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="H5" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="I5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="J5" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="K5" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="L5" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="M5" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12668,16 +12807,16 @@
       <c r="P5">
         <v>0</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>401001</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12686,28 +12825,28 @@
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="s">
+        <v>822</v>
+      </c>
+      <c r="H6" t="s">
+        <v>823</v>
+      </c>
+      <c r="I6" t="s">
         <v>816</v>
       </c>
-      <c r="H6" t="s">
-        <v>817</v>
-      </c>
-      <c r="I6" t="s">
-        <v>810</v>
-      </c>
       <c r="J6" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="K6" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="L6" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="M6" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12718,16 +12857,16 @@
       <c r="P6">
         <v>0</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>401002</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12736,28 +12875,28 @@
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="H7" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="I7" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="J7" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="K7" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L7" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="M7" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12768,16 +12907,16 @@
       <c r="P7">
         <v>0</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>401003</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12786,28 +12925,28 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="H8" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="I8" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="J8" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="K8" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="L8" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="M8" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12818,8 +12957,220 @@
       <c r="P8">
         <v>0</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>401004</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:19">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>813</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>814</v>
+      </c>
+      <c r="H9" t="s">
+        <v>815</v>
+      </c>
+      <c r="I9" t="s">
+        <v>816</v>
+      </c>
+      <c r="J9" t="s">
+        <v>817</v>
+      </c>
+      <c r="K9" t="s">
+        <v>818</v>
+      </c>
+      <c r="L9" t="s">
+        <v>819</v>
+      </c>
+      <c r="M9" t="s">
+        <v>820</v>
+      </c>
+      <c r="N9">
+        <v>92005</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>401005</v>
+      </c>
+      <c r="S9">
+        <v>406005</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:19">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>821</v>
+      </c>
+      <c r="D10">
+        <v>80</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>822</v>
+      </c>
+      <c r="H10" t="s">
+        <v>823</v>
+      </c>
+      <c r="I10" t="s">
+        <v>816</v>
+      </c>
+      <c r="J10" t="s">
+        <v>824</v>
+      </c>
+      <c r="K10" t="s">
+        <v>824</v>
+      </c>
+      <c r="L10" t="s">
+        <v>819</v>
+      </c>
+      <c r="M10" t="s">
+        <v>825</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>2500</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>401006</v>
+      </c>
+      <c r="S10">
+        <v>406006</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:19">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>826</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>827</v>
+      </c>
+      <c r="H11" t="s">
+        <v>828</v>
+      </c>
+      <c r="I11" t="s">
+        <v>816</v>
+      </c>
+      <c r="J11" t="s">
+        <v>829</v>
+      </c>
+      <c r="K11" t="s">
+        <v>830</v>
+      </c>
+      <c r="L11" t="s">
+        <v>819</v>
+      </c>
+      <c r="M11" t="s">
+        <v>825</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>2500</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>401007</v>
+      </c>
+      <c r="S11">
+        <v>406007</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:19">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>831</v>
+      </c>
+      <c r="D12">
+        <v>120</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>832</v>
+      </c>
+      <c r="H12" t="s">
+        <v>833</v>
+      </c>
+      <c r="I12" t="s">
+        <v>816</v>
+      </c>
+      <c r="J12" t="s">
+        <v>834</v>
+      </c>
+      <c r="K12" t="s">
+        <v>834</v>
+      </c>
+      <c r="L12" t="s">
+        <v>819</v>
+      </c>
+      <c r="M12" t="s">
+        <v>820</v>
+      </c>
+      <c r="N12">
+        <v>91012</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>401008</v>
+      </c>
+      <c r="S12">
+        <v>406008</v>
       </c>
     </row>
   </sheetData>
@@ -12831,7 +13182,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -12864,46 +13215,46 @@
         <v>761</v>
       </c>
       <c r="E1" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="H1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="I1" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="J1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="K1" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="L1" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="M1" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="N1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="O1" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="P1" t="s">
         <v>600</v>
       </c>
       <c r="Q1" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="R1" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -12964,52 +13315,52 @@
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -13017,55 +13368,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D4" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="E4" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="F4" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="I4" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="L4" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="M4" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="P4" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="Q4" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="R4" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -13076,22 +13427,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="D5" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="G5" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="H5" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -13132,22 +13483,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D6" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="G6" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="H6" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -13188,22 +13539,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D7" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="G7" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H7" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -13244,22 +13595,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D8" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="G8" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="H8" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -13292,9 +13643,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" customFormat="1" spans="1:18">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>401005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>891</v>
+      </c>
+      <c r="D9" t="s">
+        <v>892</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>876</v>
+      </c>
+      <c r="G9" t="s">
+        <v>877</v>
+      </c>
+      <c r="H9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>161</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -13303,168 +13699,180 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" customFormat="1" spans="1:18">
       <c r="A10" t="s">
         <v>161</v>
       </c>
       <c r="B10">
-        <v>402001</v>
+        <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="D10" t="s">
-        <v>642</v>
+        <v>894</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
+        <v>881</v>
+      </c>
+      <c r="G10" t="s">
+        <v>882</v>
+      </c>
+      <c r="H10" t="s">
+        <v>878</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>161</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:18">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11">
+        <v>401007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>895</v>
+      </c>
+      <c r="D11" t="s">
+        <v>896</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" t="s">
+        <v>885</v>
+      </c>
+      <c r="G11" t="s">
         <v>886</v>
       </c>
-      <c r="G10" t="s">
-        <v>887</v>
-      </c>
-      <c r="H10" t="s">
-        <v>872</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="s">
-        <v>161</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11">
-        <v>403001</v>
-      </c>
-      <c r="C11" t="s">
-        <v>888</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="H11" t="s">
+        <v>878</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:18">
+      <c r="A12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12">
+        <v>401008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>897</v>
+      </c>
+      <c r="D12" t="s">
+        <v>898</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" t="s">
         <v>889</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G12" t="s">
         <v>890</v>
       </c>
-      <c r="F11" t="s">
-        <v>891</v>
-      </c>
-      <c r="G11" t="s">
-        <v>892</v>
-      </c>
-      <c r="H11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>893</v>
-      </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
+      <c r="H12" t="s">
+        <v>878</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>161</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="B13">
-        <v>402002</v>
-      </c>
-      <c r="C13" t="s">
-        <v>894</v>
-      </c>
-      <c r="D13" t="s">
-        <v>895</v>
-      </c>
-      <c r="E13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" t="s">
-        <v>896</v>
-      </c>
-      <c r="G13" t="s">
-        <v>897</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="b">
-        <v>1</v>
+      <c r="B13" t="s">
+        <v>899</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -13474,26 +13882,32 @@
       </c>
     </row>
     <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
       <c r="B14">
-        <v>402003</v>
+        <v>402001</v>
       </c>
       <c r="C14" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D14" t="s">
-        <v>899</v>
+        <v>642</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G14" t="s">
-        <v>901</v>
+        <v>902</v>
+      </c>
+      <c r="H14" t="s">
+        <v>878</v>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -13510,6 +13924,9 @@
       <c r="N14" t="b">
         <v>1</v>
       </c>
+      <c r="O14" t="s">
+        <v>161</v>
+      </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
@@ -13521,8 +13938,44 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>39</v>
+      <c r="B15">
+        <v>402002</v>
+      </c>
+      <c r="C15" t="s">
+        <v>903</v>
+      </c>
+      <c r="D15" t="s">
+        <v>904</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" t="s">
+        <v>905</v>
+      </c>
+      <c r="G15" t="s">
+        <v>906</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="b">
+        <v>1</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -13533,22 +13986,22 @@
     </row>
     <row r="16" spans="1:18">
       <c r="B16">
-        <v>403002</v>
+        <v>402003</v>
       </c>
       <c r="C16" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="D16" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="E16" t="s">
-        <v>890</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="G16" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -13566,10 +14019,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>906</v>
+        <v>1</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
@@ -13582,61 +14032,61 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="B17">
-        <v>403003</v>
-      </c>
-      <c r="C17" t="s">
-        <v>907</v>
-      </c>
-      <c r="D17" t="s">
-        <v>908</v>
-      </c>
-      <c r="E17" t="s">
-        <v>890</v>
-      </c>
-      <c r="F17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G17" t="s">
-        <v>910</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>906</v>
-      </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>911</v>
+        <v>161</v>
+      </c>
+      <c r="B18">
+        <v>403001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>912</v>
+      </c>
+      <c r="D18" t="s">
+        <v>913</v>
+      </c>
+      <c r="E18" t="s">
+        <v>914</v>
+      </c>
+      <c r="F18" t="s">
+        <v>915</v>
+      </c>
+      <c r="G18" t="s">
+        <v>916</v>
+      </c>
+      <c r="H18" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>917</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -13647,22 +14097,22 @@
     </row>
     <row r="19" spans="1:18">
       <c r="B19">
-        <v>404001</v>
+        <v>403002</v>
       </c>
       <c r="C19" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="D19" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="E19" t="s">
         <v>914</v>
       </c>
       <c r="F19" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="G19" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -13683,7 +14133,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -13697,22 +14147,22 @@
     </row>
     <row r="20" spans="1:18">
       <c r="B20">
-        <v>404002</v>
+        <v>403003</v>
       </c>
       <c r="C20" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="D20" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="E20" t="s">
         <v>914</v>
       </c>
       <c r="F20" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="G20" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -13746,58 +14196,16 @@
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="B21">
-        <v>404004</v>
-      </c>
-      <c r="C21" t="s">
-        <v>923</v>
-      </c>
-      <c r="D21" t="s">
-        <v>924</v>
-      </c>
-      <c r="E21" t="s">
-        <v>914</v>
-      </c>
-      <c r="F21" t="s">
-        <v>925</v>
-      </c>
-      <c r="G21" t="s">
-        <v>926</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>927</v>
-      </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="B22">
-        <v>404005</v>
+        <v>404001</v>
       </c>
       <c r="C22" t="s">
         <v>928</v>
@@ -13806,13 +14214,13 @@
         <v>929</v>
       </c>
       <c r="E22" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F22" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G22" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -13833,7 +14241,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -13847,22 +14255,22 @@
     </row>
     <row r="23" spans="1:18">
       <c r="B23">
-        <v>404007</v>
+        <v>404002</v>
       </c>
       <c r="C23" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D23" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E23" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F23" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G23" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -13883,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -13897,22 +14305,22 @@
     </row>
     <row r="24" spans="1:18">
       <c r="B24">
-        <v>404008</v>
+        <v>404004</v>
       </c>
       <c r="C24" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D24" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E24" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F24" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G24" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -13933,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -13947,22 +14355,22 @@
     </row>
     <row r="25" spans="1:18">
       <c r="B25">
-        <v>404010</v>
+        <v>404005</v>
       </c>
       <c r="C25" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D25" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E25" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F25" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="G25" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -13983,7 +14391,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -13997,22 +14405,22 @@
     </row>
     <row r="26" spans="1:18">
       <c r="B26">
-        <v>404011</v>
+        <v>404007</v>
       </c>
       <c r="C26" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D26" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="E26" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F26" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="G26" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -14033,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -14047,22 +14455,22 @@
     </row>
     <row r="27" spans="1:18">
       <c r="B27">
-        <v>404013</v>
+        <v>404008</v>
       </c>
       <c r="C27" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D27" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E27" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F27" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="G27" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -14083,73 +14491,443 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" t="s">
-        <v>952</v>
+      <c r="B28">
+        <v>404010</v>
+      </c>
+      <c r="C28" t="s">
+        <v>956</v>
+      </c>
+      <c r="D28" t="s">
+        <v>957</v>
+      </c>
+      <c r="E28" t="s">
+        <v>930</v>
+      </c>
+      <c r="F28" t="s">
+        <v>958</v>
+      </c>
+      <c r="G28" t="s">
+        <v>959</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>943</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="B29">
+        <v>404011</v>
+      </c>
+      <c r="C29" t="s">
+        <v>960</v>
+      </c>
+      <c r="D29" t="s">
+        <v>961</v>
+      </c>
+      <c r="E29" t="s">
+        <v>930</v>
+      </c>
+      <c r="F29" t="s">
+        <v>962</v>
+      </c>
+      <c r="G29" t="s">
+        <v>963</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>938</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="B30">
+        <v>404013</v>
+      </c>
+      <c r="C30" t="s">
+        <v>964</v>
+      </c>
+      <c r="D30" t="s">
+        <v>965</v>
+      </c>
+      <c r="E30" t="s">
+        <v>930</v>
+      </c>
+      <c r="F30" t="s">
+        <v>966</v>
+      </c>
+      <c r="G30" t="s">
+        <v>967</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>943</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="B32">
         <v>405001</v>
       </c>
-      <c r="C29" t="s">
-        <v>953</v>
-      </c>
-      <c r="D29" t="s">
-        <v>954</v>
-      </c>
-      <c r="E29" t="s">
-        <v>914</v>
-      </c>
-      <c r="F29" t="s">
-        <v>955</v>
-      </c>
-      <c r="G29" t="s">
-        <v>956</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" t="b">
-        <v>1</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>927</v>
-      </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29">
+      <c r="C32" t="s">
+        <v>969</v>
+      </c>
+      <c r="D32" t="s">
+        <v>970</v>
+      </c>
+      <c r="E32" t="s">
+        <v>930</v>
+      </c>
+      <c r="F32" t="s">
+        <v>971</v>
+      </c>
+      <c r="G32" t="s">
+        <v>972</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>943</v>
+      </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="B34">
+        <v>406005</v>
+      </c>
+      <c r="C34" t="s">
+        <v>974</v>
+      </c>
+      <c r="D34" t="s">
+        <v>975</v>
+      </c>
+      <c r="E34" t="s">
+        <v>844</v>
+      </c>
+      <c r="F34" t="s">
+        <v>976</v>
+      </c>
+      <c r="G34" t="s">
+        <v>977</v>
+      </c>
+      <c r="H34" t="s">
+        <v>878</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>978</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="B35">
+        <v>406006</v>
+      </c>
+      <c r="C35" t="s">
+        <v>979</v>
+      </c>
+      <c r="D35" t="s">
+        <v>980</v>
+      </c>
+      <c r="E35" t="s">
+        <v>844</v>
+      </c>
+      <c r="F35" t="s">
+        <v>981</v>
+      </c>
+      <c r="G35" t="s">
+        <v>982</v>
+      </c>
+      <c r="H35" t="s">
+        <v>878</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>983</v>
+      </c>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="B36">
+        <v>406007</v>
+      </c>
+      <c r="C36" t="s">
+        <v>984</v>
+      </c>
+      <c r="D36" t="s">
+        <v>985</v>
+      </c>
+      <c r="E36" t="s">
+        <v>844</v>
+      </c>
+      <c r="F36" t="s">
+        <v>986</v>
+      </c>
+      <c r="G36" t="s">
+        <v>987</v>
+      </c>
+      <c r="H36" t="s">
+        <v>878</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>988</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="B37">
+        <v>406008</v>
+      </c>
+      <c r="C37" t="s">
+        <v>989</v>
+      </c>
+      <c r="D37" t="s">
+        <v>990</v>
+      </c>
+      <c r="E37" t="s">
+        <v>844</v>
+      </c>
+      <c r="F37" t="s">
+        <v>991</v>
+      </c>
+      <c r="G37" t="s">
+        <v>992</v>
+      </c>
+      <c r="H37" t="s">
+        <v>878</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>993</v>
+      </c>
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37">
         <v>0</v>
       </c>
     </row>
@@ -14987,19 +15765,19 @@
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="6.91666666666667"/>
-    <col customWidth="true" max="2" min="2" width="5.16666666666667"/>
-    <col customWidth="true" max="4" min="3" width="10.8333333333333"/>
-    <col customWidth="true" max="5" min="5" width="13.4166666666667"/>
-    <col customWidth="true" max="6" min="6" width="14"/>
-    <col customWidth="true" max="7" min="7" width="14.5"/>
-    <col customWidth="true" max="8" min="8" width="14.25"/>
-    <col customWidth="true" max="9" min="9" width="13.1666666666667"/>
-    <col customWidth="true" max="10" min="10" width="10.25"/>
-    <col customWidth="true" max="11" min="11" width="18.6666666666667"/>
-    <col customWidth="true" max="12" min="12" width="13.5"/>
-    <col customWidth="true" max="13" min="13" width="30.8333333333333"/>
-    <col customWidth="true" max="14" min="14" width="45.25"/>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
+    <col min="3" max="4" width="10.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="18.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="30.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -15078,7 +15856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="true" ht="128" customHeight="true">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="1" activeTab="11"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="1" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1190">
   <si>
     <t>##var</t>
   </si>
@@ -3340,6 +3340,201 @@
     <t>401008x1;191012x1</t>
   </si>
   <si>
+    <t>正式盲盒开箱成本</t>
+  </si>
+  <si>
+    <t>StandardBlindBoxContainerOfficial</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxContainerOfficial</t>
+  </si>
+  <si>
+    <t>DecorationBlindBoxVoucherOfficial</t>
+  </si>
+  <si>
+    <t>正式盲盒物品生成器</t>
+  </si>
+  <si>
+    <t>StandardBlindBoxV1GeneratorOfficial</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxV1GeneratorOfficial</t>
+  </si>
+  <si>
+    <t>正式 LinkTree 永久回执</t>
+  </si>
+  <si>
+    <t>LinkTreeTwitterFollowClaimOfficial</t>
+  </si>
+  <si>
+    <t>推特领奖回执</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityClaimOfficial</t>
+  </si>
+  <si>
+    <t>Steam社区领奖回执</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreClaimOfficial</t>
+  </si>
+  <si>
+    <t>Steam商店领奖回执</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileClaimOfficial</t>
+  </si>
+  <si>
+    <t>小红书领奖回执</t>
+  </si>
+  <si>
+    <t>正式 LinkTree 领取 Bundle</t>
+  </si>
+  <si>
+    <t>LinkTreeTwitterFollowRewardBundle</t>
+  </si>
+  <si>
+    <t>501001x1;192005x1</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityRewardBundle</t>
+  </si>
+  <si>
+    <t>501002x1</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreRewardBundle</t>
+  </si>
+  <si>
+    <t>501003x1</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileRewardBundle</t>
+  </si>
+  <si>
+    <t>501004x1;191012x1</t>
+  </si>
+  <si>
+    <t>正式新手一次性游玩投放</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1001PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1001游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1001 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1001.</t>
+  </si>
+  <si>
+    <t>204001x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1002PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1002游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1002 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1002.</t>
+  </si>
+  <si>
+    <t>201002x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1004PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1004游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1004 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1004.</t>
+  </si>
+  <si>
+    <t>201001x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1005PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1005游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1005 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1005.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1007PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1007游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1007 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1007.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1008PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1008游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1008 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1008.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1010PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1010游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1010 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1010.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1011PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1011游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1011 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1011.</t>
+  </si>
+  <si>
+    <t>正式长期循环游玩投放</t>
+  </si>
+  <si>
+    <t>RecurringDecorationBlindBoxDrop</t>
+  </si>
+  <si>
+    <t>循环装扮盲盒券投放</t>
+  </si>
+  <si>
+    <t>Recurring Decoration Blind Box Drop</t>
+  </si>
+  <si>
     <t>StartItemDefId</t>
   </si>
   <si>
@@ -3571,7 +3766,7 @@
     <t>游戏正常阶段持续运行的循环投放</t>
   </si>
   <si>
-    <t>长期循环装扮盲盒券</t>
+    <t>长期循环装扮盲盒券，受掉落窗口控制</t>
   </si>
   <si>
     <t>固定系统投放预留段。</t>
@@ -4260,9 +4455,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4274,10 +4472,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4934,11 +5132,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="19" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="20" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="19" customWidth="1"/>
+    <col min="23" max="23" width="7" style="20" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -4955,16 +5153,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -5045,16 +5243,16 @@
       </c>
     </row>
     <row r="2" spans="1:35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
         <v>32</v>
       </c>
@@ -5137,94 +5335,94 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:35">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:35">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="21"/>
+      <c r="M3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="4" t="s">
+      <c r="S3" s="9"/>
+      <c r="T3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="8"/>
-      <c r="X3" s="4" t="s">
+      <c r="W3" s="9"/>
+      <c r="X3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" s="4" t="s">
+      <c r="AH3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AI3" s="4" t="s">
+      <c r="AI3" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E4" t="s">
@@ -5315,72 +5513,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="18" customFormat="1" spans="1:35">
-      <c r="B5" s="18">
+    <row r="5" s="19" customFormat="1" spans="1:35">
+      <c r="B5" s="19">
         <v>1001</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <v>200</v>
       </c>
-      <c r="J5" s="18">
-        <v>0</v>
-      </c>
-      <c r="K5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18" t="s">
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18">
-        <v>0</v>
-      </c>
-      <c r="P5" s="18">
-        <v>0</v>
-      </c>
-      <c r="T5" s="18" t="s">
+      <c r="M5" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="19">
+        <v>0</v>
+      </c>
+      <c r="O5" s="19">
+        <v>0</v>
+      </c>
+      <c r="P5" s="19">
+        <v>0</v>
+      </c>
+      <c r="T5" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="U5" s="18" t="s">
+      <c r="U5" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="18">
+      <c r="V5" s="19">
         <v>1001</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="Y5" s="18" t="s">
+      <c r="W5" s="19"/>
+      <c r="Y5" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="18" t="b">
+      <c r="AA5" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5844,10 +6042,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="14">
         <v>100</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="14">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -6562,7 +6760,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="19" t="s">
+      <c r="S23" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -6920,7 +7118,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="19" t="s">
+      <c r="S28" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -6932,7 +7130,7 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="19" t="s">
+      <c r="W28" s="20" t="s">
         <v>161</v>
       </c>
       <c r="X28">
@@ -7024,7 +7222,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="19" t="s">
+      <c r="S29" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -7036,7 +7234,7 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="19" t="s">
+      <c r="W29" s="20" t="s">
         <v>161</v>
       </c>
       <c r="X29">
@@ -7413,435 +7611,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="18" customFormat="1" spans="2:31">
-      <c r="B35" s="18">
+    <row r="35" s="19" customFormat="1" spans="2:31">
+      <c r="B35" s="19">
         <v>4001</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="18">
-        <v>0</v>
-      </c>
-      <c r="J35" s="18">
-        <v>0</v>
-      </c>
-      <c r="K35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" s="18" t="s">
+      <c r="I35" s="19">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="18">
-        <v>0</v>
-      </c>
-      <c r="O35" s="18">
-        <v>0</v>
-      </c>
-      <c r="P35" s="18">
-        <v>0</v>
-      </c>
-      <c r="T35" s="18" t="s">
+      <c r="M35" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="19">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19">
+        <v>0</v>
+      </c>
+      <c r="P35" s="19">
+        <v>0</v>
+      </c>
+      <c r="T35" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="U35" s="18" t="s">
+      <c r="U35" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="X35" s="18">
+      <c r="X35" s="19">
         <v>104001</v>
       </c>
-      <c r="Y35" s="18" t="s">
+      <c r="Y35" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="18" customFormat="1" spans="2:31">
-      <c r="B36" s="18">
+      <c r="Z35" s="19"/>
+      <c r="AA35" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="19" customFormat="1" spans="2:31">
+      <c r="B36" s="19">
         <v>4002</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H36" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="18">
-        <v>0</v>
-      </c>
-      <c r="J36" s="18">
-        <v>0</v>
-      </c>
-      <c r="K36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="18" t="s">
+      <c r="I36" s="19">
+        <v>0</v>
+      </c>
+      <c r="J36" s="19">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="18">
-        <v>0</v>
-      </c>
-      <c r="O36" s="18">
-        <v>0</v>
-      </c>
-      <c r="P36" s="18">
-        <v>0</v>
-      </c>
-      <c r="T36" s="18" t="s">
+      <c r="M36" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="19">
+        <v>0</v>
+      </c>
+      <c r="O36" s="19">
+        <v>0</v>
+      </c>
+      <c r="P36" s="19">
+        <v>0</v>
+      </c>
+      <c r="T36" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="U36" s="18" t="s">
+      <c r="U36" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="X36" s="18">
+      <c r="X36" s="19">
         <v>104002</v>
       </c>
-      <c r="Y36" s="18" t="s">
+      <c r="Y36" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="18" customFormat="1" spans="2:31">
-      <c r="B37" s="18">
+      <c r="Z36" s="19"/>
+      <c r="AA36" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="19" customFormat="1" spans="2:31">
+      <c r="B37" s="19">
         <v>4003</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="18">
-        <v>0</v>
-      </c>
-      <c r="J37" s="18">
-        <v>0</v>
-      </c>
-      <c r="K37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" s="18" t="s">
+      <c r="I37" s="19">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="18">
-        <v>0</v>
-      </c>
-      <c r="O37" s="18">
-        <v>0</v>
-      </c>
-      <c r="P37" s="18">
-        <v>0</v>
-      </c>
-      <c r="T37" s="18" t="s">
+      <c r="M37" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="19">
+        <v>0</v>
+      </c>
+      <c r="O37" s="19">
+        <v>0</v>
+      </c>
+      <c r="P37" s="19">
+        <v>0</v>
+      </c>
+      <c r="T37" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="U37" s="18" t="s">
+      <c r="U37" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="X37" s="18">
+      <c r="X37" s="19">
         <v>104003</v>
       </c>
-      <c r="Y37" s="18" t="s">
+      <c r="Y37" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="18" customFormat="1" spans="2:31">
-      <c r="B38" s="18">
+      <c r="Z37" s="19"/>
+      <c r="AA37" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="19" customFormat="1" spans="2:31">
+      <c r="B38" s="19">
         <v>4004</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="18">
-        <v>0</v>
-      </c>
-      <c r="J38" s="18">
-        <v>0</v>
-      </c>
-      <c r="K38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" s="18" t="s">
+      <c r="I38" s="19">
+        <v>0</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="18">
-        <v>0</v>
-      </c>
-      <c r="O38" s="18">
-        <v>0</v>
-      </c>
-      <c r="P38" s="18">
-        <v>0</v>
-      </c>
-      <c r="T38" s="18" t="s">
+      <c r="M38" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="19">
+        <v>0</v>
+      </c>
+      <c r="O38" s="19">
+        <v>0</v>
+      </c>
+      <c r="P38" s="19">
+        <v>0</v>
+      </c>
+      <c r="T38" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="U38" s="18" t="s">
+      <c r="U38" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="X38" s="18">
+      <c r="X38" s="19">
         <v>104004</v>
       </c>
-      <c r="Y38" s="18" t="s">
+      <c r="Y38" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="18" customFormat="1" spans="2:31">
-      <c r="B39" s="18">
+      <c r="Z38" s="19"/>
+      <c r="AA38" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="19" customFormat="1" spans="2:31">
+      <c r="B39" s="19">
         <v>4005</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I39" s="18">
-        <v>0</v>
-      </c>
-      <c r="J39" s="18">
-        <v>0</v>
-      </c>
-      <c r="K39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="18" t="s">
+      <c r="I39" s="19">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="18">
-        <v>0</v>
-      </c>
-      <c r="O39" s="18">
-        <v>0</v>
-      </c>
-      <c r="P39" s="18">
-        <v>0</v>
-      </c>
-      <c r="T39" s="18" t="s">
+      <c r="M39" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="19">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="U39" s="18" t="s">
+      <c r="U39" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="X39" s="18">
+      <c r="X39" s="19">
         <v>104005</v>
       </c>
-      <c r="Y39" s="18" t="s">
+      <c r="Y39" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="18" customFormat="1" spans="2:31">
-      <c r="B40" s="18">
+      <c r="Z39" s="19"/>
+      <c r="AA39" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="19" customFormat="1" spans="2:31">
+      <c r="B40" s="19">
         <v>4006</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="H40" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" s="18">
-        <v>0</v>
-      </c>
-      <c r="K40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" s="18" t="s">
+      <c r="I40" s="19">
+        <v>0</v>
+      </c>
+      <c r="J40" s="19">
+        <v>0</v>
+      </c>
+      <c r="K40" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40" s="18">
-        <v>0</v>
-      </c>
-      <c r="O40" s="18">
-        <v>0</v>
-      </c>
-      <c r="P40" s="18">
-        <v>0</v>
-      </c>
-      <c r="T40" s="18" t="s">
+      <c r="M40" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="19">
+        <v>0</v>
+      </c>
+      <c r="O40" s="19">
+        <v>0</v>
+      </c>
+      <c r="P40" s="19">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="U40" s="18" t="s">
+      <c r="U40" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="X40" s="18">
+      <c r="X40" s="19">
         <v>104006</v>
       </c>
-      <c r="Y40" s="18" t="s">
+      <c r="Y40" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="18" t="b">
+      <c r="Z40" s="19"/>
+      <c r="AA40" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8389,87 +8587,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="18" customFormat="1" spans="2:31">
-      <c r="B49" s="18">
+    <row r="49" s="19" customFormat="1" spans="2:31">
+      <c r="B49" s="19">
         <v>6001</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="18" t="s">
+      <c r="F49" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I49" s="18">
-        <v>300</v>
-      </c>
-      <c r="J49" s="18">
-        <v>0</v>
-      </c>
-      <c r="K49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="18" t="s">
+      <c r="I49" s="19">
+        <v>300</v>
+      </c>
+      <c r="J49" s="19">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M49" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="18">
-        <v>0</v>
-      </c>
-      <c r="O49" s="18">
-        <v>0</v>
-      </c>
-      <c r="P49" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" s="18" t="s">
+      <c r="M49" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="19">
+        <v>0</v>
+      </c>
+      <c r="O49" s="19">
+        <v>0</v>
+      </c>
+      <c r="P49" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="U49" s="18" t="s">
+      <c r="U49" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="X49" s="18">
+      <c r="X49" s="19">
         <v>106001</v>
       </c>
-      <c r="Y49" s="18" t="s">
+      <c r="Y49" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z49" s="18"/>
-      <c r="AA49" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="18" t="b">
+      <c r="Z49" s="19"/>
+      <c r="AA49" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8525,7 +8723,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="19" t="s">
+      <c r="S50" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -8608,7 +8806,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="19" t="s">
+      <c r="S51" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -8691,7 +8889,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="19" t="s">
+      <c r="S52" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -8774,7 +8972,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="19" t="s">
+      <c r="S53" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -8857,7 +9055,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="19" t="s">
+      <c r="S54" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -8940,7 +9138,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="19" t="s">
+      <c r="S55" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -9023,7 +9221,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="19" t="s">
+      <c r="S56" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -9106,7 +9304,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="19" t="s">
+      <c r="S57" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -9189,7 +9387,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="19" t="s">
+      <c r="S58" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -9272,7 +9470,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="19" t="s">
+      <c r="S59" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -9507,72 +9705,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="18" customFormat="1" spans="2:31">
-      <c r="B63" s="18">
+    <row r="63" s="19" customFormat="1" spans="2:31">
+      <c r="B63" s="19">
         <v>7004</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="H63" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="I63" s="18">
-        <v>300</v>
-      </c>
-      <c r="J63" s="18">
-        <v>0</v>
-      </c>
-      <c r="K63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="18" t="s">
+      <c r="I63" s="19">
+        <v>300</v>
+      </c>
+      <c r="J63" s="19">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63" s="18">
-        <v>0</v>
-      </c>
-      <c r="O63" s="18">
-        <v>0</v>
-      </c>
-      <c r="P63" s="18">
-        <v>0</v>
-      </c>
-      <c r="T63" s="18" t="s">
+      <c r="M63" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="19">
+        <v>0</v>
+      </c>
+      <c r="O63" s="19">
+        <v>0</v>
+      </c>
+      <c r="P63" s="19">
+        <v>0</v>
+      </c>
+      <c r="T63" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="U63" s="18" t="s">
+      <c r="U63" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="X63" s="18">
+      <c r="X63" s="19">
         <v>107004</v>
       </c>
-      <c r="Y63" s="18" t="s">
+      <c r="Y63" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z63" s="18"/>
-      <c r="AA63" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="18" t="b">
+      <c r="Z63" s="19"/>
+      <c r="AA63" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9589,7 +9787,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="14" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -9657,7 +9855,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="13" t="s">
+      <c r="H65" s="14" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -9832,7 +10030,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="19" t="s">
+      <c r="S67" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -9915,7 +10113,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="19" t="s">
+      <c r="S68" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -9998,7 +10196,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="19" t="s">
+      <c r="S69" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -10081,7 +10279,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="19" t="s">
+      <c r="S70" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -10164,7 +10362,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="19" t="s">
+      <c r="S71" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -10247,7 +10445,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="19" t="s">
+      <c r="S72" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -10330,7 +10528,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="19" t="s">
+      <c r="S73" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -10413,7 +10611,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="19" t="s">
+      <c r="S74" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -10496,7 +10694,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="19" t="s">
+      <c r="S75" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -10579,7 +10777,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="19" t="s">
+      <c r="S76" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -10733,7 +10931,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="19" t="s">
+      <c r="S78" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -10745,7 +10943,7 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="19" t="s">
+      <c r="W78" s="20" t="s">
         <v>161</v>
       </c>
       <c r="X78">
@@ -10834,7 +11032,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="19" t="s">
+      <c r="S79" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -10917,7 +11115,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="19" t="s">
+      <c r="S80" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -11000,7 +11198,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="19" t="s">
+      <c r="S81" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -11083,7 +11281,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="19" t="s">
+      <c r="S82" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -11166,7 +11364,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="19" t="s">
+      <c r="S83" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -11249,7 +11447,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="19" t="s">
+      <c r="S84" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -11539,7 +11737,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="19" t="s">
+      <c r="S88" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -11551,7 +11749,7 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="19" t="s">
+      <c r="W88" s="20" t="s">
         <v>161</v>
       </c>
       <c r="X88">
@@ -11643,7 +11841,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="19" t="s">
+      <c r="S89" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -11655,7 +11853,7 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="19" t="s">
+      <c r="W89" s="20" t="s">
         <v>161</v>
       </c>
       <c r="X89">
@@ -11818,7 +12016,7 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="19" t="s">
+      <c r="W91" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X91">
@@ -11898,7 +12096,7 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="19" t="s">
+      <c r="W92" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X92">
@@ -11978,7 +12176,7 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="19" t="s">
+      <c r="W93" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X93">
@@ -12058,7 +12256,7 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="19" t="s">
+      <c r="W94" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X94">
@@ -12138,7 +12336,7 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="19" t="s">
+      <c r="W95" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X95">
@@ -12218,7 +12416,7 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="19" t="s">
+      <c r="W96" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X96">
@@ -12298,7 +12496,7 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="19" t="s">
+      <c r="W97" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X97">
@@ -12372,7 +12570,7 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="19" t="s">
+      <c r="W98" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X98">
@@ -12529,7 +12727,7 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="19" t="s">
+      <c r="W100" s="20" t="s">
         <v>446</v>
       </c>
       <c r="X100">
@@ -12554,216 +12752,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" s="18" customFormat="1" spans="2:31">
-      <c r="B101" s="18">
+    <row r="101" s="19" customFormat="1" spans="2:31">
+      <c r="B101" s="19">
         <v>10001</v>
       </c>
-      <c r="C101" s="18" t="s">
+      <c r="C101" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D101" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E101" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="H101" s="18" t="s">
+      <c r="H101" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I101" s="18">
-        <v>300</v>
-      </c>
-      <c r="J101" s="18">
-        <v>0</v>
-      </c>
-      <c r="K101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" s="18" t="s">
+      <c r="I101" s="19">
+        <v>300</v>
+      </c>
+      <c r="J101" s="19">
+        <v>0</v>
+      </c>
+      <c r="K101" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101" s="18">
-        <v>0</v>
-      </c>
-      <c r="O101" s="18">
-        <v>0</v>
-      </c>
-      <c r="P101" s="18">
-        <v>0</v>
-      </c>
-      <c r="T101" s="18" t="s">
+      <c r="M101" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="19">
+        <v>0</v>
+      </c>
+      <c r="O101" s="19">
+        <v>0</v>
+      </c>
+      <c r="P101" s="19">
+        <v>0</v>
+      </c>
+      <c r="T101" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="U101" s="18" t="s">
+      <c r="U101" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="X101" s="18">
+      <c r="X101" s="19">
         <v>110001</v>
       </c>
-      <c r="Y101" s="18" t="s">
+      <c r="Y101" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z101" s="18"/>
-      <c r="AA101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" s="18" customFormat="1" spans="2:31">
-      <c r="B102" s="18">
+      <c r="Z101" s="19"/>
+      <c r="AA101" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="19" customFormat="1" spans="2:31">
+      <c r="B102" s="19">
         <v>11001</v>
       </c>
-      <c r="C102" s="18" t="s">
+      <c r="C102" s="19" t="s">
         <v>488</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="E102" s="18" t="s">
+      <c r="E102" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="H102" s="18" t="s">
+      <c r="H102" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I102" s="18">
-        <v>300</v>
-      </c>
-      <c r="J102" s="18">
-        <v>0</v>
-      </c>
-      <c r="K102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" s="18" t="s">
+      <c r="I102" s="19">
+        <v>300</v>
+      </c>
+      <c r="J102" s="19">
+        <v>0</v>
+      </c>
+      <c r="K102" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102" s="18">
-        <v>0</v>
-      </c>
-      <c r="O102" s="18">
-        <v>0</v>
-      </c>
-      <c r="P102" s="18">
-        <v>0</v>
-      </c>
-      <c r="T102" s="18" t="s">
+      <c r="M102" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="19">
+        <v>0</v>
+      </c>
+      <c r="O102" s="19">
+        <v>0</v>
+      </c>
+      <c r="P102" s="19">
+        <v>0</v>
+      </c>
+      <c r="T102" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="U102" s="18" t="s">
+      <c r="U102" s="19" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="18" t="s">
+      <c r="W102" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="X102" s="18">
+      <c r="X102" s="19">
         <v>111001</v>
       </c>
-      <c r="Y102" s="18" t="s">
+      <c r="Y102" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z102" s="18"/>
-      <c r="AA102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" s="18" customFormat="1" spans="2:31">
-      <c r="B103" s="18">
+      <c r="Z102" s="19"/>
+      <c r="AA102" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="19" customFormat="1" spans="2:31">
+      <c r="B103" s="19">
         <v>11002</v>
       </c>
-      <c r="C103" s="18" t="s">
+      <c r="C103" s="19" t="s">
         <v>494</v>
       </c>
-      <c r="D103" s="18" t="s">
+      <c r="D103" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E103" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="G103" s="18">
+      <c r="G103" s="19">
         <v>11001</v>
       </c>
-      <c r="H103" s="18" t="s">
+      <c r="H103" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I103" s="18">
-        <v>300</v>
-      </c>
-      <c r="J103" s="18">
-        <v>0</v>
-      </c>
-      <c r="K103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" s="18" t="s">
+      <c r="I103" s="19">
+        <v>300</v>
+      </c>
+      <c r="J103" s="19">
+        <v>0</v>
+      </c>
+      <c r="K103" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="M103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103" s="18">
-        <v>0</v>
-      </c>
-      <c r="O103" s="18">
-        <v>0</v>
-      </c>
-      <c r="P103" s="18">
-        <v>0</v>
-      </c>
-      <c r="T103" s="18" t="s">
+      <c r="M103" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="19">
+        <v>0</v>
+      </c>
+      <c r="O103" s="19">
+        <v>0</v>
+      </c>
+      <c r="P103" s="19">
+        <v>0</v>
+      </c>
+      <c r="T103" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="U103" s="18" t="s">
+      <c r="U103" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="X103" s="18">
+      <c r="X103" s="19">
         <v>111002</v>
       </c>
-      <c r="Y103" s="18" t="s">
+      <c r="Y103" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="Z103" s="18"/>
-      <c r="AA103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="18" t="b">
+      <c r="Z103" s="19"/>
+      <c r="AA103" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12786,7 +12984,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="13" t="s">
+      <c r="H104" s="14" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -12819,7 +13017,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="19" t="s">
+      <c r="S104" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -12869,7 +13067,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="13" t="s">
+      <c r="H105" s="14" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -12902,7 +13100,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="19" t="s">
+      <c r="S105" s="20" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -12970,14 +13168,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="19"/>
+      <c r="S106" s="20"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="19" t="s">
+      <c r="W106" s="20" t="s">
         <v>509</v>
       </c>
       <c r="X106">
@@ -13040,7 +13238,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="19"/>
+      <c r="S107" s="20"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -13050,7 +13248,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="19" t="s">
+      <c r="W107" s="20" t="s">
         <v>509</v>
       </c>
       <c r="X107">
@@ -13260,62 +13458,62 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="77" customHeight="1" spans="1:19">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="77" customHeight="1" spans="1:19">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="2" t="s">
         <v>837</v>
       </c>
     </row>
@@ -13625,10 +13823,10 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>401005</v>
+        <v>501001</v>
       </c>
       <c r="S9">
-        <v>406005</v>
+        <v>601001</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:19">
@@ -13678,10 +13876,10 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>401006</v>
+        <v>501002</v>
       </c>
       <c r="S10">
-        <v>406006</v>
+        <v>601002</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:19">
@@ -13731,10 +13929,10 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>401007</v>
+        <v>501003</v>
       </c>
       <c r="S11">
-        <v>406007</v>
+        <v>601003</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:19">
@@ -13784,10 +13982,10 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>401008</v>
+        <v>501004</v>
       </c>
       <c r="S12">
-        <v>406008</v>
+        <v>601004</v>
       </c>
     </row>
   </sheetData>
@@ -13799,11 +13997,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.4166666666667" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="18.0833333333333" customWidth="1"/>
@@ -13927,56 +14125,56 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="72" customHeight="1" spans="1:18">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="72" customHeight="1" spans="1:18">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>893</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>894</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="2" t="s">
         <v>904</v>
       </c>
     </row>
@@ -14855,7 +15053,7 @@
         <v>1</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -14905,7 +15103,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -14955,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -15005,7 +15203,7 @@
         <v>1</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -15055,7 +15253,7 @@
         <v>1</v>
       </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -15105,7 +15303,7 @@
         <v>1</v>
       </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -15155,7 +15353,7 @@
         <v>1</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -15205,7 +15403,7 @@
         <v>1</v>
       </c>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -15313,7 +15511,7 @@
         <v>1</v>
       </c>
       <c r="Q32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -15536,6 +15734,1579 @@
         <v>0</v>
       </c>
       <c r="R37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C39" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>161</v>
+      </c>
+      <c r="F39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" t="s">
+        <v>161</v>
+      </c>
+      <c r="K39" t="s">
+        <v>161</v>
+      </c>
+      <c r="L39" t="s">
+        <v>161</v>
+      </c>
+      <c r="M39" t="s">
+        <v>161</v>
+      </c>
+      <c r="N39" t="s">
+        <v>161</v>
+      </c>
+      <c r="O39" t="s">
+        <v>161</v>
+      </c>
+      <c r="P39" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>161</v>
+      </c>
+      <c r="R39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40">
+        <v>201001</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D40" t="s">
+        <v>947</v>
+      </c>
+      <c r="E40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" t="s">
+        <v>948</v>
+      </c>
+      <c r="G40" t="s">
+        <v>949</v>
+      </c>
+      <c r="H40" t="s">
+        <v>161</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>161</v>
+      </c>
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41">
+        <v>201002</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D41" t="s">
+        <v>951</v>
+      </c>
+      <c r="E41" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" t="s">
+        <v>952</v>
+      </c>
+      <c r="G41" t="s">
+        <v>953</v>
+      </c>
+      <c r="H41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>161</v>
+      </c>
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42">
+        <v>204001</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D42" t="s">
+        <v>682</v>
+      </c>
+      <c r="E42" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" t="s">
+        <v>944</v>
+      </c>
+      <c r="G42" t="s">
+        <v>945</v>
+      </c>
+      <c r="H42" t="s">
+        <v>161</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>161</v>
+      </c>
+      <c r="P42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" t="s">
+        <v>161</v>
+      </c>
+      <c r="K43" t="s">
+        <v>161</v>
+      </c>
+      <c r="L43" t="s">
+        <v>161</v>
+      </c>
+      <c r="M43" t="s">
+        <v>161</v>
+      </c>
+      <c r="N43" t="s">
+        <v>161</v>
+      </c>
+      <c r="O43" t="s">
+        <v>161</v>
+      </c>
+      <c r="P43" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>161</v>
+      </c>
+      <c r="R43" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44">
+        <v>301001</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D44" t="s">
+        <v>962</v>
+      </c>
+      <c r="E44" t="s">
+        <v>957</v>
+      </c>
+      <c r="F44" t="s">
+        <v>963</v>
+      </c>
+      <c r="G44" t="s">
+        <v>964</v>
+      </c>
+      <c r="H44" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>965</v>
+      </c>
+      <c r="P44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45">
+        <v>301002</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D45" t="s">
+        <v>967</v>
+      </c>
+      <c r="E45" t="s">
+        <v>957</v>
+      </c>
+      <c r="F45" t="s">
+        <v>968</v>
+      </c>
+      <c r="G45" t="s">
+        <v>969</v>
+      </c>
+      <c r="H45" t="s">
+        <v>161</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>965</v>
+      </c>
+      <c r="P45" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C46" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" t="s">
+        <v>161</v>
+      </c>
+      <c r="G46" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" t="s">
+        <v>161</v>
+      </c>
+      <c r="I46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46" t="s">
+        <v>161</v>
+      </c>
+      <c r="K46" t="s">
+        <v>161</v>
+      </c>
+      <c r="L46" t="s">
+        <v>161</v>
+      </c>
+      <c r="M46" t="s">
+        <v>161</v>
+      </c>
+      <c r="N46" t="s">
+        <v>161</v>
+      </c>
+      <c r="O46" t="s">
+        <v>161</v>
+      </c>
+      <c r="P46" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>161</v>
+      </c>
+      <c r="R46" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47">
+        <v>501001</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" t="s">
+        <v>919</v>
+      </c>
+      <c r="G47" t="s">
+        <v>920</v>
+      </c>
+      <c r="H47" t="s">
+        <v>921</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>161</v>
+      </c>
+      <c r="P47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48">
+        <v>501002</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E48" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" t="s">
+        <v>924</v>
+      </c>
+      <c r="G48" t="s">
+        <v>925</v>
+      </c>
+      <c r="H48" t="s">
+        <v>921</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>161</v>
+      </c>
+      <c r="P48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49">
+        <v>501003</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E49" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" t="s">
+        <v>928</v>
+      </c>
+      <c r="G49" t="s">
+        <v>929</v>
+      </c>
+      <c r="H49" t="s">
+        <v>921</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>161</v>
+      </c>
+      <c r="P49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50">
+        <v>501004</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>932</v>
+      </c>
+      <c r="G50" t="s">
+        <v>933</v>
+      </c>
+      <c r="H50" t="s">
+        <v>921</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>161</v>
+      </c>
+      <c r="P50" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C51" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" t="s">
+        <v>161</v>
+      </c>
+      <c r="F51" t="s">
+        <v>161</v>
+      </c>
+      <c r="G51" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" t="s">
+        <v>161</v>
+      </c>
+      <c r="I51" t="s">
+        <v>161</v>
+      </c>
+      <c r="J51" t="s">
+        <v>161</v>
+      </c>
+      <c r="K51" t="s">
+        <v>161</v>
+      </c>
+      <c r="L51" t="s">
+        <v>161</v>
+      </c>
+      <c r="M51" t="s">
+        <v>161</v>
+      </c>
+      <c r="N51" t="s">
+        <v>161</v>
+      </c>
+      <c r="O51" t="s">
+        <v>161</v>
+      </c>
+      <c r="P51" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>161</v>
+      </c>
+      <c r="R51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52">
+        <v>601001</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E52" t="s">
+        <v>887</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H52" t="s">
+        <v>921</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>1054</v>
+      </c>
+      <c r="P52" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53">
+        <v>601002</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E53" t="s">
+        <v>887</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H53" t="s">
+        <v>921</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>1056</v>
+      </c>
+      <c r="P53" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54">
+        <v>601003</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E54" t="s">
+        <v>887</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H54" t="s">
+        <v>921</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P54" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55">
+        <v>601004</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E55" t="s">
+        <v>887</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H55" t="s">
+        <v>921</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>1060</v>
+      </c>
+      <c r="P55" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C56" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" t="s">
+        <v>161</v>
+      </c>
+      <c r="F56" t="s">
+        <v>161</v>
+      </c>
+      <c r="G56" t="s">
+        <v>161</v>
+      </c>
+      <c r="H56" t="s">
+        <v>161</v>
+      </c>
+      <c r="I56" t="s">
+        <v>161</v>
+      </c>
+      <c r="J56" t="s">
+        <v>161</v>
+      </c>
+      <c r="K56" t="s">
+        <v>161</v>
+      </c>
+      <c r="L56" t="s">
+        <v>161</v>
+      </c>
+      <c r="M56" t="s">
+        <v>161</v>
+      </c>
+      <c r="N56" t="s">
+        <v>161</v>
+      </c>
+      <c r="O56" t="s">
+        <v>161</v>
+      </c>
+      <c r="P56" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>161</v>
+      </c>
+      <c r="R56" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>161</v>
+      </c>
+      <c r="B57">
+        <v>700001</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E57" t="s">
+        <v>621</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H57" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>1066</v>
+      </c>
+      <c r="P57" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58">
+        <v>700002</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E58" t="s">
+        <v>621</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H58" t="s">
+        <v>161</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P58" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>161</v>
+      </c>
+      <c r="B59">
+        <v>700004</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E59" t="s">
+        <v>621</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H59" t="s">
+        <v>161</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P59" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>161</v>
+      </c>
+      <c r="B60">
+        <v>700005</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E60" t="s">
+        <v>621</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H60" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P60" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61">
+        <v>700007</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E61" t="s">
+        <v>621</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H61" t="s">
+        <v>161</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P61" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62">
+        <v>700008</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E62" t="s">
+        <v>621</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H62" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P62" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63">
+        <v>700010</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E63" t="s">
+        <v>621</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H63" t="s">
+        <v>161</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P63" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64">
+        <v>700011</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E64" t="s">
+        <v>621</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H64" t="s">
+        <v>161</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P64" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C65" t="s">
+        <v>161</v>
+      </c>
+      <c r="D65" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" t="s">
+        <v>161</v>
+      </c>
+      <c r="F65" t="s">
+        <v>161</v>
+      </c>
+      <c r="G65" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65" t="s">
+        <v>161</v>
+      </c>
+      <c r="I65" t="s">
+        <v>161</v>
+      </c>
+      <c r="J65" t="s">
+        <v>161</v>
+      </c>
+      <c r="K65" t="s">
+        <v>161</v>
+      </c>
+      <c r="L65" t="s">
+        <v>161</v>
+      </c>
+      <c r="M65" t="s">
+        <v>161</v>
+      </c>
+      <c r="N65" t="s">
+        <v>161</v>
+      </c>
+      <c r="O65" t="s">
+        <v>161</v>
+      </c>
+      <c r="P65" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>161</v>
+      </c>
+      <c r="R65" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>161</v>
+      </c>
+      <c r="B66">
+        <v>701001</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E66" t="s">
+        <v>621</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H66" t="s">
+        <v>161</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P66" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66">
         <v>0</v>
       </c>
     </row>
@@ -15561,7 +17332,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{9ab3edca-2e89-40f6-8d77-6a22e32bb9ff}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{a6f8058b-4dba-4734-8a34-b85bc85182b6}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -15588,35 +17359,35 @@
   <cols>
     <col min="3" max="3" width="14.0833333333333" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4166666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1036</v>
+        <v>1101</v>
       </c>
       <c r="D1" t="s">
-        <v>1037</v>
+        <v>1102</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1038</v>
+      <c r="F1" s="2" t="s">
+        <v>1103</v>
       </c>
       <c r="G1" t="s">
-        <v>1039</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -15631,7 +17402,7 @@
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
@@ -15639,22 +17410,22 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="G3" t="s">
@@ -15662,25 +17433,25 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1040</v>
+        <v>1105</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1041</v>
+        <v>1106</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F4" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>598</v>
       </c>
     </row>
@@ -15697,14 +17468,14 @@
       <c r="D5">
         <v>199999</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1044</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -15720,14 +17491,14 @@
       <c r="D6">
         <v>299999</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1046</v>
+      <c r="E6" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1111</v>
       </c>
       <c r="G6" t="s">
-        <v>1047</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
@@ -15743,14 +17514,14 @@
       <c r="D7">
         <v>229999</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>1049</v>
+      <c r="E7" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1114</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1050</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8" ht="34.8" spans="1:7">
@@ -15766,14 +17537,14 @@
       <c r="D8">
         <v>299999</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>1052</v>
+      <c r="E8" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1117</v>
       </c>
       <c r="G8" t="s">
-        <v>1053</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" ht="69.6" spans="1:7">
@@ -15790,13 +17561,13 @@
         <v>399999</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>1055</v>
+        <v>1119</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1120</v>
       </c>
       <c r="G9" t="s">
-        <v>1056</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" ht="34.8" spans="1:7">
@@ -15813,13 +17584,13 @@
         <v>301999</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>1058</v>
+        <v>1122</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1123</v>
       </c>
       <c r="G10" t="s">
-        <v>1059</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="11" ht="34.8" spans="1:7">
@@ -15836,13 +17607,13 @@
         <v>302999</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>1061</v>
+        <v>1125</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1126</v>
       </c>
       <c r="G11" t="s">
-        <v>1062</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="12" ht="34.8" spans="1:7">
@@ -15859,13 +17630,13 @@
         <v>399999</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>1064</v>
+        <v>1128</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1129</v>
       </c>
       <c r="G12" t="s">
-        <v>1065</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="13" ht="87" spans="1:7">
@@ -15882,13 +17653,13 @@
         <v>499999</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>1067</v>
+        <v>1131</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1132</v>
       </c>
       <c r="G13" t="s">
-        <v>1068</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="14" ht="52.2" spans="1:7">
@@ -15904,14 +17675,14 @@
       <c r="D14">
         <v>409999</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>1070</v>
+      <c r="E14" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1135</v>
       </c>
       <c r="G14" t="s">
-        <v>1071</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" ht="52.2" spans="1:7">
@@ -15928,13 +17699,13 @@
         <v>499999</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>1073</v>
+        <v>1137</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1138</v>
       </c>
       <c r="G15" t="s">
-        <v>1074</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="16" ht="52.2" spans="1:7">
@@ -15951,13 +17722,13 @@
         <v>599999</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>1076</v>
+        <v>1140</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1141</v>
       </c>
       <c r="G16" t="s">
-        <v>1077</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="17" ht="34.8" spans="1:7">
@@ -15974,13 +17745,13 @@
         <v>501999</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>1079</v>
+        <v>1143</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1144</v>
       </c>
       <c r="G17" t="s">
-        <v>1080</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="18" ht="34.8" spans="1:7">
@@ -15997,13 +17768,13 @@
         <v>502999</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>1082</v>
+        <v>1146</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1147</v>
       </c>
       <c r="G18" t="s">
-        <v>1083</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="19" ht="34.8" spans="1:7">
@@ -16020,13 +17791,13 @@
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>1085</v>
+        <v>1149</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1150</v>
       </c>
       <c r="G19" t="s">
-        <v>1086</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="20" ht="87" spans="1:7">
@@ -16043,13 +17814,13 @@
         <v>699999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>1088</v>
+        <v>1152</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1153</v>
       </c>
       <c r="G20" t="s">
-        <v>1089</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -16066,13 +17837,13 @@
         <v>601999</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>1091</v>
+        <v>1155</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1156</v>
       </c>
       <c r="G21" t="s">
-        <v>1092</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -16089,13 +17860,13 @@
         <v>602999</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>1094</v>
+        <v>1158</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1159</v>
       </c>
       <c r="G22" t="s">
-        <v>1095</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="23" ht="34.8" spans="1:7">
@@ -16112,13 +17883,13 @@
         <v>603999</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>1097</v>
+        <v>1161</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1162</v>
       </c>
       <c r="G23" t="s">
-        <v>1098</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="24" ht="34.8" spans="1:7">
@@ -16135,13 +17906,13 @@
         <v>699999</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>1100</v>
+        <v>1164</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1165</v>
       </c>
       <c r="G24" t="s">
-        <v>1101</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -16158,13 +17929,13 @@
         <v>799999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>1103</v>
+        <v>1167</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1168</v>
       </c>
       <c r="G25" t="s">
-        <v>1104</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="26" ht="52.2" spans="1:7">
@@ -16181,13 +17952,13 @@
         <v>709999</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>1106</v>
+        <v>1170</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1171</v>
       </c>
       <c r="G26" t="s">
-        <v>1107</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -16204,13 +17975,13 @@
         <v>700999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>1109</v>
+        <v>1173</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1174</v>
       </c>
       <c r="G27" t="s">
-        <v>1110</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -16227,13 +17998,13 @@
         <v>701999</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>1112</v>
+        <v>1176</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1177</v>
       </c>
       <c r="G28" t="s">
-        <v>1113</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="29" ht="34.8" spans="1:7">
@@ -16250,13 +18021,13 @@
         <v>709999</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>1115</v>
+        <v>1179</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>1180</v>
       </c>
       <c r="G29" t="s">
-        <v>1116</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="30" ht="34.8" spans="1:7">
@@ -16273,13 +18044,13 @@
         <v>799999</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>1118</v>
+        <v>1182</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>1183</v>
       </c>
       <c r="G30" t="s">
-        <v>1119</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="31" ht="34.8" spans="1:7">
@@ -16296,10 +18067,10 @@
         <v>999999</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1120</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>1121</v>
+        <v>1185</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>1186</v>
       </c>
       <c r="G31" t="s">
         <v>629</v>
@@ -16319,61 +18090,52 @@
         <v>99999</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>1123</v>
+        <v>1187</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>1188</v>
       </c>
       <c r="G32" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="33" spans="5:6">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5">
       <c r="E33" s="6"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="35" spans="5:6">
+    </row>
+    <row r="35" spans="5:5">
       <c r="E35" s="6"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="5:6">
+    </row>
+    <row r="36" spans="5:5">
       <c r="E36" s="6"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="5:6">
+    </row>
+    <row r="37" spans="5:5">
       <c r="E37" s="6"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="5:6">
+    </row>
+    <row r="38" spans="5:5">
       <c r="E38" s="6"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" spans="5:6">
+    </row>
+    <row r="39" spans="5:5">
       <c r="E39" s="6"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="5:6">
+    </row>
+    <row r="40" spans="5:5">
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="5:6">
+    <row r="41" spans="5:5">
       <c r="E41" s="6"/>
     </row>
-    <row r="43" spans="5:6">
+    <row r="43" spans="5:5">
       <c r="E43" s="6"/>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="5:6">
+    </row>
+    <row r="44" spans="5:5">
       <c r="E44" s="6"/>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="5:6">
+    </row>
+    <row r="45" spans="5:5">
       <c r="E45" s="6"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="47" spans="5:6">
+    </row>
+    <row r="47" spans="5:5">
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="5:6">
+    <row r="48" spans="5:5">
       <c r="E48" s="6"/>
     </row>
   </sheetData>
@@ -16395,35 +18157,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>513</v>
       </c>
       <c r="E2" t="s">
@@ -16432,130 +18194,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="10">
-        <v>1</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="11" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="11">
         <v>2</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="11" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="11">
         <v>4</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="11" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="11">
         <v>8</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="11" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>540</v>
       </c>
       <c r="E6" t="s">
@@ -16564,278 +18326,278 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="11">
         <v>16</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="11">
         <v>32</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="11" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="11">
         <v>64</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="11" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="11">
         <v>128</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="11" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="11">
         <v>256</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="11" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="11">
         <v>512</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="11">
         <v>1024</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="11">
         <v>2048</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>593</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
     </row>
     <row r="34" s="5" customFormat="1" spans="1:2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -16843,7 +18605,7 @@
       </c>
     </row>
     <row r="35" s="5" customFormat="1" spans="1:2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -16851,7 +18613,7 @@
       </c>
     </row>
     <row r="36" s="5" customFormat="1" spans="1:2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -16859,10 +18621,10 @@
       </c>
     </row>
     <row r="37" s="5" customFormat="1" spans="1:2">
-      <c r="A37" s="7"/>
+      <c r="A37" s="8"/>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -16870,7 +18632,7 @@
       </c>
     </row>
     <row r="39" s="5" customFormat="1" spans="1:2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -16878,7 +18640,7 @@
       </c>
     </row>
     <row r="40" s="5" customFormat="1" spans="1:2">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -16886,7 +18648,7 @@
       </c>
     </row>
     <row r="41" s="5" customFormat="1" spans="1:2">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="7" t="s">
         <v>598</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -16894,7 +18656,7 @@
       </c>
     </row>
     <row r="42" s="5" customFormat="1" spans="1:2">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="8" t="s">
         <v>602</v>
       </c>
       <c r="B42" s="5" t="s">
@@ -16903,7 +18665,7 @@
     </row>
     <row r="43" s="5" customFormat="1"/>
     <row r="44" s="5" customFormat="1" spans="1:2">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -16911,7 +18673,7 @@
       </c>
     </row>
     <row r="45" s="5" customFormat="1" spans="1:2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -16919,7 +18681,7 @@
       </c>
     </row>
     <row r="46" s="5" customFormat="1" spans="1:2">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B46" s="5" t="s">
@@ -16927,7 +18689,7 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B48" s="5" t="s">
@@ -16935,11 +18697,11 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="6"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B50" s="5" t="s">
@@ -16950,14 +18712,14 @@
       <c r="G50" s="5"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="6"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B52" s="5" t="s">
@@ -16966,7 +18728,7 @@
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B53" s="5" t="s">
@@ -16975,7 +18737,7 @@
       <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B54" s="5" t="s">
@@ -16984,7 +18746,7 @@
       <c r="G54" s="5"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B56" s="5" t="s">
@@ -16992,7 +18754,7 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B57" s="5" t="s">
@@ -17002,7 +18764,7 @@
       <c r="F57" s="5"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B58" s="5" t="s">
@@ -17011,7 +18773,7 @@
       <c r="C58" s="5"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B60" s="5" t="s">
@@ -17019,7 +18781,7 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B61" s="5" t="s">
@@ -17027,7 +18789,7 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B62" s="5" t="s">
@@ -17035,7 +18797,7 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B64" s="5" t="s">
@@ -17043,7 +18805,7 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B65" s="5" t="s">
@@ -17051,7 +18813,7 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B66" s="5" t="s">
@@ -17060,7 +18822,7 @@
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B67" s="5" t="s">
@@ -17069,7 +18831,7 @@
       <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B68" s="5" t="s">
@@ -17078,7 +18840,7 @@
       <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B69" t="s">
@@ -17086,7 +18848,7 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="7" t="s">
         <v>602</v>
       </c>
       <c r="B70" t="s">
@@ -17098,7 +18860,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B72" s="5" t="s">
@@ -17106,7 +18868,7 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B73" s="5" t="s">
@@ -17114,7 +18876,7 @@
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="8" t="s">
         <v>598</v>
       </c>
       <c r="B74" s="5" t="s">
@@ -17123,7 +18885,7 @@
       <c r="C74" s="5"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="7" t="s">
         <v>594</v>
       </c>
       <c r="B76" t="s">
@@ -17131,7 +18893,7 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B77" t="s">
@@ -17139,7 +18901,7 @@
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="7"/>
+      <c r="A78" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17161,7 +18923,7 @@
     <col min="6" max="6" width="8.75" customWidth="1"/>
     <col min="7" max="7" width="19.1666666666667" customWidth="1"/>
     <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="9" width="20.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="16.75" customWidth="1"/>
     <col min="10" max="10" width="36.75" customWidth="1"/>
     <col min="11" max="11" width="25.1666666666667" customWidth="1"/>
     <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
@@ -17170,7 +18932,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -17214,7 +18976,7 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -17257,49 +19019,49 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="109" customHeight="1" spans="1:14">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:14">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="2" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="4" s="5" customFormat="1" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -17349,10 +19111,10 @@
       <c r="C5" t="s">
         <v>670</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>672</v>
       </c>
       <c r="F5">
@@ -17377,10 +19139,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>402002</v>
+        <v>201001</v>
       </c>
       <c r="N5">
-        <v>403002</v>
+        <v>301001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -17390,10 +19152,10 @@
       <c r="C6" t="s">
         <v>675</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>672</v>
       </c>
       <c r="F6">
@@ -17418,10 +19180,10 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>402003</v>
+        <v>201002</v>
       </c>
       <c r="N6">
-        <v>403003</v>
+        <v>301002</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -17431,10 +19193,10 @@
       <c r="C7" t="s">
         <v>677</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>672</v>
       </c>
       <c r="F7">
@@ -17475,7 +19237,7 @@
       <c r="D8" t="s">
         <v>679</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>680</v>
       </c>
       <c r="F8">
@@ -17513,10 +19275,10 @@
       <c r="C9" t="s">
         <v>682</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>672</v>
       </c>
       <c r="F9">
@@ -17541,20 +19303,20 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>402001</v>
+        <v>204001</v>
       </c>
       <c r="N9">
-        <v>403001</v>
+        <v>301001</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="E15" s="10"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="E16" s="10"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="10"/>
+      <c r="E17" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17584,7 +19346,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -17622,7 +19384,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -17659,47 +19421,47 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
@@ -17765,7 +19527,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>404001</v>
+        <v>700001</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -17803,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>404002</v>
+        <v>700002</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -17879,7 +19641,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>404004</v>
+        <v>700003</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -17917,7 +19679,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>404005</v>
+        <v>700004</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -17993,7 +19755,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>404007</v>
+        <v>700005</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -18031,7 +19793,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>404008</v>
+        <v>700006</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -18107,7 +19869,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>404010</v>
+        <v>700007</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -18145,7 +19907,7 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>404011</v>
+        <v>700008</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -18226,7 +19988,7 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>405001</v>
+        <v>701001</v>
       </c>
       <c r="K18">
         <v>360</v>
@@ -18254,7 +20016,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18298,24 +20060,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="2" t="s">
         <v>667</v>
       </c>
     </row>
@@ -18355,7 +20117,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="12">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -18376,7 +20138,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -18397,7 +20159,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -18415,10 +20177,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>900</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -18436,10 +20198,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>180</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -18460,7 +20222,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -18472,7 +20234,7 @@
       <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -18490,7 +20252,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18511,7 +20273,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="12">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -18535,7 +20297,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -18556,7 +20318,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -18577,7 +20339,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="12">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -18598,7 +20360,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="12">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -18610,7 +20372,7 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="12">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -18778,7 +20540,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="12">
         <f t="shared" ref="F28:F33" si="1">E28/10000</f>
         <v>0</v>
       </c>
@@ -18802,7 +20564,7 @@
       <c r="E29">
         <v>6700</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="12">
         <f t="shared" si="1"/>
         <v>0.67</v>
       </c>
@@ -18823,7 +20585,7 @@
       <c r="E30">
         <v>2200</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
@@ -18841,10 +20603,10 @@
       <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="14">
         <v>900</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="12">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -18862,10 +20624,10 @@
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <v>180</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="12">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -18886,7 +20648,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="12">
         <f t="shared" si="1"/>
         <v>0.002</v>
       </c>
@@ -18895,7 +20657,7 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="F34" s="11">
+      <c r="F34" s="12">
         <f>SUM(F28:F33)</f>
         <v>1</v>
       </c>
@@ -18988,35 +20750,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>745</v>
       </c>
     </row>
@@ -20064,13 +21826,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -20099,13 +21861,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -20133,28 +21895,28 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:12">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>764</v>
       </c>
     </row>
@@ -20223,10 +21985,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -20246,10 +22008,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -20269,10 +22031,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -20292,10 +22054,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>140</v>
       </c>
       <c r="E9" t="s">
@@ -20315,10 +22077,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -20338,10 +22100,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>507</v>
       </c>
       <c r="E11" t="s">
@@ -20361,10 +22123,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>563</v>
       </c>
       <c r="E12" t="s">
@@ -20398,10 +22160,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -20415,10 +22177,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
@@ -20432,10 +22194,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
@@ -20563,42 +22325,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="10"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="10"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20619,7 +22381,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -20633,13 +22395,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -20647,13 +22409,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>801</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4577,7 +4577,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4631,6 +4631,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="6" tint="0.6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1" tint="0.5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4834,25 +4841,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="15"/>
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="totalRow" dxfId="13"/>
-      <tableStyleElement type="firstColumn" dxfId="12"/>
-      <tableStyleElement type="lastColumn" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="25"/>
-      <tableStyleElement type="totalRow" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="21"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="20"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="19"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="18"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="17"/>
-      <tableStyleElement type="pageFieldValues" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstRowStripe" dxfId="24"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="23"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="22"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="21"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="20"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="19"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="18"/>
+      <tableStyleElement type="pageFieldValues" dxfId="17"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -14942,7 +14949,7 @@
         <v>965</v>
       </c>
       <c r="P19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -14992,7 +14999,7 @@
         <v>965</v>
       </c>
       <c r="P20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -17312,17 +17319,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I$1:I$1048576">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N$1:N$1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P$1:P$1048576">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="between" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",P1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Q$1:Q$1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17332,7 +17344,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{a6f8058b-4dba-4734-8a34-b85bc85182b6}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{17c95734-177e-44e8-a870-573cc7e0bf34}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -19641,7 +19653,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>700003</v>
+        <v>700004</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -19679,7 +19691,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>700004</v>
+        <v>700005</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -19755,7 +19767,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>700005</v>
+        <v>700007</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -19793,7 +19805,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>700006</v>
+        <v>700008</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -19869,7 +19881,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>700007</v>
+        <v>700010</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -19907,7 +19919,7 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>700008</v>
+        <v>700011</v>
       </c>
       <c r="K15">
         <v>0</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="1" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2780" uniqueCount="1195">
   <si>
     <t>##var</t>
   </si>
@@ -2270,7 +2270,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>盲盒招待券</t>
+    <t>新手盲盒招待券专用，后续招待券需新建ID</t>
   </si>
   <si>
     <t>UI\BlindBox\HintIcon_Common_Ticket.png</t>
@@ -2279,6 +2279,9 @@
     <t>BlindBoxId</t>
   </si>
   <si>
+    <t>VoucherUpgradeBlindBoxIds</t>
+  </si>
+  <si>
     <t>IsLoopTrack</t>
   </si>
   <si>
@@ -2303,9 +2306,15 @@
     <t>SteamDropMaxPerWindow</t>
   </si>
   <si>
+    <t>(list#sep=|),int</t>
+  </si>
+  <si>
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
+    <t>按优先级填写可使用票券升级为的 BlindBox.Id。展示本行盲盒时，客户端按列表顺序检查对应盲盒的开箱票券，首个票券充足的盲盒将替代本行配置的 BlindBoxId；均不可用时仍展示原盲盒。留空表示不允许升级。</t>
+  </si>
+  <si>
     <t>TRUE 表示正常阶段循环装扮券生产行</t>
   </si>
   <si>
@@ -2331,6 +2340,9 @@
   </si>
   <si>
     <t>前 12 条控制新手顺序；正常阶段只保留一条循环装扮券生产行</t>
+  </si>
+  <si>
+    <t>可升级票券盲盒列表</t>
   </si>
   <si>
     <t>是循环生效的</t>
@@ -3062,6 +3074,9 @@
   </si>
   <si>
     <t>DecorationBlindBoxVoucher</t>
+  </si>
+  <si>
+    <t>盲盒招待券</t>
   </si>
   <si>
     <t>Decoration Blind Box Voucher</t>
@@ -13355,55 +13370,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="F1" t="s">
         <v>640</v>
       </c>
       <c r="G1" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="H1" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I1" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="J1" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="K1" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="L1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="M1" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="N1" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O1" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="P1" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="Q1" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="R1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="S1" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -13441,10 +13456,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="M2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -13470,58 +13485,58 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -13529,58 +13544,58 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C4" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D4" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E4" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="F4" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="G4" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="H4" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="I4" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="J4" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="K4" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="L4" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="M4" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="N4" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="O4" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="P4" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="Q4" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="R4" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="S4" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -13588,7 +13603,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -13600,25 +13615,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="H5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I5" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="K5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="L5" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="M5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -13638,7 +13653,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -13650,25 +13665,25 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="H6" t="s">
+        <v>870</v>
+      </c>
+      <c r="I6" t="s">
+        <v>863</v>
+      </c>
+      <c r="J6" t="s">
+        <v>871</v>
+      </c>
+      <c r="K6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L6" t="s">
         <v>866</v>
       </c>
-      <c r="I6" t="s">
-        <v>859</v>
-      </c>
-      <c r="J6" t="s">
-        <v>867</v>
-      </c>
-      <c r="K6" t="s">
-        <v>867</v>
-      </c>
-      <c r="L6" t="s">
-        <v>862</v>
-      </c>
       <c r="M6" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13688,7 +13703,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -13700,25 +13715,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H7" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="I7" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J7" t="s">
+        <v>876</v>
+      </c>
+      <c r="K7" t="s">
+        <v>877</v>
+      </c>
+      <c r="L7" t="s">
+        <v>866</v>
+      </c>
+      <c r="M7" t="s">
         <v>872</v>
-      </c>
-      <c r="K7" t="s">
-        <v>873</v>
-      </c>
-      <c r="L7" t="s">
-        <v>862</v>
-      </c>
-      <c r="M7" t="s">
-        <v>868</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -13738,7 +13753,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -13750,25 +13765,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="H8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="I8" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J8" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="K8" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="L8" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="M8" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -13788,7 +13803,7 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -13800,25 +13815,25 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="H9" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I9" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J9" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="K9" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="L9" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="M9" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="N9">
         <v>92005</v>
@@ -13841,7 +13856,7 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -13853,25 +13868,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="H10" t="s">
+        <v>870</v>
+      </c>
+      <c r="I10" t="s">
+        <v>863</v>
+      </c>
+      <c r="J10" t="s">
+        <v>871</v>
+      </c>
+      <c r="K10" t="s">
+        <v>871</v>
+      </c>
+      <c r="L10" t="s">
         <v>866</v>
       </c>
-      <c r="I10" t="s">
-        <v>859</v>
-      </c>
-      <c r="J10" t="s">
-        <v>867</v>
-      </c>
-      <c r="K10" t="s">
-        <v>867</v>
-      </c>
-      <c r="L10" t="s">
-        <v>862</v>
-      </c>
       <c r="M10" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -13894,7 +13909,7 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -13906,25 +13921,25 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H11" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="I11" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J11" t="s">
+        <v>876</v>
+      </c>
+      <c r="K11" t="s">
+        <v>877</v>
+      </c>
+      <c r="L11" t="s">
+        <v>866</v>
+      </c>
+      <c r="M11" t="s">
         <v>872</v>
-      </c>
-      <c r="K11" t="s">
-        <v>873</v>
-      </c>
-      <c r="L11" t="s">
-        <v>862</v>
-      </c>
-      <c r="M11" t="s">
-        <v>868</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -13947,7 +13962,7 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -13959,25 +13974,25 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="H12" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="I12" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J12" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="K12" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="L12" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="M12" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="N12">
         <v>91012</v>
@@ -14034,49 +14049,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="E1" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="H1" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I1" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="J1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="K1" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="L1" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="M1" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="N1" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="O1" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="P1" t="s">
         <v>640</v>
       </c>
       <c r="Q1" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="R1" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -14137,52 +14152,52 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -14190,55 +14205,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C4" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D4" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="E4" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="F4" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I4" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="L4" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="M4" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="P4" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="Q4" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="R4" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -14249,22 +14264,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D5" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="G5" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="H5" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -14305,22 +14320,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="D6" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="G6" t="s">
+        <v>929</v>
+      </c>
+      <c r="H6" t="s">
         <v>925</v>
-      </c>
-      <c r="H6" t="s">
-        <v>921</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -14361,22 +14376,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D7" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G7" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="H7" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -14417,22 +14432,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="D8" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="G8" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H8" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -14473,22 +14488,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D9" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="E9" t="s">
         <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="G9" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="H9" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -14529,22 +14544,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D10" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="G10" t="s">
+        <v>929</v>
+      </c>
+      <c r="H10" t="s">
         <v>925</v>
-      </c>
-      <c r="H10" t="s">
-        <v>921</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -14585,22 +14600,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="D11" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="E11" t="s">
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G11" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="H11" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -14641,22 +14656,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D12" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E12" t="s">
         <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="G12" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H12" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -14694,7 +14709,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -14705,19 +14720,19 @@
         <v>402001</v>
       </c>
       <c r="C14" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D14" t="s">
-        <v>682</v>
+        <v>948</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="G14" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -14755,19 +14770,19 @@
         <v>402002</v>
       </c>
       <c r="C15" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="D15" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E15" t="s">
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="G15" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -14802,19 +14817,19 @@
         <v>402003</v>
       </c>
       <c r="C16" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D16" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E16" t="s">
         <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="G16" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -14849,7 +14864,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -14860,19 +14875,19 @@
         <v>403001</v>
       </c>
       <c r="C18" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="D18" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="E18" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="F18" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="G18" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="H18" t="s">
         <v>161</v>
@@ -14896,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -14913,19 +14928,19 @@
         <v>403002</v>
       </c>
       <c r="C19" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="D19" t="s">
+        <v>967</v>
+      </c>
+      <c r="E19" t="s">
         <v>962</v>
       </c>
-      <c r="E19" t="s">
-        <v>957</v>
-      </c>
       <c r="F19" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="G19" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -14946,7 +14961,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -14963,19 +14978,19 @@
         <v>403003</v>
       </c>
       <c r="C20" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="D20" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="E20" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="F20" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="G20" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -14996,7 +15011,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -15013,7 +15028,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -15021,19 +15036,19 @@
         <v>404001</v>
       </c>
       <c r="C22" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="D22" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="E22" t="s">
         <v>621</v>
       </c>
       <c r="F22" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="G22" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -15054,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -15071,19 +15086,19 @@
         <v>404002</v>
       </c>
       <c r="C23" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="D23" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="E23" t="s">
         <v>621</v>
       </c>
       <c r="F23" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="G23" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -15104,7 +15119,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -15121,19 +15136,19 @@
         <v>404004</v>
       </c>
       <c r="C24" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="D24" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="E24" t="s">
         <v>621</v>
       </c>
       <c r="F24" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="G24" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -15154,7 +15169,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -15171,19 +15186,19 @@
         <v>404005</v>
       </c>
       <c r="C25" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D25" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E25" t="s">
         <v>621</v>
       </c>
       <c r="F25" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="G25" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -15204,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -15221,19 +15236,19 @@
         <v>404007</v>
       </c>
       <c r="C26" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="D26" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="E26" t="s">
         <v>621</v>
       </c>
       <c r="F26" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="G26" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -15254,7 +15269,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -15271,19 +15286,19 @@
         <v>404008</v>
       </c>
       <c r="C27" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="D27" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="E27" t="s">
         <v>621</v>
       </c>
       <c r="F27" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G27" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -15304,7 +15319,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -15321,19 +15336,19 @@
         <v>404010</v>
       </c>
       <c r="C28" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="D28" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="E28" t="s">
         <v>621</v>
       </c>
       <c r="F28" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="G28" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -15354,7 +15369,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -15371,19 +15386,19 @@
         <v>404011</v>
       </c>
       <c r="C29" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="D29" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="E29" t="s">
         <v>621</v>
       </c>
       <c r="F29" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="G29" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -15404,7 +15419,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -15421,19 +15436,19 @@
         <v>404013</v>
       </c>
       <c r="C30" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D30" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="E30" t="s">
         <v>621</v>
       </c>
       <c r="F30" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="G30" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -15454,7 +15469,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -15471,7 +15486,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -15479,19 +15494,19 @@
         <v>405001</v>
       </c>
       <c r="C32" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="D32" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="E32" t="s">
         <v>621</v>
       </c>
       <c r="F32" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="G32" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -15512,7 +15527,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -15529,7 +15544,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -15537,22 +15552,22 @@
         <v>406005</v>
       </c>
       <c r="C34" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="D34" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="E34" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F34" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="G34" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="H34" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -15573,7 +15588,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -15590,22 +15605,22 @@
         <v>406006</v>
       </c>
       <c r="C35" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D35" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="E35" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F35" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="G35" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="H35" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -15626,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -15643,22 +15658,22 @@
         <v>406007</v>
       </c>
       <c r="C36" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="D36" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="E36" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F36" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="G36" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="H36" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -15679,7 +15694,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -15696,22 +15711,22 @@
         <v>406008</v>
       </c>
       <c r="C37" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D37" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="E37" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F37" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="G37" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="H37" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -15732,7 +15747,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -15754,7 +15769,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="C39" t="s">
         <v>161</v>
@@ -15813,19 +15828,19 @@
         <v>201001</v>
       </c>
       <c r="C40" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="D40" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="G40" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="H40" t="s">
         <v>161</v>
@@ -15869,19 +15884,19 @@
         <v>201002</v>
       </c>
       <c r="C41" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="D41" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="G41" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="H41" t="s">
         <v>161</v>
@@ -15925,19 +15940,19 @@
         <v>204001</v>
       </c>
       <c r="C42" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="D42" t="s">
-        <v>682</v>
+        <v>948</v>
       </c>
       <c r="E42" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="G42" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="H42" t="s">
         <v>161</v>
@@ -15978,7 +15993,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
@@ -16037,19 +16052,19 @@
         <v>301001</v>
       </c>
       <c r="C44" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="D44" t="s">
+        <v>967</v>
+      </c>
+      <c r="E44" t="s">
         <v>962</v>
       </c>
-      <c r="E44" t="s">
-        <v>957</v>
-      </c>
       <c r="F44" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="G44" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="H44" t="s">
         <v>161</v>
@@ -16073,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -16093,19 +16108,19 @@
         <v>301002</v>
       </c>
       <c r="C45" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="D45" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="E45" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="F45" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="G45" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="H45" t="s">
         <v>161</v>
@@ -16129,7 +16144,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -16146,7 +16161,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="C46" t="s">
         <v>161</v>
@@ -16205,22 +16220,22 @@
         <v>501001</v>
       </c>
       <c r="C47" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="D47" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="E47" t="s">
         <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="G47" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="H47" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -16261,22 +16276,22 @@
         <v>501002</v>
       </c>
       <c r="C48" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D48" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="E48" t="s">
         <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="G48" t="s">
+        <v>929</v>
+      </c>
+      <c r="H48" t="s">
         <v>925</v>
-      </c>
-      <c r="H48" t="s">
-        <v>921</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -16317,22 +16332,22 @@
         <v>501003</v>
       </c>
       <c r="C49" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="D49" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="E49" t="s">
         <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G49" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="H49" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -16373,22 +16388,22 @@
         <v>501004</v>
       </c>
       <c r="C50" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D50" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="E50" t="s">
         <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="G50" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H50" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -16426,7 +16441,7 @@
         <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C51" t="s">
         <v>161</v>
@@ -16485,22 +16500,22 @@
         <v>601001</v>
       </c>
       <c r="C52" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="D52" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="E52" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F52" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="G52" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="H52" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -16521,7 +16536,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -16541,22 +16556,22 @@
         <v>601002</v>
       </c>
       <c r="C53" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="D53" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="E53" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F53" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="G53" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="H53" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -16577,7 +16592,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -16597,22 +16612,22 @@
         <v>601003</v>
       </c>
       <c r="C54" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="D54" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="E54" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F54" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="G54" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="H54" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -16633,7 +16648,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -16653,22 +16668,22 @@
         <v>601004</v>
       </c>
       <c r="C55" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D55" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="E55" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F55" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="G55" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="H55" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -16689,7 +16704,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -16706,7 +16721,7 @@
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C56" t="s">
         <v>161</v>
@@ -16765,19 +16780,19 @@
         <v>700001</v>
       </c>
       <c r="C57" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D57" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="E57" t="s">
         <v>621</v>
       </c>
       <c r="F57" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="G57" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="H57" t="s">
         <v>161</v>
@@ -16801,7 +16816,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -16821,19 +16836,19 @@
         <v>700002</v>
       </c>
       <c r="C58" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="D58" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E58" t="s">
         <v>621</v>
       </c>
       <c r="F58" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="G58" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="H58" t="s">
         <v>161</v>
@@ -16857,7 +16872,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -16877,19 +16892,19 @@
         <v>700004</v>
       </c>
       <c r="C59" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="D59" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="E59" t="s">
         <v>621</v>
       </c>
       <c r="F59" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="G59" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="H59" t="s">
         <v>161</v>
@@ -16913,7 +16928,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -16933,19 +16948,19 @@
         <v>700005</v>
       </c>
       <c r="C60" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="D60" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E60" t="s">
         <v>621</v>
       </c>
       <c r="F60" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="G60" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="H60" t="s">
         <v>161</v>
@@ -16969,7 +16984,7 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -16989,19 +17004,19 @@
         <v>700007</v>
       </c>
       <c r="C61" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="D61" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="E61" t="s">
         <v>621</v>
       </c>
       <c r="F61" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="G61" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="H61" t="s">
         <v>161</v>
@@ -17025,7 +17040,7 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -17045,19 +17060,19 @@
         <v>700008</v>
       </c>
       <c r="C62" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="D62" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="E62" t="s">
         <v>621</v>
       </c>
       <c r="F62" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="G62" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="H62" t="s">
         <v>161</v>
@@ -17081,7 +17096,7 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -17101,19 +17116,19 @@
         <v>700010</v>
       </c>
       <c r="C63" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="D63" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="E63" t="s">
         <v>621</v>
       </c>
       <c r="F63" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="G63" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="H63" t="s">
         <v>161</v>
@@ -17137,7 +17152,7 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -17157,19 +17172,19 @@
         <v>700011</v>
       </c>
       <c r="C64" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="D64" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E64" t="s">
         <v>621</v>
       </c>
       <c r="F64" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="G64" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="H64" t="s">
         <v>161</v>
@@ -17193,7 +17208,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -17210,7 +17225,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="C65" t="s">
         <v>161</v>
@@ -17269,19 +17284,19 @@
         <v>701001</v>
       </c>
       <c r="C66" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="D66" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="E66" t="s">
         <v>621</v>
       </c>
       <c r="F66" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="G66" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="H66" t="s">
         <v>161</v>
@@ -17305,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -17344,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{17c95734-177e-44e8-a870-573cc7e0bf34}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{dfb75271-c949-4268-89da-6f5f4d702f58}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -17383,19 +17398,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="D1" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="G1" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -17452,13 +17467,13 @@
         <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>596</v>
@@ -17481,13 +17496,13 @@
         <v>199999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -17504,13 +17519,13 @@
         <v>299999</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="G6" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
@@ -17527,13 +17542,13 @@
         <v>229999</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" ht="34.8" spans="1:7">
@@ -17550,13 +17565,13 @@
         <v>299999</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="G8" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="9" ht="69.6" spans="1:7">
@@ -17573,13 +17588,13 @@
         <v>399999</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="G9" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="10" ht="34.8" spans="1:7">
@@ -17596,13 +17611,13 @@
         <v>301999</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="G10" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="11" ht="34.8" spans="1:7">
@@ -17619,13 +17634,13 @@
         <v>302999</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="G11" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="12" ht="34.8" spans="1:7">
@@ -17642,13 +17657,13 @@
         <v>399999</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="G12" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="13" ht="87" spans="1:7">
@@ -17665,13 +17680,13 @@
         <v>499999</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="G13" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="14" ht="52.2" spans="1:7">
@@ -17688,13 +17703,13 @@
         <v>409999</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="G14" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="15" ht="52.2" spans="1:7">
@@ -17711,13 +17726,13 @@
         <v>499999</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="G15" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="16" ht="52.2" spans="1:7">
@@ -17734,13 +17749,13 @@
         <v>599999</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="G16" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="17" ht="34.8" spans="1:7">
@@ -17757,13 +17772,13 @@
         <v>501999</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="G17" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="18" ht="34.8" spans="1:7">
@@ -17780,13 +17795,13 @@
         <v>502999</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="G18" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="19" ht="34.8" spans="1:7">
@@ -17803,13 +17818,13 @@
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="G19" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="20" ht="87" spans="1:7">
@@ -17826,13 +17841,13 @@
         <v>699999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="G20" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -17849,13 +17864,13 @@
         <v>601999</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="G21" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -17872,13 +17887,13 @@
         <v>602999</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="G22" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="23" ht="34.8" spans="1:7">
@@ -17895,13 +17910,13 @@
         <v>603999</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="G23" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="24" ht="34.8" spans="1:7">
@@ -17918,13 +17933,13 @@
         <v>699999</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="G24" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -17941,13 +17956,13 @@
         <v>799999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="G25" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="26" ht="52.2" spans="1:7">
@@ -17964,13 +17979,13 @@
         <v>709999</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="G26" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -17987,13 +18002,13 @@
         <v>700999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="G27" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -18010,13 +18025,13 @@
         <v>701999</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="G28" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="29" ht="34.8" spans="1:7">
@@ -18033,13 +18048,13 @@
         <v>709999</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="G29" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="30" ht="34.8" spans="1:7">
@@ -18056,13 +18071,13 @@
         <v>799999</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="G30" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="31" ht="34.8" spans="1:7">
@@ -18079,10 +18094,10 @@
         <v>999999</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G31" t="s">
         <v>629</v>
@@ -18102,13 +18117,13 @@
         <v>99999</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="G32" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="33" spans="5:5">
@@ -18929,7 +18944,7 @@
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="35.25" customWidth="1"/>
     <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
     <col min="5" max="5" width="22.8333333333333" customWidth="1"/>
     <col min="6" max="6" width="8.75" customWidth="1"/>
@@ -19339,25 +19354,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
-    <col min="3" max="4" width="10.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.4166666666667" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="14.25" customWidth="1"/>
-    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="18.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="30.8333333333333" customWidth="1"/>
-    <col min="14" max="14" width="45.25" customWidth="1"/>
+    <col min="3" max="3" width="10.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="18.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
+    <col min="10" max="10" width="13.1666666666667" customWidth="1"/>
+    <col min="11" max="11" width="10.25" customWidth="1"/>
+    <col min="12" max="12" width="18.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="30.8333333333333" customWidth="1"/>
+    <col min="15" max="15" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -19383,10 +19400,10 @@
         <v>689</v>
       </c>
       <c r="I1" t="s">
+        <v>690</v>
+      </c>
+      <c r="J1" t="s">
         <v>640</v>
-      </c>
-      <c r="J1" t="s">
-        <v>690</v>
       </c>
       <c r="K1" t="s">
         <v>691</v>
@@ -19394,8 +19411,11 @@
       <c r="L1" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="M1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
@@ -19406,10 +19426,10 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E2" t="s">
         <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
@@ -19421,10 +19441,10 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
         <v>35</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
@@ -19432,47 +19452,53 @@
       <c r="L2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:14">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>699</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>704</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
@@ -19483,48 +19509,48 @@
         <v>658</v>
       </c>
       <c r="D4" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E4" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F4" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="G4" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H4" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="I4" t="s">
+        <v>711</v>
+      </c>
+      <c r="J4" t="s">
         <v>667</v>
       </c>
-      <c r="J4" t="s">
-        <v>708</v>
-      </c>
       <c r="K4" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="M4" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>714</v>
+      </c>
+      <c r="N4" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
         <v>4001</v>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
+      <c r="E5" t="b">
+        <v>0</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -19533,89 +19559,92 @@
         <v>30</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>700001</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>1002</v>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>90</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>60</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>90</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6">
         <v>700002</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="M6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>2001</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>4001</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>150</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>60</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>150</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -19623,113 +19652,116 @@
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="M7" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>1001</v>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8">
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>210</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>60</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>210</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8">
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8">
         <v>700004</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>1002</v>
       </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>270</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>60</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>270</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <v>700005</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
       <c r="L9">
         <v>0</v>
       </c>
-      <c r="M9" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>2001</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
+        <v>4001</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>330</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>60</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>330</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -19737,113 +19769,116 @@
       <c r="L10">
         <v>0</v>
       </c>
-      <c r="M10" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1001</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11">
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>390</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>60</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>390</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11">
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11">
         <v>700007</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>1002</v>
       </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12">
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>450</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>60</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>450</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12">
         <v>700008</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
       <c r="L12">
         <v>0</v>
       </c>
-      <c r="M12" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>2001</v>
       </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13">
+      <c r="D13">
+        <v>4001</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>510</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>60</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>510</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -19851,113 +19886,116 @@
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14">
         <v>1001</v>
       </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14">
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>570</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>60</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>570</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14">
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14">
         <v>700010</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
       <c r="L14">
         <v>0</v>
       </c>
-      <c r="M14" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15">
         <v>1002</v>
       </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15">
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>630</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>60</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>630</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15">
         <v>700011</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
       <c r="L15">
         <v>0</v>
       </c>
-      <c r="M15" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16">
         <v>2001</v>
       </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
+        <v>4001</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>690</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>60</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>690</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -19965,51 +20003,54 @@
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18">
         <v>1001</v>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18">
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18">
         <v>780</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>180</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
       </c>
       <c r="H18">
         <v>-1</v>
       </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18">
+      <c r="I18">
+        <v>-1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18">
         <v>701001</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>360</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>2</v>
       </c>
-      <c r="M18" t="s">
-        <v>724</v>
+      <c r="N18" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -20043,10 +20084,10 @@
         <v>684</v>
       </c>
       <c r="D1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G1" t="s">
         <v>640</v>
@@ -20077,16 +20118,16 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="2" t="s">
@@ -20107,13 +20148,13 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G4" t="s">
         <v>667</v>
       </c>
       <c r="H4" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -20293,7 +20334,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -20531,7 +20572,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -20560,7 +20601,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -20706,28 +20747,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="I1" t="s">
         <v>640</v>
       </c>
       <c r="J1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -20770,28 +20811,28 @@
         <v>161</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>667</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -20802,31 +20843,31 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D4" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="F4" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="G4" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="H4" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="I4" t="s">
         <v>667</v>
       </c>
       <c r="J4" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="K4" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -21242,7 +21283,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -21277,7 +21318,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -21376,7 +21417,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -21411,7 +21452,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -21574,7 +21615,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -21609,7 +21650,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -21644,7 +21685,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -21851,25 +21892,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="F1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="H1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="K1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="L1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -21913,23 +21954,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -21946,28 +21987,28 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="G4" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="H4" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="I4" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J4" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="K4" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="L4" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -21981,16 +22022,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="F5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="K5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -22004,16 +22045,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="F6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H6" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K6" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -22027,16 +22068,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F7" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H7" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="K7" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -22050,16 +22091,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="F8" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H8" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="K8" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -22073,16 +22114,16 @@
         <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="F9" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H9" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="K9" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -22096,16 +22137,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F10" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H10" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="K10" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -22119,16 +22160,16 @@
         <v>507</v>
       </c>
       <c r="E11" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F11" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H11" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J11" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -22142,16 +22183,16 @@
         <v>563</v>
       </c>
       <c r="E12" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F12" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H12" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J12" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -22179,10 +22220,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -22199,7 +22240,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -22216,10 +22257,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -22241,7 +22282,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -22255,7 +22296,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -22269,7 +22310,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -22293,7 +22334,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -22400,10 +22441,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -22428,10 +22469,10 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17359,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{dfb75271-c949-4268-89da-6f5f4d702f58}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{790218c5-6fe7-4efd-b57d-d8e61d2defee}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -20021,6 +20021,9 @@
       </c>
       <c r="C18">
         <v>1001</v>
+      </c>
+      <c r="D18">
+        <v>4001</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17359,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{790218c5-6fe7-4efd-b57d-d8e61d2defee}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{dc4d9282-0273-4831-a7f7-04c18381e143}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -17359,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{dc4d9282-0273-4831-a7f7-04c18381e143}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{588c4c17-dcd4-4a55-b2e8-516931d6d82f}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17359,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{588c4c17-dcd4-4a55-b2e8-516931d6d82f}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{aec0b8aa-6a85-464d-a048-659c0f191b38}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17359,7 +17359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{aec0b8aa-6a85-464d-a048-659c0f191b38}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0e754b0f-c854-4e58-9394-75f0f32f6700}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="4" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
     <sheet name="SteamItemDef" sheetId="18" r:id="rId11"/>
     <sheet name="SteamItemDefIdRange" sheetId="19" r:id="rId12"/>
+    <sheet name="RefreshmentConfig" sheetId="20" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2780" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1222">
   <si>
     <t>##var</t>
   </si>
@@ -3815,6 +3816,87 @@
   </si>
   <si>
     <t>不分配正式或测试定义</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>DurationHands</t>
+  </si>
+  <si>
+    <t>LuckyDealMode</t>
+  </si>
+  <si>
+    <t>LuckyDealTriggerChance</t>
+  </si>
+  <si>
+    <t>InteractionHintSfxCue</t>
+  </si>
+  <si>
+    <t>UseSfxCue</t>
+  </si>
+  <si>
+    <t>BalloonOffsetY</t>
+  </si>
+  <si>
+    <t>int#ref=TbItem</t>
+  </si>
+  <si>
+    <t>ELuckyDealMode</t>
+  </si>
+  <si>
+    <t>关联 `Item.Id` 的唯一配置。仅允许填写 `ItemType = Refreshment` 的物品；</t>
+  </si>
+  <si>
+    <t>使用成功后获得的 BUFF 持续牌局数。每次成功下注并开始新局时消耗 1 局；建议填写 1-99。</t>
+  </si>
+  <si>
+    <t>决定幸运发牌的具体规则。第一版只支持 `GuidedDraw`；其他枚举为后续预留，暂勿配置。</t>
+  </si>
+  <si>
+    <t>BUFF 生效期间，每局开始时触发幸运发牌的概率。填写 0-1 小数，例如 `0.75` 表示 75%；未触发也会消耗该局。</t>
+  </si>
+  <si>
+    <t>点击桌面 Refreshment 时，播放交互提示动画所用的 AudioManager 逻辑 Cue。填空则静音；不要填写文件扩展名或资源路径。</t>
+  </si>
+  <si>
+    <t>玩家确认使用 Refreshment 并激活 BUFF 时播放的 AudioManager 逻辑 Cue。可按饮品/食物/器具分别配置；填空则静音。</t>
+  </si>
+  <si>
+    <t>在 PSD 导出定位的基础上，对 UseBalloon 和 StatusBalloon 同时追加的 Y 轴像素偏移。正数向下、负数向上；例如热气使气球偏高时填写正数。</t>
+  </si>
+  <si>
+    <t>关联物品 ID</t>
+  </si>
+  <si>
+    <t>持续局数</t>
+  </si>
+  <si>
+    <t>幸运发牌模式</t>
+  </si>
+  <si>
+    <t>Look校验品质</t>
+  </si>
+  <si>
+    <t>幸运触发概率</t>
+  </si>
+  <si>
+    <t>交互提示音效</t>
+  </si>
+  <si>
+    <t>使用音效</t>
+  </si>
+  <si>
+    <t>气球高度微调</t>
+  </si>
+  <si>
+    <t>GuidedDraw</t>
+  </si>
+  <si>
+    <t>Refreshment_Hint</t>
+  </si>
+  <si>
+    <t>Refreshment_BuffStart</t>
   </si>
 </sst>
 </file>
@@ -4475,10 +4557,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5357,7 +5439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:35">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:35">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -5366,71 +5448,71 @@
       <c r="D3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L3" s="21"/>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="S3" s="9"/>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
       <c r="W3" s="9"/>
-      <c r="X3" s="2" t="s">
+      <c r="X3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -13480,62 +13562,62 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="77" customHeight="1" spans="1:19">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:19">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="1" t="s">
         <v>841</v>
       </c>
     </row>
@@ -14147,56 +14229,56 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="72" customHeight="1" spans="1:18">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:18">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>896</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>897</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>898</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>908</v>
       </c>
     </row>
@@ -17359,7 +17441,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0e754b0f-c854-4e58-9394-75f0f32f6700}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{f89870a8-043b-4c6b-b4fa-20da56ae4c55}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -17385,8 +17467,8 @@
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17403,10 +17485,10 @@
       <c r="D1" t="s">
         <v>1107</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>1108</v>
       </c>
       <c r="G1" t="s">
@@ -17426,10 +17508,10 @@
       <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
@@ -17437,22 +17519,22 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G3" t="s">
@@ -17495,10 +17577,10 @@
       <c r="D5">
         <v>199999</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -17518,10 +17600,10 @@
       <c r="D6">
         <v>299999</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>1116</v>
       </c>
       <c r="G6" t="s">
@@ -17541,10 +17623,10 @@
       <c r="D7">
         <v>229999</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>1119</v>
       </c>
       <c r="G7" s="5" t="s">
@@ -17564,10 +17646,10 @@
       <c r="D8">
         <v>299999</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>1122</v>
       </c>
       <c r="G8" t="s">
@@ -17587,10 +17669,10 @@
       <c r="D9">
         <v>399999</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>1125</v>
       </c>
       <c r="G9" t="s">
@@ -17610,10 +17692,10 @@
       <c r="D10">
         <v>301999</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>1128</v>
       </c>
       <c r="G10" t="s">
@@ -17633,10 +17715,10 @@
       <c r="D11">
         <v>302999</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>1131</v>
       </c>
       <c r="G11" t="s">
@@ -17656,10 +17738,10 @@
       <c r="D12">
         <v>399999</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>1134</v>
       </c>
       <c r="G12" t="s">
@@ -17679,10 +17761,10 @@
       <c r="D13">
         <v>499999</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>1137</v>
       </c>
       <c r="G13" t="s">
@@ -17702,10 +17784,10 @@
       <c r="D14">
         <v>409999</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>1140</v>
       </c>
       <c r="G14" t="s">
@@ -17728,7 +17810,7 @@
       <c r="E15" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>1143</v>
       </c>
       <c r="G15" t="s">
@@ -17751,7 +17833,7 @@
       <c r="E16" s="6" t="s">
         <v>1145</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="G16" t="s">
@@ -17774,7 +17856,7 @@
       <c r="E17" s="6" t="s">
         <v>1148</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>1149</v>
       </c>
       <c r="G17" t="s">
@@ -17794,10 +17876,10 @@
       <c r="D18">
         <v>502999</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>1152</v>
       </c>
       <c r="G18" t="s">
@@ -17820,7 +17902,7 @@
       <c r="E19" s="6" t="s">
         <v>1154</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>1155</v>
       </c>
       <c r="G19" t="s">
@@ -17843,7 +17925,7 @@
       <c r="E20" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="G20" t="s">
@@ -17866,7 +17948,7 @@
       <c r="E21" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="G21" t="s">
@@ -17889,7 +17971,7 @@
       <c r="E22" s="6" t="s">
         <v>1163</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>1164</v>
       </c>
       <c r="G22" t="s">
@@ -17912,7 +17994,7 @@
       <c r="E23" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="G23" t="s">
@@ -17935,7 +18017,7 @@
       <c r="E24" s="6" t="s">
         <v>1169</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>1170</v>
       </c>
       <c r="G24" t="s">
@@ -17958,7 +18040,7 @@
       <c r="E25" s="6" t="s">
         <v>1172</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>1173</v>
       </c>
       <c r="G25" t="s">
@@ -17978,10 +18060,10 @@
       <c r="D26">
         <v>709999</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="G26" t="s">
@@ -18004,7 +18086,7 @@
       <c r="E27" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>1179</v>
       </c>
       <c r="G27" t="s">
@@ -18027,7 +18109,7 @@
       <c r="E28" s="6" t="s">
         <v>1181</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>1182</v>
       </c>
       <c r="G28" t="s">
@@ -18050,7 +18132,7 @@
       <c r="E29" s="6" t="s">
         <v>1184</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>1185</v>
       </c>
       <c r="G29" t="s">
@@ -18070,10 +18152,10 @@
       <c r="D30">
         <v>799999</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>1188</v>
       </c>
       <c r="G30" t="s">
@@ -18096,7 +18178,7 @@
       <c r="E31" s="6" t="s">
         <v>1190</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>1191</v>
       </c>
       <c r="G31" t="s">
@@ -18119,7 +18201,7 @@
       <c r="E32" s="6" t="s">
         <v>1192</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>1193</v>
       </c>
       <c r="G32" t="s">
@@ -18164,6 +18246,481 @@
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="17.9166666666667" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="12.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="20.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="20.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="19.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F2" t="s">
+        <v>646</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6">
+        <v>9001</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E6" t="str">
+        <f>LOOKUP(B6,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F6">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <f>LOOKUP(B6,Item!B:B,Item!D:D)</f>
+        <v>红茶</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7">
+        <v>9002</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E7" t="str">
+        <f>LOOKUP(B7,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <f>LOOKUP(B7,Item!B:B,Item!D:D)</f>
+        <v>波尔多</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8">
+        <v>9003</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E8" t="str">
+        <f>LOOKUP(B8,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F8">
+        <v>0.8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="str">
+        <f>LOOKUP(B8,Item!B:B,Item!D:D)</f>
+        <v>勃艮第</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9">
+        <v>9004</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E9" t="str">
+        <f>LOOKUP(B9,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F9">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <f>LOOKUP(B9,Item!B:B,Item!D:D)</f>
+        <v>霞多丽</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10">
+        <v>9005</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E10" t="str">
+        <f>LOOKUP(B10,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F10">
+        <v>0.8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <f>LOOKUP(B10,Item!B:B,Item!D:D)</f>
+        <v>子弹杯</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11">
+        <v>9006</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E11" t="str">
+        <f>LOOKUP(B11,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <f>LOOKUP(B11,Item!B:B,Item!D:D)</f>
+        <v>郁金香杯</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12">
+        <v>9007</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E12" t="str">
+        <f>LOOKUP(B12,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F12">
+        <v>0.8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="str">
+        <f>LOOKUP(B12,Item!B:B,Item!D:D)</f>
+        <v>平底杯</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13">
+        <v>9008</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E13" t="str">
+        <f>LOOKUP(B13,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F13">
+        <v>0.9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <f>LOOKUP(B13,Item!B:B,Item!D:D)</f>
+        <v>年份酒</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14">
+        <v>9009</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E14" t="str">
+        <f>LOOKUP(B14,Item!B:B,Item!H:H)</f>
+        <v>优秀</v>
+      </c>
+      <c r="F14">
+        <v>0.7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="str">
+        <f>LOOKUP(B14,Item!B:B,Item!D:D)</f>
+        <v>凉白开</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15">
+        <v>9010</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E15" t="str">
+        <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F15">
+        <v>0.9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="str">
+        <f>LOOKUP(B15,Item!B:B,Item!D:D)</f>
+        <v>威士忌</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16">
+        <v>9011</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E16" t="str">
+        <f>LOOKUP(B16,Item!B:B,Item!H:H)</f>
+        <v>传说</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I16">
+        <v>30</v>
+      </c>
+      <c r="J16" t="str">
+        <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>
+        <v>威士忌雪茄</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19046,44 +19603,44 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:14">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:14">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>657</v>
       </c>
     </row>
@@ -19456,45 +20013,45 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:14">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:14">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>705</v>
       </c>
     </row>
@@ -20116,24 +20673,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>733</v>
       </c>
       <c r="F3" s="13"/>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>667</v>
       </c>
     </row>
@@ -20806,35 +21363,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>749</v>
       </c>
     </row>
@@ -21951,7 +22508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -21959,20 +22516,20 @@
       <c r="C3" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>768</v>
       </c>
     </row>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="4" activeTab="12"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="3" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17441,7 +17441,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{f89870a8-043b-4c6b-b4fa-20da56ae4c55}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0b57cc69-9c91-4dc2-a510-e937c2d4e167}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -18386,7 +18386,7 @@
         <v>9001</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>1219</v>
@@ -18417,7 +18417,7 @@
         <v>9002</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>1219</v>
@@ -18448,7 +18448,7 @@
         <v>9003</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>1219</v>
@@ -18479,7 +18479,7 @@
         <v>9004</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>1219</v>
@@ -18510,7 +18510,7 @@
         <v>9005</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
         <v>1219</v>
@@ -18541,7 +18541,7 @@
         <v>9006</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>1219</v>
@@ -18572,7 +18572,7 @@
         <v>9007</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
         <v>1219</v>
@@ -18603,7 +18603,7 @@
         <v>9008</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>1219</v>
@@ -18634,7 +18634,7 @@
         <v>9009</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>1219</v>
@@ -18665,7 +18665,7 @@
         <v>9010</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>1219</v>
@@ -18696,7 +18696,7 @@
         <v>9011</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>1219</v>
@@ -18715,7 +18715,7 @@
         <v>1221</v>
       </c>
       <c r="I16">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J16" t="str">
         <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -17441,7 +17441,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0b57cc69-9c91-4dc2-a510-e937c2d4e167}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{4886b946-d4c6-4d55-b771-5272ee43f1ba}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -18256,7 +18256,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -18271,7 +18271,7 @@
     <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -18381,12 +18381,13 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>9001</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <f>3</f>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>1219</v>
@@ -18411,13 +18412,17 @@
         <f>LOOKUP(B6,Item!B:B,Item!D:D)</f>
         <v>红茶</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>9002</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <f t="shared" ref="C7:C16" si="0">3</f>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>1219</v>
@@ -18442,13 +18447,17 @@
         <f>LOOKUP(B7,Item!B:B,Item!D:D)</f>
         <v>波尔多</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="B8">
         <v>9003</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>1219</v>
@@ -18473,13 +18482,17 @@
         <f>LOOKUP(B8,Item!B:B,Item!D:D)</f>
         <v>勃艮第</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="B9">
         <v>9004</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>1219</v>
@@ -18504,13 +18517,17 @@
         <f>LOOKUP(B9,Item!B:B,Item!D:D)</f>
         <v>霞多丽</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="B10">
         <v>9005</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
         <v>1219</v>
@@ -18535,13 +18552,17 @@
         <f>LOOKUP(B10,Item!B:B,Item!D:D)</f>
         <v>子弹杯</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="B11">
         <v>9006</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
         <v>1219</v>
@@ -18566,13 +18587,17 @@
         <f>LOOKUP(B11,Item!B:B,Item!D:D)</f>
         <v>郁金香杯</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12">
         <v>9007</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>1219</v>
@@ -18597,13 +18622,17 @@
         <f>LOOKUP(B12,Item!B:B,Item!D:D)</f>
         <v>平底杯</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="B13">
         <v>9008</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>1219</v>
@@ -18628,13 +18657,17 @@
         <f>LOOKUP(B13,Item!B:B,Item!D:D)</f>
         <v>年份酒</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="B14">
         <v>9009</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>1219</v>
@@ -18659,13 +18692,17 @@
         <f>LOOKUP(B14,Item!B:B,Item!D:D)</f>
         <v>凉白开</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="B15">
         <v>9010</v>
       </c>
       <c r="C15">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>1219</v>
@@ -18690,13 +18727,17 @@
         <f>LOOKUP(B15,Item!B:B,Item!D:D)</f>
         <v>威士忌</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="B16">
         <v>9011</v>
       </c>
       <c r="C16">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
         <v>1219</v>
@@ -18720,6 +18761,9 @@
       <c r="J16" t="str">
         <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>
         <v>威士忌雪茄</v>
+      </c>
+      <c r="K16">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -17441,7 +17441,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{4886b946-d4c6-4d55-b771-5272ee43f1ba}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ff1444a6-f929-4e09-bc5d-9e5f1b39e99f}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -18256,7 +18256,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -18271,7 +18271,7 @@
     <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -18381,13 +18381,12 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>9001</v>
       </c>
       <c r="C6">
-        <f>3</f>
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>1219</v>
@@ -18412,17 +18411,13 @@
         <f>LOOKUP(B6,Item!B:B,Item!D:D)</f>
         <v>红茶</v>
       </c>
-      <c r="K6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>9002</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:C16" si="0">3</f>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>1219</v>
@@ -18447,17 +18442,13 @@
         <f>LOOKUP(B7,Item!B:B,Item!D:D)</f>
         <v>波尔多</v>
       </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>9003</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>1219</v>
@@ -18482,17 +18473,13 @@
         <f>LOOKUP(B8,Item!B:B,Item!D:D)</f>
         <v>勃艮第</v>
       </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9">
         <v>9004</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>1219</v>
@@ -18517,17 +18504,13 @@
         <f>LOOKUP(B9,Item!B:B,Item!D:D)</f>
         <v>霞多丽</v>
       </c>
-      <c r="K9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10">
         <v>9005</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
         <v>1219</v>
@@ -18552,17 +18535,13 @@
         <f>LOOKUP(B10,Item!B:B,Item!D:D)</f>
         <v>子弹杯</v>
       </c>
-      <c r="K10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11">
         <v>9006</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>1219</v>
@@ -18587,17 +18566,13 @@
         <f>LOOKUP(B11,Item!B:B,Item!D:D)</f>
         <v>郁金香杯</v>
       </c>
-      <c r="K11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12">
         <v>9007</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
         <v>1219</v>
@@ -18622,17 +18597,13 @@
         <f>LOOKUP(B12,Item!B:B,Item!D:D)</f>
         <v>平底杯</v>
       </c>
-      <c r="K12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13">
         <v>9008</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>1219</v>
@@ -18657,17 +18628,13 @@
         <f>LOOKUP(B13,Item!B:B,Item!D:D)</f>
         <v>年份酒</v>
       </c>
-      <c r="K13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14">
         <v>9009</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>1219</v>
@@ -18692,17 +18659,13 @@
         <f>LOOKUP(B14,Item!B:B,Item!D:D)</f>
         <v>凉白开</v>
       </c>
-      <c r="K14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15">
         <v>9010</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>1219</v>
@@ -18727,17 +18690,13 @@
         <f>LOOKUP(B15,Item!B:B,Item!D:D)</f>
         <v>威士忌</v>
       </c>
-      <c r="K15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16">
         <v>9011</v>
       </c>
       <c r="C16">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>1219</v>
@@ -18761,9 +18720,6 @@
       <c r="J16" t="str">
         <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>
         <v>威士忌雪茄</v>
-      </c>
-      <c r="K16">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735" firstSheet="3" activeTab="12"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,12 @@
     <sheet name="BlindBoxRarityRate" sheetId="14" r:id="rId5"/>
     <sheet name="BlindBoxRevealPath" sheetId="15" r:id="rId6"/>
     <sheet name="BlindBoxVisual" sheetId="16" r:id="rId7"/>
-    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
-    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
-    <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
-    <sheet name="SteamItemDef" sheetId="18" r:id="rId11"/>
-    <sheet name="SteamItemDefIdRange" sheetId="19" r:id="rId12"/>
-    <sheet name="RefreshmentConfig" sheetId="20" r:id="rId13"/>
+    <sheet name="RefreshmentConfig" sheetId="20" r:id="rId8"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
+    <sheet name="LinkTree" sheetId="17" r:id="rId11"/>
+    <sheet name="SteamItemDef" sheetId="18" r:id="rId12"/>
+    <sheet name="SteamItemDefIdRange" sheetId="19" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="1239">
   <si>
     <t>##var</t>
   </si>
@@ -2608,6 +2608,87 @@
     <t>实际上特殊品质的盲盒没有显示图片的机会</t>
   </si>
   <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>DurationHands</t>
+  </si>
+  <si>
+    <t>LuckyDealMode</t>
+  </si>
+  <si>
+    <t>LuckyDealTriggerChance</t>
+  </si>
+  <si>
+    <t>InteractionHintSfxCue</t>
+  </si>
+  <si>
+    <t>UseSfxCue</t>
+  </si>
+  <si>
+    <t>BalloonOffsetY</t>
+  </si>
+  <si>
+    <t>int#ref=TbItem</t>
+  </si>
+  <si>
+    <t>ELuckyDealMode</t>
+  </si>
+  <si>
+    <t>关联 `Item.Id` 的唯一配置。仅允许填写 `ItemType = Refreshment` 的物品；</t>
+  </si>
+  <si>
+    <t>使用成功后获得的 BUFF 持续牌局数。每次成功下注并开始新局时消耗 1 局；建议填写 1-99。</t>
+  </si>
+  <si>
+    <t>决定幸运发牌的具体规则。第一版只支持 `GuidedDraw`；其他枚举为后续预留，暂勿配置。</t>
+  </si>
+  <si>
+    <t>BUFF 生效期间，每局开始时触发幸运发牌的概率。填写 0-1 小数，例如 `0.75` 表示 75%；未触发也会消耗该局。</t>
+  </si>
+  <si>
+    <t>点击桌面 Refreshment 时，播放交互提示动画所用的 AudioManager 逻辑 Cue。填空则静音；不要填写文件扩展名或资源路径。</t>
+  </si>
+  <si>
+    <t>玩家确认使用 Refreshment 并激活 BUFF 时播放的 AudioManager 逻辑 Cue。可按饮品/食物/器具分别配置；填空则静音。</t>
+  </si>
+  <si>
+    <t>在 PSD 导出定位的基础上，对 UseBalloon 和 StatusBalloon 同时追加的 Y 轴像素偏移。正数向下、负数向上；例如热气使气球偏高时填写正数。</t>
+  </si>
+  <si>
+    <t>关联物品 ID</t>
+  </si>
+  <si>
+    <t>持续局数</t>
+  </si>
+  <si>
+    <t>幸运发牌模式</t>
+  </si>
+  <si>
+    <t>Look校验品质</t>
+  </si>
+  <si>
+    <t>幸运触发概率</t>
+  </si>
+  <si>
+    <t>交互提示音效</t>
+  </si>
+  <si>
+    <t>使用音效</t>
+  </si>
+  <si>
+    <t>气球高度微调</t>
+  </si>
+  <si>
+    <t>GuidedDraw</t>
+  </si>
+  <si>
+    <t>Refreshment_Hint</t>
+  </si>
+  <si>
+    <t>Refreshment_BuffStart</t>
+  </si>
+  <si>
     <t>TabName</t>
   </si>
   <si>
@@ -3581,10 +3662,10 @@
     <t>可消耗库存物品总段；具体用途继续使用子段划分。</t>
   </si>
   <si>
-    <t>通常保存在玩家 Steam 库存中、等待被消耗的可堆叠物品</t>
-  </si>
-  <si>
-    <t>盲盒券、熔炼材料</t>
+    <t>通常保存在玩家 Steam 库存中、等待被消耗的可堆叠物品，游戏内玩家不可见</t>
+  </si>
+  <si>
+    <t>熔炼材料</t>
   </si>
   <si>
     <t>盲盒开箱成本与 BlindBox 一一对应：SteamOpenCostItemDefId = 200000 + BlindBox.Id。采用该映射的 BlindBox.Id 必须为 1-29999，并由转换器校验。</t>
@@ -3596,13 +3677,22 @@
     <t>BlindBox 1001 的开箱成本 ItemDef 为 201001</t>
   </si>
   <si>
+    <t>历史盲盒券与开箱成本冻结段。</t>
+  </si>
+  <si>
+    <t>兼容旧ID</t>
+  </si>
+  <si>
+    <t>201001、201002、204001 只保留兼容，不再分配新定义或改变身份。</t>
+  </si>
+  <si>
     <t>可消耗库存物品的后续功能预留段。</t>
   </si>
   <si>
-    <t>盲盒券以外的可堆叠材料</t>
-  </si>
-  <si>
-    <t>230xxx 可用于熔炼助燃剂等材料</t>
+    <t>可堆叠材料</t>
+  </si>
+  <si>
+    <t>210xxx 可用于熔炼助燃剂等材料</t>
   </si>
   <si>
     <t>Generator 与交换产物定义总段；同一个权重随机池可以被多种途径使用，不要求与 BlindBox 一一对应。</t>
@@ -3614,6 +3704,9 @@
     <t>301xxx 盲盒 Generator、302xxx 熔炼 Generator</t>
   </si>
   <si>
+    <t>随机奖励 Generator 总段；同一个权重随机池可以被多种途径使用，不要求与 BlindBox 一一对应。</t>
+  </si>
+  <si>
     <t>盲盒随机奖池 Generator 子段。</t>
   </si>
   <si>
@@ -3623,6 +3716,9 @@
     <t>标准盲盒、新手盲盒等 Generator</t>
   </si>
   <si>
+    <t>盲盒奖励池 Generatorz 。可以被 PlaytimeGenerator 直接引用，也兼容历史 Exchange。</t>
+  </si>
+  <si>
     <t>熔炼随机奖池 Generator 子段。</t>
   </si>
   <si>
@@ -3776,6 +3872,30 @@
     <t>新手盲盒队列中的 Steam 投放</t>
   </si>
   <si>
+    <t>新手一次性 PlaytimeGenerator 总段，同时包含历史券版与新版直接奖励。</t>
+  </si>
+  <si>
+    <t>精细控制新手前期能接触到的奖励范围，保证前期体验的稳定性</t>
+  </si>
+  <si>
+    <t>历史新手券 PlaytimeGenerator 子段，永久冻结。</t>
+  </si>
+  <si>
+    <t>兼容</t>
+  </si>
+  <si>
+    <t>旧的新手12个奖励</t>
+  </si>
+  <si>
+    <t>新版新手直接奖励 PlaytimeGenerator 子段</t>
+  </si>
+  <si>
+    <t>新手阶段的 PlaytimeGenerator</t>
+  </si>
+  <si>
+    <t>前12个奖励当中的装扮奖励</t>
+  </si>
+  <si>
     <t>长期循环投放子段。</t>
   </si>
   <si>
@@ -3785,6 +3905,18 @@
     <t>长期循环装扮盲盒券，受掉落窗口控制</t>
   </si>
   <si>
+    <t>长期循环 PlaytimeGenerator 总段</t>
+  </si>
+  <si>
+    <t>同时包含历史券版与新版直接奖励。</t>
+  </si>
+  <si>
+    <t>历史循环券 PlaytimeGenerator 子段，永久冻结。</t>
+  </si>
+  <si>
+    <t>新版循环直接奖励 PlaytimeGenerator 子段</t>
+  </si>
+  <si>
     <t>固定系统投放预留段。</t>
   </si>
   <si>
@@ -3816,87 +3948,6 @@
   </si>
   <si>
     <t>不分配正式或测试定义</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>DurationHands</t>
-  </si>
-  <si>
-    <t>LuckyDealMode</t>
-  </si>
-  <si>
-    <t>LuckyDealTriggerChance</t>
-  </si>
-  <si>
-    <t>InteractionHintSfxCue</t>
-  </si>
-  <si>
-    <t>UseSfxCue</t>
-  </si>
-  <si>
-    <t>BalloonOffsetY</t>
-  </si>
-  <si>
-    <t>int#ref=TbItem</t>
-  </si>
-  <si>
-    <t>ELuckyDealMode</t>
-  </si>
-  <si>
-    <t>关联 `Item.Id` 的唯一配置。仅允许填写 `ItemType = Refreshment` 的物品；</t>
-  </si>
-  <si>
-    <t>使用成功后获得的 BUFF 持续牌局数。每次成功下注并开始新局时消耗 1 局；建议填写 1-99。</t>
-  </si>
-  <si>
-    <t>决定幸运发牌的具体规则。第一版只支持 `GuidedDraw`；其他枚举为后续预留，暂勿配置。</t>
-  </si>
-  <si>
-    <t>BUFF 生效期间，每局开始时触发幸运发牌的概率。填写 0-1 小数，例如 `0.75` 表示 75%；未触发也会消耗该局。</t>
-  </si>
-  <si>
-    <t>点击桌面 Refreshment 时，播放交互提示动画所用的 AudioManager 逻辑 Cue。填空则静音；不要填写文件扩展名或资源路径。</t>
-  </si>
-  <si>
-    <t>玩家确认使用 Refreshment 并激活 BUFF 时播放的 AudioManager 逻辑 Cue。可按饮品/食物/器具分别配置；填空则静音。</t>
-  </si>
-  <si>
-    <t>在 PSD 导出定位的基础上，对 UseBalloon 和 StatusBalloon 同时追加的 Y 轴像素偏移。正数向下、负数向上；例如热气使气球偏高时填写正数。</t>
-  </si>
-  <si>
-    <t>关联物品 ID</t>
-  </si>
-  <si>
-    <t>持续局数</t>
-  </si>
-  <si>
-    <t>幸运发牌模式</t>
-  </si>
-  <si>
-    <t>Look校验品质</t>
-  </si>
-  <si>
-    <t>幸运触发概率</t>
-  </si>
-  <si>
-    <t>交互提示音效</t>
-  </si>
-  <si>
-    <t>使用音效</t>
-  </si>
-  <si>
-    <t>气球高度微调</t>
-  </si>
-  <si>
-    <t>GuidedDraw</t>
-  </si>
-  <si>
-    <t>Refreshment_Hint</t>
-  </si>
-  <si>
-    <t>Refreshment_BuffStart</t>
   </si>
 </sst>
 </file>
@@ -3909,8 +3960,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -4072,12 +4130,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4422,16 +4486,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4440,37 +4501,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4485,82 +4546,85 @@
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4574,16 +4638,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4595,31 +4677,34 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5236,11 +5321,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="20" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="27" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="20" customWidth="1"/>
+    <col min="23" max="23" width="7" style="27" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -5439,7 +5524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:35">
+    <row r="3" s="2" customFormat="1" ht="121.8" spans="1:35">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -5448,71 +5533,71 @@
       <c r="D3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="1" t="s">
+      <c r="L3" s="28"/>
+      <c r="M3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="9"/>
-      <c r="T3" s="1" t="s">
+      <c r="S3" s="15"/>
+      <c r="T3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="9"/>
-      <c r="X3" s="1" t="s">
+      <c r="W3" s="15"/>
+      <c r="X3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Z3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AA3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AB3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AD3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AE3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AG3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AH3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AI3" s="2" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5617,72 +5702,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="19" customFormat="1" spans="1:35">
-      <c r="B5" s="19">
+    <row r="5" s="26" customFormat="1" spans="1:35">
+      <c r="B5" s="26">
         <v>1001</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="26">
         <v>200</v>
       </c>
-      <c r="J5" s="19">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="26">
+        <v>0</v>
+      </c>
+      <c r="K5" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19">
-        <v>0</v>
-      </c>
-      <c r="T5" s="19" t="s">
+      <c r="M5" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="26">
+        <v>0</v>
+      </c>
+      <c r="O5" s="26">
+        <v>0</v>
+      </c>
+      <c r="P5" s="26">
+        <v>0</v>
+      </c>
+      <c r="T5" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="26">
         <v>1001</v>
       </c>
-      <c r="W5" s="19"/>
-      <c r="Y5" s="19" t="s">
+      <c r="W5" s="26"/>
+      <c r="Y5" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="19" t="b">
+      <c r="AA5" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6146,10 +6231,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="20">
         <v>100</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="20">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -6864,7 +6949,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="20" t="s">
+      <c r="S23" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -7222,7 +7307,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="20" t="s">
+      <c r="S28" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -7234,7 +7319,7 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="20" t="s">
+      <c r="W28" s="27" t="s">
         <v>161</v>
       </c>
       <c r="X28">
@@ -7326,7 +7411,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="20" t="s">
+      <c r="S29" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -7338,7 +7423,7 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="20" t="s">
+      <c r="W29" s="27" t="s">
         <v>161</v>
       </c>
       <c r="X29">
@@ -7715,435 +7800,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="19" customFormat="1" spans="2:31">
-      <c r="B35" s="19">
+    <row r="35" s="26" customFormat="1" spans="2:31">
+      <c r="B35" s="26">
         <v>4001</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="19">
-        <v>0</v>
-      </c>
-      <c r="J35" s="19">
-        <v>0</v>
-      </c>
-      <c r="K35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" s="19" t="s">
+      <c r="I35" s="26">
+        <v>0</v>
+      </c>
+      <c r="J35" s="26">
+        <v>0</v>
+      </c>
+      <c r="K35" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="19">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
-        <v>0</v>
-      </c>
-      <c r="P35" s="19">
-        <v>0</v>
-      </c>
-      <c r="T35" s="19" t="s">
+      <c r="M35" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="26">
+        <v>0</v>
+      </c>
+      <c r="O35" s="26">
+        <v>0</v>
+      </c>
+      <c r="P35" s="26">
+        <v>0</v>
+      </c>
+      <c r="T35" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="U35" s="19" t="s">
+      <c r="U35" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="X35" s="19">
+      <c r="X35" s="26">
         <v>104001</v>
       </c>
-      <c r="Y35" s="19" t="s">
+      <c r="Y35" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="19" customFormat="1" spans="2:31">
-      <c r="B36" s="19">
+      <c r="Z35" s="26"/>
+      <c r="AA35" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="26" customFormat="1" spans="2:31">
+      <c r="B36" s="26">
         <v>4002</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F36" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="19">
-        <v>0</v>
-      </c>
-      <c r="J36" s="19">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="19" t="s">
+      <c r="I36" s="26">
+        <v>0</v>
+      </c>
+      <c r="J36" s="26">
+        <v>0</v>
+      </c>
+      <c r="K36" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="19">
-        <v>0</v>
-      </c>
-      <c r="O36" s="19">
-        <v>0</v>
-      </c>
-      <c r="P36" s="19">
-        <v>0</v>
-      </c>
-      <c r="T36" s="19" t="s">
+      <c r="M36" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="26">
+        <v>0</v>
+      </c>
+      <c r="O36" s="26">
+        <v>0</v>
+      </c>
+      <c r="P36" s="26">
+        <v>0</v>
+      </c>
+      <c r="T36" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="U36" s="19" t="s">
+      <c r="U36" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="X36" s="19">
+      <c r="X36" s="26">
         <v>104002</v>
       </c>
-      <c r="Y36" s="19" t="s">
+      <c r="Y36" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="19" customFormat="1" spans="2:31">
-      <c r="B37" s="19">
+      <c r="Z36" s="26"/>
+      <c r="AA36" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="26" customFormat="1" spans="2:31">
+      <c r="B37" s="26">
         <v>4003</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" s="19" t="s">
+      <c r="I37" s="26">
+        <v>0</v>
+      </c>
+      <c r="J37" s="26">
+        <v>0</v>
+      </c>
+      <c r="K37" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19" t="s">
+      <c r="M37" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="26">
+        <v>0</v>
+      </c>
+      <c r="O37" s="26">
+        <v>0</v>
+      </c>
+      <c r="P37" s="26">
+        <v>0</v>
+      </c>
+      <c r="T37" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="U37" s="19" t="s">
+      <c r="U37" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="X37" s="19">
+      <c r="X37" s="26">
         <v>104003</v>
       </c>
-      <c r="Y37" s="19" t="s">
+      <c r="Y37" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="19" customFormat="1" spans="2:31">
-      <c r="B38" s="19">
+      <c r="Z37" s="26"/>
+      <c r="AA37" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="26" customFormat="1" spans="2:31">
+      <c r="B38" s="26">
         <v>4004</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="I38" s="26">
+        <v>0</v>
+      </c>
+      <c r="J38" s="26">
+        <v>0</v>
+      </c>
+      <c r="K38" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19" t="s">
+      <c r="M38" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="26">
+        <v>0</v>
+      </c>
+      <c r="O38" s="26">
+        <v>0</v>
+      </c>
+      <c r="P38" s="26">
+        <v>0</v>
+      </c>
+      <c r="T38" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="U38" s="19" t="s">
+      <c r="U38" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="X38" s="19">
+      <c r="X38" s="26">
         <v>104004</v>
       </c>
-      <c r="Y38" s="19" t="s">
+      <c r="Y38" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="19" customFormat="1" spans="2:31">
-      <c r="B39" s="19">
+      <c r="Z38" s="26"/>
+      <c r="AA38" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="26" customFormat="1" spans="2:31">
+      <c r="B39" s="26">
         <v>4005</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="19" t="s">
+      <c r="I39" s="26">
+        <v>0</v>
+      </c>
+      <c r="J39" s="26">
+        <v>0</v>
+      </c>
+      <c r="K39" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19" t="s">
+      <c r="M39" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="26">
+        <v>0</v>
+      </c>
+      <c r="O39" s="26">
+        <v>0</v>
+      </c>
+      <c r="P39" s="26">
+        <v>0</v>
+      </c>
+      <c r="T39" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="U39" s="19" t="s">
+      <c r="U39" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="X39" s="19">
+      <c r="X39" s="26">
         <v>104005</v>
       </c>
-      <c r="Y39" s="19" t="s">
+      <c r="Y39" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z39" s="19"/>
-      <c r="AA39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="19" customFormat="1" spans="2:31">
-      <c r="B40" s="19">
+      <c r="Z39" s="26"/>
+      <c r="AA39" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="26" customFormat="1" spans="2:31">
+      <c r="B40" s="26">
         <v>4006</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="19">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19">
-        <v>0</v>
-      </c>
-      <c r="K40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" s="19" t="s">
+      <c r="I40" s="26">
+        <v>0</v>
+      </c>
+      <c r="J40" s="26">
+        <v>0</v>
+      </c>
+      <c r="K40" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40" s="19">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19">
-        <v>0</v>
-      </c>
-      <c r="P40" s="19">
-        <v>0</v>
-      </c>
-      <c r="T40" s="19" t="s">
+      <c r="M40" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="26">
+        <v>0</v>
+      </c>
+      <c r="O40" s="26">
+        <v>0</v>
+      </c>
+      <c r="P40" s="26">
+        <v>0</v>
+      </c>
+      <c r="T40" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="U40" s="19" t="s">
+      <c r="U40" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="X40" s="19">
+      <c r="X40" s="26">
         <v>104006</v>
       </c>
-      <c r="Y40" s="19" t="s">
+      <c r="Y40" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z40" s="19"/>
-      <c r="AA40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="19" t="b">
+      <c r="Z40" s="26"/>
+      <c r="AA40" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8691,87 +8776,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="19" customFormat="1" spans="2:31">
-      <c r="B49" s="19">
+    <row r="49" s="26" customFormat="1" spans="2:31">
+      <c r="B49" s="26">
         <v>6001</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="19" t="s">
+      <c r="F49" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I49" s="19">
-        <v>300</v>
-      </c>
-      <c r="J49" s="19">
-        <v>0</v>
-      </c>
-      <c r="K49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="19" t="s">
+      <c r="I49" s="26">
+        <v>300</v>
+      </c>
+      <c r="J49" s="26">
+        <v>0</v>
+      </c>
+      <c r="K49" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M49" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="19">
-        <v>0</v>
-      </c>
-      <c r="O49" s="19">
-        <v>0</v>
-      </c>
-      <c r="P49" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" s="19" t="s">
+      <c r="M49" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="26">
+        <v>0</v>
+      </c>
+      <c r="O49" s="26">
+        <v>0</v>
+      </c>
+      <c r="P49" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="U49" s="19" t="s">
+      <c r="U49" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="X49" s="19">
+      <c r="X49" s="26">
         <v>106001</v>
       </c>
-      <c r="Y49" s="19" t="s">
+      <c r="Y49" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="19" t="b">
+      <c r="Z49" s="26"/>
+      <c r="AA49" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8827,7 +8912,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="20" t="s">
+      <c r="S50" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -8910,7 +8995,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="20" t="s">
+      <c r="S51" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -8993,7 +9078,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="20" t="s">
+      <c r="S52" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -9076,7 +9161,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="20" t="s">
+      <c r="S53" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -9159,7 +9244,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="20" t="s">
+      <c r="S54" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -9242,7 +9327,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="20" t="s">
+      <c r="S55" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -9325,7 +9410,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="20" t="s">
+      <c r="S56" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -9408,7 +9493,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="20" t="s">
+      <c r="S57" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -9491,7 +9576,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="20" t="s">
+      <c r="S58" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -9574,7 +9659,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="20" t="s">
+      <c r="S59" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -9809,72 +9894,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="19" customFormat="1" spans="2:31">
-      <c r="B63" s="19">
+    <row r="63" s="26" customFormat="1" spans="2:31">
+      <c r="B63" s="26">
         <v>7004</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="I63" s="19">
-        <v>300</v>
-      </c>
-      <c r="J63" s="19">
-        <v>0</v>
-      </c>
-      <c r="K63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="19" t="s">
+      <c r="I63" s="26">
+        <v>300</v>
+      </c>
+      <c r="J63" s="26">
+        <v>0</v>
+      </c>
+      <c r="K63" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63" s="19">
-        <v>0</v>
-      </c>
-      <c r="O63" s="19">
-        <v>0</v>
-      </c>
-      <c r="P63" s="19">
-        <v>0</v>
-      </c>
-      <c r="T63" s="19" t="s">
+      <c r="M63" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="26">
+        <v>0</v>
+      </c>
+      <c r="O63" s="26">
+        <v>0</v>
+      </c>
+      <c r="P63" s="26">
+        <v>0</v>
+      </c>
+      <c r="T63" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="U63" s="19" t="s">
+      <c r="U63" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="X63" s="19">
+      <c r="X63" s="26">
         <v>107004</v>
       </c>
-      <c r="Y63" s="19" t="s">
+      <c r="Y63" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z63" s="19"/>
-      <c r="AA63" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="19" t="b">
+      <c r="Z63" s="26"/>
+      <c r="AA63" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9891,7 +9976,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="14" t="s">
+      <c r="H64" s="20" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -9959,7 +10044,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="14" t="s">
+      <c r="H65" s="20" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -10134,7 +10219,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="20" t="s">
+      <c r="S67" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -10217,7 +10302,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="20" t="s">
+      <c r="S68" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -10300,7 +10385,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="20" t="s">
+      <c r="S69" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -10383,7 +10468,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="20" t="s">
+      <c r="S70" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -10466,7 +10551,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="20" t="s">
+      <c r="S71" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -10549,7 +10634,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="20" t="s">
+      <c r="S72" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -10632,7 +10717,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="20" t="s">
+      <c r="S73" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -10715,7 +10800,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="20" t="s">
+      <c r="S74" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -10798,7 +10883,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="20" t="s">
+      <c r="S75" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -10881,7 +10966,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="20" t="s">
+      <c r="S76" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -11035,7 +11120,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="20" t="s">
+      <c r="S78" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -11047,7 +11132,7 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="20" t="s">
+      <c r="W78" s="27" t="s">
         <v>161</v>
       </c>
       <c r="X78">
@@ -11136,7 +11221,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="20" t="s">
+      <c r="S79" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -11219,7 +11304,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="20" t="s">
+      <c r="S80" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -11302,7 +11387,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="20" t="s">
+      <c r="S81" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -11385,7 +11470,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="20" t="s">
+      <c r="S82" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -11468,7 +11553,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="20" t="s">
+      <c r="S83" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -11551,7 +11636,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="20" t="s">
+      <c r="S84" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -11841,7 +11926,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="20" t="s">
+      <c r="S88" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -11853,7 +11938,7 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="20" t="s">
+      <c r="W88" s="27" t="s">
         <v>161</v>
       </c>
       <c r="X88">
@@ -11945,7 +12030,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="20" t="s">
+      <c r="S89" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -11957,7 +12042,7 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="20" t="s">
+      <c r="W89" s="27" t="s">
         <v>161</v>
       </c>
       <c r="X89">
@@ -12120,7 +12205,7 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="20" t="s">
+      <c r="W91" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X91">
@@ -12200,7 +12285,7 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="20" t="s">
+      <c r="W92" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X92">
@@ -12280,7 +12365,7 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="20" t="s">
+      <c r="W93" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X93">
@@ -12360,7 +12445,7 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="20" t="s">
+      <c r="W94" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X94">
@@ -12440,7 +12525,7 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="20" t="s">
+      <c r="W95" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X95">
@@ -12520,7 +12605,7 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="20" t="s">
+      <c r="W96" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X96">
@@ -12600,7 +12685,7 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="20" t="s">
+      <c r="W97" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X97">
@@ -12674,7 +12759,7 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="20" t="s">
+      <c r="W98" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X98">
@@ -12831,7 +12916,7 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="20" t="s">
+      <c r="W100" s="27" t="s">
         <v>446</v>
       </c>
       <c r="X100">
@@ -12856,216 +12941,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" s="19" customFormat="1" spans="2:31">
-      <c r="B101" s="19">
+    <row r="101" s="26" customFormat="1" spans="2:31">
+      <c r="B101" s="26">
         <v>10001</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="26" t="s">
         <v>483</v>
       </c>
-      <c r="D101" s="19" t="s">
+      <c r="D101" s="26" t="s">
         <v>484</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" s="26" t="s">
         <v>485</v>
       </c>
-      <c r="H101" s="19" t="s">
+      <c r="H101" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I101" s="19">
-        <v>300</v>
-      </c>
-      <c r="J101" s="19">
-        <v>0</v>
-      </c>
-      <c r="K101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" s="19" t="s">
+      <c r="I101" s="26">
+        <v>300</v>
+      </c>
+      <c r="J101" s="26">
+        <v>0</v>
+      </c>
+      <c r="K101" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101" s="19">
-        <v>0</v>
-      </c>
-      <c r="O101" s="19">
-        <v>0</v>
-      </c>
-      <c r="P101" s="19">
-        <v>0</v>
-      </c>
-      <c r="T101" s="19" t="s">
+      <c r="M101" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="26">
+        <v>0</v>
+      </c>
+      <c r="O101" s="26">
+        <v>0</v>
+      </c>
+      <c r="P101" s="26">
+        <v>0</v>
+      </c>
+      <c r="T101" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="U101" s="19" t="s">
+      <c r="U101" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="X101" s="19">
+      <c r="X101" s="26">
         <v>110001</v>
       </c>
-      <c r="Y101" s="19" t="s">
+      <c r="Y101" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z101" s="19"/>
-      <c r="AA101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" s="19" customFormat="1" spans="2:31">
-      <c r="B102" s="19">
+      <c r="Z101" s="26"/>
+      <c r="AA101" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="26" customFormat="1" spans="2:31">
+      <c r="B102" s="26">
         <v>11001</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C102" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D102" s="26" t="s">
         <v>489</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E102" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="H102" s="19" t="s">
+      <c r="H102" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I102" s="19">
-        <v>300</v>
-      </c>
-      <c r="J102" s="19">
-        <v>0</v>
-      </c>
-      <c r="K102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" s="19" t="s">
+      <c r="I102" s="26">
+        <v>300</v>
+      </c>
+      <c r="J102" s="26">
+        <v>0</v>
+      </c>
+      <c r="K102" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102" s="19">
-        <v>0</v>
-      </c>
-      <c r="O102" s="19">
-        <v>0</v>
-      </c>
-      <c r="P102" s="19">
-        <v>0</v>
-      </c>
-      <c r="T102" s="19" t="s">
+      <c r="M102" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="26">
+        <v>0</v>
+      </c>
+      <c r="O102" s="26">
+        <v>0</v>
+      </c>
+      <c r="P102" s="26">
+        <v>0</v>
+      </c>
+      <c r="T102" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="U102" s="19" t="s">
+      <c r="U102" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="19" t="s">
+      <c r="W102" s="26" t="s">
         <v>493</v>
       </c>
-      <c r="X102" s="19">
+      <c r="X102" s="26">
         <v>111001</v>
       </c>
-      <c r="Y102" s="19" t="s">
+      <c r="Y102" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z102" s="19"/>
-      <c r="AA102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" s="19" customFormat="1" spans="2:31">
-      <c r="B103" s="19">
+      <c r="Z102" s="26"/>
+      <c r="AA102" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="26" customFormat="1" spans="2:31">
+      <c r="B103" s="26">
         <v>11002</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="26" t="s">
         <v>494</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="26" t="s">
         <v>495</v>
       </c>
-      <c r="E103" s="19" t="s">
+      <c r="E103" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="G103" s="19">
+      <c r="G103" s="26">
         <v>11001</v>
       </c>
-      <c r="H103" s="19" t="s">
+      <c r="H103" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I103" s="19">
-        <v>300</v>
-      </c>
-      <c r="J103" s="19">
-        <v>0</v>
-      </c>
-      <c r="K103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" s="19" t="s">
+      <c r="I103" s="26">
+        <v>300</v>
+      </c>
+      <c r="J103" s="26">
+        <v>0</v>
+      </c>
+      <c r="K103" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103" s="19">
-        <v>0</v>
-      </c>
-      <c r="O103" s="19">
-        <v>0</v>
-      </c>
-      <c r="P103" s="19">
-        <v>0</v>
-      </c>
-      <c r="T103" s="19" t="s">
+      <c r="M103" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="26">
+        <v>0</v>
+      </c>
+      <c r="O103" s="26">
+        <v>0</v>
+      </c>
+      <c r="P103" s="26">
+        <v>0</v>
+      </c>
+      <c r="T103" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="U103" s="19" t="s">
+      <c r="U103" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="X103" s="19">
+      <c r="X103" s="26">
         <v>111002</v>
       </c>
-      <c r="Y103" s="19" t="s">
+      <c r="Y103" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Z103" s="19"/>
-      <c r="AA103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="19" t="b">
+      <c r="Z103" s="26"/>
+      <c r="AA103" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13088,7 +13173,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="14" t="s">
+      <c r="H104" s="20" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -13121,7 +13206,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="20" t="s">
+      <c r="S104" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -13171,7 +13256,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="14" t="s">
+      <c r="H105" s="20" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -13204,7 +13289,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="20" t="s">
+      <c r="S105" s="27" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -13272,14 +13357,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="20"/>
+      <c r="S106" s="27"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="20" t="s">
+      <c r="W106" s="27" t="s">
         <v>509</v>
       </c>
       <c r="X106">
@@ -13342,7 +13427,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="20"/>
+      <c r="S107" s="27"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -13352,7 +13437,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="20" t="s">
+      <c r="W107" s="27" t="s">
         <v>509</v>
       </c>
       <c r="X107">
@@ -13420,6 +13505,180 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D3" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
+        <v>485</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>499</v>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S12"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
@@ -13452,55 +13711,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="F1" t="s">
         <v>640</v>
       </c>
       <c r="G1" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="H1" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="I1" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="J1" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="K1" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="L1" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="M1" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="N1" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="O1" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="P1" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="Q1" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="R1" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="S1" t="s">
-        <v>821</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -13538,10 +13797,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="M2" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -13562,63 +13821,63 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:19">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="77" customHeight="1" spans="1:19">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>841</v>
+      <c r="B3" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -13626,58 +13885,58 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="C4" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="D4" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E4" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F4" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G4" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="H4" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="I4" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="J4" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
       <c r="K4" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="L4" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="M4" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="N4" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="O4" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="P4" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="Q4" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="R4" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
       <c r="S4" t="s">
-        <v>859</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -13685,7 +13944,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -13697,25 +13956,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="H5" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="I5" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J5" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="K5" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="L5" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M5" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -13735,7 +13994,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -13747,25 +14006,25 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="H6" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="I6" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J6" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="K6" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="L6" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M6" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13785,7 +14044,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -13797,25 +14056,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="H7" t="s">
-        <v>875</v>
+        <v>902</v>
       </c>
       <c r="I7" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J7" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="K7" t="s">
-        <v>877</v>
+        <v>904</v>
       </c>
       <c r="L7" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M7" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -13835,7 +14094,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>878</v>
+        <v>905</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -13847,25 +14106,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
       <c r="H8" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="I8" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J8" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="K8" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="L8" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M8" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -13885,7 +14144,7 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -13897,25 +14156,25 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="H9" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="I9" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J9" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="K9" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="L9" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M9" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N9">
         <v>92005</v>
@@ -13938,7 +14197,7 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -13950,25 +14209,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="H10" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="I10" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J10" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="K10" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="L10" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M10" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -13991,7 +14250,7 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -14003,25 +14262,25 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="H11" t="s">
-        <v>875</v>
+        <v>902</v>
       </c>
       <c r="I11" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J11" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="K11" t="s">
-        <v>877</v>
+        <v>904</v>
       </c>
       <c r="L11" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M11" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -14044,7 +14303,7 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>878</v>
+        <v>905</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -14056,25 +14315,25 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
       <c r="H12" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="I12" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J12" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="K12" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="L12" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M12" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N12">
         <v>91012</v>
@@ -14098,7 +14357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R66"/>
@@ -14131,49 +14390,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="E1" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>883</v>
+        <v>910</v>
       </c>
       <c r="H1" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="I1" t="s">
-        <v>885</v>
+        <v>912</v>
       </c>
       <c r="J1" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="K1" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="L1" t="s">
-        <v>888</v>
+        <v>915</v>
       </c>
       <c r="M1" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="N1" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="O1" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="P1" t="s">
         <v>640</v>
       </c>
       <c r="Q1" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="R1" t="s">
-        <v>893</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -14229,57 +14488,57 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:18">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="2" customFormat="1" ht="72" customHeight="1" spans="1:18">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>897</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>924</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>908</v>
+      <c r="H3" s="16" t="s">
+        <v>925</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -14287,55 +14546,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="C4" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="D4" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
       <c r="E4" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="F4" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
       <c r="I4" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="L4" t="s">
-        <v>916</v>
+        <v>943</v>
       </c>
       <c r="M4" t="s">
-        <v>917</v>
+        <v>944</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="P4" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="Q4" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="R4" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -14346,22 +14605,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="D5" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G5" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H5" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -14402,22 +14661,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="D6" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G6" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H6" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -14458,22 +14717,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="D7" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G7" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H7" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -14514,22 +14773,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="D8" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G8" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H8" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -14570,22 +14829,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="D9" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
       <c r="E9" t="s">
         <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G9" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H9" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -14626,22 +14885,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="D10" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G10" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H10" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -14682,22 +14941,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
       <c r="D11" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="E11" t="s">
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G11" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H11" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -14738,22 +14997,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="D12" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="E12" t="s">
         <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G12" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H12" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -14791,7 +15050,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -14802,19 +15061,19 @@
         <v>402001</v>
       </c>
       <c r="C14" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="D14" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="G14" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -14852,19 +15111,19 @@
         <v>402002</v>
       </c>
       <c r="C15" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="D15" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="E15" t="s">
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="G15" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -14899,19 +15158,19 @@
         <v>402003</v>
       </c>
       <c r="C16" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
       <c r="D16" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="E16" t="s">
         <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="G16" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -14946,7 +15205,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -14957,19 +15216,19 @@
         <v>403001</v>
       </c>
       <c r="C18" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="D18" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="E18" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F18" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="G18" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
       <c r="H18" t="s">
         <v>161</v>
@@ -14993,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -15010,19 +15269,19 @@
         <v>403002</v>
       </c>
       <c r="C19" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="D19" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="E19" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F19" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="G19" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -15043,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -15060,19 +15319,19 @@
         <v>403003</v>
       </c>
       <c r="C20" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="D20" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="E20" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F20" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="G20" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -15093,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -15110,7 +15369,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -15118,19 +15377,19 @@
         <v>404001</v>
       </c>
       <c r="C22" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="D22" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
       <c r="E22" t="s">
         <v>621</v>
       </c>
       <c r="F22" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
       <c r="G22" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -15151,7 +15410,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -15168,19 +15427,19 @@
         <v>404002</v>
       </c>
       <c r="C23" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="D23" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
       <c r="E23" t="s">
         <v>621</v>
       </c>
       <c r="F23" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="G23" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -15201,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -15218,19 +15477,19 @@
         <v>404004</v>
       </c>
       <c r="C24" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
       <c r="D24" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
       <c r="E24" t="s">
         <v>621</v>
       </c>
       <c r="F24" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
       <c r="G24" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -15251,7 +15510,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -15268,19 +15527,19 @@
         <v>404005</v>
       </c>
       <c r="C25" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="D25" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
       <c r="E25" t="s">
         <v>621</v>
       </c>
       <c r="F25" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
       <c r="G25" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -15301,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -15318,19 +15577,19 @@
         <v>404007</v>
       </c>
       <c r="C26" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
       <c r="D26" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="E26" t="s">
         <v>621</v>
       </c>
       <c r="F26" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="G26" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -15351,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -15368,19 +15627,19 @@
         <v>404008</v>
       </c>
       <c r="C27" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
       <c r="D27" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
       <c r="E27" t="s">
         <v>621</v>
       </c>
       <c r="F27" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
       <c r="G27" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -15401,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -15418,19 +15677,19 @@
         <v>404010</v>
       </c>
       <c r="C28" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
       <c r="D28" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="E28" t="s">
         <v>621</v>
       </c>
       <c r="F28" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
       <c r="G28" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -15451,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -15468,19 +15727,19 @@
         <v>404011</v>
       </c>
       <c r="C29" t="s">
-        <v>1007</v>
+        <v>1034</v>
       </c>
       <c r="D29" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
       <c r="E29" t="s">
         <v>621</v>
       </c>
       <c r="F29" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="G29" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -15501,7 +15760,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -15518,19 +15777,19 @@
         <v>404013</v>
       </c>
       <c r="C30" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
       <c r="D30" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
       <c r="E30" t="s">
         <v>621</v>
       </c>
       <c r="F30" t="s">
-        <v>1013</v>
+        <v>1040</v>
       </c>
       <c r="G30" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -15551,7 +15810,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -15568,7 +15827,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>1015</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -15576,19 +15835,19 @@
         <v>405001</v>
       </c>
       <c r="C32" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="D32" t="s">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="E32" t="s">
         <v>621</v>
       </c>
       <c r="F32" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="G32" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -15609,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -15626,7 +15885,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -15634,22 +15893,22 @@
         <v>406005</v>
       </c>
       <c r="C34" t="s">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="D34" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="E34" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F34" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="G34" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="H34" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -15670,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -15687,22 +15946,22 @@
         <v>406006</v>
       </c>
       <c r="C35" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
       <c r="D35" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="E35" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F35" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="G35" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="H35" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -15723,7 +15982,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -15740,22 +15999,22 @@
         <v>406007</v>
       </c>
       <c r="C36" t="s">
-        <v>1031</v>
+        <v>1058</v>
       </c>
       <c r="D36" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="E36" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F36" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
       <c r="G36" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="H36" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -15776,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -15793,22 +16052,22 @@
         <v>406008</v>
       </c>
       <c r="C37" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
       <c r="D37" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="E37" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F37" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="G37" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
       <c r="H37" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -15829,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1040</v>
+        <v>1067</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -15851,7 +16110,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>1041</v>
+        <v>1068</v>
       </c>
       <c r="C39" t="s">
         <v>161</v>
@@ -15910,19 +16169,19 @@
         <v>201001</v>
       </c>
       <c r="C40" t="s">
-        <v>1042</v>
+        <v>1069</v>
       </c>
       <c r="D40" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="G40" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="H40" t="s">
         <v>161</v>
@@ -15966,19 +16225,19 @@
         <v>201002</v>
       </c>
       <c r="C41" t="s">
-        <v>1043</v>
+        <v>1070</v>
       </c>
       <c r="D41" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="G41" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="H41" t="s">
         <v>161</v>
@@ -16022,19 +16281,19 @@
         <v>204001</v>
       </c>
       <c r="C42" t="s">
-        <v>1044</v>
+        <v>1071</v>
       </c>
       <c r="D42" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="E42" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="G42" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="H42" t="s">
         <v>161</v>
@@ -16075,7 +16334,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
@@ -16134,19 +16393,19 @@
         <v>301001</v>
       </c>
       <c r="C44" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
       <c r="D44" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="E44" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F44" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="G44" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="H44" t="s">
         <v>161</v>
@@ -16170,7 +16429,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -16190,19 +16449,19 @@
         <v>301002</v>
       </c>
       <c r="C45" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
       <c r="D45" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="E45" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F45" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="G45" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="H45" t="s">
         <v>161</v>
@@ -16226,7 +16485,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -16243,7 +16502,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>1048</v>
+        <v>1075</v>
       </c>
       <c r="C46" t="s">
         <v>161</v>
@@ -16302,22 +16561,22 @@
         <v>501001</v>
       </c>
       <c r="C47" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
       <c r="D47" t="s">
-        <v>1050</v>
+        <v>1077</v>
       </c>
       <c r="E47" t="s">
         <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G47" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H47" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -16358,22 +16617,22 @@
         <v>501002</v>
       </c>
       <c r="C48" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
       <c r="D48" t="s">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="E48" t="s">
         <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G48" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H48" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -16414,22 +16673,22 @@
         <v>501003</v>
       </c>
       <c r="C49" t="s">
-        <v>1053</v>
+        <v>1080</v>
       </c>
       <c r="D49" t="s">
-        <v>1054</v>
+        <v>1081</v>
       </c>
       <c r="E49" t="s">
         <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G49" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H49" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -16470,22 +16729,22 @@
         <v>501004</v>
       </c>
       <c r="C50" t="s">
-        <v>1055</v>
+        <v>1082</v>
       </c>
       <c r="D50" t="s">
-        <v>1056</v>
+        <v>1083</v>
       </c>
       <c r="E50" t="s">
         <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G50" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H50" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -16523,7 +16782,7 @@
         <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>1057</v>
+        <v>1084</v>
       </c>
       <c r="C51" t="s">
         <v>161</v>
@@ -16582,22 +16841,22 @@
         <v>601001</v>
       </c>
       <c r="C52" t="s">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="D52" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="E52" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F52" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="G52" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="H52" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -16618,7 +16877,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -16638,22 +16897,22 @@
         <v>601002</v>
       </c>
       <c r="C53" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
       <c r="D53" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="E53" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F53" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="G53" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="H53" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -16674,7 +16933,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>1061</v>
+        <v>1088</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -16694,22 +16953,22 @@
         <v>601003</v>
       </c>
       <c r="C54" t="s">
-        <v>1062</v>
+        <v>1089</v>
       </c>
       <c r="D54" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="E54" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F54" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
       <c r="G54" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="H54" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -16730,7 +16989,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>1063</v>
+        <v>1090</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -16750,22 +17009,22 @@
         <v>601004</v>
       </c>
       <c r="C55" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D55" t="s">
         <v>1064</v>
       </c>
-      <c r="D55" t="s">
-        <v>1037</v>
-      </c>
       <c r="E55" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F55" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="G55" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
       <c r="H55" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -16786,7 +17045,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -16803,7 +17062,7 @@
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="C56" t="s">
         <v>161</v>
@@ -16862,19 +17121,19 @@
         <v>700001</v>
       </c>
       <c r="C57" t="s">
-        <v>1067</v>
+        <v>1094</v>
       </c>
       <c r="D57" t="s">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="E57" t="s">
         <v>621</v>
       </c>
       <c r="F57" t="s">
-        <v>1069</v>
+        <v>1096</v>
       </c>
       <c r="G57" t="s">
-        <v>1070</v>
+        <v>1097</v>
       </c>
       <c r="H57" t="s">
         <v>161</v>
@@ -16898,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>1071</v>
+        <v>1098</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -16918,19 +17177,19 @@
         <v>700002</v>
       </c>
       <c r="C58" t="s">
-        <v>1072</v>
+        <v>1099</v>
       </c>
       <c r="D58" t="s">
-        <v>1073</v>
+        <v>1100</v>
       </c>
       <c r="E58" t="s">
         <v>621</v>
       </c>
       <c r="F58" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="G58" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="H58" t="s">
         <v>161</v>
@@ -16954,7 +17213,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -16974,19 +17233,19 @@
         <v>700004</v>
       </c>
       <c r="C59" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
       <c r="D59" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
       <c r="E59" t="s">
         <v>621</v>
       </c>
       <c r="F59" t="s">
-        <v>1079</v>
+        <v>1106</v>
       </c>
       <c r="G59" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
       <c r="H59" t="s">
         <v>161</v>
@@ -17010,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -17030,19 +17289,19 @@
         <v>700005</v>
       </c>
       <c r="C60" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
       <c r="D60" t="s">
-        <v>1083</v>
+        <v>1110</v>
       </c>
       <c r="E60" t="s">
         <v>621</v>
       </c>
       <c r="F60" t="s">
-        <v>1084</v>
+        <v>1111</v>
       </c>
       <c r="G60" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
       <c r="H60" t="s">
         <v>161</v>
@@ -17066,7 +17325,7 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -17086,19 +17345,19 @@
         <v>700007</v>
       </c>
       <c r="C61" t="s">
-        <v>1086</v>
+        <v>1113</v>
       </c>
       <c r="D61" t="s">
-        <v>1087</v>
+        <v>1114</v>
       </c>
       <c r="E61" t="s">
         <v>621</v>
       </c>
       <c r="F61" t="s">
-        <v>1088</v>
+        <v>1115</v>
       </c>
       <c r="G61" t="s">
-        <v>1089</v>
+        <v>1116</v>
       </c>
       <c r="H61" t="s">
         <v>161</v>
@@ -17122,7 +17381,7 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -17142,19 +17401,19 @@
         <v>700008</v>
       </c>
       <c r="C62" t="s">
-        <v>1090</v>
+        <v>1117</v>
       </c>
       <c r="D62" t="s">
-        <v>1091</v>
+        <v>1118</v>
       </c>
       <c r="E62" t="s">
         <v>621</v>
       </c>
       <c r="F62" t="s">
-        <v>1092</v>
+        <v>1119</v>
       </c>
       <c r="G62" t="s">
-        <v>1093</v>
+        <v>1120</v>
       </c>
       <c r="H62" t="s">
         <v>161</v>
@@ -17178,7 +17437,7 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -17198,19 +17457,19 @@
         <v>700010</v>
       </c>
       <c r="C63" t="s">
-        <v>1094</v>
+        <v>1121</v>
       </c>
       <c r="D63" t="s">
-        <v>1095</v>
+        <v>1122</v>
       </c>
       <c r="E63" t="s">
         <v>621</v>
       </c>
       <c r="F63" t="s">
-        <v>1096</v>
+        <v>1123</v>
       </c>
       <c r="G63" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="H63" t="s">
         <v>161</v>
@@ -17234,7 +17493,7 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -17254,19 +17513,19 @@
         <v>700011</v>
       </c>
       <c r="C64" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
       <c r="D64" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
       <c r="E64" t="s">
         <v>621</v>
       </c>
       <c r="F64" t="s">
-        <v>1100</v>
+        <v>1127</v>
       </c>
       <c r="G64" t="s">
-        <v>1101</v>
+        <v>1128</v>
       </c>
       <c r="H64" t="s">
         <v>161</v>
@@ -17290,7 +17549,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -17307,7 +17566,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
       <c r="C65" t="s">
         <v>161</v>
@@ -17366,19 +17625,19 @@
         <v>701001</v>
       </c>
       <c r="C66" t="s">
-        <v>1103</v>
+        <v>1130</v>
       </c>
       <c r="D66" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
       <c r="E66" t="s">
         <v>621</v>
       </c>
       <c r="F66" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="G66" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="H66" t="s">
         <v>161</v>
@@ -17402,7 +17661,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -17441,7 +17700,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ff1444a6-f929-4e09-bc5d-9e5f1b39e99f}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{b4d7ea45-828b-4c01-bc33-eac63545d4aa}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -17460,15 +17719,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="25.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4166666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17480,19 +17739,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="D1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1108</v>
+        <v>1134</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1135</v>
       </c>
       <c r="G1" t="s">
-        <v>1109</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -17508,10 +17767,10 @@
       <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
@@ -17519,22 +17778,22 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="G3" t="s">
@@ -17549,13 +17808,13 @@
         <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1111</v>
+        <v>1138</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1112</v>
+        <v>1139</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>596</v>
@@ -17577,17 +17836,17 @@
       <c r="D5">
         <v>199999</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="6" ht="52.2" spans="1:7">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="6" ht="69.6" spans="1:7">
       <c r="A6" t="s">
         <v>161</v>
       </c>
@@ -17600,336 +17859,327 @@
       <c r="D6">
         <v>299999</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1116</v>
+      <c r="E6" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1143</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
-      <c r="A7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="9">
         <v>1003</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>201000</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="9">
         <v>229999</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="8" ht="34.8" spans="1:7">
-      <c r="A8" t="s">
-        <v>161</v>
-      </c>
+      <c r="E7" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="8" ht="84" customHeight="1" spans="1:7">
       <c r="B8">
+        <v>1003</v>
+      </c>
+      <c r="C8">
+        <v>201000</v>
+      </c>
+      <c r="D8">
+        <v>209999</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" spans="1:7">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
         <v>1004</v>
       </c>
-      <c r="C8">
-        <v>230000</v>
-      </c>
-      <c r="D8">
+      <c r="C9">
+        <v>210000</v>
+      </c>
+      <c r="D9">
         <v>299999</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="9" ht="69.6" spans="1:7">
-      <c r="A9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9">
+      <c r="E9" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="10" ht="69.6" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="9">
         <v>1005</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="9">
         <v>300000</v>
       </c>
-      <c r="D9">
+      <c r="D10" s="9">
         <v>399999</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="10" ht="34.8" spans="1:7">
-      <c r="A10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10">
+      <c r="E10" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="11" ht="67" customHeight="1" spans="1:7">
+      <c r="B11">
+        <v>1005</v>
+      </c>
+      <c r="C11">
+        <v>300000</v>
+      </c>
+      <c r="D11">
+        <v>399999</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="12" ht="34.8" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="9">
         <v>1006</v>
       </c>
-      <c r="C10">
+      <c r="C12" s="9">
         <v>301000</v>
       </c>
-      <c r="D10">
+      <c r="D12" s="9">
         <v>301999</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="11" ht="34.8" spans="1:7">
-      <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11">
+      <c r="E12" s="10" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13">
+        <v>301000</v>
+      </c>
+      <c r="D13">
+        <v>301999</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="14" ht="34.8" spans="1:7">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14">
         <v>1007</v>
       </c>
-      <c r="C11">
+      <c r="C14">
         <v>302000</v>
       </c>
-      <c r="D11">
+      <c r="D14">
         <v>302999</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="12" ht="34.8" spans="1:7">
-      <c r="A12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12">
+      <c r="E14" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="15" ht="34.8" spans="1:7">
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15">
         <v>1008</v>
       </c>
-      <c r="C12">
+      <c r="C15">
         <v>303000</v>
       </c>
-      <c r="D12">
+      <c r="D15">
         <v>399999</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="13" ht="87" spans="1:7">
-      <c r="A13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13">
+      <c r="E15" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="16" ht="87" spans="1:7">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16">
         <v>1009</v>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>400000</v>
       </c>
-      <c r="D13">
+      <c r="D16">
         <v>499999</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="14" ht="52.2" spans="1:7">
-      <c r="A14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14">
+      <c r="E16" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="17" ht="52.2" spans="1:7">
+      <c r="A17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17">
         <v>1010</v>
       </c>
-      <c r="C14">
+      <c r="C17">
         <v>400000</v>
       </c>
-      <c r="D14">
+      <c r="D17">
         <v>409999</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="15" ht="52.2" spans="1:7">
-      <c r="A15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15">
+      <c r="E17" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="18" ht="52.2" spans="1:7">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18">
         <v>1011</v>
       </c>
-      <c r="C15">
+      <c r="C18">
         <v>410000</v>
       </c>
-      <c r="D15">
+      <c r="D18">
         <v>499999</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="16" ht="52.2" spans="1:7">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16">
+      <c r="E18" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="19" ht="52.2" spans="1:7">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19">
         <v>1012</v>
       </c>
-      <c r="C16">
+      <c r="C19">
         <v>500000</v>
-      </c>
-      <c r="D16">
-        <v>599999</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="17" ht="34.8" spans="1:7">
-      <c r="A17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17">
-        <v>1013</v>
-      </c>
-      <c r="C17">
-        <v>501000</v>
-      </c>
-      <c r="D17">
-        <v>501999</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="18" ht="34.8" spans="1:7">
-      <c r="A18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18">
-        <v>1014</v>
-      </c>
-      <c r="C18">
-        <v>502000</v>
-      </c>
-      <c r="D18">
-        <v>502999</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="19" ht="34.8" spans="1:7">
-      <c r="A19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19">
-        <v>1015</v>
-      </c>
-      <c r="C19">
-        <v>503000</v>
       </c>
       <c r="D19">
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>1155</v>
+        <v>1177</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1178</v>
       </c>
       <c r="G19" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="20" ht="87" spans="1:7">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="20" ht="34.8" spans="1:7">
       <c r="A20" t="s">
         <v>161</v>
       </c>
       <c r="B20">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C20">
-        <v>600000</v>
+        <v>501000</v>
       </c>
       <c r="D20">
-        <v>699999</v>
+        <v>501999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>1158</v>
+        <v>1180</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1181</v>
       </c>
       <c r="G20" t="s">
-        <v>1159</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -17937,22 +18187,22 @@
         <v>161</v>
       </c>
       <c r="B21">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C21">
-        <v>601000</v>
+        <v>502000</v>
       </c>
       <c r="D21">
-        <v>601999</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>1161</v>
+        <v>502999</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1184</v>
       </c>
       <c r="G21" t="s">
-        <v>1162</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -17960,45 +18210,45 @@
         <v>161</v>
       </c>
       <c r="B22">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C22">
-        <v>602000</v>
+        <v>503000</v>
       </c>
       <c r="D22">
-        <v>602999</v>
+        <v>599999</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1163</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>1164</v>
+        <v>1186</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1187</v>
       </c>
       <c r="G22" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="23" ht="34.8" spans="1:7">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="23" ht="87" spans="1:7">
       <c r="A23" t="s">
         <v>161</v>
       </c>
       <c r="B23">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C23">
-        <v>603000</v>
+        <v>600000</v>
       </c>
       <c r="D23">
-        <v>603999</v>
+        <v>699999</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>1167</v>
+        <v>1189</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1190</v>
       </c>
       <c r="G23" t="s">
-        <v>1168</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="24" ht="34.8" spans="1:7">
@@ -18006,22 +18256,22 @@
         <v>161</v>
       </c>
       <c r="B24">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C24">
-        <v>604000</v>
+        <v>601000</v>
       </c>
       <c r="D24">
-        <v>699999</v>
+        <v>601999</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>1170</v>
+        <v>1192</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1193</v>
       </c>
       <c r="G24" t="s">
-        <v>1171</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -18029,45 +18279,45 @@
         <v>161</v>
       </c>
       <c r="B25">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C25">
-        <v>700000</v>
+        <v>602000</v>
       </c>
       <c r="D25">
-        <v>799999</v>
+        <v>602999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>1173</v>
+        <v>1195</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1196</v>
       </c>
       <c r="G25" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="26" ht="52.2" spans="1:7">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="26" ht="34.8" spans="1:7">
       <c r="A26" t="s">
         <v>161</v>
       </c>
       <c r="B26">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C26">
-        <v>700000</v>
+        <v>603000</v>
       </c>
       <c r="D26">
-        <v>709999</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>1176</v>
+        <v>603999</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1199</v>
       </c>
       <c r="G26" t="s">
-        <v>1177</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -18075,22 +18325,22 @@
         <v>161</v>
       </c>
       <c r="B27">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C27">
-        <v>700000</v>
+        <v>604000</v>
       </c>
       <c r="D27">
-        <v>700999</v>
+        <v>699999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>1179</v>
+        <v>1201</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1202</v>
       </c>
       <c r="G27" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -18098,629 +18348,338 @@
         <v>161</v>
       </c>
       <c r="B28">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C28">
-        <v>701000</v>
+        <v>700000</v>
       </c>
       <c r="D28">
-        <v>701999</v>
+        <v>799999</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>1182</v>
+        <v>1204</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1205</v>
       </c>
       <c r="G28" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="29" ht="34.8" spans="1:7">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="29" ht="52.2" spans="1:7">
       <c r="A29" t="s">
         <v>161</v>
       </c>
       <c r="B29">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C29">
-        <v>702000</v>
+        <v>700000</v>
       </c>
       <c r="D29">
         <v>709999</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>1185</v>
+      <c r="E29" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>1208</v>
       </c>
       <c r="G29" t="s">
-        <v>1186</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="30" ht="34.8" spans="1:7">
-      <c r="A30" t="s">
-        <v>161</v>
-      </c>
-      <c r="B30">
+      <c r="A30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1023</v>
+      </c>
+      <c r="C30" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D30" s="9">
+        <v>700999</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="31" ht="52.2" spans="1:7">
+      <c r="B31">
+        <v>1023</v>
+      </c>
+      <c r="C31">
+        <v>700000</v>
+      </c>
+      <c r="D31">
+        <v>700999</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="32" ht="34.8" spans="1:7">
+      <c r="B32">
+        <v>1029</v>
+      </c>
+      <c r="C32">
+        <v>700000</v>
+      </c>
+      <c r="D32">
+        <v>700099</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="33" ht="34.8" spans="1:7">
+      <c r="B33">
+        <v>1030</v>
+      </c>
+      <c r="C33">
+        <v>700100</v>
+      </c>
+      <c r="D33">
+        <v>700999</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="34" ht="34.8" spans="1:7">
+      <c r="A34" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="9">
+        <v>1024</v>
+      </c>
+      <c r="C34" s="9">
+        <v>701000</v>
+      </c>
+      <c r="D34" s="9">
+        <v>701999</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="35" ht="71" customHeight="1" spans="1:7">
+      <c r="B35">
+        <v>1024</v>
+      </c>
+      <c r="C35">
+        <v>701000</v>
+      </c>
+      <c r="D35">
+        <v>701999</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="36" ht="71" customHeight="1" spans="1:7">
+      <c r="B36">
+        <v>1031</v>
+      </c>
+      <c r="C36">
+        <v>701000</v>
+      </c>
+      <c r="D36">
+        <v>701099</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="37" ht="71" customHeight="1" spans="1:7">
+      <c r="B37">
+        <v>1032</v>
+      </c>
+      <c r="C37">
+        <v>701100</v>
+      </c>
+      <c r="D37">
+        <v>701999</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="38" ht="34.8" spans="1:7">
+      <c r="A38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38">
+        <v>1025</v>
+      </c>
+      <c r="C38">
+        <v>702000</v>
+      </c>
+      <c r="D38">
+        <v>709999</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="39" ht="34.8" spans="1:7">
+      <c r="A39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39">
         <v>1026</v>
       </c>
-      <c r="C30">
+      <c r="C39">
         <v>710000</v>
       </c>
-      <c r="D30">
+      <c r="D39">
         <v>799999</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="31" ht="34.8" spans="1:7">
-      <c r="A31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31">
+      <c r="E39" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="40" ht="34.8" spans="1:7">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40">
         <v>1027</v>
       </c>
-      <c r="C31">
+      <c r="C40">
         <v>800000</v>
       </c>
-      <c r="D31">
+      <c r="D40">
         <v>999999</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="E40" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G40" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="32" ht="34.8" spans="1:7">
-      <c r="A32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32">
+    <row r="41" ht="34.8" spans="1:7">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41">
         <v>1028</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
         <v>99999</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="5:5">
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="5:5">
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="5:5">
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="5:5">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="5:5">
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="5:5">
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="5:5">
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="5:5">
-      <c r="E45" s="6"/>
-    </row>
-    <row r="47" spans="5:5">
+      <c r="E41" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="E42" s="14"/>
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:7">
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="5:5">
+    <row r="48" spans="1:7">
       <c r="E48" s="6"/>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
-  <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="17.9166666666667" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="12.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="20.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="20.0833333333333" customWidth="1"/>
-    <col min="8" max="8" width="19.9166666666667" customWidth="1"/>
-    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F2" t="s">
-        <v>646</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="198" customHeight="1" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1217</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6">
-        <v>9001</v>
-      </c>
-      <c r="C6">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E6" t="str">
-        <f>LOOKUP(B6,Item!B:B,Item!H:H)</f>
-        <v>史诗</v>
-      </c>
-      <c r="F6">
-        <v>0.9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="str">
-        <f>LOOKUP(B6,Item!B:B,Item!D:D)</f>
-        <v>红茶</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7">
-        <v>9002</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E7" t="str">
-        <f>LOOKUP(B7,Item!B:B,Item!H:H)</f>
-        <v>稀有</v>
-      </c>
-      <c r="F7">
-        <v>0.8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="str">
-        <f>LOOKUP(B7,Item!B:B,Item!D:D)</f>
-        <v>波尔多</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8">
-        <v>9003</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E8" t="str">
-        <f>LOOKUP(B8,Item!B:B,Item!H:H)</f>
-        <v>稀有</v>
-      </c>
-      <c r="F8">
-        <v>0.8</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="str">
-        <f>LOOKUP(B8,Item!B:B,Item!D:D)</f>
-        <v>勃艮第</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9">
-        <v>9004</v>
-      </c>
-      <c r="C9">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E9" t="str">
-        <f>LOOKUP(B9,Item!B:B,Item!H:H)</f>
-        <v>史诗</v>
-      </c>
-      <c r="F9">
-        <v>0.9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="str">
-        <f>LOOKUP(B9,Item!B:B,Item!D:D)</f>
-        <v>霞多丽</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10">
-        <v>9005</v>
-      </c>
-      <c r="C10">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E10" t="str">
-        <f>LOOKUP(B10,Item!B:B,Item!H:H)</f>
-        <v>稀有</v>
-      </c>
-      <c r="F10">
-        <v>0.8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="str">
-        <f>LOOKUP(B10,Item!B:B,Item!D:D)</f>
-        <v>子弹杯</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11">
-        <v>9006</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E11" t="str">
-        <f>LOOKUP(B11,Item!B:B,Item!H:H)</f>
-        <v>稀有</v>
-      </c>
-      <c r="F11">
-        <v>0.8</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="str">
-        <f>LOOKUP(B11,Item!B:B,Item!D:D)</f>
-        <v>郁金香杯</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12">
-        <v>9007</v>
-      </c>
-      <c r="C12">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E12" t="str">
-        <f>LOOKUP(B12,Item!B:B,Item!H:H)</f>
-        <v>稀有</v>
-      </c>
-      <c r="F12">
-        <v>0.8</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="str">
-        <f>LOOKUP(B12,Item!B:B,Item!D:D)</f>
-        <v>平底杯</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13">
-        <v>9008</v>
-      </c>
-      <c r="C13">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E13" t="str">
-        <f>LOOKUP(B13,Item!B:B,Item!H:H)</f>
-        <v>史诗</v>
-      </c>
-      <c r="F13">
-        <v>0.9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H13" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="str">
-        <f>LOOKUP(B13,Item!B:B,Item!D:D)</f>
-        <v>年份酒</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14">
-        <v>9009</v>
-      </c>
-      <c r="C14">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E14" t="str">
-        <f>LOOKUP(B14,Item!B:B,Item!H:H)</f>
-        <v>优秀</v>
-      </c>
-      <c r="F14">
-        <v>0.7</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="str">
-        <f>LOOKUP(B14,Item!B:B,Item!D:D)</f>
-        <v>凉白开</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15">
-        <v>9010</v>
-      </c>
-      <c r="C15">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E15" t="str">
-        <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
-        <v>史诗</v>
-      </c>
-      <c r="F15">
-        <v>0.9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="str">
-        <f>LOOKUP(B15,Item!B:B,Item!D:D)</f>
-        <v>威士忌</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16">
-        <v>9011</v>
-      </c>
-      <c r="C16">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E16" t="str">
-        <f>LOOKUP(B16,Item!B:B,Item!H:H)</f>
-        <v>传说</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16" t="str">
-        <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>
-        <v>威士忌雪茄</v>
-      </c>
+    <row r="49" spans="5:5">
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="6"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="6"/>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18741,35 +18700,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="21" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="17" t="s">
         <v>513</v>
       </c>
       <c r="E2" t="s">
@@ -18778,130 +18737,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="11">
-        <v>1</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="J2" s="17">
+        <v>1</v>
+      </c>
+      <c r="K2" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="17" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="17" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11" t="s">
+      <c r="G3" s="17"/>
+      <c r="H3" s="17" t="s">
         <v>521</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="17">
         <v>2</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="17" t="s">
         <v>524</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="17" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="17" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="17" t="s">
         <v>529</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="17">
         <v>4</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="17" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="17" t="s">
         <v>535</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="17">
         <v>8</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="17" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="17" t="s">
         <v>540</v>
       </c>
       <c r="E6" t="s">
@@ -18910,278 +18869,278 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="17">
         <v>16</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="17" t="s">
         <v>544</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="17" t="s">
         <v>545</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="17" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="17" t="s">
         <v>547</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="17" t="s">
         <v>548</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
+      <c r="G7" s="17"/>
+      <c r="H7" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="17">
         <v>32</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="17" t="s">
         <v>552</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="17" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="17" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="17" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="17" t="s">
         <v>556</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="17" t="s">
         <v>557</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="17">
         <v>64</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="17" t="s">
         <v>558</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="17" t="s">
         <v>559</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="17" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>561</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="17" t="s">
         <v>562</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="17" t="s">
         <v>563</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="17" t="s">
         <v>565</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="17">
         <v>128</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="17" t="s">
         <v>566</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="P9" s="17" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="17" t="s">
         <v>569</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="17" t="s">
         <v>570</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <v>256</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="17" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="17" t="s">
         <v>573</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="17" t="s">
         <v>574</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="17" t="s">
         <v>575</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="17">
         <v>512</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="17" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="17" t="s">
         <v>577</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="17">
         <v>1024</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="17" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="17" t="s">
         <v>582</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="17" t="s">
         <v>583</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="17">
         <v>2048</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="17" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="17" t="s">
         <v>585</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="17" t="s">
         <v>586</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="17" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="17" t="s">
         <v>587</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="17" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="17" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="17" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="17" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="17" t="s">
         <v>591</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="17" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="15"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="34" s="5" customFormat="1" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -19189,7 +19148,7 @@
       </c>
     </row>
     <row r="35" s="5" customFormat="1" spans="1:2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="25" t="s">
         <v>596</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -19208,7 +19167,7 @@
       <c r="A37" s="8"/>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -19216,7 +19175,7 @@
       </c>
     </row>
     <row r="39" s="5" customFormat="1" spans="1:2">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="25" t="s">
         <v>596</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -19224,7 +19183,7 @@
       </c>
     </row>
     <row r="40" s="5" customFormat="1" spans="1:2">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="25" t="s">
         <v>602</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -19232,7 +19191,7 @@
       </c>
     </row>
     <row r="41" s="5" customFormat="1" spans="1:2">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="25" t="s">
         <v>598</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -19249,7 +19208,7 @@
     </row>
     <row r="43" s="5" customFormat="1"/>
     <row r="44" s="5" customFormat="1" spans="1:2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -19257,7 +19216,7 @@
       </c>
     </row>
     <row r="45" s="5" customFormat="1" spans="1:2">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="25" t="s">
         <v>596</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -19273,7 +19232,7 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B48" s="5" t="s">
@@ -19281,11 +19240,11 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="7"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B50" s="5" t="s">
@@ -19296,14 +19255,14 @@
       <c r="G50" s="5"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7"/>
+      <c r="A51" s="25"/>
       <c r="B51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="25" t="s">
         <v>594</v>
       </c>
       <c r="B52" s="5" t="s">
@@ -19312,7 +19271,7 @@
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="25" t="s">
         <v>596</v>
       </c>
       <c r="